--- a/2026/EL MIRADOR/ENERO/Enero - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/ENERO/Enero - EL MIRADOR.xlsx
@@ -8,28 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\EL MIRADOR\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8016D8-EA04-4B2F-A3C4-8E2992CA0DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EE2876-5846-482B-AAA6-4B4CF02FF30C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
     <sheet name="ANOTACIONES" sheetId="3" r:id="rId3"/>
-    <sheet name="SUELDOS" sheetId="5" r:id="rId4"/>
-    <sheet name="Hoja1" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$155</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$149</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">SUELDOS!$A$3:$J$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$150</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="366">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -876,36 +873,6 @@
   </si>
   <si>
     <t>Ayala, Agustin</t>
-  </si>
-  <si>
-    <t>AYALA</t>
-  </si>
-  <si>
-    <t>3B</t>
-  </si>
-  <si>
-    <t>3D</t>
-  </si>
-  <si>
-    <t>3E</t>
-  </si>
-  <si>
-    <t>3F</t>
-  </si>
-  <si>
-    <t>4D</t>
-  </si>
-  <si>
-    <t>4E</t>
-  </si>
-  <si>
-    <t>4F</t>
-  </si>
-  <si>
-    <t>5E</t>
-  </si>
-  <si>
-    <t>5F</t>
   </si>
   <si>
     <t>Monotributo Sra. Miriam</t>
@@ -1008,15 +975,6 @@
     <t>IMPORTANTE: Quienes estan en violeta NO ha respetado los centavos al abonar. Para la proxima oportunidad, solicitamos que los respeten.</t>
   </si>
   <si>
-    <t>Firma</t>
-  </si>
-  <si>
-    <t>__________________________________</t>
-  </si>
-  <si>
-    <t>Aclaracion</t>
-  </si>
-  <si>
     <t>Walter Gabriel Ledesma</t>
   </si>
   <si>
@@ -1172,13 +1130,16 @@
   </si>
   <si>
     <t>Las casillas coloreadas en la columna Gastos Par/SUM de color rojo corresponden a multas aplicadas por el uso del SUM. En consecuencia, la unidad funcional involucrada no podrá acceder al uso del mismo por tiempo indeterminado. Por otro lado, las casillas coloreadas en amarillo, corresponden a llaves.</t>
+  </si>
+  <si>
+    <t>Diferencia en Factura de Articulos de limpieza (Mes anterior) con monto erroneo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
@@ -1186,8 +1147,7 @@
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.000_-;\-&quot;$&quot;\ * #,##0.000_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.000_-;\-&quot;$&quot;\ * #,##0.000_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="23" x14ac:knownFonts="1">
     <font>
@@ -1795,7 +1755,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="304">
+  <cellXfs count="290">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1960,7 +1920,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2019,18 +1978,6 @@
     <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="11" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2048,7 +1995,7 @@
     <xf numFmtId="165" fontId="11" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="22" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2056,6 +2003,37 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="10" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2131,6 +2109,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2224,55 +2205,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="10" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2639,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R159"/>
+  <dimension ref="A1:R160"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.42578125" customWidth="1"/>
@@ -2689,7 +2621,7 @@
       <c r="A3" s="113"/>
       <c r="B3" s="122"/>
       <c r="C3" s="122" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="D3" s="122"/>
       <c r="E3" s="122" t="s">
@@ -2719,7 +2651,7 @@
       <c r="A5" s="117"/>
       <c r="B5" s="122"/>
       <c r="C5" s="122" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="D5" s="122"/>
       <c r="E5" s="122" t="s">
@@ -2762,108 +2694,108 @@
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="213" t="s">
+      <c r="A14" s="233" t="s">
         <v>260</v>
       </c>
-      <c r="B14" s="213"/>
-      <c r="C14" s="213"/>
-      <c r="D14" s="213"/>
-      <c r="E14" s="213"/>
-      <c r="F14" s="213"/>
-      <c r="G14" s="213"/>
-      <c r="H14" s="213"/>
-      <c r="I14" s="213"/>
-      <c r="J14" s="213"/>
+      <c r="B14" s="233"/>
+      <c r="C14" s="233"/>
+      <c r="D14" s="233"/>
+      <c r="E14" s="233"/>
+      <c r="F14" s="233"/>
+      <c r="G14" s="233"/>
+      <c r="H14" s="233"/>
+      <c r="I14" s="233"/>
+      <c r="J14" s="233"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="213"/>
-      <c r="B15" s="213"/>
-      <c r="C15" s="213"/>
-      <c r="D15" s="213"/>
-      <c r="E15" s="213"/>
-      <c r="F15" s="213"/>
-      <c r="G15" s="213"/>
-      <c r="H15" s="213"/>
-      <c r="I15" s="213"/>
-      <c r="J15" s="213"/>
+      <c r="A15" s="233"/>
+      <c r="B15" s="233"/>
+      <c r="C15" s="233"/>
+      <c r="D15" s="233"/>
+      <c r="E15" s="233"/>
+      <c r="F15" s="233"/>
+      <c r="G15" s="233"/>
+      <c r="H15" s="233"/>
+      <c r="I15" s="233"/>
+      <c r="J15" s="233"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="213"/>
-      <c r="B16" s="213"/>
-      <c r="C16" s="213"/>
-      <c r="D16" s="213"/>
-      <c r="E16" s="213"/>
-      <c r="F16" s="213"/>
-      <c r="G16" s="213"/>
-      <c r="H16" s="213"/>
-      <c r="I16" s="213"/>
-      <c r="J16" s="213"/>
+      <c r="A16" s="233"/>
+      <c r="B16" s="233"/>
+      <c r="C16" s="233"/>
+      <c r="D16" s="233"/>
+      <c r="E16" s="233"/>
+      <c r="F16" s="233"/>
+      <c r="G16" s="233"/>
+      <c r="H16" s="233"/>
+      <c r="I16" s="233"/>
+      <c r="J16" s="233"/>
     </row>
     <row r="17" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="213"/>
-      <c r="B17" s="213"/>
-      <c r="C17" s="213"/>
-      <c r="D17" s="213"/>
-      <c r="E17" s="213"/>
-      <c r="F17" s="213"/>
-      <c r="G17" s="213"/>
-      <c r="H17" s="213"/>
-      <c r="I17" s="213"/>
-      <c r="J17" s="213"/>
+      <c r="A17" s="233"/>
+      <c r="B17" s="233"/>
+      <c r="C17" s="233"/>
+      <c r="D17" s="233"/>
+      <c r="E17" s="233"/>
+      <c r="F17" s="233"/>
+      <c r="G17" s="233"/>
+      <c r="H17" s="233"/>
+      <c r="I17" s="233"/>
+      <c r="J17" s="233"/>
     </row>
     <row r="18" spans="1:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="213"/>
-      <c r="B18" s="213"/>
-      <c r="C18" s="213"/>
-      <c r="D18" s="213"/>
-      <c r="E18" s="213"/>
-      <c r="F18" s="213"/>
-      <c r="G18" s="213"/>
-      <c r="H18" s="213"/>
-      <c r="I18" s="213"/>
-      <c r="J18" s="213"/>
+      <c r="A18" s="233"/>
+      <c r="B18" s="233"/>
+      <c r="C18" s="233"/>
+      <c r="D18" s="233"/>
+      <c r="E18" s="233"/>
+      <c r="F18" s="233"/>
+      <c r="G18" s="233"/>
+      <c r="H18" s="233"/>
+      <c r="I18" s="233"/>
+      <c r="J18" s="233"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="H19" s="94"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="222" t="s">
-        <v>337</v>
-      </c>
-      <c r="B20" s="222"/>
-      <c r="C20" s="222"/>
-      <c r="D20" s="222"/>
-      <c r="E20" s="222"/>
-      <c r="F20" s="222"/>
-      <c r="G20" s="222"/>
-      <c r="H20" s="222"/>
-      <c r="I20" s="222"/>
-      <c r="J20" s="222"/>
+      <c r="A20" s="242" t="s">
+        <v>324</v>
+      </c>
+      <c r="B20" s="242"/>
+      <c r="C20" s="242"/>
+      <c r="D20" s="242"/>
+      <c r="E20" s="242"/>
+      <c r="F20" s="242"/>
+      <c r="G20" s="242"/>
+      <c r="H20" s="242"/>
+      <c r="I20" s="242"/>
+      <c r="J20" s="242"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="222"/>
-      <c r="B21" s="222"/>
-      <c r="C21" s="222"/>
-      <c r="D21" s="222"/>
-      <c r="E21" s="222"/>
-      <c r="F21" s="222"/>
-      <c r="G21" s="222"/>
-      <c r="H21" s="222"/>
-      <c r="I21" s="222"/>
-      <c r="J21" s="222"/>
+      <c r="A21" s="242"/>
+      <c r="B21" s="242"/>
+      <c r="C21" s="242"/>
+      <c r="D21" s="242"/>
+      <c r="E21" s="242"/>
+      <c r="F21" s="242"/>
+      <c r="G21" s="242"/>
+      <c r="H21" s="242"/>
+      <c r="I21" s="242"/>
+      <c r="J21" s="242"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="222"/>
-      <c r="B22" s="222"/>
-      <c r="C22" s="222"/>
-      <c r="D22" s="222"/>
-      <c r="E22" s="222"/>
-      <c r="F22" s="222"/>
-      <c r="G22" s="222"/>
-      <c r="H22" s="222"/>
-      <c r="I22" s="222"/>
-      <c r="J22" s="222"/>
+      <c r="A22" s="242"/>
+      <c r="B22" s="242"/>
+      <c r="C22" s="242"/>
+      <c r="D22" s="242"/>
+      <c r="E22" s="242"/>
+      <c r="F22" s="242"/>
+      <c r="G22" s="242"/>
+      <c r="H22" s="242"/>
+      <c r="I22" s="242"/>
+      <c r="J22" s="242"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H23" s="94"/>
@@ -2914,7 +2846,7 @@
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
-      <c r="D26" s="292">
+      <c r="D26" s="221">
         <v>1124512</v>
       </c>
       <c r="E26" s="58"/>
@@ -2930,7 +2862,7 @@
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
-      <c r="D27" s="292">
+      <c r="D27" s="221">
         <v>39622.699999999997</v>
       </c>
       <c r="E27" s="58"/>
@@ -2946,7 +2878,7 @@
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
-      <c r="D28" s="292">
+      <c r="D28" s="221">
         <f>1726*80</f>
         <v>138080</v>
       </c>
@@ -2963,7 +2895,7 @@
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
-      <c r="D29" s="292">
+      <c r="D29" s="221">
         <v>23553.4</v>
       </c>
       <c r="E29" s="58"/>
@@ -2975,11 +2907,11 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
-      <c r="D30" s="292">
+      <c r="D30" s="221">
         <v>65596.5</v>
       </c>
       <c r="E30" s="58"/>
@@ -2995,7 +2927,7 @@
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
-      <c r="D31" s="292">
+      <c r="D31" s="221">
         <v>120000</v>
       </c>
       <c r="E31" s="58"/>
@@ -3007,11 +2939,11 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
-      <c r="D32" s="292">
+      <c r="D32" s="221">
         <v>-44192.27</v>
       </c>
       <c r="E32" s="58"/>
@@ -3027,7 +2959,7 @@
       </c>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
-      <c r="D33" s="293">
+      <c r="D33" s="222">
         <f>SUM(D26:D32)</f>
         <v>1467172.3299999998</v>
       </c>
@@ -3044,7 +2976,7 @@
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
-      <c r="D34" s="294"/>
+      <c r="D34" s="223"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
@@ -3058,7 +2990,7 @@
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
-      <c r="D35" s="292">
+      <c r="D35" s="221">
         <v>562256</v>
       </c>
       <c r="E35" s="58"/>
@@ -3074,7 +3006,7 @@
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
-      <c r="D36" s="292">
+      <c r="D36" s="221">
         <f>D27</f>
         <v>39622.699999999997</v>
       </c>
@@ -3091,7 +3023,7 @@
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
-      <c r="D37" s="292">
+      <c r="D37" s="221">
         <f>D28</f>
         <v>138080</v>
       </c>
@@ -3108,7 +3040,7 @@
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
-      <c r="D38" s="292">
+      <c r="D38" s="221">
         <f>D29</f>
         <v>23553.4</v>
       </c>
@@ -3121,11 +3053,11 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
-      <c r="D39" s="292">
+      <c r="D39" s="221">
         <f>D30</f>
         <v>65596.5</v>
       </c>
@@ -3142,7 +3074,7 @@
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
-      <c r="D40" s="292">
+      <c r="D40" s="221">
         <v>60000</v>
       </c>
       <c r="E40" s="58"/>
@@ -3154,11 +3086,11 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
-      <c r="D41" s="292">
+      <c r="D41" s="221">
         <v>-101801.65</v>
       </c>
       <c r="E41" s="58"/>
@@ -3174,7 +3106,7 @@
       </c>
       <c r="B42" s="91"/>
       <c r="C42" s="91"/>
-      <c r="D42" s="293">
+      <c r="D42" s="222">
         <f>SUM(D35:D41)</f>
         <v>787306.95</v>
       </c>
@@ -3191,7 +3123,7 @@
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="33"/>
-      <c r="D43" s="295">
+      <c r="D43" s="224">
         <f>D33+D42</f>
         <v>2254479.2799999998</v>
       </c>
@@ -3230,11 +3162,11 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="32" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
-      <c r="D44" s="296">
+      <c r="D44" s="225">
         <v>254504.03</v>
       </c>
       <c r="E44" s="58"/>
@@ -3249,7 +3181,7 @@
       <c r="A45" s="32"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
-      <c r="D45" s="292"/>
+      <c r="D45" s="221"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
@@ -3264,7 +3196,7 @@
       </c>
       <c r="B46" s="33"/>
       <c r="C46" s="33"/>
-      <c r="D46" s="295">
+      <c r="D46" s="224">
         <f>SUM(D44:D44)</f>
         <v>254504.03</v>
       </c>
@@ -3307,7 +3239,7 @@
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
-      <c r="D47" s="296"/>
+      <c r="D47" s="225"/>
       <c r="E47" s="58">
         <f>D47*91.91%</f>
         <v>0</v>
@@ -3321,13 +3253,13 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="B48" s="6"/>
-      <c r="C48" s="211">
+      <c r="C48" s="202">
         <v>46024</v>
       </c>
-      <c r="D48" s="292">
+      <c r="D48" s="221">
         <v>71000</v>
       </c>
       <c r="E48" s="58">
@@ -3343,13 +3275,13 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="B49" s="6"/>
-      <c r="C49" s="211">
+      <c r="C49" s="202">
         <v>46024</v>
       </c>
-      <c r="D49" s="292">
+      <c r="D49" s="221">
         <v>71000</v>
       </c>
       <c r="E49" s="58">
@@ -3365,13 +3297,13 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="B50" s="6"/>
-      <c r="C50" s="211">
+      <c r="C50" s="202">
         <v>46024</v>
       </c>
-      <c r="D50" s="292">
+      <c r="D50" s="221">
         <v>36025</v>
       </c>
       <c r="E50" s="58">
@@ -3387,13 +3319,13 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="B51" s="6"/>
-      <c r="C51" s="211">
+      <c r="C51" s="202">
         <v>46024</v>
       </c>
-      <c r="D51" s="292">
+      <c r="D51" s="221">
         <v>78006.05</v>
       </c>
       <c r="E51" s="58">
@@ -3409,13 +3341,13 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="B52" s="6"/>
-      <c r="C52" s="211">
+      <c r="C52" s="202">
         <v>46025</v>
       </c>
-      <c r="D52" s="292">
+      <c r="D52" s="221">
         <v>37040</v>
       </c>
       <c r="E52" s="58">
@@ -3433,7 +3365,7 @@
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
-      <c r="D53" s="292"/>
+      <c r="D53" s="221"/>
       <c r="E53" s="58"/>
       <c r="F53" s="58"/>
       <c r="G53" s="58"/>
@@ -3448,7 +3380,7 @@
       </c>
       <c r="B54" s="33"/>
       <c r="C54" s="33"/>
-      <c r="D54" s="295">
+      <c r="D54" s="224">
         <f>SUM(D48:D53)</f>
         <v>293071.05</v>
       </c>
@@ -3476,7 +3408,7 @@
       </c>
       <c r="B55" s="35"/>
       <c r="C55" s="35"/>
-      <c r="D55" s="292"/>
+      <c r="D55" s="221"/>
       <c r="E55" s="49"/>
       <c r="F55" s="49"/>
       <c r="G55" s="49"/>
@@ -3491,7 +3423,7 @@
       </c>
       <c r="B56" s="35"/>
       <c r="C56" s="35"/>
-      <c r="D56" s="292"/>
+      <c r="D56" s="221"/>
       <c r="E56" s="49"/>
       <c r="F56" s="49"/>
       <c r="G56" s="49"/>
@@ -3505,12 +3437,12 @@
         <v>248</v>
       </c>
       <c r="B57" s="35" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="C57" s="35" t="s">
-        <v>329</v>
-      </c>
-      <c r="D57" s="292">
+        <v>316</v>
+      </c>
+      <c r="D57" s="221">
         <v>249469</v>
       </c>
       <c r="E57" s="49"/>
@@ -3526,12 +3458,12 @@
         <v>248</v>
       </c>
       <c r="B58" s="35" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="C58" s="35" t="s">
-        <v>345</v>
-      </c>
-      <c r="D58" s="292">
+        <v>332</v>
+      </c>
+      <c r="D58" s="221">
         <v>249469</v>
       </c>
       <c r="E58" s="49"/>
@@ -3548,7 +3480,7 @@
       </c>
       <c r="B59" s="33"/>
       <c r="C59" s="33"/>
-      <c r="D59" s="297">
+      <c r="D59" s="226">
         <f>SUM(D56:D58)</f>
         <v>498938</v>
       </c>
@@ -3591,7 +3523,7 @@
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
-      <c r="D60" s="286"/>
+      <c r="D60" s="215"/>
       <c r="E60" s="45"/>
       <c r="F60" s="45"/>
       <c r="G60" s="45"/>
@@ -3606,9 +3538,9 @@
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="D61" s="286">
+        <v>353</v>
+      </c>
+      <c r="D61" s="215">
         <v>56231.41</v>
       </c>
       <c r="E61" s="114"/>
@@ -3621,13 +3553,13 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="D62" s="286">
+        <v>353</v>
+      </c>
+      <c r="D62" s="215">
         <v>64941</v>
       </c>
       <c r="E62" s="114"/>
@@ -3640,15 +3572,15 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="C63" s="200" t="s">
-        <v>350</v>
-      </c>
-      <c r="D63" s="286">
+        <v>344</v>
+      </c>
+      <c r="C63" s="191" t="s">
+        <v>337</v>
+      </c>
+      <c r="D63" s="215">
         <v>64941</v>
       </c>
       <c r="E63" s="75"/>
@@ -3665,7 +3597,7 @@
       </c>
       <c r="B64" s="33"/>
       <c r="C64" s="33"/>
-      <c r="D64" s="295">
+      <c r="D64" s="224">
         <f>SUM(D60:D63)</f>
         <v>186113.41</v>
       </c>
@@ -3708,7 +3640,7 @@
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
-      <c r="D65" s="298"/>
+      <c r="D65" s="227"/>
       <c r="E65" s="46"/>
       <c r="F65" s="46"/>
       <c r="G65" s="46"/>
@@ -3723,9 +3655,9 @@
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="D66" s="286">
+        <v>315</v>
+      </c>
+      <c r="D66" s="215">
         <v>160913</v>
       </c>
       <c r="E66" s="58">
@@ -3759,14 +3691,14 @@
       <c r="L66" s="69"/>
     </row>
     <row r="67" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="224" t="s">
+      <c r="A67" s="244" t="s">
         <v>232</v>
       </c>
-      <c r="B67" s="225"/>
+      <c r="B67" s="245"/>
       <c r="C67" s="35" t="s">
-        <v>328</v>
-      </c>
-      <c r="D67" s="286">
+        <v>315</v>
+      </c>
+      <c r="D67" s="215">
         <v>7907</v>
       </c>
       <c r="E67" s="58">
@@ -3797,19 +3729,19 @@
         <f t="shared" ref="K67:K68" si="2">SUM(E67:J67)</f>
         <v>7907</v>
       </c>
-      <c r="L67" s="285" t="s">
-        <v>376</v>
+      <c r="L67" s="214" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="68" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="224" t="s">
+      <c r="A68" s="244" t="s">
         <v>233</v>
       </c>
-      <c r="B68" s="225"/>
+      <c r="B68" s="245"/>
       <c r="C68" s="35" t="s">
-        <v>328</v>
-      </c>
-      <c r="D68" s="286">
+        <v>315</v>
+      </c>
+      <c r="D68" s="215">
         <v>7907</v>
       </c>
       <c r="E68" s="58">
@@ -3848,7 +3780,7 @@
       </c>
       <c r="B69" s="34"/>
       <c r="C69" s="34"/>
-      <c r="D69" s="295">
+      <c r="D69" s="224">
         <f>SUM(D66:D68)</f>
         <v>176727</v>
       </c>
@@ -3891,7 +3823,7 @@
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
-      <c r="D70" s="291"/>
+      <c r="D70" s="220"/>
       <c r="E70" s="46"/>
       <c r="F70" s="46"/>
       <c r="G70" s="46"/>
@@ -3906,9 +3838,9 @@
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="35" t="s">
-        <v>356</v>
-      </c>
-      <c r="D71" s="299">
+        <v>343</v>
+      </c>
+      <c r="D71" s="228">
         <v>1469353.32</v>
       </c>
       <c r="E71" s="68">
@@ -3952,9 +3884,9 @@
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="35" t="s">
-        <v>345</v>
-      </c>
-      <c r="D72" s="299">
+        <v>332</v>
+      </c>
+      <c r="D72" s="228">
         <v>2331402.6</v>
       </c>
       <c r="E72" s="68">
@@ -3998,9 +3930,9 @@
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="D73" s="286">
+        <v>315</v>
+      </c>
+      <c r="D73" s="215">
         <v>124753.28</v>
       </c>
       <c r="E73" s="68">
@@ -4031,13 +3963,13 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="B74" s="6"/>
       <c r="C74" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="D74" s="286">
+        <v>335</v>
+      </c>
+      <c r="D74" s="215">
         <v>352314.06</v>
       </c>
       <c r="E74" s="68">
@@ -4061,14 +3993,14 @@
       <c r="N74" s="84"/>
     </row>
     <row r="75" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="220" t="s">
-        <v>341</v>
-      </c>
-      <c r="B75" s="226"/>
+      <c r="A75" s="240" t="s">
+        <v>328</v>
+      </c>
+      <c r="B75" s="246"/>
       <c r="C75" s="35" t="s">
-        <v>345</v>
-      </c>
-      <c r="D75" s="286">
+        <v>332</v>
+      </c>
+      <c r="D75" s="215">
         <v>40000</v>
       </c>
       <c r="E75" s="68">
@@ -4098,14 +4030,14 @@
       </c>
     </row>
     <row r="76" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="220" t="s">
-        <v>369</v>
-      </c>
-      <c r="B76" s="226"/>
-      <c r="C76" s="200" t="s">
-        <v>370</v>
-      </c>
-      <c r="D76" s="286">
+      <c r="A76" s="240" t="s">
+        <v>356</v>
+      </c>
+      <c r="B76" s="246"/>
+      <c r="C76" s="191" t="s">
+        <v>357</v>
+      </c>
+      <c r="D76" s="215">
         <v>130000</v>
       </c>
       <c r="E76" s="68">
@@ -4130,10 +4062,10 @@
         <v>277</v>
       </c>
       <c r="B77" s="35"/>
-      <c r="C77" s="200" t="s">
-        <v>350</v>
-      </c>
-      <c r="D77" s="286">
+      <c r="C77" s="191" t="s">
+        <v>337</v>
+      </c>
+      <c r="D77" s="215">
         <v>993952.65</v>
       </c>
       <c r="E77" s="68">
@@ -4182,10 +4114,10 @@
         <v>278</v>
       </c>
       <c r="B78" s="35"/>
-      <c r="C78" s="200" t="s">
-        <v>350</v>
-      </c>
-      <c r="D78" s="286">
+      <c r="C78" s="191" t="s">
+        <v>337</v>
+      </c>
+      <c r="D78" s="215">
         <v>5460.69</v>
       </c>
       <c r="E78" s="68">
@@ -4230,14 +4162,14 @@
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="143" t="s">
+      <c r="A79" s="142" t="s">
         <v>276</v>
       </c>
-      <c r="B79" s="142"/>
+      <c r="B79" s="141"/>
       <c r="C79" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="D79" s="286">
+        <v>353</v>
+      </c>
+      <c r="D79" s="215">
         <v>100000</v>
       </c>
       <c r="E79" s="68">
@@ -4287,32 +4219,32 @@
       </c>
       <c r="B80" s="34"/>
       <c r="C80" s="34"/>
-      <c r="D80" s="295">
-        <f>SUM(D71:D79)</f>
+      <c r="D80" s="224">
+        <f t="shared" ref="D80:J80" si="14">SUM(D71:D79)</f>
         <v>5547236.6000000006</v>
       </c>
       <c r="E80" s="42">
-        <f>SUM(E71:E79)</f>
+        <f t="shared" si="14"/>
         <v>5214025.0903200004</v>
       </c>
       <c r="F80" s="42">
-        <f>SUM(F71:F79)</f>
+        <f t="shared" si="14"/>
         <v>52921.828008000004</v>
       </c>
       <c r="G80" s="42">
-        <f>SUM(G71:G79)</f>
+        <f t="shared" si="14"/>
         <v>62722.166528000002</v>
       </c>
       <c r="H80" s="42">
-        <f>SUM(H71:H79)</f>
+        <f t="shared" si="14"/>
         <v>59292.048046000004</v>
       </c>
       <c r="I80" s="42">
-        <f>SUM(I71:I79)</f>
+        <f t="shared" si="14"/>
         <v>73012.521974000003</v>
       </c>
       <c r="J80" s="42">
-        <f>SUM(J71:J79)</f>
+        <f t="shared" si="14"/>
         <v>85262.945124000005</v>
       </c>
       <c r="K80" s="43">
@@ -4332,7 +4264,7 @@
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
-      <c r="D81" s="291"/>
+      <c r="D81" s="220"/>
       <c r="E81" s="46"/>
       <c r="F81" s="46"/>
       <c r="G81" s="46"/>
@@ -4345,7 +4277,7 @@
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
-      <c r="D82" s="291"/>
+      <c r="D82" s="220"/>
       <c r="E82" s="45"/>
       <c r="F82" s="45"/>
       <c r="G82" s="45"/>
@@ -4360,7 +4292,7 @@
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
-      <c r="D83" s="291"/>
+      <c r="D83" s="220"/>
       <c r="E83" s="45"/>
       <c r="F83" s="45"/>
       <c r="G83" s="45"/>
@@ -4371,13 +4303,13 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="B84" s="35"/>
       <c r="C84" s="35" t="s">
-        <v>345</v>
-      </c>
-      <c r="D84" s="286">
+        <v>332</v>
+      </c>
+      <c r="D84" s="215">
         <v>606800</v>
       </c>
       <c r="E84" s="68">
@@ -4408,13 +4340,13 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="B85" s="35"/>
       <c r="C85" s="35" t="s">
-        <v>345</v>
-      </c>
-      <c r="D85" s="286">
+        <v>332</v>
+      </c>
+      <c r="D85" s="215">
         <v>216800</v>
       </c>
       <c r="E85" s="68">
@@ -4430,13 +4362,13 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="B86" s="35"/>
       <c r="C86" s="35" t="s">
-        <v>359</v>
-      </c>
-      <c r="D86" s="286">
+        <v>346</v>
+      </c>
+      <c r="D86" s="215">
         <v>1300</v>
       </c>
       <c r="E86" s="68">
@@ -4467,17 +4399,17 @@
     </row>
     <row r="87" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="71" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="B87" s="35"/>
-      <c r="C87" s="212" t="s">
-        <v>355</v>
-      </c>
-      <c r="D87" s="286">
+      <c r="C87" s="203" t="s">
+        <v>342</v>
+      </c>
+      <c r="D87" s="215">
         <v>350000</v>
       </c>
       <c r="E87" s="68">
-        <f t="shared" ref="E87:E95" si="14">D87</f>
+        <f t="shared" ref="E87:E95" si="15">D87</f>
         <v>350000</v>
       </c>
       <c r="F87" s="58"/>
@@ -4488,18 +4420,18 @@
       <c r="L87" s="69"/>
     </row>
     <row r="88" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="229" t="s">
-        <v>360</v>
-      </c>
-      <c r="B88" s="230"/>
+      <c r="A88" s="249" t="s">
+        <v>347</v>
+      </c>
+      <c r="B88" s="250"/>
       <c r="C88" s="35" t="s">
-        <v>345</v>
-      </c>
-      <c r="D88" s="286">
+        <v>332</v>
+      </c>
+      <c r="D88" s="215">
         <v>250000</v>
       </c>
       <c r="E88" s="68">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>250000</v>
       </c>
       <c r="F88" s="58"/>
@@ -4511,17 +4443,17 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="B89" s="35"/>
       <c r="C89" s="35" t="s">
-        <v>345</v>
-      </c>
-      <c r="D89" s="286">
+        <v>332</v>
+      </c>
+      <c r="D89" s="215">
         <v>32800</v>
       </c>
       <c r="E89" s="68">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>32800</v>
       </c>
       <c r="F89" s="58"/>
@@ -4533,17 +4465,17 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="B90" s="35"/>
       <c r="C90" s="35" t="s">
-        <v>350</v>
-      </c>
-      <c r="D90" s="286">
+        <v>337</v>
+      </c>
+      <c r="D90" s="215">
         <v>50000</v>
       </c>
       <c r="E90" s="68">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>50000</v>
       </c>
       <c r="F90" s="75"/>
@@ -4555,17 +4487,17 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="45" t="s">
-        <v>364</v>
-      </c>
-      <c r="B91" s="275"/>
+        <v>351</v>
+      </c>
+      <c r="B91" s="204"/>
       <c r="C91" s="35" t="s">
-        <v>365</v>
-      </c>
-      <c r="D91" s="286">
+        <v>352</v>
+      </c>
+      <c r="D91" s="215">
         <v>60000</v>
       </c>
       <c r="E91" s="68">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>60000</v>
       </c>
       <c r="F91" s="75"/>
@@ -4577,17 +4509,17 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="45" t="s">
-        <v>364</v>
-      </c>
-      <c r="B92" s="275"/>
+        <v>351</v>
+      </c>
+      <c r="B92" s="204"/>
       <c r="C92" s="35" t="s">
-        <v>365</v>
-      </c>
-      <c r="D92" s="286">
+        <v>352</v>
+      </c>
+      <c r="D92" s="215">
         <v>50000</v>
       </c>
       <c r="E92" s="68">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>50000</v>
       </c>
       <c r="F92" s="75"/>
@@ -4598,18 +4530,18 @@
       <c r="L92" s="69"/>
     </row>
     <row r="93" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="224" t="s">
-        <v>363</v>
-      </c>
-      <c r="B93" s="225"/>
-      <c r="C93" s="138" t="s">
-        <v>362</v>
-      </c>
-      <c r="D93" s="286">
+      <c r="A93" s="244" t="s">
+        <v>350</v>
+      </c>
+      <c r="B93" s="245"/>
+      <c r="C93" s="137" t="s">
+        <v>349</v>
+      </c>
+      <c r="D93" s="215">
         <v>307200</v>
       </c>
       <c r="E93" s="68">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>307200</v>
       </c>
       <c r="F93" s="75"/>
@@ -4620,18 +4552,18 @@
       <c r="L93" s="69"/>
     </row>
     <row r="94" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="224" t="s">
-        <v>344</v>
-      </c>
-      <c r="B94" s="225"/>
-      <c r="C94" s="138" t="s">
-        <v>362</v>
-      </c>
-      <c r="D94" s="286">
+      <c r="A94" s="244" t="s">
+        <v>331</v>
+      </c>
+      <c r="B94" s="245"/>
+      <c r="C94" s="137" t="s">
+        <v>349</v>
+      </c>
+      <c r="D94" s="215">
         <v>191400</v>
       </c>
       <c r="E94" s="68">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>191400</v>
       </c>
       <c r="F94" s="75"/>
@@ -4642,18 +4574,18 @@
       <c r="L94" s="69"/>
     </row>
     <row r="95" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="227" t="s">
-        <v>343</v>
-      </c>
-      <c r="B95" s="228"/>
-      <c r="C95" s="138" t="s">
-        <v>362</v>
-      </c>
-      <c r="D95" s="286">
+      <c r="A95" s="247" t="s">
+        <v>330</v>
+      </c>
+      <c r="B95" s="248"/>
+      <c r="C95" s="137" t="s">
+        <v>349</v>
+      </c>
+      <c r="D95" s="215">
         <v>95700</v>
       </c>
       <c r="E95" s="68">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>95700</v>
       </c>
       <c r="F95" s="58"/>
@@ -4670,32 +4602,32 @@
       </c>
       <c r="B96" s="33"/>
       <c r="C96" s="33"/>
-      <c r="D96" s="295">
-        <f>SUM(D84:D95)</f>
+      <c r="D96" s="224">
+        <f t="shared" ref="D96:J96" si="16">SUM(D84:D95)</f>
         <v>2212000</v>
       </c>
       <c r="E96" s="42">
-        <f>SUM(E84:E95)</f>
+        <f t="shared" si="16"/>
         <v>2170649.2000000002</v>
       </c>
       <c r="F96" s="42">
-        <f>SUM(F84:F95)</f>
+        <f t="shared" si="16"/>
         <v>6567.4800000000005</v>
       </c>
       <c r="G96" s="42">
-        <f>SUM(G84:G95)</f>
+        <f t="shared" si="16"/>
         <v>7783.68</v>
       </c>
       <c r="H96" s="42">
-        <f>SUM(H84:H95)</f>
+        <f t="shared" si="16"/>
         <v>7358.0099999999993</v>
       </c>
       <c r="I96" s="42">
-        <f>SUM(I84:I95)</f>
+        <f t="shared" si="16"/>
         <v>9060.69</v>
       </c>
       <c r="J96" s="42">
-        <f>SUM(J84:J95)</f>
+        <f t="shared" si="16"/>
         <v>10580.94</v>
       </c>
       <c r="K96" s="43">
@@ -4712,7 +4644,7 @@
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
-      <c r="D97" s="291"/>
+      <c r="D97" s="220"/>
       <c r="E97" s="46"/>
       <c r="F97" s="46"/>
       <c r="G97" s="46"/>
@@ -4725,7 +4657,7 @@
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
-      <c r="D98" s="291"/>
+      <c r="D98" s="220"/>
       <c r="E98" s="45"/>
       <c r="F98" s="45"/>
       <c r="G98" s="45"/>
@@ -4740,7 +4672,7 @@
       </c>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
-      <c r="D99" s="291"/>
+      <c r="D99" s="220"/>
       <c r="E99" s="45"/>
       <c r="F99" s="45"/>
       <c r="G99" s="45"/>
@@ -4757,7 +4689,7 @@
         <v>37</v>
       </c>
       <c r="C100" s="6"/>
-      <c r="D100" s="286">
+      <c r="D100" s="215">
         <v>753700</v>
       </c>
       <c r="E100" s="68">
@@ -4785,14 +4717,14 @@
         <v>13114.38</v>
       </c>
       <c r="L100" s="69" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="32"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
-      <c r="D101" s="286"/>
+      <c r="D101" s="215"/>
       <c r="E101" s="68"/>
       <c r="F101" s="68"/>
       <c r="G101" s="68"/>
@@ -4806,7 +4738,7 @@
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
-      <c r="D102" s="291"/>
+      <c r="D102" s="220"/>
       <c r="E102" s="47"/>
       <c r="F102" s="47"/>
       <c r="G102" s="47"/>
@@ -4822,7 +4754,7 @@
       </c>
       <c r="B103" s="33"/>
       <c r="C103" s="33"/>
-      <c r="D103" s="295">
+      <c r="D103" s="224">
         <f>SUM(D100:D102)</f>
         <v>753700</v>
       </c>
@@ -4831,19 +4763,19 @@
         <v>702448.4</v>
       </c>
       <c r="F103" s="42">
-        <f t="shared" ref="F103:I103" si="15">SUM(F100:F102)</f>
+        <f t="shared" ref="F103:I103" si="17">SUM(F100:F102)</f>
         <v>8139.96</v>
       </c>
       <c r="G103" s="42">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9647.36</v>
       </c>
       <c r="H103" s="42">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9119.77</v>
       </c>
       <c r="I103" s="42">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>11230.13</v>
       </c>
       <c r="J103" s="42">
@@ -4866,7 +4798,7 @@
       </c>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
-      <c r="D104" s="286">
+      <c r="D104" s="215">
         <f>720+151.2+166246.56</f>
         <v>167117.76000000001</v>
       </c>
@@ -4940,27 +4872,27 @@
         <v>167117.76000000001</v>
       </c>
       <c r="E106" s="67">
-        <f t="shared" ref="E106:J106" si="16">SUM(E104:E105)</f>
+        <f t="shared" ref="E106:J106" si="18">SUM(E104:E105)</f>
         <v>155753.75232000003</v>
       </c>
       <c r="F106" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1804.8718080000001</v>
       </c>
       <c r="G106" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>2139.1073280000001</v>
       </c>
       <c r="H106" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>2022.124896</v>
       </c>
       <c r="I106" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>2490.0546240000003</v>
       </c>
       <c r="J106" s="67">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>2907.8490240000001</v>
       </c>
       <c r="K106" s="43">
@@ -4987,7 +4919,7 @@
     </row>
     <row r="108" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="100" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="B108" s="101"/>
       <c r="C108" s="101"/>
@@ -5049,31 +4981,31 @@
       <c r="B110" s="11"/>
       <c r="C110" s="4"/>
       <c r="D110" s="86">
-        <f>SUM(D108+D59+D54+D106+D103+D96+D80+D69+D46+D43+D64)</f>
+        <f t="shared" ref="D110:J110" si="19">SUM(D108+D59+D54+D106+D103+D96+D80+D69+D46+D43+D64)</f>
         <v>15667206.089999998</v>
       </c>
       <c r="E110" s="86">
-        <f>SUM(E108+E59+E54+E106+E103+E96+E80+E69+E46+E43+E64)</f>
+        <f t="shared" si="19"/>
         <v>14774830.686399998</v>
       </c>
       <c r="F110" s="86">
-        <f>SUM(F108+F59+F54+F106+F103+F96+F80+F69+F46+F43+F64)</f>
+        <f t="shared" si="19"/>
         <v>141730.21116000001</v>
       </c>
       <c r="G110" s="86">
-        <f>SUM(G108+G59+G54+G106+G103+G96+G80+G69+G46+G43+G64)</f>
+        <f t="shared" si="19"/>
         <v>167976.54656000002</v>
       </c>
       <c r="H110" s="86">
-        <f>SUM(H108+H59+H54+H106+H103+H96+H80+H69+H46+H43+H64)</f>
+        <f t="shared" si="19"/>
         <v>158790.32916999998</v>
       </c>
       <c r="I110" s="86">
-        <f>SUM(I108+I59+I54+I106+I103+I96+I80+I69+I46+I43+I64)</f>
+        <f t="shared" si="19"/>
         <v>195535.19872999997</v>
       </c>
       <c r="J110" s="86">
-        <f>SUM(J108+J59+J54+J106+J103+J96+J80+J69+J46+J43+J64)</f>
+        <f t="shared" si="19"/>
         <v>228343.11798000001</v>
       </c>
       <c r="K110" s="61">
@@ -5111,10 +5043,10 @@
     </row>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="B113" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="C113" s="128">
         <v>25000</v>
@@ -5164,12 +5096,12 @@
       <c r="I117" s="60"/>
     </row>
     <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="218" t="s">
+      <c r="A118" s="238" t="s">
         <v>34</v>
       </c>
-      <c r="B118" s="219"/>
-      <c r="C118" s="219"/>
-      <c r="D118" s="219"/>
+      <c r="B118" s="239"/>
+      <c r="C118" s="239"/>
+      <c r="D118" s="239"/>
       <c r="E118" s="80" t="s">
         <v>11</v>
       </c>
@@ -5190,8 +5122,8 @@
       </c>
     </row>
     <row r="119" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="220"/>
-      <c r="B119" s="221"/>
+      <c r="A119" s="240"/>
+      <c r="B119" s="241"/>
       <c r="C119" s="82"/>
       <c r="D119" s="44"/>
       <c r="E119" s="68">
@@ -5205,8 +5137,8 @@
       <c r="J119" s="58"/>
     </row>
     <row r="120" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="220"/>
-      <c r="B120" s="221"/>
+      <c r="A120" s="240"/>
+      <c r="B120" s="241"/>
       <c r="C120" s="82"/>
       <c r="D120" s="44"/>
       <c r="E120" s="68"/>
@@ -5217,11 +5149,11 @@
       <c r="J120" s="58"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="215" t="s">
+      <c r="A121" s="235" t="s">
         <v>17</v>
       </c>
-      <c r="B121" s="216"/>
-      <c r="C121" s="217"/>
+      <c r="B121" s="236"/>
+      <c r="C121" s="237"/>
       <c r="D121" s="79">
         <f>SUM(D119:D120)</f>
         <v>0</v>
@@ -5271,22 +5203,22 @@
         <f>D110-D108</f>
         <v>12343887.129999999</v>
       </c>
-      <c r="D125" s="223" t="s">
-        <v>315</v>
-      </c>
-      <c r="E125" s="223"/>
-      <c r="F125" s="223"/>
-      <c r="G125" s="223"/>
-      <c r="H125" s="223"/>
-      <c r="I125" s="223"/>
+      <c r="D125" s="243" t="s">
+        <v>305</v>
+      </c>
+      <c r="E125" s="243"/>
+      <c r="F125" s="243"/>
+      <c r="G125" s="243"/>
+      <c r="H125" s="243"/>
+      <c r="I125" s="243"/>
     </row>
     <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D126" s="223"/>
-      <c r="E126" s="223"/>
-      <c r="F126" s="223"/>
-      <c r="G126" s="223"/>
-      <c r="H126" s="223"/>
-      <c r="I126" s="223"/>
+      <c r="D126" s="243"/>
+      <c r="E126" s="243"/>
+      <c r="F126" s="243"/>
+      <c r="G126" s="243"/>
+      <c r="H126" s="243"/>
+      <c r="I126" s="243"/>
     </row>
     <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="16" t="s">
@@ -5294,12 +5226,12 @@
       </c>
       <c r="B127" s="17"/>
       <c r="C127" s="18"/>
-      <c r="D127" s="223"/>
-      <c r="E127" s="223"/>
-      <c r="F127" s="223"/>
-      <c r="G127" s="223"/>
-      <c r="H127" s="223"/>
-      <c r="I127" s="223"/>
+      <c r="D127" s="243"/>
+      <c r="E127" s="243"/>
+      <c r="F127" s="243"/>
+      <c r="G127" s="243"/>
+      <c r="H127" s="243"/>
+      <c r="I127" s="243"/>
     </row>
     <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="19" t="s">
@@ -5309,12 +5241,12 @@
         <v>-1002261.6181467418</v>
       </c>
       <c r="C128" s="20"/>
-      <c r="D128" s="223"/>
-      <c r="E128" s="223"/>
-      <c r="F128" s="223"/>
-      <c r="G128" s="223"/>
-      <c r="H128" s="223"/>
-      <c r="I128" s="223"/>
+      <c r="D128" s="243"/>
+      <c r="E128" s="243"/>
+      <c r="F128" s="243"/>
+      <c r="G128" s="243"/>
+      <c r="H128" s="243"/>
+      <c r="I128" s="243"/>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="21" t="s">
@@ -5327,12 +5259,12 @@
       <c r="C129" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D129" s="223"/>
-      <c r="E129" s="223"/>
-      <c r="F129" s="223"/>
-      <c r="G129" s="223"/>
-      <c r="H129" s="223"/>
-      <c r="I129" s="223"/>
+      <c r="D129" s="243"/>
+      <c r="E129" s="243"/>
+      <c r="F129" s="243"/>
+      <c r="G129" s="243"/>
+      <c r="H129" s="243"/>
+      <c r="I129" s="243"/>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="21" t="s">
@@ -5343,12 +5275,12 @@
         <v>-12343887.129999999</v>
       </c>
       <c r="C130" s="18"/>
-      <c r="D130" s="223"/>
-      <c r="E130" s="223"/>
-      <c r="F130" s="223"/>
-      <c r="G130" s="223"/>
-      <c r="H130" s="223"/>
-      <c r="I130" s="223"/>
+      <c r="D130" s="243"/>
+      <c r="E130" s="243"/>
+      <c r="F130" s="243"/>
+      <c r="G130" s="243"/>
+      <c r="H130" s="243"/>
+      <c r="I130" s="243"/>
       <c r="K130" s="44"/>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -5360,29 +5292,29 @@
         <v>0</v>
       </c>
       <c r="C131" s="18"/>
-      <c r="D131" s="223"/>
-      <c r="E131" s="223"/>
-      <c r="F131" s="223"/>
-      <c r="G131" s="223"/>
-      <c r="H131" s="223"/>
-      <c r="I131" s="223"/>
+      <c r="D131" s="243"/>
+      <c r="E131" s="243"/>
+      <c r="F131" s="243"/>
+      <c r="G131" s="243"/>
+      <c r="H131" s="243"/>
+      <c r="I131" s="243"/>
       <c r="K131" s="52"/>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="21" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="B132" s="30">
-        <f>B141</f>
+        <f>B142</f>
         <v>143267</v>
       </c>
       <c r="C132" s="18"/>
-      <c r="D132" s="223"/>
-      <c r="E132" s="223"/>
-      <c r="F132" s="223"/>
-      <c r="G132" s="223"/>
-      <c r="H132" s="223"/>
-      <c r="I132" s="223"/>
+      <c r="D132" s="243"/>
+      <c r="E132" s="243"/>
+      <c r="F132" s="243"/>
+      <c r="G132" s="243"/>
+      <c r="H132" s="243"/>
+      <c r="I132" s="243"/>
       <c r="K132" s="52"/>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -5390,122 +5322,132 @@
         <v>32</v>
       </c>
       <c r="B133" s="83">
-        <f>-B146</f>
+        <f>-B147</f>
         <v>-120000</v>
       </c>
       <c r="C133" s="22"/>
-      <c r="D133" s="223"/>
-      <c r="E133" s="223"/>
-      <c r="F133" s="223"/>
-      <c r="G133" s="223"/>
-      <c r="H133" s="223"/>
-      <c r="I133" s="223"/>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A134" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="B134" s="207">
+      <c r="D133" s="243"/>
+      <c r="E133" s="243"/>
+      <c r="F133" s="243"/>
+      <c r="G133" s="243"/>
+      <c r="H133" s="243"/>
+      <c r="I133" s="243"/>
+    </row>
+    <row r="134" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="232" t="s">
+        <v>365</v>
+      </c>
+      <c r="B134" s="30">
+        <v>426600</v>
+      </c>
+      <c r="C134" s="22"/>
+      <c r="D134" s="243"/>
+      <c r="E134" s="243"/>
+      <c r="F134" s="243"/>
+      <c r="G134" s="243"/>
+      <c r="H134" s="243"/>
+      <c r="I134" s="243"/>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="B135" s="198">
         <f>-87300</f>
         <v>-87300</v>
       </c>
-      <c r="C134" s="22"/>
-      <c r="D134" s="223"/>
-      <c r="E134" s="223"/>
-      <c r="F134" s="223"/>
-      <c r="G134" s="223"/>
-      <c r="H134" s="223"/>
-      <c r="I134" s="223"/>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A135" s="21" t="s">
+      <c r="C135" s="22"/>
+      <c r="D135" s="243"/>
+      <c r="E135" s="243"/>
+      <c r="F135" s="243"/>
+      <c r="G135" s="243"/>
+      <c r="H135" s="243"/>
+      <c r="I135" s="243"/>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B135" s="83">
+      <c r="B136" s="83">
         <f>-C115</f>
         <v>-25000</v>
       </c>
-      <c r="C135" s="22"/>
-      <c r="D135" s="223"/>
-      <c r="E135" s="223"/>
-      <c r="F135" s="223"/>
-      <c r="G135" s="223"/>
-      <c r="H135" s="223"/>
-      <c r="I135" s="223"/>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A136" s="21"/>
-      <c r="B136" s="170"/>
       <c r="C136" s="22"/>
-      <c r="D136" s="223"/>
-      <c r="E136" s="223"/>
-      <c r="F136" s="223"/>
-      <c r="G136" s="223"/>
-      <c r="H136" s="223"/>
-      <c r="I136" s="223"/>
+      <c r="D136" s="243"/>
+      <c r="E136" s="243"/>
+      <c r="F136" s="243"/>
+      <c r="G136" s="243"/>
+      <c r="H136" s="243"/>
+      <c r="I136" s="243"/>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A137" s="19" t="s">
+      <c r="A137" s="21"/>
+      <c r="B137" s="169"/>
+      <c r="C137" s="22"/>
+      <c r="D137" s="243"/>
+      <c r="E137" s="243"/>
+      <c r="F137" s="243"/>
+      <c r="G137" s="243"/>
+      <c r="H137" s="243"/>
+      <c r="I137" s="243"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B137" s="23">
-        <f>SUM(B128:B136)</f>
-        <v>1340472.6013971008</v>
-      </c>
-      <c r="C137" s="70"/>
-      <c r="D137" s="223"/>
-      <c r="E137" s="223"/>
-      <c r="F137" s="223"/>
-      <c r="G137" s="223"/>
-      <c r="H137" s="223"/>
-      <c r="I137" s="223"/>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A138" s="22"/>
-      <c r="C138" s="18"/>
-      <c r="D138" s="223"/>
-      <c r="E138" s="223"/>
-      <c r="F138" s="223"/>
-      <c r="G138" s="223"/>
-      <c r="H138" s="223"/>
-      <c r="I138" s="223"/>
+      <c r="B138" s="23">
+        <f>SUM(B128:B137)</f>
+        <v>1767072.6013971008</v>
+      </c>
+      <c r="C138" s="70"/>
+      <c r="D138" s="243"/>
+      <c r="E138" s="243"/>
+      <c r="F138" s="243"/>
+      <c r="G138" s="243"/>
+      <c r="H138" s="243"/>
+      <c r="I138" s="243"/>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A139" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="B139" s="8"/>
+      <c r="A139" s="22"/>
       <c r="C139" s="18"/>
-      <c r="D139" s="223"/>
-      <c r="E139" s="223"/>
-      <c r="F139" s="223"/>
-      <c r="G139" s="223"/>
-      <c r="H139" s="223"/>
-      <c r="I139" s="223"/>
-    </row>
-    <row r="140" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="19" t="s">
-        <v>375</v>
-      </c>
-      <c r="B140" s="30">
-        <v>143267</v>
-      </c>
+      <c r="D139" s="243"/>
+      <c r="E139" s="243"/>
+      <c r="F139" s="243"/>
+      <c r="G139" s="243"/>
+      <c r="H139" s="243"/>
+      <c r="I139" s="243"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="B140" s="8"/>
       <c r="C140" s="18"/>
-      <c r="D140" s="25"/>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A141" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="B141" s="37">
-        <f>SUM(B139:B140)</f>
+      <c r="D140" s="243"/>
+      <c r="E140" s="243"/>
+      <c r="F140" s="243"/>
+      <c r="G140" s="243"/>
+      <c r="H140" s="243"/>
+      <c r="I140" s="243"/>
+    </row>
+    <row r="141" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="B141" s="30">
         <v>143267</v>
       </c>
       <c r="C141" s="18"/>
       <c r="D141" s="25"/>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A142" s="22"/>
+      <c r="A142" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="B142" s="37">
+        <f>SUM(B140:B141)</f>
+        <v>143267</v>
+      </c>
       <c r="C142" s="18"/>
       <c r="D142" s="25"/>
     </row>
@@ -5515,141 +5457,146 @@
       <c r="D143" s="25"/>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A144" s="22"/>
       <c r="C144" s="18"/>
-      <c r="D144" s="43"/>
-      <c r="E144" s="84"/>
-      <c r="F144" s="84"/>
-      <c r="G144" s="84"/>
-      <c r="H144" s="84"/>
-      <c r="I144" s="84"/>
+      <c r="D144" s="25"/>
     </row>
     <row r="145" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A145" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B145" s="8">
-        <v>80000</v>
-      </c>
-      <c r="C145" s="24"/>
-      <c r="D145" s="84"/>
+      <c r="C145" s="18"/>
+      <c r="D145" s="43"/>
       <c r="E145" s="84"/>
       <c r="F145" s="84"/>
       <c r="G145" s="84"/>
       <c r="H145" s="84"/>
       <c r="I145" s="84"/>
-      <c r="J145" s="84"/>
-    </row>
-    <row r="146" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="B146" s="31">
-        <v>120000</v>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A146" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B146" s="8">
+        <v>80000</v>
       </c>
       <c r="C146" s="24"/>
       <c r="D146" s="84"/>
-      <c r="E146" s="88"/>
-      <c r="F146" s="88"/>
-      <c r="G146" s="88"/>
-      <c r="H146" s="88"/>
-      <c r="I146" s="88"/>
-    </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="E146" s="84"/>
+      <c r="F146" s="84"/>
+      <c r="G146" s="84"/>
+      <c r="H146" s="84"/>
+      <c r="I146" s="84"/>
+      <c r="J146" s="84"/>
+    </row>
+    <row r="147" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="B147" s="83">
+        <v>255</v>
+      </c>
+      <c r="B147" s="31">
+        <v>120000</v>
+      </c>
+      <c r="C147" s="24"/>
+      <c r="D147" s="84"/>
+      <c r="E147" s="88"/>
+      <c r="F147" s="88"/>
+      <c r="G147" s="88"/>
+      <c r="H147" s="88"/>
+      <c r="I147" s="88"/>
+    </row>
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A148" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="B148" s="83">
         <v>-20000</v>
       </c>
-      <c r="C147" s="24"/>
-      <c r="D147" s="43"/>
-      <c r="E147" s="43"/>
-      <c r="F147" s="43"/>
-      <c r="G147" s="43"/>
-      <c r="H147" s="43"/>
-      <c r="I147" s="43"/>
-    </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A148" s="36" t="s">
+      <c r="C148" s="24"/>
+      <c r="D148" s="43"/>
+      <c r="E148" s="43"/>
+      <c r="F148" s="43"/>
+      <c r="G148" s="43"/>
+      <c r="H148" s="43"/>
+      <c r="I148" s="43"/>
+    </row>
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A149" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B148" s="37">
-        <f>SUM(B145:B147)</f>
+      <c r="B149" s="37">
+        <f>SUM(B146:B148)</f>
         <v>180000</v>
       </c>
-      <c r="C148" s="24"/>
-    </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="C149" s="25"/>
-      <c r="D149" s="84"/>
+      <c r="C149" s="24"/>
     </row>
     <row r="150" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B150" s="22"/>
-      <c r="C150" s="18"/>
-    </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="R152" s="9"/>
-    </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B155" s="214"/>
-      <c r="C155" s="214"/>
-      <c r="D155" s="214"/>
-      <c r="E155" s="214"/>
-      <c r="F155" s="90"/>
-      <c r="G155" s="90"/>
-      <c r="H155" s="90"/>
-      <c r="I155" s="90"/>
+      <c r="C150" s="25"/>
+      <c r="D150" s="84"/>
+    </row>
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B151" s="22"/>
+      <c r="C151" s="18"/>
+    </row>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R153" s="9"/>
     </row>
     <row r="156" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B156" s="214"/>
-      <c r="C156" s="214"/>
-      <c r="D156" s="214"/>
-      <c r="E156" s="214"/>
+      <c r="B156" s="234"/>
+      <c r="C156" s="234"/>
+      <c r="D156" s="234"/>
+      <c r="E156" s="234"/>
       <c r="F156" s="90"/>
       <c r="G156" s="90"/>
       <c r="H156" s="90"/>
       <c r="I156" s="90"/>
     </row>
     <row r="157" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B157" s="214"/>
-      <c r="C157" s="214"/>
-      <c r="D157" s="214"/>
-      <c r="E157" s="214"/>
+      <c r="B157" s="234"/>
+      <c r="C157" s="234"/>
+      <c r="D157" s="234"/>
+      <c r="E157" s="234"/>
       <c r="F157" s="90"/>
       <c r="G157" s="90"/>
       <c r="H157" s="90"/>
       <c r="I157" s="90"/>
     </row>
     <row r="158" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B158" s="214"/>
-      <c r="C158" s="214"/>
-      <c r="D158" s="214"/>
-      <c r="E158" s="214"/>
+      <c r="B158" s="234"/>
+      <c r="C158" s="234"/>
+      <c r="D158" s="234"/>
+      <c r="E158" s="234"/>
       <c r="F158" s="90"/>
       <c r="G158" s="90"/>
       <c r="H158" s="90"/>
       <c r="I158" s="90"/>
     </row>
     <row r="159" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B159" s="214"/>
-      <c r="C159" s="214"/>
-      <c r="D159" s="214"/>
-      <c r="E159" s="214"/>
+      <c r="B159" s="234"/>
+      <c r="C159" s="234"/>
+      <c r="D159" s="234"/>
+      <c r="E159" s="234"/>
       <c r="F159" s="90"/>
       <c r="G159" s="90"/>
       <c r="H159" s="90"/>
       <c r="I159" s="90"/>
     </row>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B160" s="234"/>
+      <c r="C160" s="234"/>
+      <c r="D160" s="234"/>
+      <c r="E160" s="234"/>
+      <c r="F160" s="90"/>
+      <c r="G160" s="90"/>
+      <c r="H160" s="90"/>
+      <c r="I160" s="90"/>
+    </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A14:J18"/>
-    <mergeCell ref="B155:E159"/>
+    <mergeCell ref="B156:E160"/>
     <mergeCell ref="A121:C121"/>
     <mergeCell ref="A118:D118"/>
     <mergeCell ref="A120:B120"/>
     <mergeCell ref="A119:B119"/>
     <mergeCell ref="A20:J22"/>
-    <mergeCell ref="D125:I139"/>
+    <mergeCell ref="D125:I140"/>
     <mergeCell ref="A67:B67"/>
     <mergeCell ref="A68:B68"/>
     <mergeCell ref="A75:B75"/>
@@ -5691,177 +5638,177 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="263" t="s">
-        <v>377</v>
-      </c>
-      <c r="B1" s="264"/>
-      <c r="C1" s="264"/>
-      <c r="D1" s="264"/>
-      <c r="E1" s="264"/>
-      <c r="F1" s="159" t="s">
-        <v>306</v>
-      </c>
-      <c r="G1" s="159"/>
-      <c r="H1" s="159"/>
-      <c r="I1" s="159"/>
-      <c r="J1" s="159"/>
-      <c r="K1" s="208" t="s">
+      <c r="A1" s="284" t="s">
+        <v>364</v>
+      </c>
+      <c r="B1" s="285"/>
+      <c r="C1" s="285"/>
+      <c r="D1" s="285"/>
+      <c r="E1" s="285"/>
+      <c r="F1" s="158" t="s">
+        <v>296</v>
+      </c>
+      <c r="G1" s="158"/>
+      <c r="H1" s="158"/>
+      <c r="I1" s="158"/>
+      <c r="J1" s="158"/>
+      <c r="K1" s="199" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="239">
+      <c r="L1" s="260">
         <f>RESUMEN!D110-RESUMEN!D108</f>
         <v>12343887.129999999</v>
       </c>
-      <c r="M1" s="240"/>
-      <c r="N1" s="160"/>
+      <c r="M1" s="261"/>
+      <c r="N1" s="159"/>
       <c r="O1" s="59"/>
     </row>
     <row r="2" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="265"/>
-      <c r="B2" s="266"/>
-      <c r="C2" s="266"/>
-      <c r="D2" s="266"/>
-      <c r="E2" s="266"/>
+      <c r="A2" s="286"/>
+      <c r="B2" s="287"/>
+      <c r="C2" s="287"/>
+      <c r="D2" s="287"/>
+      <c r="E2" s="287"/>
       <c r="F2" s="7" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
-      <c r="K2" s="209" t="s">
+      <c r="K2" s="200" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="209"/>
-      <c r="M2" s="210">
+      <c r="L2" s="200"/>
+      <c r="M2" s="201">
         <v>15667206.09</v>
       </c>
-      <c r="N2" s="161"/>
+      <c r="N2" s="160"/>
       <c r="O2" s="59"/>
     </row>
     <row r="3" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="265"/>
-      <c r="B3" s="266"/>
-      <c r="C3" s="266"/>
-      <c r="D3" s="266"/>
-      <c r="E3" s="266"/>
+      <c r="A3" s="286"/>
+      <c r="B3" s="287"/>
+      <c r="C3" s="287"/>
+      <c r="D3" s="287"/>
+      <c r="E3" s="287"/>
       <c r="F3" s="7" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
-      <c r="J3" s="162"/>
+      <c r="J3" s="161"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
-      <c r="M3" s="163"/>
-      <c r="N3" s="164"/>
+      <c r="M3" s="162"/>
+      <c r="N3" s="163"/>
       <c r="O3" s="15"/>
     </row>
     <row r="4" spans="1:18" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="267"/>
-      <c r="B4" s="268"/>
-      <c r="C4" s="268"/>
-      <c r="D4" s="268"/>
-      <c r="E4" s="268"/>
-      <c r="F4" s="165"/>
-      <c r="G4" s="165"/>
-      <c r="H4" s="165"/>
-      <c r="I4" s="165"/>
-      <c r="J4" s="166"/>
-      <c r="K4" s="165"/>
-      <c r="L4" s="165"/>
-      <c r="M4" s="167"/>
-      <c r="N4" s="168"/>
+      <c r="A4" s="288"/>
+      <c r="B4" s="289"/>
+      <c r="C4" s="289"/>
+      <c r="D4" s="289"/>
+      <c r="E4" s="289"/>
+      <c r="F4" s="164"/>
+      <c r="G4" s="164"/>
+      <c r="H4" s="164"/>
+      <c r="I4" s="164"/>
+      <c r="J4" s="165"/>
+      <c r="K4" s="164"/>
+      <c r="L4" s="164"/>
+      <c r="M4" s="166"/>
+      <c r="N4" s="167"/>
       <c r="O4" s="15"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="248" t="s">
-        <v>327</v>
-      </c>
-      <c r="D5" s="249"/>
-      <c r="E5" s="249"/>
-      <c r="F5" s="249"/>
-      <c r="G5" s="249"/>
-      <c r="H5" s="249"/>
-      <c r="I5" s="249"/>
-      <c r="J5" s="249"/>
-      <c r="K5" s="249"/>
-      <c r="L5" s="249"/>
-      <c r="M5" s="249"/>
-      <c r="N5" s="250"/>
+      <c r="C5" s="269" t="s">
+        <v>314</v>
+      </c>
+      <c r="D5" s="270"/>
+      <c r="E5" s="270"/>
+      <c r="F5" s="270"/>
+      <c r="G5" s="270"/>
+      <c r="H5" s="270"/>
+      <c r="I5" s="270"/>
+      <c r="J5" s="270"/>
+      <c r="K5" s="270"/>
+      <c r="L5" s="270"/>
+      <c r="M5" s="270"/>
+      <c r="N5" s="271"/>
       <c r="O5" s="15"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="251"/>
-      <c r="D6" s="252"/>
-      <c r="E6" s="252"/>
-      <c r="F6" s="252"/>
-      <c r="G6" s="252"/>
-      <c r="H6" s="252"/>
-      <c r="I6" s="252"/>
-      <c r="J6" s="252"/>
-      <c r="K6" s="252"/>
-      <c r="L6" s="252"/>
-      <c r="M6" s="252"/>
-      <c r="N6" s="253"/>
+      <c r="C6" s="272"/>
+      <c r="D6" s="273"/>
+      <c r="E6" s="273"/>
+      <c r="F6" s="273"/>
+      <c r="G6" s="273"/>
+      <c r="H6" s="273"/>
+      <c r="I6" s="273"/>
+      <c r="J6" s="273"/>
+      <c r="K6" s="273"/>
+      <c r="L6" s="273"/>
+      <c r="M6" s="273"/>
+      <c r="N6" s="274"/>
       <c r="O6" s="15"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="251"/>
-      <c r="D7" s="252"/>
-      <c r="E7" s="252"/>
-      <c r="F7" s="252"/>
-      <c r="G7" s="252"/>
-      <c r="H7" s="252"/>
-      <c r="I7" s="252"/>
-      <c r="J7" s="252"/>
-      <c r="K7" s="252"/>
-      <c r="L7" s="252"/>
-      <c r="M7" s="252"/>
-      <c r="N7" s="253"/>
+      <c r="C7" s="272"/>
+      <c r="D7" s="273"/>
+      <c r="E7" s="273"/>
+      <c r="F7" s="273"/>
+      <c r="G7" s="273"/>
+      <c r="H7" s="273"/>
+      <c r="I7" s="273"/>
+      <c r="J7" s="273"/>
+      <c r="K7" s="273"/>
+      <c r="L7" s="273"/>
+      <c r="M7" s="273"/>
+      <c r="N7" s="274"/>
       <c r="O7" s="15"/>
     </row>
     <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="254"/>
-      <c r="D8" s="255"/>
-      <c r="E8" s="255"/>
-      <c r="F8" s="255"/>
-      <c r="G8" s="255"/>
-      <c r="H8" s="255"/>
-      <c r="I8" s="255"/>
-      <c r="J8" s="255"/>
-      <c r="K8" s="255"/>
-      <c r="L8" s="255"/>
-      <c r="M8" s="255"/>
-      <c r="N8" s="256"/>
+      <c r="C8" s="275"/>
+      <c r="D8" s="276"/>
+      <c r="E8" s="276"/>
+      <c r="F8" s="276"/>
+      <c r="G8" s="276"/>
+      <c r="H8" s="276"/>
+      <c r="I8" s="276"/>
+      <c r="J8" s="276"/>
+      <c r="K8" s="276"/>
+      <c r="L8" s="276"/>
+      <c r="M8" s="276"/>
+      <c r="N8" s="277"/>
       <c r="P8" s="84"/>
     </row>
     <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="257" t="s">
-        <v>322</v>
-      </c>
-      <c r="D9" s="258"/>
-      <c r="E9" s="258"/>
-      <c r="F9" s="258"/>
-      <c r="G9" s="258"/>
-      <c r="H9" s="258"/>
-      <c r="I9" s="258"/>
-      <c r="J9" s="258"/>
-      <c r="K9" s="258"/>
-      <c r="L9" s="258"/>
-      <c r="M9" s="258"/>
-      <c r="N9" s="259"/>
+      <c r="C9" s="278" t="s">
+        <v>312</v>
+      </c>
+      <c r="D9" s="279"/>
+      <c r="E9" s="279"/>
+      <c r="F9" s="279"/>
+      <c r="G9" s="279"/>
+      <c r="H9" s="279"/>
+      <c r="I9" s="279"/>
+      <c r="J9" s="279"/>
+      <c r="K9" s="279"/>
+      <c r="L9" s="279"/>
+      <c r="M9" s="279"/>
+      <c r="N9" s="280"/>
       <c r="P9" t="s">
         <v>250</v>
       </c>
@@ -5873,18 +5820,18 @@
     <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="260"/>
-      <c r="D10" s="261"/>
-      <c r="E10" s="261"/>
-      <c r="F10" s="261"/>
-      <c r="G10" s="261"/>
-      <c r="H10" s="261"/>
-      <c r="I10" s="261"/>
-      <c r="J10" s="261"/>
-      <c r="K10" s="261"/>
-      <c r="L10" s="261"/>
-      <c r="M10" s="261"/>
-      <c r="N10" s="262"/>
+      <c r="C10" s="281"/>
+      <c r="D10" s="282"/>
+      <c r="E10" s="282"/>
+      <c r="F10" s="282"/>
+      <c r="G10" s="282"/>
+      <c r="H10" s="282"/>
+      <c r="I10" s="282"/>
+      <c r="J10" s="282"/>
+      <c r="K10" s="282"/>
+      <c r="L10" s="282"/>
+      <c r="M10" s="282"/>
+      <c r="N10" s="283"/>
       <c r="P10" t="s">
         <v>251</v>
       </c>
@@ -5894,46 +5841,46 @@
       </c>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="231" t="s">
+      <c r="A11" s="251" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="233" t="s">
+      <c r="B11" s="253" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="231" t="s">
+      <c r="C11" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="235" t="s">
+      <c r="D11" s="255" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="235" t="s">
+      <c r="E11" s="255" t="s">
         <v>269</v>
       </c>
-      <c r="F11" s="231" t="s">
+      <c r="F11" s="251" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="231" t="s">
+      <c r="G11" s="251" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="231" t="s">
+      <c r="H11" s="251" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="241" t="s">
+      <c r="I11" s="262" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="243" t="s">
+      <c r="J11" s="264" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="243" t="s">
+      <c r="K11" s="264" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="246" t="s">
+      <c r="L11" s="267" t="s">
         <v>40</v>
       </c>
-      <c r="M11" s="243" t="s">
+      <c r="M11" s="264" t="s">
         <v>280</v>
       </c>
-      <c r="N11" s="243" t="s">
+      <c r="N11" s="264" t="s">
         <v>279</v>
       </c>
       <c r="P11" t="s">
@@ -5945,20 +5892,20 @@
       </c>
     </row>
     <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="232"/>
-      <c r="B12" s="234"/>
-      <c r="C12" s="232"/>
-      <c r="D12" s="236"/>
-      <c r="E12" s="236"/>
-      <c r="F12" s="232"/>
-      <c r="G12" s="232"/>
-      <c r="H12" s="232"/>
-      <c r="I12" s="242"/>
-      <c r="J12" s="244"/>
-      <c r="K12" s="244"/>
-      <c r="L12" s="247"/>
-      <c r="M12" s="244"/>
-      <c r="N12" s="244"/>
+      <c r="A12" s="252"/>
+      <c r="B12" s="254"/>
+      <c r="C12" s="252"/>
+      <c r="D12" s="256"/>
+      <c r="E12" s="256"/>
+      <c r="F12" s="252"/>
+      <c r="G12" s="252"/>
+      <c r="H12" s="252"/>
+      <c r="I12" s="263"/>
+      <c r="J12" s="265"/>
+      <c r="K12" s="265"/>
+      <c r="L12" s="268"/>
+      <c r="M12" s="265"/>
+      <c r="N12" s="265"/>
       <c r="P12" t="s">
         <v>253</v>
       </c>
@@ -5968,18 +5915,18 @@
       </c>
     </row>
     <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="232"/>
-      <c r="B13" s="234"/>
-      <c r="C13" s="232"/>
-      <c r="D13" s="236"/>
-      <c r="E13" s="236"/>
-      <c r="F13" s="232"/>
-      <c r="G13" s="232"/>
-      <c r="H13" s="232"/>
-      <c r="I13" s="242"/>
-      <c r="J13" s="244"/>
-      <c r="K13" s="245"/>
-      <c r="L13" s="247"/>
+      <c r="A13" s="252"/>
+      <c r="B13" s="254"/>
+      <c r="C13" s="252"/>
+      <c r="D13" s="256"/>
+      <c r="E13" s="256"/>
+      <c r="F13" s="252"/>
+      <c r="G13" s="252"/>
+      <c r="H13" s="252"/>
+      <c r="I13" s="263"/>
+      <c r="J13" s="265"/>
+      <c r="K13" s="266"/>
+      <c r="L13" s="268"/>
       <c r="M13" s="132" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 16/02</v>
@@ -6008,39 +5955,39 @@
         <v>175</v>
       </c>
       <c r="E14" s="108" t="s">
-        <v>313</v>
-      </c>
-      <c r="F14" s="144">
+        <v>303</v>
+      </c>
+      <c r="F14" s="143">
         <v>1.0800000000000001E-2</v>
       </c>
-      <c r="G14" s="138">
+      <c r="G14" s="137">
         <v>274719.32308800006</v>
       </c>
-      <c r="H14" s="286"/>
-      <c r="I14" s="145">
+      <c r="H14" s="215"/>
+      <c r="I14" s="144">
         <f>G14-H14</f>
         <v>274719.32308800006</v>
       </c>
-      <c r="J14" s="146">
-        <v>0</v>
-      </c>
-      <c r="K14" s="146">
+      <c r="J14" s="145">
+        <v>0</v>
+      </c>
+      <c r="K14" s="145">
         <v>141730.21116000001</v>
       </c>
-      <c r="L14" s="169">
-        <v>0</v>
-      </c>
-      <c r="M14" s="147">
+      <c r="L14" s="168">
+        <v>0</v>
+      </c>
+      <c r="M14" s="146">
         <f>K14+J14+I14+L14</f>
         <v>416449.53424800007</v>
       </c>
-      <c r="N14" s="148">
+      <c r="N14" s="147">
         <f>M14*6% + M14</f>
         <v>441436.50630288007</v>
       </c>
       <c r="O14" s="115"/>
-      <c r="Q14" s="237"/>
-      <c r="R14" s="237"/>
+      <c r="Q14" s="257"/>
+      <c r="R14" s="257"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
@@ -6049,42 +5996,42 @@
         <v>117</v>
       </c>
       <c r="D15" s="108" t="s">
-        <v>372</v>
-      </c>
-      <c r="E15" s="206"/>
-      <c r="F15" s="144">
+        <v>359</v>
+      </c>
+      <c r="E15" s="197"/>
+      <c r="F15" s="143">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="G15" s="138">
+      <c r="G15" s="137">
         <v>183831.27180800005</v>
       </c>
-      <c r="H15" s="286">
+      <c r="H15" s="215">
         <v>61277</v>
       </c>
-      <c r="I15" s="145">
+      <c r="I15" s="144">
         <f t="shared" ref="I15:I131" si="0">G15-H15</f>
         <v>122554.27180800005</v>
       </c>
-      <c r="J15" s="146">
-        <v>0</v>
-      </c>
-      <c r="K15" s="146">
+      <c r="J15" s="145">
+        <v>0</v>
+      </c>
+      <c r="K15" s="145">
         <v>167976.54656000002</v>
       </c>
-      <c r="L15" s="169">
-        <v>0</v>
-      </c>
-      <c r="M15" s="147">
+      <c r="L15" s="168">
+        <v>0</v>
+      </c>
+      <c r="M15" s="146">
         <f t="shared" ref="M15:M18" si="1">K15+J15+I15+L15</f>
         <v>290530.81836800009</v>
       </c>
-      <c r="N15" s="148">
+      <c r="N15" s="147">
         <f t="shared" ref="N15:N18" si="2">M15*6% + M15</f>
         <v>307962.66747008008</v>
       </c>
       <c r="O15" s="115"/>
-      <c r="Q15" s="237"/>
-      <c r="R15" s="237"/>
+      <c r="Q15" s="257"/>
+      <c r="R15" s="257"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
@@ -6098,36 +6045,36 @@
         <v>267</v>
       </c>
       <c r="E16" s="108" t="s">
-        <v>371</v>
-      </c>
-      <c r="F16" s="144">
+        <v>358</v>
+      </c>
+      <c r="F16" s="143">
         <v>1.21E-2</v>
       </c>
-      <c r="G16" s="286">
+      <c r="G16" s="215">
         <v>160512.294448</v>
       </c>
-      <c r="H16" s="286">
+      <c r="H16" s="215">
         <f t="shared" ref="H16:H21" si="3">G16</f>
         <v>160512.294448</v>
       </c>
-      <c r="I16" s="145">
+      <c r="I16" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J16" s="146">
-        <v>0</v>
-      </c>
-      <c r="K16" s="146">
+      <c r="J16" s="145">
+        <v>0</v>
+      </c>
+      <c r="K16" s="145">
         <v>158790.32916999998</v>
       </c>
-      <c r="L16" s="169">
-        <v>0</v>
-      </c>
-      <c r="M16" s="147">
+      <c r="L16" s="168">
+        <v>0</v>
+      </c>
+      <c r="M16" s="146">
         <f t="shared" si="1"/>
         <v>158790.32916999998</v>
       </c>
-      <c r="N16" s="148">
+      <c r="N16" s="147">
         <f t="shared" si="2"/>
         <v>168317.74892019999</v>
       </c>
@@ -6146,31 +6093,31 @@
         <v>176</v>
       </c>
       <c r="E17" s="108"/>
-      <c r="F17" s="144">
+      <c r="F17" s="143">
         <v>1.49E-2</v>
       </c>
-      <c r="G17" s="138">
+      <c r="G17" s="137">
         <v>551052.91796400002</v>
       </c>
-      <c r="H17" s="286"/>
-      <c r="I17" s="145">
+      <c r="H17" s="215"/>
+      <c r="I17" s="144">
         <f t="shared" si="0"/>
         <v>551052.91796400002</v>
       </c>
-      <c r="J17" s="146">
-        <v>0</v>
-      </c>
-      <c r="K17" s="146">
+      <c r="J17" s="145">
+        <v>0</v>
+      </c>
+      <c r="K17" s="145">
         <v>195535.19872999997</v>
       </c>
-      <c r="L17" s="169">
-        <v>0</v>
-      </c>
-      <c r="M17" s="147">
+      <c r="L17" s="168">
+        <v>0</v>
+      </c>
+      <c r="M17" s="146">
         <f t="shared" si="1"/>
         <v>746588.11669399997</v>
       </c>
-      <c r="N17" s="148">
+      <c r="N17" s="147">
         <f t="shared" si="2"/>
         <v>791383.40369563992</v>
       </c>
@@ -6182,41 +6129,41 @@
         <v>118</v>
       </c>
       <c r="B18" s="6"/>
-      <c r="C18" s="149" t="s">
+      <c r="C18" s="148" t="s">
         <v>116</v>
       </c>
-      <c r="D18" s="150" t="s">
+      <c r="D18" s="149" t="s">
         <v>268</v>
       </c>
-      <c r="E18" s="150"/>
-      <c r="F18" s="151">
+      <c r="E18" s="149"/>
+      <c r="F18" s="150">
         <v>1.7399999999999999E-2</v>
       </c>
-      <c r="G18" s="152">
+      <c r="G18" s="151">
         <v>469159.55509584001</v>
       </c>
-      <c r="H18" s="287">
+      <c r="H18" s="216">
         <f>G18</f>
         <v>469159.55509584001</v>
       </c>
-      <c r="I18" s="153">
+      <c r="I18" s="152">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J18" s="154">
-        <v>0</v>
-      </c>
-      <c r="K18" s="154">
+      <c r="J18" s="153">
+        <v>0</v>
+      </c>
+      <c r="K18" s="153">
         <v>228343.11798000001</v>
       </c>
-      <c r="L18" s="301">
-        <v>0</v>
-      </c>
-      <c r="M18" s="155">
+      <c r="L18" s="230">
+        <v>0</v>
+      </c>
+      <c r="M18" s="154">
         <f t="shared" si="1"/>
         <v>228343.11798000001</v>
       </c>
-      <c r="N18" s="156">
+      <c r="N18" s="155">
         <f t="shared" si="2"/>
         <v>242043.7050588</v>
       </c>
@@ -6228,43 +6175,43 @@
         <v>120</v>
       </c>
       <c r="B19" s="6"/>
-      <c r="C19" s="201" t="s">
+      <c r="C19" s="192" t="s">
         <v>44</v>
       </c>
       <c r="D19" s="135" t="s">
         <v>177</v>
       </c>
       <c r="E19" s="135"/>
-      <c r="F19" s="137">
+      <c r="F19" s="136">
         <v>1.8800000000000001E-2</v>
       </c>
-      <c r="G19" s="202">
+      <c r="G19" s="193">
         <v>261193.01</v>
       </c>
-      <c r="H19" s="288">
+      <c r="H19" s="217">
         <f>G19</f>
         <v>261193.01</v>
       </c>
-      <c r="I19" s="203">
+      <c r="I19" s="194">
         <f>G19-H19</f>
         <v>0</v>
       </c>
-      <c r="J19" s="204">
+      <c r="J19" s="195">
         <f t="shared" ref="J19:J50" si="4">M$8*F19</f>
         <v>0</v>
       </c>
-      <c r="K19" s="204">
+      <c r="K19" s="195">
         <f>M$2*F19</f>
         <v>294543.47449200001</v>
       </c>
-      <c r="L19" s="300">
-        <v>0</v>
-      </c>
-      <c r="M19" s="205">
+      <c r="L19" s="229">
+        <v>0</v>
+      </c>
+      <c r="M19" s="196">
         <f>ROUND((K19+J19+I19+L19),0) + O19</f>
         <v>294543.01</v>
       </c>
-      <c r="N19" s="205">
+      <c r="N19" s="196">
         <f>ROUND((M19*6% + M19 ),0) + O19</f>
         <v>312216.01</v>
       </c>
@@ -6272,7 +6219,7 @@
         <v>0.01</v>
       </c>
       <c r="P19" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="R19" s="43"/>
     </row>
@@ -6288,36 +6235,36 @@
         <v>178</v>
       </c>
       <c r="E20" s="135"/>
-      <c r="F20" s="137">
+      <c r="F20" s="136">
         <v>8.3999999999999995E-3</v>
       </c>
-      <c r="G20" s="138">
+      <c r="G20" s="137">
         <v>131605.01999999999</v>
       </c>
-      <c r="H20" s="286">
+      <c r="H20" s="215">
         <f t="shared" ref="H20" si="5">G20</f>
         <v>131605.01999999999</v>
       </c>
-      <c r="I20" s="145">
+      <c r="I20" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J20" s="146">
+      <c r="J20" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K20" s="146">
+      <c r="K20" s="145">
         <f t="shared" ref="K20:K50" si="6">M$2*F20</f>
         <v>131604.53115599998</v>
       </c>
-      <c r="L20" s="169">
-        <v>0</v>
-      </c>
-      <c r="M20" s="148">
+      <c r="L20" s="168">
+        <v>0</v>
+      </c>
+      <c r="M20" s="147">
         <f>ROUND((K20+J20+I20+L20),0) + O20</f>
         <v>131605.01999999999</v>
       </c>
-      <c r="N20" s="148">
+      <c r="N20" s="147">
         <f t="shared" ref="N20:N83" si="7">ROUND((M20*6% + M20 ),0) + O20</f>
         <v>139501.01999999999</v>
       </c>
@@ -6339,36 +6286,36 @@
         <v>179</v>
       </c>
       <c r="E21" s="135"/>
-      <c r="F21" s="137">
+      <c r="F21" s="136">
         <v>2.01E-2</v>
       </c>
-      <c r="G21" s="138">
+      <c r="G21" s="137">
         <v>333806.03000000003</v>
       </c>
-      <c r="H21" s="286">
+      <c r="H21" s="215">
         <f t="shared" si="3"/>
         <v>333806.03000000003</v>
       </c>
-      <c r="I21" s="145">
+      <c r="I21" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J21" s="146">
+      <c r="J21" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K21" s="146">
+      <c r="K21" s="145">
         <f t="shared" si="6"/>
         <v>314910.84240899998</v>
       </c>
-      <c r="L21" s="169">
+      <c r="L21" s="168">
         <v>20000</v>
       </c>
-      <c r="M21" s="148">
+      <c r="M21" s="147">
         <f t="shared" ref="M21:M83" si="8">ROUND((K21+J21+I21+L21),0) + O21</f>
         <v>334911.03000000003</v>
       </c>
-      <c r="N21" s="148">
+      <c r="N21" s="147">
         <f t="shared" si="7"/>
         <v>355006.03</v>
       </c>
@@ -6382,44 +6329,44 @@
         <v>122</v>
       </c>
       <c r="B22" s="6"/>
-      <c r="C22" s="276" t="s">
+      <c r="C22" s="205" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="277" t="s">
+      <c r="D22" s="206" t="s">
         <v>180</v>
       </c>
-      <c r="E22" s="278" t="s">
-        <v>298</v>
-      </c>
-      <c r="F22" s="279">
+      <c r="E22" s="207" t="s">
+        <v>288</v>
+      </c>
+      <c r="F22" s="208">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G22" s="280">
+      <c r="G22" s="209">
         <v>146444.04</v>
       </c>
-      <c r="H22" s="289">
+      <c r="H22" s="218">
         <v>147222</v>
       </c>
-      <c r="I22" s="281">
+      <c r="I22" s="210">
         <f t="shared" si="0"/>
         <v>-777.95999999999185</v>
       </c>
-      <c r="J22" s="282">
+      <c r="J22" s="211">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K22" s="282">
+      <c r="K22" s="211">
         <f t="shared" si="6"/>
         <v>147271.737246</v>
       </c>
-      <c r="L22" s="283">
-        <v>0</v>
-      </c>
-      <c r="M22" s="284">
+      <c r="L22" s="212">
+        <v>0</v>
+      </c>
+      <c r="M22" s="213">
         <f t="shared" si="8"/>
         <v>146494.04</v>
       </c>
-      <c r="N22" s="284">
+      <c r="N22" s="213">
         <f t="shared" si="7"/>
         <v>155284.04</v>
       </c>
@@ -6428,7 +6375,7 @@
         <v>0.04</v>
       </c>
       <c r="P22" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
@@ -6443,36 +6390,36 @@
         <v>181</v>
       </c>
       <c r="E23" s="135" t="s">
-        <v>318</v>
-      </c>
-      <c r="F23" s="137">
+        <v>308</v>
+      </c>
+      <c r="F23" s="136">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G23" s="138">
+      <c r="G23" s="137">
         <v>156305.04999999999</v>
       </c>
-      <c r="H23" s="286">
+      <c r="H23" s="215">
         <f>19700+136605.05</f>
         <v>156305.04999999999</v>
       </c>
-      <c r="I23" s="145">
+      <c r="I23" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J23" s="146">
+      <c r="J23" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K23" s="146">
+      <c r="K23" s="145">
         <f t="shared" si="6"/>
         <v>136304.69298299999</v>
       </c>
-      <c r="L23" s="169"/>
-      <c r="M23" s="148">
+      <c r="L23" s="168"/>
+      <c r="M23" s="147">
         <f t="shared" si="8"/>
         <v>136305.04999999999</v>
       </c>
-      <c r="N23" s="148">
+      <c r="N23" s="147">
         <f t="shared" si="7"/>
         <v>144483.04999999999</v>
       </c>
@@ -6493,38 +6440,38 @@
         <v>182</v>
       </c>
       <c r="E24" s="135" t="s">
-        <v>312</v>
-      </c>
-      <c r="F24" s="137">
+        <v>302</v>
+      </c>
+      <c r="F24" s="136">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G24" s="138">
+      <c r="G24" s="137">
         <v>148838.06</v>
       </c>
-      <c r="H24" s="286">
+      <c r="H24" s="215">
         <f t="shared" ref="H24" si="10">G24</f>
         <v>148838.06</v>
       </c>
-      <c r="I24" s="145">
+      <c r="I24" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J24" s="146">
+      <c r="J24" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K24" s="146">
+      <c r="K24" s="145">
         <f t="shared" si="6"/>
         <v>148838.45785499999</v>
       </c>
-      <c r="L24" s="169">
-        <v>0</v>
-      </c>
-      <c r="M24" s="148">
+      <c r="L24" s="168">
+        <v>0</v>
+      </c>
+      <c r="M24" s="147">
         <f t="shared" si="8"/>
         <v>148838.06</v>
       </c>
-      <c r="N24" s="148">
+      <c r="N24" s="147">
         <f t="shared" si="7"/>
         <v>157768.06</v>
       </c>
@@ -6545,38 +6492,38 @@
         <v>182</v>
       </c>
       <c r="E25" s="135" t="s">
-        <v>326</v>
-      </c>
-      <c r="F25" s="137">
+        <v>313</v>
+      </c>
+      <c r="F25" s="136">
         <v>1.6500000000000001E-2</v>
       </c>
-      <c r="G25" s="138">
+      <c r="G25" s="137">
         <v>300495.07</v>
       </c>
-      <c r="H25" s="286">
+      <c r="H25" s="215">
         <f>G25</f>
         <v>300495.07</v>
       </c>
-      <c r="I25" s="145">
+      <c r="I25" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J25" s="146">
+      <c r="J25" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K25" s="146">
+      <c r="K25" s="145">
         <f t="shared" si="6"/>
         <v>258508.90048500002</v>
       </c>
-      <c r="L25" s="169">
-        <v>0</v>
-      </c>
-      <c r="M25" s="148">
+      <c r="L25" s="168">
+        <v>0</v>
+      </c>
+      <c r="M25" s="147">
         <f t="shared" si="8"/>
         <v>258509.07</v>
       </c>
-      <c r="N25" s="148">
+      <c r="N25" s="147">
         <f t="shared" si="7"/>
         <v>274020.07</v>
       </c>
@@ -6597,36 +6544,36 @@
         <v>270</v>
       </c>
       <c r="E26" s="135"/>
-      <c r="F26" s="137">
+      <c r="F26" s="136">
         <v>7.3000000000000001E-3</v>
       </c>
-      <c r="G26" s="138">
+      <c r="G26" s="137">
         <v>114371.08</v>
       </c>
-      <c r="H26" s="286">
+      <c r="H26" s="215">
         <f>G26</f>
         <v>114371.08</v>
       </c>
-      <c r="I26" s="145">
+      <c r="I26" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J26" s="146">
+      <c r="J26" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K26" s="146">
+      <c r="K26" s="145">
         <f t="shared" si="6"/>
         <v>114370.60445699999</v>
       </c>
-      <c r="L26" s="169">
+      <c r="L26" s="168">
         <v>20000</v>
       </c>
-      <c r="M26" s="148">
+      <c r="M26" s="147">
         <f t="shared" si="8"/>
         <v>134371.07999999999</v>
       </c>
-      <c r="N26" s="148">
+      <c r="N26" s="147">
         <f t="shared" si="7"/>
         <v>142433.07999999999</v>
       </c>
@@ -6640,46 +6587,46 @@
         <v>120</v>
       </c>
       <c r="B27" s="35"/>
-      <c r="C27" s="276" t="s">
+      <c r="C27" s="205" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="277" t="s">
+      <c r="D27" s="206" t="s">
         <v>182</v>
       </c>
-      <c r="E27" s="278" t="s">
-        <v>374</v>
-      </c>
-      <c r="F27" s="279">
+      <c r="E27" s="207" t="s">
+        <v>361</v>
+      </c>
+      <c r="F27" s="208">
         <v>1.78E-2</v>
       </c>
-      <c r="G27" s="280">
+      <c r="G27" s="209">
         <v>535348.09</v>
       </c>
-      <c r="H27" s="289">
+      <c r="H27" s="218">
         <f>278876+258100</f>
         <v>536976</v>
       </c>
-      <c r="I27" s="281">
+      <c r="I27" s="210">
         <f t="shared" si="0"/>
         <v>-1627.9100000000326</v>
       </c>
-      <c r="J27" s="282">
+      <c r="J27" s="211">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K27" s="282">
+      <c r="K27" s="211">
         <f t="shared" si="6"/>
         <v>278876.26840200002</v>
       </c>
-      <c r="L27" s="302">
+      <c r="L27" s="231">
         <f>13000*3</f>
         <v>39000</v>
       </c>
-      <c r="M27" s="284">
+      <c r="M27" s="213">
         <f t="shared" si="8"/>
         <v>316248.09000000003</v>
       </c>
-      <c r="N27" s="284">
+      <c r="N27" s="213">
         <f t="shared" si="7"/>
         <v>335223.09000000003</v>
       </c>
@@ -6697,39 +6644,39 @@
         <v>53</v>
       </c>
       <c r="D28" s="108" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="E28" s="135"/>
-      <c r="F28" s="137">
+      <c r="F28" s="136">
         <v>9.4000000000000004E-3</v>
       </c>
       <c r="G28" s="44">
         <v>133172.1</v>
       </c>
-      <c r="H28" s="286">
+      <c r="H28" s="215">
         <f t="shared" ref="H28:H29" si="11">G28</f>
         <v>133172.1</v>
       </c>
-      <c r="I28" s="145">
+      <c r="I28" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J28" s="146">
+      <c r="J28" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K28" s="146">
+      <c r="K28" s="145">
         <f t="shared" si="6"/>
         <v>147271.737246</v>
       </c>
-      <c r="L28" s="169">
-        <v>0</v>
-      </c>
-      <c r="M28" s="148">
+      <c r="L28" s="168">
+        <v>0</v>
+      </c>
+      <c r="M28" s="147">
         <f t="shared" si="8"/>
         <v>147272.1</v>
       </c>
-      <c r="N28" s="148">
+      <c r="N28" s="147">
         <f t="shared" si="7"/>
         <v>156108.1</v>
       </c>
@@ -6747,39 +6694,39 @@
         <v>54</v>
       </c>
       <c r="D29" s="108" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="E29" s="135"/>
-      <c r="F29" s="137">
+      <c r="F29" s="136">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G29" s="138">
+      <c r="G29" s="137">
         <v>136305.10999999999</v>
       </c>
-      <c r="H29" s="286">
+      <c r="H29" s="215">
         <f t="shared" si="11"/>
         <v>136305.10999999999</v>
       </c>
-      <c r="I29" s="145">
+      <c r="I29" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J29" s="146">
+      <c r="J29" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K29" s="146">
+      <c r="K29" s="145">
         <f t="shared" si="6"/>
         <v>136304.69298299999</v>
       </c>
-      <c r="L29" s="169">
+      <c r="L29" s="168">
         <v>20000</v>
       </c>
-      <c r="M29" s="148">
+      <c r="M29" s="147">
         <f t="shared" si="8"/>
         <v>156305.10999999999</v>
       </c>
-      <c r="N29" s="148">
+      <c r="N29" s="147">
         <f t="shared" si="7"/>
         <v>165683.10999999999</v>
       </c>
@@ -6800,33 +6747,33 @@
         <v>183</v>
       </c>
       <c r="E30" s="135"/>
-      <c r="F30" s="137">
+      <c r="F30" s="136">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G30" s="138">
+      <c r="G30" s="137">
         <v>666589.12</v>
       </c>
-      <c r="H30" s="286"/>
-      <c r="I30" s="145">
+      <c r="H30" s="215"/>
+      <c r="I30" s="144">
         <f t="shared" si="0"/>
         <v>666589.12</v>
       </c>
-      <c r="J30" s="146">
+      <c r="J30" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K30" s="146">
+      <c r="K30" s="145">
         <f t="shared" si="6"/>
         <v>148838.45785499999</v>
       </c>
-      <c r="L30" s="169">
-        <v>0</v>
-      </c>
-      <c r="M30" s="148">
+      <c r="L30" s="168">
+        <v>0</v>
+      </c>
+      <c r="M30" s="147">
         <f t="shared" si="8"/>
         <v>815428.12</v>
       </c>
-      <c r="N30" s="148">
+      <c r="N30" s="147">
         <f t="shared" si="7"/>
         <v>864354.12</v>
       </c>
@@ -6847,36 +6794,36 @@
         <v>184</v>
       </c>
       <c r="E31" s="135"/>
-      <c r="F31" s="137">
+      <c r="F31" s="136">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="G31" s="138">
+      <c r="G31" s="137">
         <v>276942.13</v>
       </c>
-      <c r="H31" s="286">
+      <c r="H31" s="215">
         <f>G31</f>
         <v>276942.13</v>
       </c>
-      <c r="I31" s="145">
+      <c r="I31" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J31" s="146">
+      <c r="J31" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K31" s="146">
+      <c r="K31" s="145">
         <f t="shared" si="6"/>
         <v>256942.17987600001</v>
       </c>
-      <c r="L31" s="169">
-        <v>0</v>
-      </c>
-      <c r="M31" s="148">
+      <c r="L31" s="168">
+        <v>0</v>
+      </c>
+      <c r="M31" s="147">
         <f t="shared" si="8"/>
         <v>256942.13</v>
       </c>
-      <c r="N31" s="148">
+      <c r="N31" s="147">
         <f t="shared" si="7"/>
         <v>272359.13</v>
       </c>
@@ -6899,36 +6846,36 @@
       <c r="E32" s="135" t="s">
         <v>271</v>
       </c>
-      <c r="F32" s="137">
+      <c r="F32" s="136">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="G32" s="138">
+      <c r="G32" s="137">
         <v>112804.14</v>
       </c>
-      <c r="H32" s="286">
+      <c r="H32" s="215">
         <f>G32</f>
         <v>112804.14</v>
       </c>
-      <c r="I32" s="145">
+      <c r="I32" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J32" s="146">
+      <c r="J32" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K32" s="146">
+      <c r="K32" s="145">
         <f t="shared" si="6"/>
         <v>112803.883848</v>
       </c>
-      <c r="L32" s="169">
-        <v>0</v>
-      </c>
-      <c r="M32" s="148">
+      <c r="L32" s="168">
+        <v>0</v>
+      </c>
+      <c r="M32" s="147">
         <f t="shared" si="8"/>
         <v>112804.14</v>
       </c>
-      <c r="N32" s="148">
+      <c r="N32" s="147">
         <f t="shared" si="7"/>
         <v>119572.14</v>
       </c>
@@ -6949,36 +6896,36 @@
         <v>185</v>
       </c>
       <c r="E33" s="135"/>
-      <c r="F33" s="137">
+      <c r="F33" s="136">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G33" s="138">
+      <c r="G33" s="137">
         <v>271043.15000000002</v>
       </c>
-      <c r="H33" s="286">
+      <c r="H33" s="215">
         <f>G33</f>
         <v>271043.15000000002</v>
       </c>
-      <c r="I33" s="157">
+      <c r="I33" s="156">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J33" s="146">
+      <c r="J33" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K33" s="146">
+      <c r="K33" s="145">
         <f t="shared" si="6"/>
         <v>271042.66535699996</v>
       </c>
-      <c r="L33" s="169">
+      <c r="L33" s="168">
         <v>25000</v>
       </c>
-      <c r="M33" s="148">
+      <c r="M33" s="147">
         <f t="shared" si="8"/>
         <v>296043.15000000002</v>
       </c>
-      <c r="N33" s="148">
+      <c r="N33" s="147">
         <f t="shared" si="7"/>
         <v>313806.15000000002</v>
       </c>
@@ -6988,47 +6935,47 @@
       </c>
     </row>
     <row r="34" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A34" s="140" t="s">
+      <c r="A34" s="139" t="s">
         <v>122</v>
       </c>
-      <c r="B34" s="139"/>
+      <c r="B34" s="138"/>
       <c r="C34" s="35" t="s">
         <v>59</v>
       </c>
       <c r="D34" s="108" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="E34" s="135"/>
-      <c r="F34" s="137">
+      <c r="F34" s="136">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G34" s="138">
+      <c r="G34" s="137">
         <v>139543.16</v>
       </c>
-      <c r="H34" s="286">
+      <c r="H34" s="215">
         <f>G34</f>
         <v>139543.16</v>
       </c>
-      <c r="I34" s="145">
+      <c r="I34" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J34" s="146">
+      <c r="J34" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K34" s="146">
+      <c r="K34" s="145">
         <f t="shared" si="6"/>
         <v>147271.737246</v>
       </c>
-      <c r="L34" s="169">
-        <v>0</v>
-      </c>
-      <c r="M34" s="148">
+      <c r="L34" s="168">
+        <v>0</v>
+      </c>
+      <c r="M34" s="147">
         <f t="shared" si="8"/>
         <v>147272.16</v>
       </c>
-      <c r="N34" s="148">
+      <c r="N34" s="147">
         <f t="shared" si="7"/>
         <v>156108.16</v>
       </c>
@@ -7037,7 +6984,7 @@
         <v>0.16</v>
       </c>
       <c r="P34" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
     </row>
     <row r="35" spans="1:113" x14ac:dyDescent="0.25">
@@ -7052,38 +6999,38 @@
         <v>183</v>
       </c>
       <c r="E35" s="135" t="s">
-        <v>301</v>
-      </c>
-      <c r="F35" s="137">
+        <v>291</v>
+      </c>
+      <c r="F35" s="136">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G35" s="138">
+      <c r="G35" s="137">
         <v>136305.17000000001</v>
       </c>
-      <c r="H35" s="286">
+      <c r="H35" s="215">
         <f t="shared" ref="H35" si="12">G35</f>
         <v>136305.17000000001</v>
       </c>
-      <c r="I35" s="145">
+      <c r="I35" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J35" s="146">
+      <c r="J35" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K35" s="146">
+      <c r="K35" s="145">
         <f t="shared" si="6"/>
         <v>136304.69298299999</v>
       </c>
-      <c r="L35" s="169">
-        <v>0</v>
-      </c>
-      <c r="M35" s="148">
+      <c r="L35" s="168">
+        <v>0</v>
+      </c>
+      <c r="M35" s="147">
         <f t="shared" si="8"/>
         <v>136305.17000000001</v>
       </c>
-      <c r="N35" s="148">
+      <c r="N35" s="147">
         <f t="shared" si="7"/>
         <v>144483.17000000001</v>
       </c>
@@ -7104,33 +7051,33 @@
         <v>183</v>
       </c>
       <c r="E36" s="135"/>
-      <c r="F36" s="137">
+      <c r="F36" s="136">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G36" s="138">
+      <c r="G36" s="137">
         <v>148838.18</v>
       </c>
-      <c r="H36" s="286"/>
-      <c r="I36" s="157">
+      <c r="H36" s="215"/>
+      <c r="I36" s="156">
         <f t="shared" si="0"/>
         <v>148838.18</v>
       </c>
-      <c r="J36" s="146">
+      <c r="J36" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K36" s="146">
+      <c r="K36" s="145">
         <f t="shared" si="6"/>
         <v>148838.45785499999</v>
       </c>
-      <c r="L36" s="169">
-        <v>0</v>
-      </c>
-      <c r="M36" s="148">
+      <c r="L36" s="168">
+        <v>0</v>
+      </c>
+      <c r="M36" s="147">
         <f t="shared" si="8"/>
         <v>297677.18</v>
       </c>
-      <c r="N36" s="148">
+      <c r="N36" s="147">
         <f t="shared" si="7"/>
         <v>315538.18</v>
       </c>
@@ -7151,36 +7098,36 @@
         <v>186</v>
       </c>
       <c r="E37" s="135" t="s">
-        <v>299</v>
-      </c>
-      <c r="F37" s="137">
+        <v>289</v>
+      </c>
+      <c r="F37" s="136">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="G37" s="138">
+      <c r="G37" s="137">
         <v>256942.19</v>
       </c>
-      <c r="H37" s="286">
+      <c r="H37" s="215">
         <f t="shared" ref="H37" si="13">G37</f>
         <v>256942.19</v>
       </c>
-      <c r="I37" s="145">
+      <c r="I37" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J37" s="146">
+      <c r="J37" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K37" s="146">
+      <c r="K37" s="145">
         <f t="shared" si="6"/>
         <v>256942.17987600001</v>
       </c>
-      <c r="L37" s="169"/>
-      <c r="M37" s="148">
+      <c r="L37" s="168"/>
+      <c r="M37" s="147">
         <f t="shared" si="8"/>
         <v>256942.19</v>
       </c>
-      <c r="N37" s="148">
+      <c r="N37" s="147">
         <f t="shared" si="7"/>
         <v>272359.19</v>
       </c>
@@ -7189,7 +7136,7 @@
         <v>0.19000000000000003</v>
       </c>
       <c r="P37" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
     </row>
     <row r="38" spans="1:113" x14ac:dyDescent="0.25">
@@ -7204,36 +7151,36 @@
         <v>222</v>
       </c>
       <c r="E38" s="135"/>
-      <c r="F38" s="137">
+      <c r="F38" s="136">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="G38" s="138">
+      <c r="G38" s="137">
         <v>112804.2</v>
       </c>
-      <c r="H38" s="286">
+      <c r="H38" s="215">
         <f>G38</f>
         <v>112804.2</v>
       </c>
-      <c r="I38" s="145">
+      <c r="I38" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J38" s="146">
+      <c r="J38" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K38" s="146">
+      <c r="K38" s="145">
         <f t="shared" si="6"/>
         <v>112803.883848</v>
       </c>
-      <c r="L38" s="169">
+      <c r="L38" s="168">
         <v>20000</v>
       </c>
-      <c r="M38" s="148">
+      <c r="M38" s="147">
         <f t="shared" si="8"/>
         <v>132804.20000000001</v>
       </c>
-      <c r="N38" s="148">
+      <c r="N38" s="147">
         <f t="shared" si="7"/>
         <v>140772.20000000001</v>
       </c>
@@ -7242,7 +7189,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:113" s="141" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="108" t="s">
         <v>120</v>
       </c>
@@ -7254,39 +7201,39 @@
         <v>187</v>
       </c>
       <c r="E39" s="135"/>
-      <c r="F39" s="137">
+      <c r="F39" s="136">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G39" s="138">
+      <c r="G39" s="137">
         <v>271043.21000000002</v>
       </c>
-      <c r="H39" s="286">
+      <c r="H39" s="215">
         <v>287306.21000000002</v>
       </c>
-      <c r="I39" s="145">
+      <c r="I39" s="144">
         <f t="shared" si="0"/>
         <v>-16263</v>
       </c>
-      <c r="J39" s="146">
+      <c r="J39" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K39" s="146">
+      <c r="K39" s="145">
         <f t="shared" si="6"/>
         <v>271042.66535699996</v>
       </c>
-      <c r="L39" s="169">
-        <v>0</v>
-      </c>
-      <c r="M39" s="148">
+      <c r="L39" s="168">
+        <v>0</v>
+      </c>
+      <c r="M39" s="147">
         <f t="shared" si="8"/>
         <v>254780.21</v>
       </c>
-      <c r="N39" s="148">
+      <c r="N39" s="147">
         <f t="shared" si="7"/>
         <v>270067.21000000002</v>
       </c>
-      <c r="O39" s="181">
+      <c r="O39" s="180">
         <f t="shared" si="9"/>
         <v>0.21000000000000005</v>
       </c>
@@ -7389,7 +7336,7 @@
       <c r="DH39" s="73"/>
       <c r="DI39" s="73"/>
     </row>
-    <row r="40" spans="1:113" s="141" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="108" t="s">
         <v>122</v>
       </c>
@@ -7401,40 +7348,40 @@
         <v>281</v>
       </c>
       <c r="E40" s="135"/>
-      <c r="F40" s="137">
+      <c r="F40" s="136">
         <v>9.4000000000000004E-3</v>
       </c>
       <c r="G40" s="44">
         <v>220907.22</v>
       </c>
-      <c r="H40" s="286"/>
-      <c r="I40" s="145">
+      <c r="H40" s="215"/>
+      <c r="I40" s="144">
         <f t="shared" si="0"/>
         <v>220907.22</v>
       </c>
-      <c r="J40" s="146">
+      <c r="J40" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K40" s="146">
+      <c r="K40" s="145">
         <f t="shared" si="6"/>
         <v>147271.737246</v>
       </c>
-      <c r="L40" s="169"/>
-      <c r="M40" s="148">
+      <c r="L40" s="168"/>
+      <c r="M40" s="147">
         <f t="shared" si="8"/>
         <v>368179.22</v>
       </c>
-      <c r="N40" s="148">
+      <c r="N40" s="147">
         <f t="shared" si="7"/>
         <v>390270.22</v>
       </c>
-      <c r="O40" s="181">
+      <c r="O40" s="180">
         <f t="shared" si="9"/>
         <v>0.22000000000000006</v>
       </c>
       <c r="P40" s="73" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="Q40" s="73"/>
       <c r="R40" s="73"/>
@@ -7534,7 +7481,7 @@
       <c r="DH40" s="73"/>
       <c r="DI40" s="73"/>
     </row>
-    <row r="41" spans="1:113" s="141" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="108" t="s">
         <v>122</v>
       </c>
@@ -7546,45 +7493,45 @@
         <v>183</v>
       </c>
       <c r="E41" s="135"/>
-      <c r="F41" s="137">
+      <c r="F41" s="136">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G41" s="138">
+      <c r="G41" s="137">
         <v>136305.23000000001</v>
       </c>
-      <c r="H41" s="286">
+      <c r="H41" s="215">
         <f>G41</f>
         <v>136305.23000000001</v>
       </c>
-      <c r="I41" s="145">
+      <c r="I41" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J41" s="146">
+      <c r="J41" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K41" s="146">
+      <c r="K41" s="145">
         <f t="shared" si="6"/>
         <v>136304.69298299999</v>
       </c>
-      <c r="L41" s="169">
-        <v>0</v>
-      </c>
-      <c r="M41" s="148">
+      <c r="L41" s="168">
+        <v>0</v>
+      </c>
+      <c r="M41" s="147">
         <f t="shared" si="8"/>
         <v>136305.23000000001</v>
       </c>
-      <c r="N41" s="148">
+      <c r="N41" s="147">
         <f t="shared" si="7"/>
         <v>144484.23000000001</v>
       </c>
-      <c r="O41" s="181">
+      <c r="O41" s="180">
         <f t="shared" si="9"/>
         <v>0.23000000000000007</v>
       </c>
       <c r="P41" s="73" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="Q41" s="73"/>
       <c r="R41" s="73"/>
@@ -7684,7 +7631,7 @@
       <c r="DH41" s="73"/>
       <c r="DI41" s="73"/>
     </row>
-    <row r="42" spans="1:113" s="141" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="108" t="s">
         <v>122</v>
       </c>
@@ -7696,37 +7643,37 @@
         <v>281</v>
       </c>
       <c r="E42" s="135"/>
-      <c r="F42" s="137">
+      <c r="F42" s="136">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G42" s="158">
+      <c r="G42" s="157">
         <v>148838.24</v>
       </c>
-      <c r="H42" s="286"/>
-      <c r="I42" s="145">
+      <c r="H42" s="215"/>
+      <c r="I42" s="144">
         <f t="shared" si="0"/>
         <v>148838.24</v>
       </c>
-      <c r="J42" s="146">
+      <c r="J42" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K42" s="146">
+      <c r="K42" s="145">
         <f t="shared" si="6"/>
         <v>148838.45785499999</v>
       </c>
-      <c r="L42" s="169">
-        <v>0</v>
-      </c>
-      <c r="M42" s="148">
+      <c r="L42" s="168">
+        <v>0</v>
+      </c>
+      <c r="M42" s="147">
         <f t="shared" si="8"/>
         <v>297677.24</v>
       </c>
-      <c r="N42" s="148">
+      <c r="N42" s="147">
         <f t="shared" si="7"/>
         <v>315538.24</v>
       </c>
-      <c r="O42" s="181">
+      <c r="O42" s="180">
         <f t="shared" si="9"/>
         <v>0.24000000000000007</v>
       </c>
@@ -7841,36 +7788,36 @@
         <v>188</v>
       </c>
       <c r="E43" s="135"/>
-      <c r="F43" s="137">
+      <c r="F43" s="136">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="G43" s="138">
+      <c r="G43" s="137">
         <v>256942.25</v>
       </c>
-      <c r="H43" s="286">
+      <c r="H43" s="215">
         <f t="shared" ref="H43" si="14">G43</f>
         <v>256942.25</v>
       </c>
-      <c r="I43" s="145">
+      <c r="I43" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J43" s="146">
+      <c r="J43" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K43" s="146">
+      <c r="K43" s="145">
         <f t="shared" si="6"/>
         <v>256942.17987600001</v>
       </c>
-      <c r="L43" s="169">
-        <v>0</v>
-      </c>
-      <c r="M43" s="148">
+      <c r="L43" s="168">
+        <v>0</v>
+      </c>
+      <c r="M43" s="147">
         <f t="shared" si="8"/>
         <v>256942.25</v>
       </c>
-      <c r="N43" s="148">
+      <c r="N43" s="147">
         <f t="shared" si="7"/>
         <v>272359.25</v>
       </c>
@@ -7893,36 +7840,36 @@
       <c r="E44" s="135" t="s">
         <v>272</v>
       </c>
-      <c r="F44" s="137">
+      <c r="F44" s="136">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="G44" s="138">
+      <c r="G44" s="137">
         <v>112804.26</v>
       </c>
-      <c r="H44" s="286">
+      <c r="H44" s="215">
         <f t="shared" ref="H44:H45" si="15">G44</f>
         <v>112804.26</v>
       </c>
-      <c r="I44" s="145">
+      <c r="I44" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J44" s="146">
+      <c r="J44" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K44" s="146">
+      <c r="K44" s="145">
         <f t="shared" si="6"/>
         <v>112803.883848</v>
       </c>
-      <c r="L44" s="169">
-        <v>0</v>
-      </c>
-      <c r="M44" s="148">
+      <c r="L44" s="168">
+        <v>0</v>
+      </c>
+      <c r="M44" s="147">
         <f t="shared" si="8"/>
         <v>112804.26</v>
       </c>
-      <c r="N44" s="148">
+      <c r="N44" s="147">
         <f t="shared" si="7"/>
         <v>119573.26</v>
       </c>
@@ -7943,36 +7890,36 @@
         <v>190</v>
       </c>
       <c r="E45" s="135"/>
-      <c r="F45" s="137">
+      <c r="F45" s="136">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G45" s="138">
+      <c r="G45" s="137">
         <v>271043.27</v>
       </c>
-      <c r="H45" s="286">
+      <c r="H45" s="215">
         <f t="shared" si="15"/>
         <v>271043.27</v>
       </c>
-      <c r="I45" s="145">
+      <c r="I45" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J45" s="146">
+      <c r="J45" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K45" s="146">
+      <c r="K45" s="145">
         <f t="shared" si="6"/>
         <v>271042.66535699996</v>
       </c>
-      <c r="L45" s="169">
-        <v>0</v>
-      </c>
-      <c r="M45" s="148">
+      <c r="L45" s="168">
+        <v>0</v>
+      </c>
+      <c r="M45" s="147">
         <f t="shared" si="8"/>
         <v>271043.27</v>
       </c>
-      <c r="N45" s="148">
+      <c r="N45" s="147">
         <f t="shared" si="7"/>
         <v>287306.27</v>
       </c>
@@ -7988,47 +7935,47 @@
       </c>
     </row>
     <row r="46" spans="1:113" x14ac:dyDescent="0.25">
-      <c r="A46" s="173" t="s">
+      <c r="A46" s="172" t="s">
         <v>122</v>
       </c>
-      <c r="B46" s="172"/>
+      <c r="B46" s="171"/>
       <c r="C46" s="35" t="s">
         <v>71</v>
       </c>
       <c r="D46" s="108" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="E46" s="135"/>
-      <c r="F46" s="137">
+      <c r="F46" s="136">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G46" s="138">
+      <c r="G46" s="137">
         <v>147272.28</v>
       </c>
-      <c r="H46" s="286">
+      <c r="H46" s="215">
         <f>G46</f>
         <v>147272.28</v>
       </c>
-      <c r="I46" s="145">
+      <c r="I46" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J46" s="146">
+      <c r="J46" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K46" s="146">
+      <c r="K46" s="145">
         <f t="shared" si="6"/>
         <v>147271.737246</v>
       </c>
-      <c r="L46" s="169">
-        <v>0</v>
-      </c>
-      <c r="M46" s="148">
+      <c r="L46" s="168">
+        <v>0</v>
+      </c>
+      <c r="M46" s="147">
         <f t="shared" si="8"/>
         <v>147272.28</v>
       </c>
-      <c r="N46" s="148">
+      <c r="N46" s="147">
         <f t="shared" si="7"/>
         <v>156109.28</v>
       </c>
@@ -8049,35 +7996,35 @@
         <v>181</v>
       </c>
       <c r="E47" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="F47" s="137">
+        <v>307</v>
+      </c>
+      <c r="F47" s="136">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G47" s="148">
+      <c r="G47" s="147">
         <v>136305.29</v>
       </c>
-      <c r="H47" s="286"/>
-      <c r="I47" s="145">
+      <c r="H47" s="215"/>
+      <c r="I47" s="144">
         <f t="shared" si="0"/>
         <v>136305.29</v>
       </c>
-      <c r="J47" s="146">
+      <c r="J47" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K47" s="146">
+      <c r="K47" s="145">
         <f t="shared" si="6"/>
         <v>136304.69298299999</v>
       </c>
-      <c r="L47" s="169">
-        <v>0</v>
-      </c>
-      <c r="M47" s="148">
+      <c r="L47" s="168">
+        <v>0</v>
+      </c>
+      <c r="M47" s="147">
         <f t="shared" si="8"/>
         <v>272610.28999999998</v>
       </c>
-      <c r="N47" s="148">
+      <c r="N47" s="147">
         <f t="shared" si="7"/>
         <v>288967.28999999998</v>
       </c>
@@ -8098,36 +8045,36 @@
         <v>191</v>
       </c>
       <c r="E48" s="135"/>
-      <c r="F48" s="137">
+      <c r="F48" s="136">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G48" s="138">
+      <c r="G48" s="137">
         <v>148838.29999999999</v>
       </c>
-      <c r="H48" s="286">
+      <c r="H48" s="215">
         <f>G48</f>
         <v>148838.29999999999</v>
       </c>
-      <c r="I48" s="145">
+      <c r="I48" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J48" s="146">
+      <c r="J48" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K48" s="146">
+      <c r="K48" s="145">
         <f t="shared" si="6"/>
         <v>148838.45785499999</v>
       </c>
-      <c r="L48" s="169">
-        <v>0</v>
-      </c>
-      <c r="M48" s="148">
+      <c r="L48" s="168">
+        <v>0</v>
+      </c>
+      <c r="M48" s="147">
         <f t="shared" si="8"/>
         <v>148838.29999999999</v>
       </c>
-      <c r="N48" s="148">
+      <c r="N48" s="147">
         <f t="shared" si="7"/>
         <v>157769.29999999999</v>
       </c>
@@ -8148,36 +8095,36 @@
         <v>192</v>
       </c>
       <c r="E49" s="135"/>
-      <c r="F49" s="137">
+      <c r="F49" s="136">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="G49" s="138">
+      <c r="G49" s="137">
         <v>256942.31</v>
       </c>
-      <c r="H49" s="286">
+      <c r="H49" s="215">
         <f t="shared" ref="H49:H50" si="16">G49</f>
         <v>256942.31</v>
       </c>
-      <c r="I49" s="145">
+      <c r="I49" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J49" s="146">
+      <c r="J49" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K49" s="146">
+      <c r="K49" s="145">
         <f t="shared" si="6"/>
         <v>256942.17987600001</v>
       </c>
-      <c r="L49" s="169">
-        <v>0</v>
-      </c>
-      <c r="M49" s="148">
+      <c r="L49" s="168">
+        <v>0</v>
+      </c>
+      <c r="M49" s="147">
         <f t="shared" si="8"/>
         <v>256942.31</v>
       </c>
-      <c r="N49" s="148">
+      <c r="N49" s="147">
         <f t="shared" si="7"/>
         <v>272359.31</v>
       </c>
@@ -8198,34 +8145,34 @@
         <v>193</v>
       </c>
       <c r="E50" s="135"/>
-      <c r="F50" s="137">
+      <c r="F50" s="136">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="G50" s="138">
+      <c r="G50" s="137">
         <v>127620.32</v>
       </c>
-      <c r="H50" s="286">
+      <c r="H50" s="215">
         <f t="shared" si="16"/>
         <v>127620.32</v>
       </c>
-      <c r="I50" s="145">
+      <c r="I50" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J50" s="146">
+      <c r="J50" s="145">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K50" s="146">
+      <c r="K50" s="145">
         <f t="shared" si="6"/>
         <v>112803.883848</v>
       </c>
-      <c r="L50" s="169"/>
-      <c r="M50" s="148">
+      <c r="L50" s="168"/>
+      <c r="M50" s="147">
         <f t="shared" si="8"/>
         <v>112804.32</v>
       </c>
-      <c r="N50" s="148">
+      <c r="N50" s="147">
         <f t="shared" si="7"/>
         <v>119573.32</v>
       </c>
@@ -8247,36 +8194,36 @@
         <v>194</v>
       </c>
       <c r="E51" s="135"/>
-      <c r="F51" s="137">
+      <c r="F51" s="136">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G51" s="138">
+      <c r="G51" s="137">
         <v>271043.33</v>
       </c>
-      <c r="H51" s="286">
+      <c r="H51" s="215">
         <f>G51</f>
         <v>271043.33</v>
       </c>
-      <c r="I51" s="145">
+      <c r="I51" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J51" s="146">
+      <c r="J51" s="145">
         <f t="shared" ref="J51:J82" si="17">M$8*F51</f>
         <v>0</v>
       </c>
-      <c r="K51" s="146">
+      <c r="K51" s="145">
         <f t="shared" ref="K51:K82" si="18">M$2*F51</f>
         <v>271042.66535699996</v>
       </c>
-      <c r="L51" s="169">
-        <v>0</v>
-      </c>
-      <c r="M51" s="148">
+      <c r="L51" s="168">
+        <v>0</v>
+      </c>
+      <c r="M51" s="147">
         <f t="shared" si="8"/>
         <v>271043.33</v>
       </c>
-      <c r="N51" s="148">
+      <c r="N51" s="147">
         <f t="shared" si="7"/>
         <v>287306.33</v>
       </c>
@@ -8295,37 +8242,37 @@
         <v>77</v>
       </c>
       <c r="D52" s="108" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="E52" s="135"/>
-      <c r="F52" s="137">
+      <c r="F52" s="136">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G52" s="138">
+      <c r="G52" s="137">
         <v>147272.34</v>
       </c>
-      <c r="H52" s="286">
+      <c r="H52" s="215">
         <f>G52</f>
         <v>147272.34</v>
       </c>
-      <c r="I52" s="145">
+      <c r="I52" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J52" s="146">
+      <c r="J52" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K52" s="146">
+      <c r="K52" s="145">
         <f t="shared" si="18"/>
         <v>147271.737246</v>
       </c>
-      <c r="L52" s="169"/>
-      <c r="M52" s="148">
+      <c r="L52" s="168"/>
+      <c r="M52" s="147">
         <f t="shared" si="8"/>
         <v>147272.34</v>
       </c>
-      <c r="N52" s="148">
+      <c r="N52" s="147">
         <f t="shared" si="7"/>
         <v>156109.34</v>
       </c>
@@ -8334,7 +8281,7 @@
         <v>0.34000000000000014</v>
       </c>
       <c r="P52" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -8349,36 +8296,36 @@
         <v>223</v>
       </c>
       <c r="E53" s="135"/>
-      <c r="F53" s="137">
+      <c r="F53" s="136">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G53" s="138">
+      <c r="G53" s="137">
         <v>136305.35</v>
       </c>
-      <c r="H53" s="286">
-        <f t="shared" ref="H49:H53" si="19">G53</f>
+      <c r="H53" s="215">
+        <f t="shared" ref="H53" si="19">G53</f>
         <v>136305.35</v>
       </c>
-      <c r="I53" s="145">
+      <c r="I53" s="144">
         <f>G53-H53</f>
         <v>0</v>
       </c>
-      <c r="J53" s="146">
+      <c r="J53" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K53" s="146">
+      <c r="K53" s="145">
         <f t="shared" si="18"/>
         <v>136304.69298299999</v>
       </c>
-      <c r="L53" s="169">
-        <v>0</v>
-      </c>
-      <c r="M53" s="148">
+      <c r="L53" s="168">
+        <v>0</v>
+      </c>
+      <c r="M53" s="147">
         <f t="shared" si="8"/>
         <v>136305.35</v>
       </c>
-      <c r="N53" s="148">
+      <c r="N53" s="147">
         <f t="shared" si="7"/>
         <v>144484.35</v>
       </c>
@@ -8399,36 +8346,36 @@
         <v>195</v>
       </c>
       <c r="E54" s="135"/>
-      <c r="F54" s="137">
+      <c r="F54" s="136">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G54" s="138">
+      <c r="G54" s="137">
         <v>122573.36</v>
       </c>
-      <c r="H54" s="286">
+      <c r="H54" s="215">
         <f>G54</f>
         <v>122573.36</v>
       </c>
-      <c r="I54" s="145">
+      <c r="I54" s="144">
         <f>G54-H54</f>
         <v>0</v>
       </c>
-      <c r="J54" s="146">
+      <c r="J54" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K54" s="146">
+      <c r="K54" s="145">
         <f t="shared" si="18"/>
         <v>148838.45785499999</v>
       </c>
-      <c r="L54" s="169">
-        <v>0</v>
-      </c>
-      <c r="M54" s="148">
+      <c r="L54" s="168">
+        <v>0</v>
+      </c>
+      <c r="M54" s="147">
         <f t="shared" si="8"/>
         <v>148838.35999999999</v>
       </c>
-      <c r="N54" s="148">
+      <c r="N54" s="147">
         <f t="shared" si="7"/>
         <v>157769.35999999999</v>
       </c>
@@ -8449,36 +8396,36 @@
         <v>192</v>
       </c>
       <c r="E55" s="135"/>
-      <c r="F55" s="137">
+      <c r="F55" s="136">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="G55" s="138">
+      <c r="G55" s="137">
         <v>256942.37</v>
       </c>
-      <c r="H55" s="286">
+      <c r="H55" s="215">
         <f t="shared" ref="H55:H56" si="20">G55</f>
         <v>256942.37</v>
       </c>
-      <c r="I55" s="145">
+      <c r="I55" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J55" s="146">
+      <c r="J55" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K55" s="146">
+      <c r="K55" s="145">
         <f t="shared" si="18"/>
         <v>256942.17987600001</v>
       </c>
-      <c r="L55" s="169">
-        <v>0</v>
-      </c>
-      <c r="M55" s="148">
+      <c r="L55" s="168">
+        <v>0</v>
+      </c>
+      <c r="M55" s="147">
         <f t="shared" si="8"/>
         <v>256942.37</v>
       </c>
-      <c r="N55" s="148">
+      <c r="N55" s="147">
         <f t="shared" si="7"/>
         <v>272359.37</v>
       </c>
@@ -8502,36 +8449,36 @@
       <c r="E56" s="135" t="s">
         <v>273</v>
       </c>
-      <c r="F56" s="137">
+      <c r="F56" s="136">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="G56" s="138">
+      <c r="G56" s="137">
         <v>112804.38</v>
       </c>
-      <c r="H56" s="286">
+      <c r="H56" s="215">
         <f t="shared" si="20"/>
         <v>112804.38</v>
       </c>
-      <c r="I56" s="145">
+      <c r="I56" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J56" s="146">
+      <c r="J56" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K56" s="146">
+      <c r="K56" s="145">
         <f t="shared" si="18"/>
         <v>112803.883848</v>
       </c>
-      <c r="L56" s="169">
-        <v>0</v>
-      </c>
-      <c r="M56" s="148">
+      <c r="L56" s="168">
+        <v>0</v>
+      </c>
+      <c r="M56" s="147">
         <f t="shared" si="8"/>
         <v>112804.38</v>
       </c>
-      <c r="N56" s="148">
+      <c r="N56" s="147">
         <f t="shared" si="7"/>
         <v>119573.38</v>
       </c>
@@ -8545,42 +8492,42 @@
         <v>120</v>
       </c>
       <c r="B57" s="6"/>
-      <c r="C57" s="276" t="s">
+      <c r="C57" s="205" t="s">
         <v>82</v>
       </c>
-      <c r="D57" s="277" t="s">
+      <c r="D57" s="206" t="s">
         <v>197</v>
       </c>
-      <c r="E57" s="278"/>
-      <c r="F57" s="279">
+      <c r="E57" s="207"/>
+      <c r="F57" s="208">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G57" s="280">
+      <c r="G57" s="209">
         <v>271043.39</v>
       </c>
-      <c r="H57" s="289">
+      <c r="H57" s="218">
         <v>271043</v>
       </c>
-      <c r="I57" s="281">
+      <c r="I57" s="210">
         <f t="shared" si="0"/>
         <v>0.39000000001396984</v>
       </c>
-      <c r="J57" s="282">
+      <c r="J57" s="211">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K57" s="282">
+      <c r="K57" s="211">
         <f t="shared" si="18"/>
         <v>271042.66535699996</v>
       </c>
-      <c r="L57" s="283">
-        <v>0</v>
-      </c>
-      <c r="M57" s="284">
+      <c r="L57" s="212">
+        <v>0</v>
+      </c>
+      <c r="M57" s="213">
         <f t="shared" si="8"/>
         <v>271043.39</v>
       </c>
-      <c r="N57" s="284">
+      <c r="N57" s="213">
         <f t="shared" si="7"/>
         <v>287306.39</v>
       </c>
@@ -8601,39 +8548,39 @@
         <v>198</v>
       </c>
       <c r="E58" s="135" t="s">
-        <v>368</v>
-      </c>
-      <c r="F58" s="137">
+        <v>355</v>
+      </c>
+      <c r="F58" s="136">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G58" s="138">
+      <c r="G58" s="137">
         <v>147272.4</v>
       </c>
-      <c r="H58" s="286">
-        <f t="shared" ref="H55:H58" si="21">G58</f>
+      <c r="H58" s="215">
+        <f t="shared" ref="H58" si="21">G58</f>
         <v>147272.4</v>
       </c>
-      <c r="I58" s="145">
+      <c r="I58" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J58" s="146">
+      <c r="J58" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K58" s="146">
+      <c r="K58" s="145">
         <f t="shared" si="18"/>
         <v>147271.737246</v>
       </c>
-      <c r="L58" s="302">
+      <c r="L58" s="231">
         <f>13000*2</f>
         <v>26000</v>
       </c>
-      <c r="M58" s="148">
+      <c r="M58" s="147">
         <f t="shared" si="8"/>
         <v>173272.4</v>
       </c>
-      <c r="N58" s="148">
+      <c r="N58" s="147">
         <f t="shared" si="7"/>
         <v>183669.4</v>
       </c>
@@ -8647,43 +8594,43 @@
         <v>122</v>
       </c>
       <c r="B59" s="35"/>
-      <c r="C59" s="172" t="s">
+      <c r="C59" s="171" t="s">
         <v>84</v>
       </c>
-      <c r="D59" s="173" t="s">
+      <c r="D59" s="172" t="s">
         <v>119</v>
       </c>
-      <c r="E59" s="174"/>
-      <c r="F59" s="175">
+      <c r="E59" s="173"/>
+      <c r="F59" s="174">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G59" s="176">
+      <c r="G59" s="175">
         <v>136305.41</v>
       </c>
-      <c r="H59" s="290">
+      <c r="H59" s="219">
         <f>G59</f>
         <v>136305.41</v>
       </c>
-      <c r="I59" s="177">
+      <c r="I59" s="176">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J59" s="178">
+      <c r="J59" s="177">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K59" s="178">
+      <c r="K59" s="177">
         <f t="shared" si="18"/>
         <v>136304.69298299999</v>
       </c>
-      <c r="L59" s="179">
-        <v>0</v>
-      </c>
-      <c r="M59" s="180">
+      <c r="L59" s="178">
+        <v>0</v>
+      </c>
+      <c r="M59" s="179">
         <f t="shared" si="8"/>
         <v>136305.41</v>
       </c>
-      <c r="N59" s="180">
+      <c r="N59" s="179">
         <f t="shared" si="7"/>
         <v>144484.41</v>
       </c>
@@ -8707,34 +8654,34 @@
         <v>199</v>
       </c>
       <c r="E60" s="135"/>
-      <c r="F60" s="137">
+      <c r="F60" s="136">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G60" s="138">
+      <c r="G60" s="137">
         <v>148838.42000000001</v>
       </c>
-      <c r="H60" s="286">
+      <c r="H60" s="215">
         <f t="shared" ref="H60" si="22">G60</f>
         <v>148838.42000000001</v>
       </c>
-      <c r="I60" s="145">
+      <c r="I60" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J60" s="146">
+      <c r="J60" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K60" s="146">
+      <c r="K60" s="145">
         <f t="shared" si="18"/>
         <v>148838.45785499999</v>
       </c>
-      <c r="L60" s="169"/>
-      <c r="M60" s="148">
+      <c r="L60" s="168"/>
+      <c r="M60" s="147">
         <f t="shared" si="8"/>
         <v>148838.42000000001</v>
       </c>
-      <c r="N60" s="148">
+      <c r="N60" s="147">
         <f t="shared" si="7"/>
         <v>157769.42000000001</v>
       </c>
@@ -8743,7 +8690,7 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="P60" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -8758,36 +8705,36 @@
         <v>200</v>
       </c>
       <c r="E61" s="135"/>
-      <c r="F61" s="137">
+      <c r="F61" s="136">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="G61" s="138">
+      <c r="G61" s="137">
         <v>256942.43</v>
       </c>
-      <c r="H61" s="286">
-        <f t="shared" ref="H61:H67" si="23">G61</f>
+      <c r="H61" s="215">
+        <f t="shared" ref="H61:H65" si="23">G61</f>
         <v>256942.43</v>
       </c>
-      <c r="I61" s="145">
+      <c r="I61" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J61" s="146">
+      <c r="J61" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K61" s="146">
+      <c r="K61" s="145">
         <f t="shared" si="18"/>
         <v>256942.17987600001</v>
       </c>
-      <c r="L61" s="169">
-        <v>0</v>
-      </c>
-      <c r="M61" s="148">
+      <c r="L61" s="168">
+        <v>0</v>
+      </c>
+      <c r="M61" s="147">
         <f t="shared" si="8"/>
         <v>256942.43</v>
       </c>
-      <c r="N61" s="148">
+      <c r="N61" s="147">
         <f t="shared" si="7"/>
         <v>272359.43</v>
       </c>
@@ -8808,36 +8755,36 @@
         <v>200</v>
       </c>
       <c r="E62" s="135"/>
-      <c r="F62" s="137">
+      <c r="F62" s="136">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="G62" s="138">
+      <c r="G62" s="137">
         <v>112804.44</v>
       </c>
-      <c r="H62" s="286">
+      <c r="H62" s="215">
         <f t="shared" si="23"/>
         <v>112804.44</v>
       </c>
-      <c r="I62" s="145">
+      <c r="I62" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J62" s="146">
+      <c r="J62" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K62" s="146">
+      <c r="K62" s="145">
         <f t="shared" si="18"/>
         <v>112803.883848</v>
       </c>
-      <c r="L62" s="169">
-        <v>0</v>
-      </c>
-      <c r="M62" s="148">
+      <c r="L62" s="168">
+        <v>0</v>
+      </c>
+      <c r="M62" s="147">
         <f t="shared" si="8"/>
         <v>112804.44</v>
       </c>
-      <c r="N62" s="148">
+      <c r="N62" s="147">
         <f t="shared" si="7"/>
         <v>119573.44</v>
       </c>
@@ -8858,36 +8805,36 @@
         <v>201</v>
       </c>
       <c r="E63" s="135"/>
-      <c r="F63" s="137">
+      <c r="F63" s="136">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G63" s="138">
+      <c r="G63" s="137">
         <v>271043.45</v>
       </c>
-      <c r="H63" s="286">
+      <c r="H63" s="215">
         <f>G63</f>
         <v>271043.45</v>
       </c>
-      <c r="I63" s="145">
+      <c r="I63" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J63" s="146">
+      <c r="J63" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K63" s="146">
+      <c r="K63" s="145">
         <f t="shared" si="18"/>
         <v>271042.66535699996</v>
       </c>
-      <c r="L63" s="169">
-        <v>0</v>
-      </c>
-      <c r="M63" s="148">
+      <c r="L63" s="168">
+        <v>0</v>
+      </c>
+      <c r="M63" s="147">
         <f t="shared" si="8"/>
         <v>271043.45</v>
       </c>
-      <c r="N63" s="148">
+      <c r="N63" s="147">
         <f t="shared" si="7"/>
         <v>287306.45</v>
       </c>
@@ -8910,39 +8857,39 @@
       <c r="E64" s="135" t="s">
         <v>274</v>
       </c>
-      <c r="F64" s="137">
+      <c r="F64" s="136">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G64" s="138">
+      <c r="G64" s="137">
         <v>283572.46000000002</v>
       </c>
-      <c r="H64" s="286">
+      <c r="H64" s="215">
         <v>147272.46</v>
       </c>
-      <c r="I64" s="145">
+      <c r="I64" s="144">
         <f t="shared" si="0"/>
         <v>136300.00000000003</v>
       </c>
-      <c r="J64" s="146">
+      <c r="J64" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K64" s="146">
+      <c r="K64" s="145">
         <f t="shared" si="18"/>
         <v>147271.737246</v>
       </c>
-      <c r="L64" s="302">
+      <c r="L64" s="231">
         <v>13000</v>
       </c>
-      <c r="M64" s="148">
+      <c r="M64" s="147">
         <f t="shared" si="8"/>
         <v>296572.46000000002</v>
       </c>
-      <c r="N64" s="148">
+      <c r="N64" s="147">
         <f t="shared" si="7"/>
         <v>314367.46000000002</v>
       </c>
-      <c r="O64" s="181">
+      <c r="O64" s="180">
         <f t="shared" si="9"/>
         <v>0.46000000000000024</v>
       </c>
@@ -8959,40 +8906,40 @@
         <v>181</v>
       </c>
       <c r="E65" s="135"/>
-      <c r="F65" s="137">
+      <c r="F65" s="136">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G65" s="138">
+      <c r="G65" s="137">
         <v>144484.47</v>
       </c>
-      <c r="H65" s="286">
+      <c r="H65" s="215">
         <f t="shared" si="23"/>
         <v>144484.47</v>
       </c>
-      <c r="I65" s="145">
+      <c r="I65" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J65" s="146">
+      <c r="J65" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K65" s="146">
+      <c r="K65" s="145">
         <f t="shared" si="18"/>
         <v>136304.69298299999</v>
       </c>
-      <c r="L65" s="169">
-        <v>0</v>
-      </c>
-      <c r="M65" s="148">
+      <c r="L65" s="168">
+        <v>0</v>
+      </c>
+      <c r="M65" s="147">
         <f t="shared" si="8"/>
         <v>136305.47</v>
       </c>
-      <c r="N65" s="148">
+      <c r="N65" s="147">
         <f t="shared" si="7"/>
         <v>144484.47</v>
       </c>
-      <c r="O65" s="181">
+      <c r="O65" s="180">
         <f t="shared" si="9"/>
         <v>0.47000000000000025</v>
       </c>
@@ -9009,43 +8956,43 @@
         <v>203</v>
       </c>
       <c r="E66" s="135"/>
-      <c r="F66" s="137">
+      <c r="F66" s="136">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G66" s="138">
+      <c r="G66" s="137">
         <v>167838.48</v>
       </c>
-      <c r="H66" s="286">
+      <c r="H66" s="215">
         <v>148838.48000000001</v>
       </c>
-      <c r="I66" s="145">
+      <c r="I66" s="144">
         <f t="shared" si="0"/>
         <v>19000</v>
       </c>
-      <c r="J66" s="146">
+      <c r="J66" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K66" s="146">
+      <c r="K66" s="145">
         <f t="shared" si="18"/>
         <v>148838.45785499999</v>
       </c>
-      <c r="L66" s="169">
-        <v>0</v>
-      </c>
-      <c r="M66" s="148">
+      <c r="L66" s="168">
+        <v>0</v>
+      </c>
+      <c r="M66" s="147">
         <f t="shared" si="8"/>
         <v>167838.48</v>
       </c>
-      <c r="N66" s="148">
+      <c r="N66" s="147">
         <f t="shared" si="7"/>
         <v>177909.48</v>
       </c>
-      <c r="O66" s="181">
+      <c r="O66" s="180">
         <f t="shared" si="9"/>
         <v>0.48000000000000026</v>
       </c>
-      <c r="R66" s="199"/>
+      <c r="R66" s="190"/>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="57" t="s">
@@ -9059,34 +9006,34 @@
         <v>204</v>
       </c>
       <c r="E67" s="135"/>
-      <c r="F67" s="137">
+      <c r="F67" s="136">
         <v>1.6400000000000001E-2</v>
       </c>
-      <c r="G67" s="138">
+      <c r="G67" s="137">
         <v>268942.49</v>
       </c>
-      <c r="H67" s="286">
+      <c r="H67" s="215">
         <f t="shared" ref="H67" si="24">G67</f>
         <v>268942.49</v>
       </c>
-      <c r="I67" s="145">
+      <c r="I67" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J67" s="146">
+      <c r="J67" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K67" s="146">
+      <c r="K67" s="145">
         <f t="shared" si="18"/>
         <v>256942.17987600001</v>
       </c>
-      <c r="L67" s="169"/>
-      <c r="M67" s="148">
+      <c r="L67" s="168"/>
+      <c r="M67" s="147">
         <f t="shared" si="8"/>
         <v>256942.49</v>
       </c>
-      <c r="N67" s="148">
+      <c r="N67" s="147">
         <f t="shared" si="7"/>
         <v>272359.49</v>
       </c>
@@ -9097,10 +9044,10 @@
       <c r="R67" s="43"/>
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A68" s="140" t="s">
+      <c r="A68" s="139" t="s">
         <v>121</v>
       </c>
-      <c r="B68" s="139"/>
+      <c r="B68" s="138"/>
       <c r="C68" s="35" t="s">
         <v>93</v>
       </c>
@@ -9108,33 +9055,33 @@
         <v>205</v>
       </c>
       <c r="E68" s="135"/>
-      <c r="F68" s="137">
+      <c r="F68" s="136">
         <v>7.1999999999999998E-3</v>
       </c>
-      <c r="G68" s="138">
+      <c r="G68" s="137">
         <v>556636.5</v>
       </c>
-      <c r="H68" s="286"/>
-      <c r="I68" s="145">
+      <c r="H68" s="215"/>
+      <c r="I68" s="144">
         <f t="shared" si="0"/>
         <v>556636.5</v>
       </c>
-      <c r="J68" s="146">
+      <c r="J68" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K68" s="146">
+      <c r="K68" s="145">
         <f t="shared" si="18"/>
         <v>112803.883848</v>
       </c>
-      <c r="L68" s="169">
-        <v>0</v>
-      </c>
-      <c r="M68" s="148">
+      <c r="L68" s="168">
+        <v>0</v>
+      </c>
+      <c r="M68" s="147">
         <f t="shared" si="8"/>
         <v>669440.5</v>
       </c>
-      <c r="N68" s="148">
+      <c r="N68" s="147">
         <f t="shared" si="7"/>
         <v>709607.5</v>
       </c>
@@ -9155,36 +9102,36 @@
         <v>206</v>
       </c>
       <c r="E69" s="135"/>
-      <c r="F69" s="137">
+      <c r="F69" s="136">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G69" s="138">
+      <c r="G69" s="137">
         <v>271043.51</v>
       </c>
-      <c r="H69" s="286">
+      <c r="H69" s="215">
         <f t="shared" ref="H69" si="25">G69</f>
         <v>271043.51</v>
       </c>
-      <c r="I69" s="145">
+      <c r="I69" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J69" s="146">
+      <c r="J69" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K69" s="146">
+      <c r="K69" s="145">
         <f t="shared" si="18"/>
         <v>271042.66535699996</v>
       </c>
-      <c r="L69" s="169">
-        <v>0</v>
-      </c>
-      <c r="M69" s="148">
+      <c r="L69" s="168">
+        <v>0</v>
+      </c>
+      <c r="M69" s="147">
         <f t="shared" si="8"/>
         <v>271043.51</v>
       </c>
-      <c r="N69" s="148">
+      <c r="N69" s="147">
         <f t="shared" si="7"/>
         <v>287306.51</v>
       </c>
@@ -9205,36 +9152,36 @@
         <v>207</v>
       </c>
       <c r="E70" s="135"/>
-      <c r="F70" s="137">
+      <c r="F70" s="136">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G70" s="138">
+      <c r="G70" s="137">
         <v>419357.52</v>
       </c>
-      <c r="H70" s="286">
+      <c r="H70" s="215">
         <f>G70</f>
         <v>419357.52</v>
       </c>
-      <c r="I70" s="145">
+      <c r="I70" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J70" s="146">
+      <c r="J70" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K70" s="146">
+      <c r="K70" s="145">
         <f t="shared" si="18"/>
         <v>147271.737246</v>
       </c>
-      <c r="L70" s="169">
-        <v>0</v>
-      </c>
-      <c r="M70" s="148">
+      <c r="L70" s="168">
+        <v>0</v>
+      </c>
+      <c r="M70" s="147">
         <f t="shared" si="8"/>
         <v>147272.51999999999</v>
       </c>
-      <c r="N70" s="148">
+      <c r="N70" s="147">
         <f t="shared" si="7"/>
         <v>156109.51999999999</v>
       </c>
@@ -9255,36 +9202,36 @@
         <v>119</v>
       </c>
       <c r="E71" s="135"/>
-      <c r="F71" s="137">
+      <c r="F71" s="136">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G71" s="138">
+      <c r="G71" s="137">
         <v>136305.53</v>
       </c>
-      <c r="H71" s="286">
+      <c r="H71" s="215">
         <f t="shared" ref="H71:H73" si="26">G71</f>
         <v>136305.53</v>
       </c>
-      <c r="I71" s="145">
+      <c r="I71" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J71" s="146">
+      <c r="J71" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K71" s="146">
+      <c r="K71" s="145">
         <f t="shared" si="18"/>
         <v>136304.69298299999</v>
       </c>
-      <c r="L71" s="169">
+      <c r="L71" s="168">
         <v>20000</v>
       </c>
-      <c r="M71" s="148">
+      <c r="M71" s="147">
         <f t="shared" si="8"/>
         <v>156305.53</v>
       </c>
-      <c r="N71" s="148">
+      <c r="N71" s="147">
         <f t="shared" si="7"/>
         <v>165684.53</v>
       </c>
@@ -9308,36 +9255,36 @@
         <v>208</v>
       </c>
       <c r="E72" s="135"/>
-      <c r="F72" s="137">
+      <c r="F72" s="136">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G72" s="138">
+      <c r="G72" s="137">
         <v>148838.54</v>
       </c>
-      <c r="H72" s="286">
+      <c r="H72" s="215">
         <f t="shared" si="26"/>
         <v>148838.54</v>
       </c>
-      <c r="I72" s="145">
+      <c r="I72" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J72" s="146">
+      <c r="J72" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K72" s="146">
+      <c r="K72" s="145">
         <f t="shared" si="18"/>
         <v>148838.45785499999</v>
       </c>
-      <c r="L72" s="169">
-        <v>0</v>
-      </c>
-      <c r="M72" s="148">
+      <c r="L72" s="168">
+        <v>0</v>
+      </c>
+      <c r="M72" s="147">
         <f t="shared" si="8"/>
         <v>148838.54</v>
       </c>
-      <c r="N72" s="148">
+      <c r="N72" s="147">
         <f t="shared" si="7"/>
         <v>157769.54</v>
       </c>
@@ -9358,34 +9305,34 @@
         <v>209</v>
       </c>
       <c r="E73" s="135"/>
-      <c r="F73" s="137">
+      <c r="F73" s="136">
         <v>2.35E-2</v>
       </c>
-      <c r="G73" s="138">
+      <c r="G73" s="137">
         <v>388179.55</v>
       </c>
-      <c r="H73" s="286">
+      <c r="H73" s="215">
         <f t="shared" si="26"/>
         <v>388179.55</v>
       </c>
-      <c r="I73" s="145">
+      <c r="I73" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J73" s="146">
+      <c r="J73" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K73" s="146">
+      <c r="K73" s="145">
         <f t="shared" si="18"/>
         <v>368179.343115</v>
       </c>
-      <c r="L73" s="169"/>
-      <c r="M73" s="148">
+      <c r="L73" s="168"/>
+      <c r="M73" s="147">
         <f t="shared" si="8"/>
         <v>368179.55</v>
       </c>
-      <c r="N73" s="148">
+      <c r="N73" s="147">
         <f t="shared" si="7"/>
         <v>390270.55</v>
       </c>
@@ -9407,36 +9354,36 @@
         <v>210</v>
       </c>
       <c r="E74" s="135"/>
-      <c r="F74" s="137">
+      <c r="F74" s="136">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G74" s="138">
+      <c r="G74" s="137">
         <v>271043.56</v>
       </c>
-      <c r="H74" s="286">
+      <c r="H74" s="215">
         <f>G74</f>
         <v>271043.56</v>
       </c>
-      <c r="I74" s="145">
+      <c r="I74" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J74" s="146">
+      <c r="J74" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K74" s="146">
+      <c r="K74" s="145">
         <f t="shared" si="18"/>
         <v>271042.66535699996</v>
       </c>
-      <c r="L74" s="169">
-        <v>0</v>
-      </c>
-      <c r="M74" s="148">
+      <c r="L74" s="168">
+        <v>0</v>
+      </c>
+      <c r="M74" s="147">
         <f t="shared" si="8"/>
         <v>271043.56</v>
       </c>
-      <c r="N74" s="148">
+      <c r="N74" s="147">
         <f t="shared" si="7"/>
         <v>287306.56</v>
       </c>
@@ -9457,36 +9404,36 @@
         <v>256</v>
       </c>
       <c r="E75" s="135"/>
-      <c r="F75" s="137">
+      <c r="F75" s="136">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G75" s="138">
+      <c r="G75" s="137">
         <v>147272.57</v>
       </c>
-      <c r="H75" s="286">
+      <c r="H75" s="215">
         <f>G75</f>
         <v>147272.57</v>
       </c>
-      <c r="I75" s="145">
+      <c r="I75" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J75" s="146">
+      <c r="J75" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K75" s="146">
+      <c r="K75" s="145">
         <f t="shared" si="18"/>
         <v>147271.737246</v>
       </c>
-      <c r="L75" s="169">
-        <v>0</v>
-      </c>
-      <c r="M75" s="148">
+      <c r="L75" s="168">
+        <v>0</v>
+      </c>
+      <c r="M75" s="147">
         <f t="shared" si="8"/>
         <v>147272.57</v>
       </c>
-      <c r="N75" s="148">
+      <c r="N75" s="147">
         <f t="shared" si="7"/>
         <v>156109.57</v>
       </c>
@@ -9507,35 +9454,35 @@
         <v>211</v>
       </c>
       <c r="E76" s="135" t="s">
-        <v>300</v>
-      </c>
-      <c r="F76" s="137">
+        <v>290</v>
+      </c>
+      <c r="F76" s="136">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G76" s="138">
+      <c r="G76" s="137">
         <v>136305.57999999999</v>
       </c>
-      <c r="H76" s="286"/>
-      <c r="I76" s="145">
+      <c r="H76" s="215"/>
+      <c r="I76" s="144">
         <f t="shared" si="0"/>
         <v>136305.57999999999</v>
       </c>
-      <c r="J76" s="146">
+      <c r="J76" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K76" s="146">
+      <c r="K76" s="145">
         <f t="shared" si="18"/>
         <v>136304.69298299999</v>
       </c>
-      <c r="L76" s="169">
-        <v>0</v>
-      </c>
-      <c r="M76" s="148">
+      <c r="L76" s="168">
+        <v>0</v>
+      </c>
+      <c r="M76" s="147">
         <f t="shared" si="8"/>
         <v>272610.58</v>
       </c>
-      <c r="N76" s="148">
+      <c r="N76" s="147">
         <f t="shared" si="7"/>
         <v>288967.58</v>
       </c>
@@ -9556,36 +9503,36 @@
         <v>212</v>
       </c>
       <c r="E77" s="135"/>
-      <c r="F77" s="137">
+      <c r="F77" s="136">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G77" s="138">
+      <c r="G77" s="137">
         <v>149007.59</v>
       </c>
-      <c r="H77" s="286">
+      <c r="H77" s="215">
         <f>G77</f>
         <v>149007.59</v>
       </c>
-      <c r="I77" s="145">
+      <c r="I77" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J77" s="146">
+      <c r="J77" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K77" s="146">
+      <c r="K77" s="145">
         <f t="shared" si="18"/>
         <v>148838.45785499999</v>
       </c>
-      <c r="L77" s="169">
-        <v>0</v>
-      </c>
-      <c r="M77" s="148">
+      <c r="L77" s="168">
+        <v>0</v>
+      </c>
+      <c r="M77" s="147">
         <f t="shared" si="8"/>
         <v>148838.59</v>
       </c>
-      <c r="N77" s="148">
+      <c r="N77" s="147">
         <f t="shared" si="7"/>
         <v>157769.59</v>
       </c>
@@ -9606,36 +9553,36 @@
         <v>213</v>
       </c>
       <c r="E78" s="135"/>
-      <c r="F78" s="137">
+      <c r="F78" s="136">
         <v>2.35E-2</v>
       </c>
-      <c r="G78" s="138">
+      <c r="G78" s="137">
         <v>368179.6</v>
       </c>
-      <c r="H78" s="286">
+      <c r="H78" s="215">
         <f>G78</f>
         <v>368179.6</v>
       </c>
-      <c r="I78" s="145">
+      <c r="I78" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J78" s="146">
+      <c r="J78" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K78" s="146">
+      <c r="K78" s="145">
         <f t="shared" si="18"/>
         <v>368179.343115</v>
       </c>
-      <c r="L78" s="169">
-        <v>0</v>
-      </c>
-      <c r="M78" s="148">
+      <c r="L78" s="168">
+        <v>0</v>
+      </c>
+      <c r="M78" s="147">
         <f t="shared" si="8"/>
         <v>368179.6</v>
       </c>
-      <c r="N78" s="148">
+      <c r="N78" s="147">
         <f t="shared" si="7"/>
         <v>390270.6</v>
       </c>
@@ -9656,36 +9603,36 @@
         <v>214</v>
       </c>
       <c r="E79" s="135"/>
-      <c r="F79" s="137">
+      <c r="F79" s="136">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G79" s="138">
+      <c r="G79" s="137">
         <v>271043.61</v>
       </c>
-      <c r="H79" s="286">
+      <c r="H79" s="215">
         <f t="shared" ref="H79" si="27">G79</f>
         <v>271043.61</v>
       </c>
-      <c r="I79" s="145">
+      <c r="I79" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J79" s="146">
+      <c r="J79" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K79" s="146">
+      <c r="K79" s="145">
         <f t="shared" si="18"/>
         <v>271042.66535699996</v>
       </c>
-      <c r="L79" s="169">
-        <v>0</v>
-      </c>
-      <c r="M79" s="148">
+      <c r="L79" s="168">
+        <v>0</v>
+      </c>
+      <c r="M79" s="147">
         <f t="shared" si="8"/>
         <v>271043.61</v>
       </c>
-      <c r="N79" s="148">
+      <c r="N79" s="147">
         <f t="shared" si="7"/>
         <v>287306.61</v>
       </c>
@@ -9706,33 +9653,33 @@
         <v>215</v>
       </c>
       <c r="E80" s="135"/>
-      <c r="F80" s="137">
+      <c r="F80" s="136">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G80" s="138">
+      <c r="G80" s="137">
         <v>408372.62</v>
       </c>
-      <c r="H80" s="286"/>
-      <c r="I80" s="145">
+      <c r="H80" s="215"/>
+      <c r="I80" s="144">
         <f t="shared" si="0"/>
         <v>408372.62</v>
       </c>
-      <c r="J80" s="146">
+      <c r="J80" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K80" s="146">
+      <c r="K80" s="145">
         <f t="shared" si="18"/>
         <v>147271.737246</v>
       </c>
-      <c r="L80" s="169">
-        <v>0</v>
-      </c>
-      <c r="M80" s="148">
+      <c r="L80" s="168">
+        <v>0</v>
+      </c>
+      <c r="M80" s="147">
         <f t="shared" si="8"/>
         <v>555644.62</v>
       </c>
-      <c r="N80" s="148">
+      <c r="N80" s="147">
         <f t="shared" si="7"/>
         <v>588983.62</v>
       </c>
@@ -9746,45 +9693,45 @@
         <v>122</v>
       </c>
       <c r="B81" s="6"/>
-      <c r="C81" s="276" t="s">
+      <c r="C81" s="205" t="s">
         <v>106</v>
       </c>
-      <c r="D81" s="277" t="s">
+      <c r="D81" s="206" t="s">
         <v>216</v>
       </c>
-      <c r="E81" s="278" t="s">
+      <c r="E81" s="207" t="s">
         <v>275</v>
       </c>
-      <c r="F81" s="279">
+      <c r="F81" s="208">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G81" s="280">
+      <c r="G81" s="209">
         <v>204457.63</v>
       </c>
-      <c r="H81" s="289">
+      <c r="H81" s="218">
         <f t="shared" ref="H81" si="28">G81</f>
         <v>204457.63</v>
       </c>
-      <c r="I81" s="281">
+      <c r="I81" s="210">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J81" s="282">
+      <c r="J81" s="211">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K81" s="282">
+      <c r="K81" s="211">
         <f t="shared" si="18"/>
         <v>136304.69298299999</v>
       </c>
-      <c r="L81" s="283">
+      <c r="L81" s="212">
         <v>20000</v>
       </c>
-      <c r="M81" s="284">
+      <c r="M81" s="213">
         <f t="shared" si="8"/>
         <v>156305.63</v>
       </c>
-      <c r="N81" s="284">
+      <c r="N81" s="213">
         <f t="shared" si="7"/>
         <v>165684.63</v>
       </c>
@@ -9805,36 +9752,36 @@
         <v>217</v>
       </c>
       <c r="E82" s="135"/>
-      <c r="F82" s="137">
+      <c r="F82" s="136">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G82" s="138">
+      <c r="G82" s="137">
         <v>148838.64000000001</v>
       </c>
-      <c r="H82" s="286">
+      <c r="H82" s="215">
         <f>G82</f>
         <v>148838.64000000001</v>
       </c>
-      <c r="I82" s="145">
+      <c r="I82" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J82" s="146">
+      <c r="J82" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K82" s="146">
+      <c r="K82" s="145">
         <f t="shared" si="18"/>
         <v>148838.45785499999</v>
       </c>
-      <c r="L82" s="169">
-        <v>0</v>
-      </c>
-      <c r="M82" s="148">
+      <c r="L82" s="168">
+        <v>0</v>
+      </c>
+      <c r="M82" s="147">
         <f t="shared" si="8"/>
         <v>148838.64000000001</v>
       </c>
-      <c r="N82" s="148">
+      <c r="N82" s="147">
         <f t="shared" si="7"/>
         <v>157769.64000000001</v>
       </c>
@@ -9843,7 +9790,7 @@
         <v>0.64000000000000035</v>
       </c>
       <c r="P82" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
@@ -9855,39 +9802,39 @@
         <v>108</v>
       </c>
       <c r="D83" s="108" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E83" s="135"/>
-      <c r="F83" s="137">
+      <c r="F83" s="136">
         <v>2.35E-2</v>
       </c>
-      <c r="G83" s="138">
+      <c r="G83" s="137">
         <v>368179.65</v>
       </c>
-      <c r="H83" s="286">
+      <c r="H83" s="215">
         <f t="shared" ref="H83:H96" si="29">G83</f>
         <v>368179.65</v>
       </c>
-      <c r="I83" s="145">
+      <c r="I83" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J83" s="146">
+      <c r="J83" s="145">
         <f t="shared" ref="J83:J114" si="30">M$8*F83</f>
         <v>0</v>
       </c>
-      <c r="K83" s="146">
+      <c r="K83" s="145">
         <f t="shared" ref="K83:K114" si="31">M$2*F83</f>
         <v>368179.343115</v>
       </c>
-      <c r="L83" s="169">
-        <v>0</v>
-      </c>
-      <c r="M83" s="148">
+      <c r="L83" s="168">
+        <v>0</v>
+      </c>
+      <c r="M83" s="147">
         <f t="shared" si="8"/>
         <v>368179.65</v>
       </c>
-      <c r="N83" s="148">
+      <c r="N83" s="147">
         <f t="shared" si="7"/>
         <v>390270.65</v>
       </c>
@@ -9908,34 +9855,34 @@
         <v>218</v>
       </c>
       <c r="E84" s="135"/>
-      <c r="F84" s="137">
+      <c r="F84" s="136">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G84" s="138">
+      <c r="G84" s="137">
         <v>311043.65999999997</v>
       </c>
-      <c r="H84" s="286">
+      <c r="H84" s="215">
         <f t="shared" si="29"/>
         <v>311043.65999999997</v>
       </c>
-      <c r="I84" s="145">
+      <c r="I84" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J84" s="146">
+      <c r="J84" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K84" s="146">
+      <c r="K84" s="145">
         <f t="shared" si="31"/>
         <v>271042.66535699996</v>
       </c>
-      <c r="L84" s="169"/>
-      <c r="M84" s="148">
+      <c r="L84" s="168"/>
+      <c r="M84" s="147">
         <f t="shared" ref="M84:M131" si="32">ROUND((K84+J84+I84+L84),0) + O84</f>
         <v>271043.65999999997</v>
       </c>
-      <c r="N84" s="148">
+      <c r="N84" s="147">
         <f t="shared" ref="N84:N131" si="33">ROUND((M84*6% + M84 ),0) + O84</f>
         <v>287306.65999999997</v>
       </c>
@@ -9956,34 +9903,34 @@
         <v>219</v>
       </c>
       <c r="E85" s="135"/>
-      <c r="F85" s="137">
+      <c r="F85" s="136">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G85" s="138">
+      <c r="G85" s="137">
         <v>147272.67000000001</v>
       </c>
-      <c r="H85" s="286">
+      <c r="H85" s="215">
         <f t="shared" si="29"/>
         <v>147272.67000000001</v>
       </c>
-      <c r="I85" s="145">
+      <c r="I85" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J85" s="146">
+      <c r="J85" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K85" s="146">
+      <c r="K85" s="145">
         <f t="shared" si="31"/>
         <v>147271.737246</v>
       </c>
-      <c r="L85" s="169"/>
-      <c r="M85" s="148">
+      <c r="L85" s="168"/>
+      <c r="M85" s="147">
         <f t="shared" si="32"/>
         <v>147272.67000000001</v>
       </c>
-      <c r="N85" s="148">
+      <c r="N85" s="147">
         <f t="shared" si="33"/>
         <v>156109.67000000001</v>
       </c>
@@ -10004,36 +9951,36 @@
         <v>220</v>
       </c>
       <c r="E86" s="135"/>
-      <c r="F86" s="137">
+      <c r="F86" s="136">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G86" s="138">
+      <c r="G86" s="137">
         <v>136305.68</v>
       </c>
-      <c r="H86" s="286">
+      <c r="H86" s="215">
         <f>G86</f>
         <v>136305.68</v>
       </c>
-      <c r="I86" s="145">
+      <c r="I86" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J86" s="146">
+      <c r="J86" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K86" s="146">
+      <c r="K86" s="145">
         <f t="shared" si="31"/>
         <v>136304.69298299999</v>
       </c>
-      <c r="L86" s="169">
-        <v>0</v>
-      </c>
-      <c r="M86" s="148">
+      <c r="L86" s="168">
+        <v>0</v>
+      </c>
+      <c r="M86" s="147">
         <f t="shared" si="32"/>
         <v>136305.68</v>
       </c>
-      <c r="N86" s="148">
+      <c r="N86" s="147">
         <f t="shared" si="33"/>
         <v>144484.68</v>
       </c>
@@ -10054,36 +10001,36 @@
         <v>221</v>
       </c>
       <c r="E87" s="135"/>
-      <c r="F87" s="137">
+      <c r="F87" s="136">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G87" s="138">
+      <c r="G87" s="137">
         <v>148838.69</v>
       </c>
-      <c r="H87" s="286">
+      <c r="H87" s="215">
         <f>G87</f>
         <v>148838.69</v>
       </c>
-      <c r="I87" s="145">
+      <c r="I87" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J87" s="146">
+      <c r="J87" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K87" s="146">
+      <c r="K87" s="145">
         <f t="shared" si="31"/>
         <v>148838.45785499999</v>
       </c>
-      <c r="L87" s="169">
-        <v>0</v>
-      </c>
-      <c r="M87" s="148">
+      <c r="L87" s="168">
+        <v>0</v>
+      </c>
+      <c r="M87" s="147">
         <f t="shared" si="32"/>
         <v>148838.69</v>
       </c>
-      <c r="N87" s="148">
+      <c r="N87" s="147">
         <f t="shared" si="33"/>
         <v>157769.69</v>
       </c>
@@ -10102,36 +10049,36 @@
         <v>185</v>
       </c>
       <c r="E88" s="108"/>
-      <c r="F88" s="144">
+      <c r="F88" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G88" s="138">
+      <c r="G88" s="137">
         <v>36035.699999999997</v>
       </c>
-      <c r="H88" s="286">
+      <c r="H88" s="215">
         <f>G88</f>
         <v>36035.699999999997</v>
       </c>
-      <c r="I88" s="145">
+      <c r="I88" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J88" s="146">
+      <c r="J88" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K88" s="146">
+      <c r="K88" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L88" s="169">
-        <v>0</v>
-      </c>
-      <c r="M88" s="148">
+      <c r="L88" s="168">
+        <v>0</v>
+      </c>
+      <c r="M88" s="147">
         <f t="shared" si="32"/>
         <v>36035.699999999997</v>
       </c>
-      <c r="N88" s="148">
+      <c r="N88" s="147">
         <f t="shared" si="33"/>
         <v>38198.699999999997</v>
       </c>
@@ -10150,36 +10097,36 @@
         <v>119</v>
       </c>
       <c r="E89" s="108"/>
-      <c r="F89" s="144">
+      <c r="F89" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G89" s="138">
+      <c r="G89" s="137">
         <v>36035.71</v>
       </c>
-      <c r="H89" s="286">
+      <c r="H89" s="215">
         <f t="shared" si="29"/>
         <v>36035.71</v>
       </c>
-      <c r="I89" s="145">
+      <c r="I89" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J89" s="146">
+      <c r="J89" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K89" s="146">
+      <c r="K89" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L89" s="169">
-        <v>0</v>
-      </c>
-      <c r="M89" s="148">
+      <c r="L89" s="168">
+        <v>0</v>
+      </c>
+      <c r="M89" s="147">
         <f t="shared" si="32"/>
         <v>36035.71</v>
       </c>
-      <c r="N89" s="148">
+      <c r="N89" s="147">
         <f t="shared" si="33"/>
         <v>38198.71</v>
       </c>
@@ -10198,36 +10145,36 @@
         <v>193</v>
       </c>
       <c r="E90" s="108"/>
-      <c r="F90" s="144">
+      <c r="F90" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G90" s="138">
+      <c r="G90" s="137">
         <v>38198.720000000001</v>
       </c>
-      <c r="H90" s="286">
+      <c r="H90" s="215">
         <f t="shared" si="29"/>
         <v>38198.720000000001</v>
       </c>
-      <c r="I90" s="145">
+      <c r="I90" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J90" s="146">
+      <c r="J90" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K90" s="146">
+      <c r="K90" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L90" s="169">
-        <v>0</v>
-      </c>
-      <c r="M90" s="148">
+      <c r="L90" s="168">
+        <v>0</v>
+      </c>
+      <c r="M90" s="147">
         <f t="shared" si="32"/>
         <v>36035.72</v>
       </c>
-      <c r="N90" s="148">
+      <c r="N90" s="147">
         <f t="shared" si="33"/>
         <v>38198.720000000001</v>
       </c>
@@ -10246,36 +10193,36 @@
         <v>204</v>
       </c>
       <c r="E91" s="108"/>
-      <c r="F91" s="144">
+      <c r="F91" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G91" s="138">
+      <c r="G91" s="137">
         <v>36035.730000000003</v>
       </c>
-      <c r="H91" s="286">
+      <c r="H91" s="215">
         <f t="shared" si="29"/>
         <v>36035.730000000003</v>
       </c>
-      <c r="I91" s="145">
+      <c r="I91" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J91" s="146">
+      <c r="J91" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K91" s="146">
+      <c r="K91" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L91" s="169">
-        <v>0</v>
-      </c>
-      <c r="M91" s="148">
+      <c r="L91" s="168">
+        <v>0</v>
+      </c>
+      <c r="M91" s="147">
         <f t="shared" si="32"/>
         <v>36035.730000000003</v>
       </c>
-      <c r="N91" s="148">
+      <c r="N91" s="147">
         <f t="shared" si="33"/>
         <v>38198.730000000003</v>
       </c>
@@ -10287,43 +10234,43 @@
     <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="108"/>
       <c r="B92" s="35"/>
-      <c r="C92" s="192" t="s">
+      <c r="C92" s="183" t="s">
         <v>128</v>
       </c>
-      <c r="D92" s="193" t="s">
+      <c r="D92" s="184" t="s">
         <v>199</v>
       </c>
-      <c r="E92" s="193"/>
-      <c r="F92" s="194">
+      <c r="E92" s="184"/>
+      <c r="F92" s="185">
         <v>2.3E-3</v>
       </c>
       <c r="G92" s="44">
         <v>36035.74</v>
       </c>
-      <c r="H92" s="286">
+      <c r="H92" s="215">
         <f t="shared" si="29"/>
         <v>36035.74</v>
       </c>
-      <c r="I92" s="195">
+      <c r="I92" s="186">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J92" s="196">
+      <c r="J92" s="187">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K92" s="196">
+      <c r="K92" s="187">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L92" s="197">
-        <v>0</v>
-      </c>
-      <c r="M92" s="198">
+      <c r="L92" s="188">
+        <v>0</v>
+      </c>
+      <c r="M92" s="189">
         <f t="shared" si="32"/>
         <v>36035.74</v>
       </c>
-      <c r="N92" s="198">
+      <c r="N92" s="189">
         <f t="shared" si="33"/>
         <v>38198.74</v>
       </c>
@@ -10332,7 +10279,7 @@
         <v>0.74000000000000044</v>
       </c>
       <c r="P92" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
@@ -10345,35 +10292,35 @@
         <v>224</v>
       </c>
       <c r="E93" s="108"/>
-      <c r="F93" s="144">
+      <c r="F93" s="143">
         <v>2.3E-3</v>
       </c>
       <c r="G93" s="44">
         <v>36035.75</v>
       </c>
-      <c r="H93" s="286">
+      <c r="H93" s="215">
         <v>38198.75</v>
       </c>
-      <c r="I93" s="145">
+      <c r="I93" s="144">
         <f t="shared" si="0"/>
         <v>-2163</v>
       </c>
-      <c r="J93" s="146">
+      <c r="J93" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K93" s="146">
+      <c r="K93" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L93" s="169">
-        <v>0</v>
-      </c>
-      <c r="M93" s="148">
+      <c r="L93" s="168">
+        <v>0</v>
+      </c>
+      <c r="M93" s="147">
         <f t="shared" si="32"/>
         <v>33872.75</v>
       </c>
-      <c r="N93" s="148">
+      <c r="N93" s="147">
         <f t="shared" si="33"/>
         <v>35905.75</v>
       </c>
@@ -10392,36 +10339,36 @@
         <v>192</v>
       </c>
       <c r="E94" s="108"/>
-      <c r="F94" s="144">
+      <c r="F94" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G94" s="138">
+      <c r="G94" s="137">
         <v>36035.760000000002</v>
       </c>
-      <c r="H94" s="286">
+      <c r="H94" s="215">
         <f t="shared" si="29"/>
         <v>36035.760000000002</v>
       </c>
-      <c r="I94" s="145">
+      <c r="I94" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J94" s="146">
+      <c r="J94" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K94" s="146">
+      <c r="K94" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L94" s="169">
-        <v>0</v>
-      </c>
-      <c r="M94" s="148">
+      <c r="L94" s="168">
+        <v>0</v>
+      </c>
+      <c r="M94" s="147">
         <f t="shared" si="32"/>
         <v>36035.760000000002</v>
       </c>
-      <c r="N94" s="148">
+      <c r="N94" s="147">
         <f t="shared" si="33"/>
         <v>38198.76</v>
       </c>
@@ -10440,36 +10387,36 @@
         <v>192</v>
       </c>
       <c r="E95" s="108"/>
-      <c r="F95" s="144">
+      <c r="F95" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G95" s="138">
+      <c r="G95" s="137">
         <v>36035.769999999997</v>
       </c>
-      <c r="H95" s="286">
+      <c r="H95" s="215">
         <f t="shared" si="29"/>
         <v>36035.769999999997</v>
       </c>
-      <c r="I95" s="145">
+      <c r="I95" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J95" s="146">
+      <c r="J95" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K95" s="146">
+      <c r="K95" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L95" s="169">
-        <v>0</v>
-      </c>
-      <c r="M95" s="148">
+      <c r="L95" s="168">
+        <v>0</v>
+      </c>
+      <c r="M95" s="147">
         <f t="shared" si="32"/>
         <v>36035.769999999997</v>
       </c>
-      <c r="N95" s="148">
+      <c r="N95" s="147">
         <f t="shared" si="33"/>
         <v>38198.769999999997</v>
       </c>
@@ -10485,39 +10432,39 @@
         <v>132</v>
       </c>
       <c r="D96" s="108" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="E96" s="108"/>
-      <c r="F96" s="144">
+      <c r="F96" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G96" s="138">
+      <c r="G96" s="137">
         <v>36035.78</v>
       </c>
-      <c r="H96" s="286">
+      <c r="H96" s="215">
         <f t="shared" si="29"/>
         <v>36035.78</v>
       </c>
-      <c r="I96" s="145">
+      <c r="I96" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J96" s="146">
+      <c r="J96" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K96" s="146">
+      <c r="K96" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L96" s="169">
-        <v>0</v>
-      </c>
-      <c r="M96" s="148">
+      <c r="L96" s="168">
+        <v>0</v>
+      </c>
+      <c r="M96" s="147">
         <f t="shared" si="32"/>
         <v>36035.78</v>
       </c>
-      <c r="N96" s="148">
+      <c r="N96" s="147">
         <f t="shared" si="33"/>
         <v>38198.78</v>
       </c>
@@ -10536,33 +10483,33 @@
         <v>202</v>
       </c>
       <c r="E97" s="108"/>
-      <c r="F97" s="144">
+      <c r="F97" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G97" s="138">
+      <c r="G97" s="137">
         <v>177818.79</v>
       </c>
-      <c r="H97" s="286"/>
-      <c r="I97" s="145">
+      <c r="H97" s="215"/>
+      <c r="I97" s="144">
         <f t="shared" si="0"/>
         <v>177818.79</v>
       </c>
-      <c r="J97" s="146">
+      <c r="J97" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K97" s="146">
+      <c r="K97" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L97" s="169">
-        <v>0</v>
-      </c>
-      <c r="M97" s="148">
+      <c r="L97" s="168">
+        <v>0</v>
+      </c>
+      <c r="M97" s="147">
         <f t="shared" si="32"/>
         <v>213853.79</v>
       </c>
-      <c r="N97" s="148">
+      <c r="N97" s="147">
         <f t="shared" si="33"/>
         <v>226685.79</v>
       </c>
@@ -10581,36 +10528,36 @@
         <v>185</v>
       </c>
       <c r="E98" s="108"/>
-      <c r="F98" s="144">
+      <c r="F98" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G98" s="138">
+      <c r="G98" s="137">
         <v>36035.800000000003</v>
       </c>
-      <c r="H98" s="286">
+      <c r="H98" s="215">
         <f>G98</f>
         <v>36035.800000000003</v>
       </c>
-      <c r="I98" s="145">
+      <c r="I98" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J98" s="146">
+      <c r="J98" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K98" s="146">
+      <c r="K98" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L98" s="169">
-        <v>0</v>
-      </c>
-      <c r="M98" s="148">
+      <c r="L98" s="168">
+        <v>0</v>
+      </c>
+      <c r="M98" s="147">
         <f t="shared" si="32"/>
         <v>36035.800000000003</v>
       </c>
-      <c r="N98" s="148">
+      <c r="N98" s="147">
         <f t="shared" si="33"/>
         <v>38198.800000000003</v>
       </c>
@@ -10635,7 +10582,7 @@
       <c r="G99" s="134">
         <v>36035.81</v>
       </c>
-      <c r="H99" s="286"/>
+      <c r="H99" s="215"/>
       <c r="I99" s="56">
         <f t="shared" si="0"/>
         <v>36035.81</v>
@@ -10648,7 +10595,7 @@
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L99" s="169">
+      <c r="L99" s="168">
         <v>0</v>
       </c>
       <c r="M99" s="8">
@@ -10671,7 +10618,7 @@
         <v>136</v>
       </c>
       <c r="D100" s="108" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E100" s="108"/>
       <c r="F100" s="89">
@@ -10680,8 +10627,8 @@
       <c r="G100" s="134">
         <v>36035.82</v>
       </c>
-      <c r="H100" s="286">
-        <f t="shared" ref="H96:H104" si="35">G100</f>
+      <c r="H100" s="215">
+        <f t="shared" ref="H100:H104" si="35">G100</f>
         <v>36035.82</v>
       </c>
       <c r="I100" s="56">
@@ -10696,7 +10643,7 @@
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L100" s="169">
+      <c r="L100" s="168">
         <v>0</v>
       </c>
       <c r="M100" s="8">
@@ -10722,36 +10669,36 @@
         <v>225</v>
       </c>
       <c r="E101" s="108"/>
-      <c r="F101" s="144">
+      <c r="F101" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G101" s="138">
+      <c r="G101" s="137">
         <v>36035.83</v>
       </c>
-      <c r="H101" s="286">
+      <c r="H101" s="215">
         <f t="shared" si="35"/>
         <v>36035.83</v>
       </c>
-      <c r="I101" s="145">
+      <c r="I101" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J101" s="146">
+      <c r="J101" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K101" s="146">
+      <c r="K101" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L101" s="169">
-        <v>0</v>
-      </c>
-      <c r="M101" s="148">
+      <c r="L101" s="168">
+        <v>0</v>
+      </c>
+      <c r="M101" s="147">
         <f t="shared" si="32"/>
         <v>36035.83</v>
       </c>
-      <c r="N101" s="148">
+      <c r="N101" s="147">
         <f t="shared" si="33"/>
         <v>38198.83</v>
       </c>
@@ -10770,36 +10717,36 @@
         <v>214</v>
       </c>
       <c r="E102" s="108"/>
-      <c r="F102" s="144">
+      <c r="F102" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G102" s="138">
+      <c r="G102" s="137">
         <v>36035.839999999997</v>
       </c>
-      <c r="H102" s="286">
+      <c r="H102" s="215">
         <f t="shared" si="35"/>
         <v>36035.839999999997</v>
       </c>
-      <c r="I102" s="145">
+      <c r="I102" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J102" s="146">
+      <c r="J102" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K102" s="146">
+      <c r="K102" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L102" s="169">
-        <v>0</v>
-      </c>
-      <c r="M102" s="148">
+      <c r="L102" s="168">
+        <v>0</v>
+      </c>
+      <c r="M102" s="147">
         <f t="shared" si="32"/>
         <v>36035.839999999997</v>
       </c>
-      <c r="N102" s="148">
+      <c r="N102" s="147">
         <f t="shared" si="33"/>
         <v>38198.839999999997</v>
       </c>
@@ -10818,36 +10765,36 @@
         <v>222</v>
       </c>
       <c r="E103" s="108"/>
-      <c r="F103" s="144">
+      <c r="F103" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G103" s="138">
+      <c r="G103" s="137">
         <v>36035.85</v>
       </c>
-      <c r="H103" s="286">
+      <c r="H103" s="215">
         <f t="shared" si="35"/>
         <v>36035.85</v>
       </c>
-      <c r="I103" s="145">
+      <c r="I103" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J103" s="146">
+      <c r="J103" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K103" s="146">
+      <c r="K103" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L103" s="169">
-        <v>0</v>
-      </c>
-      <c r="M103" s="148">
+      <c r="L103" s="168">
+        <v>0</v>
+      </c>
+      <c r="M103" s="147">
         <f t="shared" si="32"/>
         <v>36035.85</v>
       </c>
-      <c r="N103" s="148">
+      <c r="N103" s="147">
         <f t="shared" si="33"/>
         <v>38198.85</v>
       </c>
@@ -10872,7 +10819,7 @@
       <c r="G104" s="134">
         <v>36035.86</v>
       </c>
-      <c r="H104" s="286">
+      <c r="H104" s="215">
         <f t="shared" si="35"/>
         <v>36035.86</v>
       </c>
@@ -10888,7 +10835,7 @@
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L104" s="169">
+      <c r="L104" s="168">
         <v>0</v>
       </c>
       <c r="M104" s="8">
@@ -10920,8 +10867,8 @@
       <c r="G105" s="134">
         <v>36035.870000000003</v>
       </c>
-      <c r="H105" s="291">
-        <f t="shared" ref="H105:H111" si="36">G105</f>
+      <c r="H105" s="220">
+        <f t="shared" ref="H105:H110" si="36">G105</f>
         <v>36035.870000000003</v>
       </c>
       <c r="I105" s="56">
@@ -10936,7 +10883,7 @@
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L105" s="169">
+      <c r="L105" s="168">
         <v>0</v>
       </c>
       <c r="M105" s="8">
@@ -10968,7 +10915,7 @@
       <c r="G106" s="134">
         <v>36076.879999999997</v>
       </c>
-      <c r="H106" s="291">
+      <c r="H106" s="220">
         <f>G106</f>
         <v>36076.879999999997</v>
       </c>
@@ -10984,7 +10931,7 @@
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L106" s="169">
+      <c r="L106" s="168">
         <v>0</v>
       </c>
       <c r="M106" s="8">
@@ -11016,7 +10963,7 @@
       <c r="G107" s="134">
         <v>40635.89</v>
       </c>
-      <c r="H107" s="291">
+      <c r="H107" s="220">
         <v>36035.89</v>
       </c>
       <c r="I107" s="56">
@@ -11031,7 +10978,7 @@
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L107" s="169">
+      <c r="L107" s="168">
         <v>0</v>
       </c>
       <c r="M107" s="8">
@@ -11063,7 +11010,7 @@
       <c r="G108" s="134">
         <v>36035.9</v>
       </c>
-      <c r="H108" s="286">
+      <c r="H108" s="215">
         <f t="shared" ref="H108" si="37">G108</f>
         <v>36035.9</v>
       </c>
@@ -11079,7 +11026,7 @@
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L108" s="169">
+      <c r="L108" s="168">
         <v>0</v>
       </c>
       <c r="M108" s="8">
@@ -11111,7 +11058,7 @@
       <c r="G109" s="134">
         <v>38198.910000000003</v>
       </c>
-      <c r="H109" s="286">
+      <c r="H109" s="215">
         <f t="shared" si="36"/>
         <v>38198.910000000003</v>
       </c>
@@ -11127,7 +11074,7 @@
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L109" s="169">
+      <c r="L109" s="168">
         <v>0</v>
       </c>
       <c r="M109" s="8">
@@ -11153,36 +11100,36 @@
         <v>208</v>
       </c>
       <c r="E110" s="108"/>
-      <c r="F110" s="144">
+      <c r="F110" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G110" s="138">
+      <c r="G110" s="137">
         <v>36035.919999999998</v>
       </c>
-      <c r="H110" s="286">
+      <c r="H110" s="215">
         <f t="shared" si="36"/>
         <v>36035.919999999998</v>
       </c>
-      <c r="I110" s="145">
+      <c r="I110" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J110" s="146">
+      <c r="J110" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K110" s="146">
+      <c r="K110" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L110" s="169">
-        <v>0</v>
-      </c>
-      <c r="M110" s="148">
+      <c r="L110" s="168">
+        <v>0</v>
+      </c>
+      <c r="M110" s="147">
         <f t="shared" si="32"/>
         <v>36035.919999999998</v>
       </c>
-      <c r="N110" s="148">
+      <c r="N110" s="147">
         <f t="shared" si="33"/>
         <v>38198.92</v>
       </c>
@@ -11201,36 +11148,36 @@
         <v>194</v>
       </c>
       <c r="E111" s="108"/>
-      <c r="F111" s="144">
+      <c r="F111" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G111" s="138">
+      <c r="G111" s="137">
         <v>36035.93</v>
       </c>
-      <c r="H111" s="286">
+      <c r="H111" s="215">
         <f>G111</f>
         <v>36035.93</v>
       </c>
-      <c r="I111" s="145">
+      <c r="I111" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J111" s="146">
+      <c r="J111" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K111" s="146">
+      <c r="K111" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L111" s="169">
-        <v>0</v>
-      </c>
-      <c r="M111" s="148">
+      <c r="L111" s="168">
+        <v>0</v>
+      </c>
+      <c r="M111" s="147">
         <f t="shared" si="32"/>
         <v>36035.93</v>
       </c>
-      <c r="N111" s="148">
+      <c r="N111" s="147">
         <f t="shared" si="33"/>
         <v>38198.93</v>
       </c>
@@ -11249,36 +11196,36 @@
         <v>177</v>
       </c>
       <c r="E112" s="108"/>
-      <c r="F112" s="144">
+      <c r="F112" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G112" s="138">
+      <c r="G112" s="137">
         <v>69386.94</v>
       </c>
-      <c r="H112" s="286">
+      <c r="H112" s="215">
         <f>G112</f>
         <v>69386.94</v>
       </c>
-      <c r="I112" s="145">
+      <c r="I112" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J112" s="146">
+      <c r="J112" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K112" s="146">
+      <c r="K112" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L112" s="169">
-        <v>0</v>
-      </c>
-      <c r="M112" s="148">
+      <c r="L112" s="168">
+        <v>0</v>
+      </c>
+      <c r="M112" s="147">
         <f t="shared" si="32"/>
         <v>36035.94</v>
       </c>
-      <c r="N112" s="148">
+      <c r="N112" s="147">
         <f t="shared" si="33"/>
         <v>38198.94</v>
       </c>
@@ -11297,36 +11244,36 @@
         <v>200</v>
       </c>
       <c r="E113" s="108"/>
-      <c r="F113" s="144">
+      <c r="F113" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G113" s="138">
+      <c r="G113" s="137">
         <v>36035.949999999997</v>
       </c>
-      <c r="H113" s="286">
+      <c r="H113" s="215">
         <f t="shared" ref="H113" si="38">G113</f>
         <v>36035.949999999997</v>
       </c>
-      <c r="I113" s="145">
+      <c r="I113" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J113" s="146">
+      <c r="J113" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K113" s="146">
+      <c r="K113" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L113" s="169">
-        <v>0</v>
-      </c>
-      <c r="M113" s="148">
+      <c r="L113" s="168">
+        <v>0</v>
+      </c>
+      <c r="M113" s="147">
         <f t="shared" si="32"/>
         <v>36035.949999999997</v>
       </c>
-      <c r="N113" s="148">
+      <c r="N113" s="147">
         <f t="shared" si="33"/>
         <v>38198.949999999997</v>
       </c>
@@ -11345,36 +11292,36 @@
         <v>221</v>
       </c>
       <c r="E114" s="108"/>
-      <c r="F114" s="144">
+      <c r="F114" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G114" s="138">
+      <c r="G114" s="137">
         <v>36035.96</v>
       </c>
-      <c r="H114" s="286">
+      <c r="H114" s="215">
         <f>G114</f>
         <v>36035.96</v>
       </c>
-      <c r="I114" s="145">
+      <c r="I114" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J114" s="146">
+      <c r="J114" s="145">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K114" s="146">
+      <c r="K114" s="145">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L114" s="169">
-        <v>0</v>
-      </c>
-      <c r="M114" s="148">
+      <c r="L114" s="168">
+        <v>0</v>
+      </c>
+      <c r="M114" s="147">
         <f t="shared" si="32"/>
         <v>36035.96</v>
       </c>
-      <c r="N114" s="148">
+      <c r="N114" s="147">
         <f t="shared" si="33"/>
         <v>38198.959999999999</v>
       </c>
@@ -11393,36 +11340,36 @@
         <v>188</v>
       </c>
       <c r="E115" s="108"/>
-      <c r="F115" s="144">
+      <c r="F115" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G115" s="138">
+      <c r="G115" s="137">
         <v>36035.97</v>
       </c>
-      <c r="H115" s="286">
+      <c r="H115" s="215">
         <f t="shared" ref="H115" si="39">G115</f>
         <v>36035.97</v>
       </c>
-      <c r="I115" s="145">
+      <c r="I115" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J115" s="146">
+      <c r="J115" s="145">
         <f t="shared" ref="J115:J131" si="40">M$8*F115</f>
         <v>0</v>
       </c>
-      <c r="K115" s="146">
+      <c r="K115" s="145">
         <f t="shared" ref="K115:K131" si="41">M$2*F115</f>
         <v>36034.574006999996</v>
       </c>
-      <c r="L115" s="169">
-        <v>0</v>
-      </c>
-      <c r="M115" s="148">
+      <c r="L115" s="168">
+        <v>0</v>
+      </c>
+      <c r="M115" s="147">
         <f t="shared" si="32"/>
         <v>36035.97</v>
       </c>
-      <c r="N115" s="148">
+      <c r="N115" s="147">
         <f t="shared" si="33"/>
         <v>38198.97</v>
       </c>
@@ -11441,38 +11388,38 @@
         <v>182</v>
       </c>
       <c r="E116" s="108" t="s">
-        <v>326</v>
-      </c>
-      <c r="F116" s="144">
+        <v>313</v>
+      </c>
+      <c r="F116" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G116" s="138">
+      <c r="G116" s="137">
         <v>38198.980000000003</v>
       </c>
-      <c r="H116" s="286">
+      <c r="H116" s="215">
         <f>G116</f>
         <v>38198.980000000003</v>
       </c>
-      <c r="I116" s="145">
+      <c r="I116" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J116" s="146">
+      <c r="J116" s="145">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="K116" s="146">
+      <c r="K116" s="145">
         <f t="shared" si="41"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L116" s="169">
-        <v>0</v>
-      </c>
-      <c r="M116" s="148">
+      <c r="L116" s="168">
+        <v>0</v>
+      </c>
+      <c r="M116" s="147">
         <f t="shared" si="32"/>
         <v>36035.980000000003</v>
       </c>
-      <c r="N116" s="148">
+      <c r="N116" s="147">
         <f t="shared" si="33"/>
         <v>38198.980000000003</v>
       </c>
@@ -11491,33 +11438,33 @@
         <v>182</v>
       </c>
       <c r="E117" s="108"/>
-      <c r="F117" s="144">
+      <c r="F117" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G117" s="138">
+      <c r="G117" s="137">
         <v>69189.990000000005</v>
       </c>
-      <c r="H117" s="286"/>
-      <c r="I117" s="145">
+      <c r="H117" s="215"/>
+      <c r="I117" s="144">
         <f t="shared" si="0"/>
         <v>69189.990000000005</v>
       </c>
-      <c r="J117" s="146">
+      <c r="J117" s="145">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="K117" s="146">
+      <c r="K117" s="145">
         <f t="shared" si="41"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L117" s="169">
-        <v>0</v>
-      </c>
-      <c r="M117" s="148">
+      <c r="L117" s="168">
+        <v>0</v>
+      </c>
+      <c r="M117" s="147">
         <f t="shared" si="32"/>
         <v>105225.99</v>
       </c>
-      <c r="N117" s="148">
+      <c r="N117" s="147">
         <f t="shared" si="33"/>
         <v>111540.99</v>
       </c>
@@ -11536,36 +11483,36 @@
         <v>183</v>
       </c>
       <c r="E118" s="108"/>
-      <c r="F118" s="144">
+      <c r="F118" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G118" s="138">
+      <c r="G118" s="137">
         <v>36036</v>
       </c>
-      <c r="H118" s="286">
+      <c r="H118" s="215">
         <f t="shared" ref="H118:H120" si="42">G118</f>
         <v>36036</v>
       </c>
-      <c r="I118" s="145">
+      <c r="I118" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J118" s="146">
+      <c r="J118" s="145">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="K118" s="146">
+      <c r="K118" s="145">
         <f t="shared" si="41"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L118" s="169">
-        <v>0</v>
-      </c>
-      <c r="M118" s="148">
+      <c r="L118" s="168">
+        <v>0</v>
+      </c>
+      <c r="M118" s="147">
         <f t="shared" si="32"/>
         <v>36036</v>
       </c>
-      <c r="N118" s="148">
+      <c r="N118" s="147">
         <f t="shared" si="33"/>
         <v>38199</v>
       </c>
@@ -11574,7 +11521,7 @@
         <v>1.0000000000000007</v>
       </c>
       <c r="P118" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.25">
@@ -11584,39 +11531,39 @@
         <v>155</v>
       </c>
       <c r="D119" s="108" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="E119" s="108"/>
-      <c r="F119" s="144">
+      <c r="F119" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G119" s="138">
+      <c r="G119" s="137">
         <v>36036.01</v>
       </c>
-      <c r="H119" s="286">
+      <c r="H119" s="215">
         <f t="shared" si="42"/>
         <v>36036.01</v>
       </c>
-      <c r="I119" s="145">
+      <c r="I119" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J119" s="146">
+      <c r="J119" s="145">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="K119" s="146">
+      <c r="K119" s="145">
         <f t="shared" si="41"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L119" s="169">
-        <v>0</v>
-      </c>
-      <c r="M119" s="148">
+      <c r="L119" s="168">
+        <v>0</v>
+      </c>
+      <c r="M119" s="147">
         <f t="shared" si="32"/>
         <v>36036.01</v>
       </c>
-      <c r="N119" s="148">
+      <c r="N119" s="147">
         <f t="shared" si="33"/>
         <v>38199.01</v>
       </c>
@@ -11635,36 +11582,36 @@
         <v>190</v>
       </c>
       <c r="E120" s="108"/>
-      <c r="F120" s="144">
+      <c r="F120" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G120" s="138">
+      <c r="G120" s="137">
         <v>36036.019999999997</v>
       </c>
-      <c r="H120" s="286">
+      <c r="H120" s="215">
         <f t="shared" si="42"/>
         <v>36036.019999999997</v>
       </c>
-      <c r="I120" s="145">
+      <c r="I120" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J120" s="146">
+      <c r="J120" s="145">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="K120" s="146">
+      <c r="K120" s="145">
         <f t="shared" si="41"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L120" s="169">
-        <v>0</v>
-      </c>
-      <c r="M120" s="148">
+      <c r="L120" s="168">
+        <v>0</v>
+      </c>
+      <c r="M120" s="147">
         <f t="shared" si="32"/>
         <v>36036.019999999997</v>
       </c>
-      <c r="N120" s="148">
+      <c r="N120" s="147">
         <f t="shared" si="33"/>
         <v>38199.019999999997</v>
       </c>
@@ -11683,36 +11630,36 @@
         <v>182</v>
       </c>
       <c r="E121" s="108"/>
-      <c r="F121" s="144">
+      <c r="F121" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G121" s="138">
+      <c r="G121" s="137">
         <v>28236.03</v>
       </c>
-      <c r="H121" s="286">
+      <c r="H121" s="215">
         <f>G121</f>
         <v>28236.03</v>
       </c>
-      <c r="I121" s="145">
+      <c r="I121" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J121" s="146">
+      <c r="J121" s="145">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="K121" s="146">
+      <c r="K121" s="145">
         <f t="shared" si="41"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L121" s="169">
-        <v>0</v>
-      </c>
-      <c r="M121" s="148">
+      <c r="L121" s="168">
+        <v>0</v>
+      </c>
+      <c r="M121" s="147">
         <f t="shared" si="32"/>
         <v>36036.03</v>
       </c>
-      <c r="N121" s="148">
+      <c r="N121" s="147">
         <f t="shared" si="33"/>
         <v>38199.03</v>
       </c>
@@ -11731,36 +11678,36 @@
         <v>218</v>
       </c>
       <c r="E122" s="108"/>
-      <c r="F122" s="144">
+      <c r="F122" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G122" s="138">
+      <c r="G122" s="137">
         <v>36036.04</v>
       </c>
-      <c r="H122" s="286">
+      <c r="H122" s="215">
         <f>G122</f>
         <v>36036.04</v>
       </c>
-      <c r="I122" s="145">
+      <c r="I122" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J122" s="146">
+      <c r="J122" s="145">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="K122" s="146">
+      <c r="K122" s="145">
         <f t="shared" si="41"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L122" s="169">
-        <v>0</v>
-      </c>
-      <c r="M122" s="148">
+      <c r="L122" s="168">
+        <v>0</v>
+      </c>
+      <c r="M122" s="147">
         <f t="shared" si="32"/>
         <v>36036.04</v>
       </c>
-      <c r="N122" s="148">
+      <c r="N122" s="147">
         <f t="shared" si="33"/>
         <v>38199.040000000001</v>
       </c>
@@ -11779,36 +11726,36 @@
         <v>213</v>
       </c>
       <c r="E123" s="108"/>
-      <c r="F123" s="144">
+      <c r="F123" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G123" s="138">
+      <c r="G123" s="137">
         <v>36036.050000000003</v>
       </c>
-      <c r="H123" s="286">
+      <c r="H123" s="215">
         <f>G123</f>
         <v>36036.050000000003</v>
       </c>
-      <c r="I123" s="145">
+      <c r="I123" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J123" s="146">
+      <c r="J123" s="145">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="K123" s="146">
+      <c r="K123" s="145">
         <f t="shared" si="41"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L123" s="169">
-        <v>0</v>
-      </c>
-      <c r="M123" s="148">
+      <c r="L123" s="168">
+        <v>0</v>
+      </c>
+      <c r="M123" s="147">
         <f t="shared" si="32"/>
         <v>36036.050000000003</v>
       </c>
-      <c r="N123" s="148">
+      <c r="N123" s="147">
         <f t="shared" si="33"/>
         <v>38199.050000000003</v>
       </c>
@@ -11827,36 +11774,36 @@
         <v>182</v>
       </c>
       <c r="E124" s="108"/>
-      <c r="F124" s="144">
+      <c r="F124" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G124" s="138">
+      <c r="G124" s="137">
         <v>15336.06</v>
       </c>
-      <c r="H124" s="286">
+      <c r="H124" s="215">
         <f>G124</f>
         <v>15336.06</v>
       </c>
-      <c r="I124" s="145">
+      <c r="I124" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J124" s="146">
+      <c r="J124" s="145">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="K124" s="146">
+      <c r="K124" s="145">
         <f t="shared" si="41"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L124" s="169">
-        <v>0</v>
-      </c>
-      <c r="M124" s="148">
+      <c r="L124" s="168">
+        <v>0</v>
+      </c>
+      <c r="M124" s="147">
         <f t="shared" si="32"/>
         <v>36036.06</v>
       </c>
-      <c r="N124" s="148">
+      <c r="N124" s="147">
         <f t="shared" si="33"/>
         <v>38199.06</v>
       </c>
@@ -11865,12 +11812,12 @@
         <v>1.0600000000000007</v>
       </c>
       <c r="P124" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A125" s="191"/>
-      <c r="B125" s="171"/>
+      <c r="A125" s="182"/>
+      <c r="B125" s="170"/>
       <c r="C125" s="35" t="s">
         <v>161</v>
       </c>
@@ -11878,37 +11825,37 @@
         <v>182</v>
       </c>
       <c r="E125" s="135" t="s">
-        <v>299</v>
-      </c>
-      <c r="F125" s="144">
+        <v>289</v>
+      </c>
+      <c r="F125" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G125" s="138">
+      <c r="G125" s="137">
         <v>59040.07</v>
       </c>
-      <c r="H125" s="286">
+      <c r="H125" s="215">
         <v>36035</v>
       </c>
-      <c r="I125" s="145">
+      <c r="I125" s="144">
         <f t="shared" si="0"/>
         <v>23005.07</v>
       </c>
-      <c r="J125" s="146">
+      <c r="J125" s="145">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="K125" s="146">
+      <c r="K125" s="145">
         <f t="shared" si="41"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L125" s="169">
-        <v>0</v>
-      </c>
-      <c r="M125" s="148">
+      <c r="L125" s="168">
+        <v>0</v>
+      </c>
+      <c r="M125" s="147">
         <f t="shared" si="32"/>
         <v>59041.07</v>
       </c>
-      <c r="N125" s="148">
+      <c r="N125" s="147">
         <f t="shared" si="33"/>
         <v>62585.07</v>
       </c>
@@ -11918,8 +11865,8 @@
       </c>
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A126" s="191"/>
-      <c r="B126" s="171"/>
+      <c r="A126" s="182"/>
+      <c r="B126" s="170"/>
       <c r="C126" s="35" t="s">
         <v>162</v>
       </c>
@@ -11927,36 +11874,36 @@
         <v>182</v>
       </c>
       <c r="E126" s="108"/>
-      <c r="F126" s="144">
+      <c r="F126" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G126" s="138">
+      <c r="G126" s="137">
         <v>36036.080000000002</v>
       </c>
-      <c r="H126" s="286">
+      <c r="H126" s="215">
         <f t="shared" ref="H126:H127" si="43">G126</f>
         <v>36036.080000000002</v>
       </c>
-      <c r="I126" s="145">
+      <c r="I126" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J126" s="146">
+      <c r="J126" s="145">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="K126" s="146">
+      <c r="K126" s="145">
         <f t="shared" si="41"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L126" s="169">
-        <v>0</v>
-      </c>
-      <c r="M126" s="148">
+      <c r="L126" s="168">
+        <v>0</v>
+      </c>
+      <c r="M126" s="147">
         <f t="shared" si="32"/>
         <v>36036.080000000002</v>
       </c>
-      <c r="N126" s="148">
+      <c r="N126" s="147">
         <f t="shared" si="33"/>
         <v>38199.08</v>
       </c>
@@ -11975,36 +11922,36 @@
         <v>216</v>
       </c>
       <c r="E127" s="108"/>
-      <c r="F127" s="144">
+      <c r="F127" s="143">
         <v>2.3E-3</v>
       </c>
-      <c r="G127" s="138">
+      <c r="G127" s="137">
         <v>36036.089999999997</v>
       </c>
-      <c r="H127" s="286">
+      <c r="H127" s="215">
         <f t="shared" si="43"/>
         <v>36036.089999999997</v>
       </c>
-      <c r="I127" s="145">
+      <c r="I127" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J127" s="146">
+      <c r="J127" s="145">
         <f t="shared" si="40"/>
         <v>0</v>
       </c>
-      <c r="K127" s="146">
+      <c r="K127" s="145">
         <f t="shared" si="41"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L127" s="169">
-        <v>0</v>
-      </c>
-      <c r="M127" s="148">
+      <c r="L127" s="168">
+        <v>0</v>
+      </c>
+      <c r="M127" s="147">
         <f t="shared" si="32"/>
         <v>36036.089999999997</v>
       </c>
-      <c r="N127" s="148">
+      <c r="N127" s="147">
         <f t="shared" si="33"/>
         <v>38199.089999999997</v>
       </c>
@@ -12029,7 +11976,7 @@
       <c r="G128" s="134">
         <v>36036.1</v>
       </c>
-      <c r="H128" s="286">
+      <c r="H128" s="215">
         <f>G128</f>
         <v>36036.1</v>
       </c>
@@ -12045,7 +11992,7 @@
         <f t="shared" si="41"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L128" s="169">
+      <c r="L128" s="168">
         <v>0</v>
       </c>
       <c r="M128" s="8">
@@ -12077,7 +12024,7 @@
       <c r="G129" s="134">
         <v>36036.11</v>
       </c>
-      <c r="H129" s="286">
+      <c r="H129" s="215">
         <f>G129</f>
         <v>36036.11</v>
       </c>
@@ -12093,7 +12040,7 @@
         <f t="shared" si="41"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L129" s="169">
+      <c r="L129" s="168">
         <v>0</v>
       </c>
       <c r="M129" s="8">
@@ -12127,7 +12074,7 @@
       <c r="G130" s="134">
         <v>36036.120000000003</v>
       </c>
-      <c r="H130" s="286">
+      <c r="H130" s="215">
         <f>G130</f>
         <v>36036.120000000003</v>
       </c>
@@ -12143,7 +12090,7 @@
         <f t="shared" si="41"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L130" s="169">
+      <c r="L130" s="168">
         <v>0</v>
       </c>
       <c r="M130" s="8">
@@ -12168,7 +12115,7 @@
         <v>167</v>
       </c>
       <c r="D131" s="108" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="E131" s="108"/>
       <c r="F131" s="89">
@@ -12177,7 +12124,7 @@
       <c r="G131" s="134">
         <v>36036.129999999997</v>
       </c>
-      <c r="H131" s="291">
+      <c r="H131" s="220">
         <f>36036.13+6006.02</f>
         <v>42042.149999999994</v>
       </c>
@@ -12193,7 +12140,7 @@
         <f t="shared" si="41"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L131" s="169">
+      <c r="L131" s="168">
         <v>0</v>
       </c>
       <c r="M131" s="8">
@@ -12254,7 +12201,7 @@
         <f>SUM(K14:K132)</f>
         <v>15462877.067300022</v>
       </c>
-      <c r="L133" s="182">
+      <c r="L133" s="181">
         <f>SUM(L14:L132)</f>
         <v>223000</v>
       </c>
@@ -12275,32 +12222,32 @@
       </c>
     </row>
     <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="238"/>
-      <c r="D135" s="238"/>
-      <c r="E135" s="238"/>
-      <c r="F135" s="238"/>
-      <c r="G135" s="238"/>
-      <c r="H135" s="238"/>
-      <c r="I135" s="238"/>
-      <c r="J135" s="238"/>
-      <c r="K135" s="238"/>
-      <c r="L135" s="238"/>
-      <c r="M135" s="238"/>
-      <c r="N135" s="238"/>
+      <c r="C135" s="259"/>
+      <c r="D135" s="259"/>
+      <c r="E135" s="259"/>
+      <c r="F135" s="259"/>
+      <c r="G135" s="259"/>
+      <c r="H135" s="259"/>
+      <c r="I135" s="259"/>
+      <c r="J135" s="259"/>
+      <c r="K135" s="259"/>
+      <c r="L135" s="259"/>
+      <c r="M135" s="259"/>
+      <c r="N135" s="259"/>
     </row>
     <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="238"/>
-      <c r="D136" s="238"/>
-      <c r="E136" s="238"/>
-      <c r="F136" s="238"/>
-      <c r="G136" s="238"/>
-      <c r="H136" s="238"/>
-      <c r="I136" s="238"/>
-      <c r="J136" s="238"/>
-      <c r="K136" s="238"/>
-      <c r="L136" s="238"/>
-      <c r="M136" s="238"/>
-      <c r="N136" s="238"/>
+      <c r="C136" s="259"/>
+      <c r="D136" s="259"/>
+      <c r="E136" s="259"/>
+      <c r="F136" s="259"/>
+      <c r="G136" s="259"/>
+      <c r="H136" s="259"/>
+      <c r="I136" s="259"/>
+      <c r="J136" s="259"/>
+      <c r="K136" s="259"/>
+      <c r="L136" s="259"/>
+      <c r="M136" s="259"/>
+      <c r="N136" s="259"/>
     </row>
     <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="77"/>
@@ -12317,118 +12264,118 @@
       <c r="N137" s="77"/>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C138" s="223" t="s">
+      <c r="C138" s="243" t="s">
         <v>260</v>
       </c>
-      <c r="D138" s="223"/>
-      <c r="E138" s="223"/>
-      <c r="F138" s="223"/>
-      <c r="G138" s="223"/>
-      <c r="H138" s="223"/>
-      <c r="I138" s="223"/>
-      <c r="J138" s="223"/>
-      <c r="K138" s="223"/>
-      <c r="L138" s="223"/>
-      <c r="M138" s="223"/>
-      <c r="N138" s="223"/>
+      <c r="D138" s="243"/>
+      <c r="E138" s="243"/>
+      <c r="F138" s="243"/>
+      <c r="G138" s="243"/>
+      <c r="H138" s="243"/>
+      <c r="I138" s="243"/>
+      <c r="J138" s="243"/>
+      <c r="K138" s="243"/>
+      <c r="L138" s="243"/>
+      <c r="M138" s="243"/>
+      <c r="N138" s="243"/>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C139" s="223"/>
-      <c r="D139" s="223"/>
-      <c r="E139" s="223"/>
-      <c r="F139" s="223"/>
-      <c r="G139" s="223"/>
-      <c r="H139" s="223"/>
-      <c r="I139" s="223"/>
-      <c r="J139" s="223"/>
-      <c r="K139" s="223"/>
-      <c r="L139" s="223"/>
-      <c r="M139" s="223"/>
-      <c r="N139" s="223"/>
+      <c r="C139" s="243"/>
+      <c r="D139" s="243"/>
+      <c r="E139" s="243"/>
+      <c r="F139" s="243"/>
+      <c r="G139" s="243"/>
+      <c r="H139" s="243"/>
+      <c r="I139" s="243"/>
+      <c r="J139" s="243"/>
+      <c r="K139" s="243"/>
+      <c r="L139" s="243"/>
+      <c r="M139" s="243"/>
+      <c r="N139" s="243"/>
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C140" s="223"/>
-      <c r="D140" s="223"/>
-      <c r="E140" s="223"/>
-      <c r="F140" s="223"/>
-      <c r="G140" s="223"/>
-      <c r="H140" s="223"/>
-      <c r="I140" s="223"/>
-      <c r="J140" s="223"/>
-      <c r="K140" s="223"/>
-      <c r="L140" s="223"/>
-      <c r="M140" s="223"/>
-      <c r="N140" s="223"/>
+      <c r="C140" s="243"/>
+      <c r="D140" s="243"/>
+      <c r="E140" s="243"/>
+      <c r="F140" s="243"/>
+      <c r="G140" s="243"/>
+      <c r="H140" s="243"/>
+      <c r="I140" s="243"/>
+      <c r="J140" s="243"/>
+      <c r="K140" s="243"/>
+      <c r="L140" s="243"/>
+      <c r="M140" s="243"/>
+      <c r="N140" s="243"/>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C141" s="223"/>
-      <c r="D141" s="223"/>
-      <c r="E141" s="223"/>
-      <c r="F141" s="223"/>
-      <c r="G141" s="223"/>
-      <c r="H141" s="223"/>
-      <c r="I141" s="223"/>
-      <c r="J141" s="223"/>
-      <c r="K141" s="223"/>
-      <c r="L141" s="223"/>
-      <c r="M141" s="223"/>
-      <c r="N141" s="223"/>
+      <c r="C141" s="243"/>
+      <c r="D141" s="243"/>
+      <c r="E141" s="243"/>
+      <c r="F141" s="243"/>
+      <c r="G141" s="243"/>
+      <c r="H141" s="243"/>
+      <c r="I141" s="243"/>
+      <c r="J141" s="243"/>
+      <c r="K141" s="243"/>
+      <c r="L141" s="243"/>
+      <c r="M141" s="243"/>
+      <c r="N141" s="243"/>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C142" s="223"/>
-      <c r="D142" s="223"/>
-      <c r="E142" s="223"/>
-      <c r="F142" s="223"/>
-      <c r="G142" s="223"/>
-      <c r="H142" s="223"/>
-      <c r="I142" s="223"/>
-      <c r="J142" s="223"/>
-      <c r="K142" s="223"/>
-      <c r="L142" s="223"/>
-      <c r="M142" s="223"/>
-      <c r="N142" s="223"/>
+      <c r="C142" s="243"/>
+      <c r="D142" s="243"/>
+      <c r="E142" s="243"/>
+      <c r="F142" s="243"/>
+      <c r="G142" s="243"/>
+      <c r="H142" s="243"/>
+      <c r="I142" s="243"/>
+      <c r="J142" s="243"/>
+      <c r="K142" s="243"/>
+      <c r="L142" s="243"/>
+      <c r="M142" s="243"/>
+      <c r="N142" s="243"/>
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C143" s="223"/>
-      <c r="D143" s="223"/>
-      <c r="E143" s="223"/>
-      <c r="F143" s="223"/>
-      <c r="G143" s="223"/>
-      <c r="H143" s="223"/>
-      <c r="I143" s="223"/>
-      <c r="J143" s="223"/>
-      <c r="K143" s="223"/>
-      <c r="L143" s="223"/>
-      <c r="M143" s="223"/>
-      <c r="N143" s="223"/>
+      <c r="C143" s="243"/>
+      <c r="D143" s="243"/>
+      <c r="E143" s="243"/>
+      <c r="F143" s="243"/>
+      <c r="G143" s="243"/>
+      <c r="H143" s="243"/>
+      <c r="I143" s="243"/>
+      <c r="J143" s="243"/>
+      <c r="K143" s="243"/>
+      <c r="L143" s="243"/>
+      <c r="M143" s="243"/>
+      <c r="N143" s="243"/>
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C144" s="223"/>
-      <c r="D144" s="223"/>
-      <c r="E144" s="223"/>
-      <c r="F144" s="223"/>
-      <c r="G144" s="223"/>
-      <c r="H144" s="223"/>
-      <c r="I144" s="223"/>
-      <c r="J144" s="223"/>
-      <c r="K144" s="223"/>
-      <c r="L144" s="223"/>
-      <c r="M144" s="223"/>
-      <c r="N144" s="223"/>
+      <c r="C144" s="243"/>
+      <c r="D144" s="243"/>
+      <c r="E144" s="243"/>
+      <c r="F144" s="243"/>
+      <c r="G144" s="243"/>
+      <c r="H144" s="243"/>
+      <c r="I144" s="243"/>
+      <c r="J144" s="243"/>
+      <c r="K144" s="243"/>
+      <c r="L144" s="243"/>
+      <c r="M144" s="243"/>
+      <c r="N144" s="243"/>
     </row>
     <row r="145" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C145" s="223"/>
-      <c r="D145" s="223"/>
-      <c r="E145" s="223"/>
-      <c r="F145" s="223"/>
-      <c r="G145" s="223"/>
-      <c r="H145" s="223"/>
-      <c r="I145" s="223"/>
-      <c r="J145" s="223"/>
-      <c r="K145" s="223"/>
-      <c r="L145" s="223"/>
-      <c r="M145" s="223"/>
-      <c r="N145" s="223"/>
+      <c r="C145" s="243"/>
+      <c r="D145" s="243"/>
+      <c r="E145" s="243"/>
+      <c r="F145" s="243"/>
+      <c r="G145" s="243"/>
+      <c r="H145" s="243"/>
+      <c r="I145" s="243"/>
+      <c r="J145" s="243"/>
+      <c r="K145" s="243"/>
+      <c r="L145" s="243"/>
+      <c r="M145" s="243"/>
+      <c r="N145" s="243"/>
     </row>
     <row r="146" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="77"/>
@@ -12459,108 +12406,108 @@
       <c r="N147" s="77"/>
     </row>
     <row r="148" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C148" s="303" t="s">
+      <c r="C148" s="258" t="s">
         <v>259</v>
       </c>
-      <c r="D148" s="303"/>
-      <c r="E148" s="303"/>
-      <c r="F148" s="303"/>
-      <c r="G148" s="303"/>
-      <c r="H148" s="303"/>
-      <c r="I148" s="303"/>
-      <c r="J148" s="303"/>
-      <c r="K148" s="303"/>
-      <c r="L148" s="303"/>
-      <c r="M148" s="303"/>
-      <c r="N148" s="303"/>
+      <c r="D148" s="258"/>
+      <c r="E148" s="258"/>
+      <c r="F148" s="258"/>
+      <c r="G148" s="258"/>
+      <c r="H148" s="258"/>
+      <c r="I148" s="258"/>
+      <c r="J148" s="258"/>
+      <c r="K148" s="258"/>
+      <c r="L148" s="258"/>
+      <c r="M148" s="258"/>
+      <c r="N148" s="258"/>
     </row>
     <row r="149" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C149" s="303"/>
-      <c r="D149" s="303"/>
-      <c r="E149" s="303"/>
-      <c r="F149" s="303"/>
-      <c r="G149" s="303"/>
-      <c r="H149" s="303"/>
-      <c r="I149" s="303"/>
-      <c r="J149" s="303"/>
-      <c r="K149" s="303"/>
-      <c r="L149" s="303"/>
-      <c r="M149" s="303"/>
-      <c r="N149" s="303"/>
+      <c r="C149" s="258"/>
+      <c r="D149" s="258"/>
+      <c r="E149" s="258"/>
+      <c r="F149" s="258"/>
+      <c r="G149" s="258"/>
+      <c r="H149" s="258"/>
+      <c r="I149" s="258"/>
+      <c r="J149" s="258"/>
+      <c r="K149" s="258"/>
+      <c r="L149" s="258"/>
+      <c r="M149" s="258"/>
+      <c r="N149" s="258"/>
     </row>
     <row r="150" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C150" s="303"/>
-      <c r="D150" s="303"/>
-      <c r="E150" s="303"/>
-      <c r="F150" s="303"/>
-      <c r="G150" s="303"/>
-      <c r="H150" s="303"/>
-      <c r="I150" s="303"/>
-      <c r="J150" s="303"/>
-      <c r="K150" s="303"/>
-      <c r="L150" s="303"/>
-      <c r="M150" s="303"/>
-      <c r="N150" s="303"/>
+      <c r="C150" s="258"/>
+      <c r="D150" s="258"/>
+      <c r="E150" s="258"/>
+      <c r="F150" s="258"/>
+      <c r="G150" s="258"/>
+      <c r="H150" s="258"/>
+      <c r="I150" s="258"/>
+      <c r="J150" s="258"/>
+      <c r="K150" s="258"/>
+      <c r="L150" s="258"/>
+      <c r="M150" s="258"/>
+      <c r="N150" s="258"/>
       <c r="P150" s="84">
         <f>L1-K133</f>
         <v>-3118989.9373000227</v>
       </c>
     </row>
     <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="303"/>
-      <c r="D151" s="303"/>
-      <c r="E151" s="303"/>
-      <c r="F151" s="303"/>
-      <c r="G151" s="303"/>
-      <c r="H151" s="303"/>
-      <c r="I151" s="303"/>
-      <c r="J151" s="303"/>
-      <c r="K151" s="303"/>
-      <c r="L151" s="303"/>
-      <c r="M151" s="303"/>
-      <c r="N151" s="303"/>
+      <c r="C151" s="258"/>
+      <c r="D151" s="258"/>
+      <c r="E151" s="258"/>
+      <c r="F151" s="258"/>
+      <c r="G151" s="258"/>
+      <c r="H151" s="258"/>
+      <c r="I151" s="258"/>
+      <c r="J151" s="258"/>
+      <c r="K151" s="258"/>
+      <c r="L151" s="258"/>
+      <c r="M151" s="258"/>
+      <c r="N151" s="258"/>
     </row>
     <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="303"/>
-      <c r="D152" s="303"/>
-      <c r="E152" s="303"/>
-      <c r="F152" s="303"/>
-      <c r="G152" s="303"/>
-      <c r="H152" s="303"/>
-      <c r="I152" s="303"/>
-      <c r="J152" s="303"/>
-      <c r="K152" s="303"/>
-      <c r="L152" s="303"/>
-      <c r="M152" s="303"/>
-      <c r="N152" s="303"/>
+      <c r="C152" s="258"/>
+      <c r="D152" s="258"/>
+      <c r="E152" s="258"/>
+      <c r="F152" s="258"/>
+      <c r="G152" s="258"/>
+      <c r="H152" s="258"/>
+      <c r="I152" s="258"/>
+      <c r="J152" s="258"/>
+      <c r="K152" s="258"/>
+      <c r="L152" s="258"/>
+      <c r="M152" s="258"/>
+      <c r="N152" s="258"/>
     </row>
     <row r="153" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="303"/>
-      <c r="D153" s="303"/>
-      <c r="E153" s="303"/>
-      <c r="F153" s="303"/>
-      <c r="G153" s="303"/>
-      <c r="H153" s="303"/>
-      <c r="I153" s="303"/>
-      <c r="J153" s="303"/>
-      <c r="K153" s="303"/>
-      <c r="L153" s="303"/>
-      <c r="M153" s="303"/>
-      <c r="N153" s="303"/>
+      <c r="C153" s="258"/>
+      <c r="D153" s="258"/>
+      <c r="E153" s="258"/>
+      <c r="F153" s="258"/>
+      <c r="G153" s="258"/>
+      <c r="H153" s="258"/>
+      <c r="I153" s="258"/>
+      <c r="J153" s="258"/>
+      <c r="K153" s="258"/>
+      <c r="L153" s="258"/>
+      <c r="M153" s="258"/>
+      <c r="N153" s="258"/>
     </row>
     <row r="154" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="303"/>
-      <c r="D154" s="303"/>
-      <c r="E154" s="303"/>
-      <c r="F154" s="303"/>
-      <c r="G154" s="303"/>
-      <c r="H154" s="303"/>
-      <c r="I154" s="303"/>
-      <c r="J154" s="303"/>
-      <c r="K154" s="303"/>
-      <c r="L154" s="303"/>
-      <c r="M154" s="303"/>
-      <c r="N154" s="303"/>
+      <c r="C154" s="258"/>
+      <c r="D154" s="258"/>
+      <c r="E154" s="258"/>
+      <c r="F154" s="258"/>
+      <c r="G154" s="258"/>
+      <c r="H154" s="258"/>
+      <c r="I154" s="258"/>
+      <c r="J154" s="258"/>
+      <c r="K154" s="258"/>
+      <c r="L154" s="258"/>
+      <c r="M154" s="258"/>
+      <c r="N154" s="258"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -12602,414 +12549,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0166F049-50A4-4ACA-9F6E-1C2F2AD24458}">
-  <dimension ref="A2:J27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="11.5703125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C3" s="271" t="str">
-        <f>RESUMEN!C5</f>
-        <v>PERÍODO: ENERO</v>
-      </c>
-      <c r="D3" s="272"/>
-      <c r="E3" s="272"/>
-      <c r="F3" s="272" t="s">
-        <v>235</v>
-      </c>
-      <c r="G3" s="272"/>
-      <c r="H3" s="272"/>
-      <c r="I3" s="272"/>
-      <c r="J3" s="273"/>
-    </row>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C4" s="1"/>
-      <c r="J4" s="183"/>
-    </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C5" s="1" t="str">
-        <f>RESUMEN!A26</f>
-        <v xml:space="preserve">Haberes </v>
-      </c>
-      <c r="G5" s="43">
-        <f>RESUMEN!D26</f>
-        <v>1124512</v>
-      </c>
-      <c r="H5" s="269" t="s">
-        <v>323</v>
-      </c>
-      <c r="I5" s="269"/>
-      <c r="J5" s="270"/>
-    </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C6" s="1" t="str">
-        <f>RESUMEN!A27</f>
-        <v>Plus pileta</v>
-      </c>
-      <c r="G6" s="43">
-        <f>RESUMEN!D27</f>
-        <v>39622.699999999997</v>
-      </c>
-      <c r="H6" s="269" t="s">
-        <v>324</v>
-      </c>
-      <c r="I6" s="269"/>
-      <c r="J6" s="270"/>
-    </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C7" s="1" t="str">
-        <f>RESUMEN!A28</f>
-        <v>Plus retiro de basura</v>
-      </c>
-      <c r="G7" s="43">
-        <f>RESUMEN!D28</f>
-        <v>138080</v>
-      </c>
-      <c r="H7" s="269"/>
-      <c r="I7" s="269"/>
-      <c r="J7" s="270"/>
-    </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C8" s="1" t="str">
-        <f>RESUMEN!A29</f>
-        <v>Plus cochera</v>
-      </c>
-      <c r="G8" s="43">
-        <f>RESUMEN!D29</f>
-        <v>23553.4</v>
-      </c>
-      <c r="J8" s="183"/>
-    </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C9" s="1" t="str">
-        <f>RESUMEN!A30</f>
-        <v>Adicional Viaticos</v>
-      </c>
-      <c r="G9" s="43">
-        <f>RESUMEN!D30</f>
-        <v>65596.5</v>
-      </c>
-      <c r="H9" s="269" t="s">
-        <v>325</v>
-      </c>
-      <c r="I9" s="269"/>
-      <c r="J9" s="270"/>
-    </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C10" s="1" t="str">
-        <f>RESUMEN!A31</f>
-        <v>Adicional remuneracion</v>
-      </c>
-      <c r="G10" s="43">
-        <f>RESUMEN!D31</f>
-        <v>120000</v>
-      </c>
-      <c r="H10" s="269" t="s">
-        <v>324</v>
-      </c>
-      <c r="I10" s="269"/>
-      <c r="J10" s="270"/>
-    </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C11" s="1"/>
-      <c r="H11" s="269"/>
-      <c r="I11" s="269"/>
-      <c r="J11" s="270"/>
-    </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C12" s="186" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="187">
-        <f>SUM(G5:G11)</f>
-        <v>1511364.5999999999</v>
-      </c>
-      <c r="J12" s="183"/>
-    </row>
-    <row r="13" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="188"/>
-      <c r="D13" s="189"/>
-      <c r="E13" s="189"/>
-      <c r="F13" s="189"/>
-      <c r="G13" s="189"/>
-      <c r="H13" s="189"/>
-      <c r="I13" s="189"/>
-      <c r="J13" s="190"/>
-    </row>
-    <row r="15" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C16" s="271" t="str">
-        <f>C3</f>
-        <v>PERÍODO: ENERO</v>
-      </c>
-      <c r="D16" s="272"/>
-      <c r="E16" s="272"/>
-      <c r="F16" s="272" t="s">
-        <v>234</v>
-      </c>
-      <c r="G16" s="272"/>
-      <c r="H16" s="272"/>
-      <c r="I16" s="272"/>
-      <c r="J16" s="273"/>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C17" s="1"/>
-      <c r="J17" s="183"/>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C18" s="1"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="269" t="s">
-        <v>323</v>
-      </c>
-      <c r="I18" s="269"/>
-      <c r="J18" s="270"/>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C19" s="1" t="str">
-        <f>RESUMEN!A35</f>
-        <v xml:space="preserve">Haberes </v>
-      </c>
-      <c r="G19" s="43">
-        <f>RESUMEN!D35</f>
-        <v>562256</v>
-      </c>
-      <c r="H19" s="269" t="s">
-        <v>324</v>
-      </c>
-      <c r="I19" s="269"/>
-      <c r="J19" s="270"/>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C20" s="1" t="e">
-        <f>RESUMEN!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G20" s="43" t="e">
-        <f>RESUMEN!#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="H20" s="269"/>
-      <c r="I20" s="269"/>
-      <c r="J20" s="270"/>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C21" s="1" t="str">
-        <f>RESUMEN!A36</f>
-        <v>Plus pileta</v>
-      </c>
-      <c r="G21" s="43">
-        <f>RESUMEN!D36</f>
-        <v>39622.699999999997</v>
-      </c>
-      <c r="J21" s="183"/>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C22" s="1" t="str">
-        <f>RESUMEN!A37</f>
-        <v>Plus retiro de basura</v>
-      </c>
-      <c r="G22" s="43">
-        <f>RESUMEN!D37</f>
-        <v>138080</v>
-      </c>
-      <c r="H22" s="269" t="s">
-        <v>325</v>
-      </c>
-      <c r="I22" s="269"/>
-      <c r="J22" s="270"/>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C23" s="1" t="str">
-        <f>RESUMEN!A38</f>
-        <v>Plus cochera</v>
-      </c>
-      <c r="G23" s="43">
-        <f>RESUMEN!D38</f>
-        <v>23553.4</v>
-      </c>
-      <c r="H23" s="269" t="s">
-        <v>324</v>
-      </c>
-      <c r="I23" s="269"/>
-      <c r="J23" s="270"/>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C24" s="1" t="str">
-        <f>RESUMEN!A39</f>
-        <v>Adicional Viaticos</v>
-      </c>
-      <c r="G24" s="43">
-        <f>RESUMEN!D39</f>
-        <v>65596.5</v>
-      </c>
-      <c r="H24" s="269"/>
-      <c r="I24" s="269"/>
-      <c r="J24" s="270"/>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C25" s="1" t="str">
-        <f>RESUMEN!A40</f>
-        <v>Adicional remuneracion</v>
-      </c>
-      <c r="G25" s="43">
-        <f>RESUMEN!D40</f>
-        <v>60000</v>
-      </c>
-      <c r="H25" s="184"/>
-      <c r="I25" s="184"/>
-      <c r="J25" s="185"/>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C26" s="186" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="187" t="e">
-        <f>SUM(G18:G25)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J26" s="183"/>
-    </row>
-    <row r="27" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="188"/>
-      <c r="D27" s="189"/>
-      <c r="E27" s="189"/>
-      <c r="F27" s="189"/>
-      <c r="G27" s="189"/>
-      <c r="H27" s="189"/>
-      <c r="I27" s="189"/>
-      <c r="J27" s="190"/>
-    </row>
-  </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="H23:J24"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H6:J7"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="H10:J11"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J20"/>
-    <mergeCell ref="H22:J22"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A8B3D07-243A-48F3-942B-AB44D486DEC8}">
-  <dimension ref="C4:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C4" s="274" t="s">
-        <v>282</v>
-      </c>
-      <c r="D4" s="274"/>
-    </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C5" s="136">
-        <v>52141.08</v>
-      </c>
-      <c r="D5" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C6" s="136">
-        <v>67140.100000000006</v>
-      </c>
-      <c r="D6" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C7" s="136">
-        <v>52121.11</v>
-      </c>
-      <c r="D7" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C8" s="136">
-        <v>67885.119999999995</v>
-      </c>
-      <c r="D8" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C9" s="136">
-        <v>67140.160000000003</v>
-      </c>
-      <c r="D9" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C10" s="136">
-        <v>62141.17</v>
-      </c>
-      <c r="D10" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C11" s="136">
-        <v>67855.179999999993</v>
-      </c>
-      <c r="D11" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C12" s="136">
-        <v>62141.23</v>
-      </c>
-      <c r="D12" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C13" s="136">
-        <v>67855.240000000005</v>
-      </c>
-      <c r="D13" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C14" s="136">
-        <f>SUM(C5:C13)</f>
-        <v>566420.39</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C4:D4"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/2026/EL MIRADOR/ENERO/Enero - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/ENERO/Enero - EL MIRADOR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\EL MIRADOR\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EE2876-5846-482B-AAA6-4B4CF02FF30C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF72D4D-D25C-427A-AEDC-1E1368733602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="367">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1129,10 +1129,13 @@
     <t>Pendiente mes de febrer0 el 02/02 se debito federacional patronal</t>
   </si>
   <si>
-    <t>Las casillas coloreadas en la columna Gastos Par/SUM de color rojo corresponden a multas aplicadas por el uso del SUM. En consecuencia, la unidad funcional involucrada no podrá acceder al uso del mismo por tiempo indeterminado. Por otro lado, las casillas coloreadas en amarillo, corresponden a llaves.</t>
-  </si>
-  <si>
     <t>Diferencia en Factura de Articulos de limpieza (Mes anterior) con monto erroneo</t>
+  </si>
+  <si>
+    <t>Las casillas coloreadas en la columna Gastos Par/SUM de color rojo corresponden a multas aplicadas por el uso del SUM. En consecuencia, la unidad funcional involucrada no podrá acceder al uso del mismo por tiempo indeterminado. Por otro lado, las casillas coloreadas en amarillo, corresponden a llaves y las verdes corresponden al mal uso del coworking.</t>
+  </si>
+  <si>
+    <t>Lorenzo, Sergio</t>
   </si>
 </sst>
 </file>
@@ -1318,7 +1321,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1400,6 +1403,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1755,7 +1764,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="290">
+  <cellXfs count="283">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1969,13 +1978,6 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="11" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="11" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2019,7 +2021,6 @@
     <xf numFmtId="44" fontId="1" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="1" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="1" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="1" fillId="10" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2089,26 +2090,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2206,6 +2195,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="15" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -2572,24 +2574,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R160"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="6" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="112"/>
       <c r="B1" s="121"/>
       <c r="C1" s="129" t="s">
@@ -2603,7 +2605,7 @@
       <c r="I1" s="110"/>
       <c r="J1" s="111"/>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="113"/>
       <c r="B2" s="122"/>
       <c r="C2" s="122" t="s">
@@ -2617,7 +2619,7 @@
       <c r="I2" s="123"/>
       <c r="J2" s="109"/>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="113"/>
       <c r="B3" s="122"/>
       <c r="C3" s="122" t="s">
@@ -2633,7 +2635,7 @@
       <c r="I3" s="123"/>
       <c r="J3" s="109"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="113"/>
       <c r="B4" s="122"/>
       <c r="C4" s="122" t="s">
@@ -2647,7 +2649,7 @@
       <c r="I4" s="123"/>
       <c r="J4" s="109"/>
     </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="117"/>
       <c r="B5" s="122"/>
       <c r="C5" s="122" t="s">
@@ -2663,7 +2665,7 @@
       <c r="I5" s="122"/>
       <c r="J5" s="118"/>
     </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="117"/>
       <c r="B6" s="122"/>
       <c r="C6" s="122" t="s">
@@ -2677,7 +2679,7 @@
       <c r="I6" s="122"/>
       <c r="J6" s="118"/>
     </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="119"/>
       <c r="B7" s="120"/>
       <c r="C7" s="120"/>
@@ -2689,118 +2691,118 @@
       <c r="I7" s="120"/>
       <c r="J7" s="124"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="233" t="s">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="225" t="s">
         <v>260</v>
       </c>
-      <c r="B14" s="233"/>
-      <c r="C14" s="233"/>
-      <c r="D14" s="233"/>
-      <c r="E14" s="233"/>
-      <c r="F14" s="233"/>
-      <c r="G14" s="233"/>
-      <c r="H14" s="233"/>
-      <c r="I14" s="233"/>
-      <c r="J14" s="233"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="233"/>
-      <c r="B15" s="233"/>
-      <c r="C15" s="233"/>
-      <c r="D15" s="233"/>
-      <c r="E15" s="233"/>
-      <c r="F15" s="233"/>
-      <c r="G15" s="233"/>
-      <c r="H15" s="233"/>
-      <c r="I15" s="233"/>
-      <c r="J15" s="233"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="233"/>
-      <c r="B16" s="233"/>
-      <c r="C16" s="233"/>
-      <c r="D16" s="233"/>
-      <c r="E16" s="233"/>
-      <c r="F16" s="233"/>
-      <c r="G16" s="233"/>
-      <c r="H16" s="233"/>
-      <c r="I16" s="233"/>
-      <c r="J16" s="233"/>
-    </row>
-    <row r="17" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="233"/>
-      <c r="B17" s="233"/>
-      <c r="C17" s="233"/>
-      <c r="D17" s="233"/>
-      <c r="E17" s="233"/>
-      <c r="F17" s="233"/>
-      <c r="G17" s="233"/>
-      <c r="H17" s="233"/>
-      <c r="I17" s="233"/>
-      <c r="J17" s="233"/>
-    </row>
-    <row r="18" spans="1:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="233"/>
-      <c r="B18" s="233"/>
-      <c r="C18" s="233"/>
-      <c r="D18" s="233"/>
-      <c r="E18" s="233"/>
-      <c r="F18" s="233"/>
-      <c r="G18" s="233"/>
-      <c r="H18" s="233"/>
-      <c r="I18" s="233"/>
-      <c r="J18" s="233"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="225"/>
+      <c r="C14" s="225"/>
+      <c r="D14" s="225"/>
+      <c r="E14" s="225"/>
+      <c r="F14" s="225"/>
+      <c r="G14" s="225"/>
+      <c r="H14" s="225"/>
+      <c r="I14" s="225"/>
+      <c r="J14" s="225"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="225"/>
+      <c r="B15" s="225"/>
+      <c r="C15" s="225"/>
+      <c r="D15" s="225"/>
+      <c r="E15" s="225"/>
+      <c r="F15" s="225"/>
+      <c r="G15" s="225"/>
+      <c r="H15" s="225"/>
+      <c r="I15" s="225"/>
+      <c r="J15" s="225"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="225"/>
+      <c r="B16" s="225"/>
+      <c r="C16" s="225"/>
+      <c r="D16" s="225"/>
+      <c r="E16" s="225"/>
+      <c r="F16" s="225"/>
+      <c r="G16" s="225"/>
+      <c r="H16" s="225"/>
+      <c r="I16" s="225"/>
+      <c r="J16" s="225"/>
+    </row>
+    <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="225"/>
+      <c r="B17" s="225"/>
+      <c r="C17" s="225"/>
+      <c r="D17" s="225"/>
+      <c r="E17" s="225"/>
+      <c r="F17" s="225"/>
+      <c r="G17" s="225"/>
+      <c r="H17" s="225"/>
+      <c r="I17" s="225"/>
+      <c r="J17" s="225"/>
+    </row>
+    <row r="18" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="225"/>
+      <c r="B18" s="225"/>
+      <c r="C18" s="225"/>
+      <c r="D18" s="225"/>
+      <c r="E18" s="225"/>
+      <c r="F18" s="225"/>
+      <c r="G18" s="225"/>
+      <c r="H18" s="225"/>
+      <c r="I18" s="225"/>
+      <c r="J18" s="225"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="H19" s="94"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="242" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="234" t="s">
         <v>324</v>
       </c>
-      <c r="B20" s="242"/>
-      <c r="C20" s="242"/>
-      <c r="D20" s="242"/>
-      <c r="E20" s="242"/>
-      <c r="F20" s="242"/>
-      <c r="G20" s="242"/>
-      <c r="H20" s="242"/>
-      <c r="I20" s="242"/>
-      <c r="J20" s="242"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="242"/>
-      <c r="B21" s="242"/>
-      <c r="C21" s="242"/>
-      <c r="D21" s="242"/>
-      <c r="E21" s="242"/>
-      <c r="F21" s="242"/>
-      <c r="G21" s="242"/>
-      <c r="H21" s="242"/>
-      <c r="I21" s="242"/>
-      <c r="J21" s="242"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="242"/>
-      <c r="B22" s="242"/>
-      <c r="C22" s="242"/>
-      <c r="D22" s="242"/>
-      <c r="E22" s="242"/>
-      <c r="F22" s="242"/>
-      <c r="G22" s="242"/>
-      <c r="H22" s="242"/>
-      <c r="I22" s="242"/>
-      <c r="J22" s="242"/>
-    </row>
-    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="234"/>
+      <c r="C20" s="234"/>
+      <c r="D20" s="234"/>
+      <c r="E20" s="234"/>
+      <c r="F20" s="234"/>
+      <c r="G20" s="234"/>
+      <c r="H20" s="234"/>
+      <c r="I20" s="234"/>
+      <c r="J20" s="234"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="234"/>
+      <c r="B21" s="234"/>
+      <c r="C21" s="234"/>
+      <c r="D21" s="234"/>
+      <c r="E21" s="234"/>
+      <c r="F21" s="234"/>
+      <c r="G21" s="234"/>
+      <c r="H21" s="234"/>
+      <c r="I21" s="234"/>
+      <c r="J21" s="234"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="234"/>
+      <c r="B22" s="234"/>
+      <c r="C22" s="234"/>
+      <c r="D22" s="234"/>
+      <c r="E22" s="234"/>
+      <c r="F22" s="234"/>
+      <c r="G22" s="234"/>
+      <c r="H22" s="234"/>
+      <c r="I22" s="234"/>
+      <c r="J22" s="234"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="94"/>
     </row>
-    <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
         <v>19</v>
       </c>
@@ -2826,7 +2828,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="50" t="s">
         <v>235</v>
       </c>
@@ -2840,13 +2842,13 @@
       <c r="I25" s="95"/>
       <c r="J25" s="95"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
-      <c r="D26" s="221">
+      <c r="D26" s="213">
         <v>1124512</v>
       </c>
       <c r="E26" s="58"/>
@@ -2856,13 +2858,13 @@
       <c r="I26" s="58"/>
       <c r="J26" s="58"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>238</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
-      <c r="D27" s="221">
+      <c r="D27" s="213">
         <v>39622.699999999997</v>
       </c>
       <c r="E27" s="58"/>
@@ -2872,13 +2874,13 @@
       <c r="I27" s="58"/>
       <c r="J27" s="58"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>236</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
-      <c r="D28" s="221">
+      <c r="D28" s="213">
         <f>1726*80</f>
         <v>138080</v>
       </c>
@@ -2889,13 +2891,13 @@
       <c r="I28" s="58"/>
       <c r="J28" s="58"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>237</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
-      <c r="D29" s="221">
+      <c r="D29" s="213">
         <v>23553.4</v>
       </c>
       <c r="E29" s="58"/>
@@ -2905,13 +2907,13 @@
       <c r="I29" s="58"/>
       <c r="J29" s="58"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>298</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
-      <c r="D30" s="221">
+      <c r="D30" s="213">
         <v>65596.5</v>
       </c>
       <c r="E30" s="58"/>
@@ -2921,13 +2923,13 @@
       <c r="I30" s="58"/>
       <c r="J30" s="58"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>239</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
-      <c r="D31" s="221">
+      <c r="D31" s="213">
         <v>120000</v>
       </c>
       <c r="E31" s="58"/>
@@ -2937,13 +2939,13 @@
       <c r="I31" s="58"/>
       <c r="J31" s="58"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>338</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
-      <c r="D32" s="221">
+      <c r="D32" s="213">
         <v>-44192.27</v>
       </c>
       <c r="E32" s="58"/>
@@ -2953,13 +2955,13 @@
       <c r="I32" s="58"/>
       <c r="J32" s="58"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="93" t="s">
         <v>168</v>
       </c>
       <c r="B33" s="91"/>
       <c r="C33" s="91"/>
-      <c r="D33" s="222">
+      <c r="D33" s="214">
         <f>SUM(D26:D32)</f>
         <v>1467172.3299999998</v>
       </c>
@@ -2970,13 +2972,13 @@
       <c r="I33" s="92"/>
       <c r="J33" s="92"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="50" t="s">
         <v>234</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
-      <c r="D34" s="223"/>
+      <c r="D34" s="215"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
@@ -2984,13 +2986,13 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>43</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
-      <c r="D35" s="221">
+      <c r="D35" s="213">
         <v>562256</v>
       </c>
       <c r="E35" s="58"/>
@@ -3000,13 +3002,13 @@
       <c r="I35" s="58"/>
       <c r="J35" s="58"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>238</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
-      <c r="D36" s="221">
+      <c r="D36" s="213">
         <f>D27</f>
         <v>39622.699999999997</v>
       </c>
@@ -3017,13 +3019,13 @@
       <c r="I36" s="58"/>
       <c r="J36" s="58"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>236</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
-      <c r="D37" s="221">
+      <c r="D37" s="213">
         <f>D28</f>
         <v>138080</v>
       </c>
@@ -3034,13 +3036,13 @@
       <c r="I37" s="58"/>
       <c r="J37" s="58"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>237</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
-      <c r="D38" s="221">
+      <c r="D38" s="213">
         <f>D29</f>
         <v>23553.4</v>
       </c>
@@ -3051,13 +3053,13 @@
       <c r="I38" s="58"/>
       <c r="J38" s="58"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>298</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
-      <c r="D39" s="221">
+      <c r="D39" s="213">
         <f>D30</f>
         <v>65596.5</v>
       </c>
@@ -3068,13 +3070,13 @@
       <c r="I39" s="58"/>
       <c r="J39" s="58"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>239</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
-      <c r="D40" s="221">
+      <c r="D40" s="213">
         <v>60000</v>
       </c>
       <c r="E40" s="58"/>
@@ -3084,13 +3086,13 @@
       <c r="I40" s="58"/>
       <c r="J40" s="58"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>339</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
-      <c r="D41" s="221">
+      <c r="D41" s="213">
         <v>-101801.65</v>
       </c>
       <c r="E41" s="58"/>
@@ -3100,13 +3102,13 @@
       <c r="I41" s="58"/>
       <c r="J41" s="58"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="93" t="s">
         <v>168</v>
       </c>
       <c r="B42" s="91"/>
       <c r="C42" s="91"/>
-      <c r="D42" s="222">
+      <c r="D42" s="214">
         <f>SUM(D35:D41)</f>
         <v>787306.95</v>
       </c>
@@ -3117,13 +3119,13 @@
       <c r="I42" s="92"/>
       <c r="J42" s="92"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="33" t="s">
         <v>1</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="33"/>
-      <c r="D43" s="224">
+      <c r="D43" s="216">
         <f>D33+D42</f>
         <v>2254479.2799999998</v>
       </c>
@@ -3160,13 +3162,13 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="32" t="s">
         <v>340</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
-      <c r="D44" s="225">
+      <c r="D44" s="217">
         <v>254504.03</v>
       </c>
       <c r="E44" s="58"/>
@@ -3177,11 +3179,11 @@
       <c r="J44" s="58"/>
       <c r="L44" s="69"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="32"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
-      <c r="D45" s="221"/>
+      <c r="D45" s="213"/>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
@@ -3190,13 +3192,13 @@
       <c r="J45" s="6"/>
       <c r="L45" s="69"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="33" t="s">
         <v>38</v>
       </c>
       <c r="B46" s="33"/>
       <c r="C46" s="33"/>
-      <c r="D46" s="224">
+      <c r="D46" s="216">
         <f>SUM(D44:D44)</f>
         <v>254504.03</v>
       </c>
@@ -3233,13 +3235,13 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="32" t="s">
         <v>249</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
-      <c r="D47" s="225"/>
+      <c r="D47" s="217"/>
       <c r="E47" s="58">
         <f>D47*91.91%</f>
         <v>0</v>
@@ -3251,15 +3253,15 @@
       <c r="J47" s="58"/>
       <c r="L47" s="69"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>341</v>
       </c>
       <c r="B48" s="6"/>
-      <c r="C48" s="202">
+      <c r="C48" s="195">
         <v>46024</v>
       </c>
-      <c r="D48" s="221">
+      <c r="D48" s="213">
         <v>71000</v>
       </c>
       <c r="E48" s="58">
@@ -3273,15 +3275,15 @@
       <c r="J48" s="58"/>
       <c r="L48" s="69"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>341</v>
       </c>
       <c r="B49" s="6"/>
-      <c r="C49" s="202">
+      <c r="C49" s="195">
         <v>46024</v>
       </c>
-      <c r="D49" s="221">
+      <c r="D49" s="213">
         <v>71000</v>
       </c>
       <c r="E49" s="58">
@@ -3295,15 +3297,15 @@
       <c r="J49" s="58"/>
       <c r="L49" s="69"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>341</v>
       </c>
       <c r="B50" s="6"/>
-      <c r="C50" s="202">
+      <c r="C50" s="195">
         <v>46024</v>
       </c>
-      <c r="D50" s="221">
+      <c r="D50" s="213">
         <v>36025</v>
       </c>
       <c r="E50" s="58">
@@ -3317,15 +3319,15 @@
       <c r="J50" s="58"/>
       <c r="L50" s="69"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>341</v>
       </c>
       <c r="B51" s="6"/>
-      <c r="C51" s="202">
+      <c r="C51" s="195">
         <v>46024</v>
       </c>
-      <c r="D51" s="221">
+      <c r="D51" s="213">
         <v>78006.05</v>
       </c>
       <c r="E51" s="58">
@@ -3339,15 +3341,15 @@
       <c r="J51" s="58"/>
       <c r="L51" s="69"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>341</v>
       </c>
       <c r="B52" s="6"/>
-      <c r="C52" s="202">
+      <c r="C52" s="195">
         <v>46025</v>
       </c>
-      <c r="D52" s="221">
+      <c r="D52" s="213">
         <v>37040</v>
       </c>
       <c r="E52" s="58">
@@ -3361,11 +3363,11 @@
       <c r="J52" s="58"/>
       <c r="L52" s="69"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
-      <c r="D53" s="221"/>
+      <c r="D53" s="213"/>
       <c r="E53" s="58"/>
       <c r="F53" s="58"/>
       <c r="G53" s="58"/>
@@ -3374,13 +3376,13 @@
       <c r="J53" s="58"/>
       <c r="L53" s="69"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="33" t="s">
         <v>17</v>
       </c>
       <c r="B54" s="33"/>
       <c r="C54" s="33"/>
-      <c r="D54" s="224">
+      <c r="D54" s="216">
         <f>SUM(D48:D53)</f>
         <v>293071.05</v>
       </c>
@@ -3402,13 +3404,13 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="32" t="s">
         <v>244</v>
       </c>
       <c r="B55" s="35"/>
       <c r="C55" s="35"/>
-      <c r="D55" s="221"/>
+      <c r="D55" s="213"/>
       <c r="E55" s="49"/>
       <c r="F55" s="49"/>
       <c r="G55" s="49"/>
@@ -3417,13 +3419,13 @@
       <c r="J55" s="49"/>
       <c r="L55" s="69"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="35" t="s">
         <v>247</v>
       </c>
       <c r="B56" s="35"/>
       <c r="C56" s="35"/>
-      <c r="D56" s="221"/>
+      <c r="D56" s="213"/>
       <c r="E56" s="49"/>
       <c r="F56" s="49"/>
       <c r="G56" s="49"/>
@@ -3432,7 +3434,7 @@
       <c r="J56" s="49"/>
       <c r="L56" s="69"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="35" t="s">
         <v>248</v>
       </c>
@@ -3442,7 +3444,7 @@
       <c r="C57" s="35" t="s">
         <v>316</v>
       </c>
-      <c r="D57" s="221">
+      <c r="D57" s="213">
         <v>249469</v>
       </c>
       <c r="E57" s="49"/>
@@ -3453,7 +3455,7 @@
       <c r="J57" s="49"/>
       <c r="L57" s="69"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="35" t="s">
         <v>248</v>
       </c>
@@ -3463,7 +3465,7 @@
       <c r="C58" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="D58" s="221">
+      <c r="D58" s="213">
         <v>249469</v>
       </c>
       <c r="E58" s="49"/>
@@ -3474,13 +3476,13 @@
       <c r="J58" s="49"/>
       <c r="L58" s="69"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="33" t="s">
         <v>246</v>
       </c>
       <c r="B59" s="33"/>
       <c r="C59" s="33"/>
-      <c r="D59" s="226">
+      <c r="D59" s="218">
         <f>SUM(D56:D58)</f>
         <v>498938</v>
       </c>
@@ -3517,13 +3519,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="32" t="s">
         <v>2</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
-      <c r="D60" s="215"/>
+      <c r="D60" s="208"/>
       <c r="E60" s="45"/>
       <c r="F60" s="45"/>
       <c r="G60" s="45"/>
@@ -3532,7 +3534,7 @@
       <c r="J60" s="6"/>
       <c r="L60" s="69"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
         <v>240</v>
       </c>
@@ -3540,7 +3542,7 @@
       <c r="C61" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="D61" s="215">
+      <c r="D61" s="208">
         <v>56231.41</v>
       </c>
       <c r="E61" s="114"/>
@@ -3551,7 +3553,7 @@
       <c r="J61" s="6"/>
       <c r="L61" s="69"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>282</v>
       </c>
@@ -3559,7 +3561,7 @@
       <c r="C62" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="D62" s="215">
+      <c r="D62" s="208">
         <v>64941</v>
       </c>
       <c r="E62" s="114"/>
@@ -3570,17 +3572,17 @@
       <c r="J62" s="6"/>
       <c r="L62" s="69"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>282</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="C63" s="191" t="s">
+      <c r="C63" s="184" t="s">
         <v>337</v>
       </c>
-      <c r="D63" s="215">
+      <c r="D63" s="208">
         <v>64941</v>
       </c>
       <c r="E63" s="75"/>
@@ -3591,13 +3593,13 @@
       <c r="J63" s="6"/>
       <c r="L63" s="69"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="33" t="s">
         <v>245</v>
       </c>
       <c r="B64" s="33"/>
       <c r="C64" s="33"/>
-      <c r="D64" s="224">
+      <c r="D64" s="216">
         <f>SUM(D60:D63)</f>
         <v>186113.41</v>
       </c>
@@ -3634,13 +3636,13 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="32" t="s">
         <v>227</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
-      <c r="D65" s="227"/>
+      <c r="D65" s="219"/>
       <c r="E65" s="46"/>
       <c r="F65" s="46"/>
       <c r="G65" s="46"/>
@@ -3649,7 +3651,7 @@
       <c r="J65" s="36"/>
       <c r="L65" s="69"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>231</v>
       </c>
@@ -3657,7 +3659,7 @@
       <c r="C66" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="D66" s="215">
+      <c r="D66" s="208">
         <v>160913</v>
       </c>
       <c r="E66" s="58">
@@ -3690,15 +3692,15 @@
       </c>
       <c r="L66" s="69"/>
     </row>
-    <row r="67" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="244" t="s">
+    <row r="67" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="236" t="s">
         <v>232</v>
       </c>
-      <c r="B67" s="245"/>
+      <c r="B67" s="237"/>
       <c r="C67" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="D67" s="215">
+      <c r="D67" s="208">
         <v>7907</v>
       </c>
       <c r="E67" s="58">
@@ -3729,19 +3731,19 @@
         <f t="shared" ref="K67:K68" si="2">SUM(E67:J67)</f>
         <v>7907</v>
       </c>
-      <c r="L67" s="214" t="s">
+      <c r="L67" s="207" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="244" t="s">
+    <row r="68" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="236" t="s">
         <v>233</v>
       </c>
-      <c r="B68" s="245"/>
+      <c r="B68" s="237"/>
       <c r="C68" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="D68" s="215">
+      <c r="D68" s="208">
         <v>7907</v>
       </c>
       <c r="E68" s="58">
@@ -3774,13 +3776,13 @@
       </c>
       <c r="L68" s="69"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="33" t="s">
         <v>3</v>
       </c>
       <c r="B69" s="34"/>
       <c r="C69" s="34"/>
-      <c r="D69" s="224">
+      <c r="D69" s="216">
         <f>SUM(D66:D68)</f>
         <v>176727</v>
       </c>
@@ -3817,13 +3819,13 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="32" t="s">
         <v>4</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
-      <c r="D70" s="220"/>
+      <c r="D70" s="212"/>
       <c r="E70" s="46"/>
       <c r="F70" s="46"/>
       <c r="G70" s="46"/>
@@ -3832,7 +3834,7 @@
       <c r="J70" s="6"/>
       <c r="L70" s="69"/>
     </row>
-    <row r="71" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="71" t="s">
         <v>241</v>
       </c>
@@ -3840,7 +3842,7 @@
       <c r="C71" s="35" t="s">
         <v>343</v>
       </c>
-      <c r="D71" s="228">
+      <c r="D71" s="220">
         <v>1469353.32</v>
       </c>
       <c r="E71" s="68">
@@ -3878,7 +3880,7 @@
       <c r="M71" s="84"/>
       <c r="N71" s="84"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>242</v>
       </c>
@@ -3886,7 +3888,7 @@
       <c r="C72" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="D72" s="228">
+      <c r="D72" s="220">
         <v>2331402.6</v>
       </c>
       <c r="E72" s="68">
@@ -3924,7 +3926,7 @@
       <c r="M72" s="84"/>
       <c r="N72" s="84"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>243</v>
       </c>
@@ -3932,7 +3934,7 @@
       <c r="C73" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="D73" s="215">
+      <c r="D73" s="208">
         <v>124753.28</v>
       </c>
       <c r="E73" s="68">
@@ -3961,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>327</v>
       </c>
@@ -3969,7 +3971,7 @@
       <c r="C74" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="D74" s="215">
+      <c r="D74" s="208">
         <v>352314.06</v>
       </c>
       <c r="E74" s="68">
@@ -3992,15 +3994,15 @@
       <c r="M74" s="84"/>
       <c r="N74" s="84"/>
     </row>
-    <row r="75" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="240" t="s">
+    <row r="75" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="232" t="s">
         <v>328</v>
       </c>
-      <c r="B75" s="246"/>
+      <c r="B75" s="238"/>
       <c r="C75" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="D75" s="215">
+      <c r="D75" s="208">
         <v>40000</v>
       </c>
       <c r="E75" s="68">
@@ -4029,15 +4031,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="240" t="s">
+    <row r="76" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="232" t="s">
         <v>356</v>
       </c>
-      <c r="B76" s="246"/>
-      <c r="C76" s="191" t="s">
+      <c r="B76" s="238"/>
+      <c r="C76" s="184" t="s">
         <v>357</v>
       </c>
-      <c r="D76" s="215">
+      <c r="D76" s="208">
         <v>130000</v>
       </c>
       <c r="E76" s="68">
@@ -4057,15 +4059,15 @@
       <c r="M76" s="84"/>
       <c r="N76" s="84"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="35" t="s">
         <v>277</v>
       </c>
       <c r="B77" s="35"/>
-      <c r="C77" s="191" t="s">
+      <c r="C77" s="184" t="s">
         <v>337</v>
       </c>
-      <c r="D77" s="215">
+      <c r="D77" s="208">
         <v>993952.65</v>
       </c>
       <c r="E77" s="68">
@@ -4109,15 +4111,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="35" t="s">
         <v>278</v>
       </c>
       <c r="B78" s="35"/>
-      <c r="C78" s="191" t="s">
+      <c r="C78" s="184" t="s">
         <v>337</v>
       </c>
-      <c r="D78" s="215">
+      <c r="D78" s="208">
         <v>5460.69</v>
       </c>
       <c r="E78" s="68">
@@ -4161,7 +4163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="142" t="s">
         <v>276</v>
       </c>
@@ -4169,7 +4171,7 @@
       <c r="C79" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="D79" s="215">
+      <c r="D79" s="208">
         <v>100000</v>
       </c>
       <c r="E79" s="68">
@@ -4213,13 +4215,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="33" t="s">
         <v>5</v>
       </c>
       <c r="B80" s="34"/>
       <c r="C80" s="34"/>
-      <c r="D80" s="224">
+      <c r="D80" s="216">
         <f t="shared" ref="D80:J80" si="14">SUM(D71:D79)</f>
         <v>5547236.6000000006</v>
       </c>
@@ -4260,11 +4262,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
-      <c r="D81" s="220"/>
+      <c r="D81" s="212"/>
       <c r="E81" s="46"/>
       <c r="F81" s="46"/>
       <c r="G81" s="46"/>
@@ -4273,11 +4275,11 @@
       <c r="J81" s="6"/>
       <c r="L81" s="69"/>
     </row>
-    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
-      <c r="D82" s="220"/>
+      <c r="D82" s="212"/>
       <c r="E82" s="45"/>
       <c r="F82" s="45"/>
       <c r="G82" s="45"/>
@@ -4286,13 +4288,13 @@
       <c r="J82" s="6"/>
       <c r="L82" s="69"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" s="32" t="s">
         <v>228</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
-      <c r="D83" s="220"/>
+      <c r="D83" s="212"/>
       <c r="E83" s="45"/>
       <c r="F83" s="45"/>
       <c r="G83" s="45"/>
@@ -4301,7 +4303,7 @@
       <c r="J83" s="6"/>
       <c r="L83" s="69"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>329</v>
       </c>
@@ -4309,7 +4311,7 @@
       <c r="C84" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="D84" s="215">
+      <c r="D84" s="208">
         <v>606800</v>
       </c>
       <c r="E84" s="68">
@@ -4338,7 +4340,7 @@
       </c>
       <c r="L84" s="69"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
         <v>333</v>
       </c>
@@ -4346,7 +4348,7 @@
       <c r="C85" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="D85" s="215">
+      <c r="D85" s="208">
         <v>216800</v>
       </c>
       <c r="E85" s="68">
@@ -4360,7 +4362,7 @@
       <c r="J85" s="58"/>
       <c r="L85" s="69"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
         <v>345</v>
       </c>
@@ -4368,7 +4370,7 @@
       <c r="C86" s="35" t="s">
         <v>346</v>
       </c>
-      <c r="D86" s="215">
+      <c r="D86" s="208">
         <v>1300</v>
       </c>
       <c r="E86" s="68">
@@ -4397,15 +4399,15 @@
       </c>
       <c r="L86" s="69"/>
     </row>
-    <row r="87" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="71" t="s">
         <v>334</v>
       </c>
       <c r="B87" s="35"/>
-      <c r="C87" s="203" t="s">
+      <c r="C87" s="196" t="s">
         <v>342</v>
       </c>
-      <c r="D87" s="215">
+      <c r="D87" s="208">
         <v>350000</v>
       </c>
       <c r="E87" s="68">
@@ -4419,15 +4421,15 @@
       <c r="J87" s="58"/>
       <c r="L87" s="69"/>
     </row>
-    <row r="88" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="249" t="s">
+    <row r="88" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="241" t="s">
         <v>347</v>
       </c>
-      <c r="B88" s="250"/>
+      <c r="B88" s="242"/>
       <c r="C88" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="D88" s="215">
+      <c r="D88" s="208">
         <v>250000</v>
       </c>
       <c r="E88" s="68">
@@ -4441,7 +4443,7 @@
       <c r="J88" s="58"/>
       <c r="L88" s="69"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>348</v>
       </c>
@@ -4449,7 +4451,7 @@
       <c r="C89" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="D89" s="215">
+      <c r="D89" s="208">
         <v>32800</v>
       </c>
       <c r="E89" s="68">
@@ -4463,7 +4465,7 @@
       <c r="J89" s="58"/>
       <c r="L89" s="69"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
         <v>336</v>
       </c>
@@ -4471,7 +4473,7 @@
       <c r="C90" s="35" t="s">
         <v>337</v>
       </c>
-      <c r="D90" s="215">
+      <c r="D90" s="208">
         <v>50000</v>
       </c>
       <c r="E90" s="68">
@@ -4485,15 +4487,15 @@
       <c r="J90" s="58"/>
       <c r="L90" s="69"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="45" t="s">
         <v>351</v>
       </c>
-      <c r="B91" s="204"/>
+      <c r="B91" s="197"/>
       <c r="C91" s="35" t="s">
         <v>352</v>
       </c>
-      <c r="D91" s="215">
+      <c r="D91" s="208">
         <v>60000</v>
       </c>
       <c r="E91" s="68">
@@ -4507,15 +4509,15 @@
       <c r="J91" s="58"/>
       <c r="L91" s="69"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="45" t="s">
         <v>351</v>
       </c>
-      <c r="B92" s="204"/>
+      <c r="B92" s="197"/>
       <c r="C92" s="35" t="s">
         <v>352</v>
       </c>
-      <c r="D92" s="215">
+      <c r="D92" s="208">
         <v>50000</v>
       </c>
       <c r="E92" s="68">
@@ -4529,15 +4531,15 @@
       <c r="J92" s="58"/>
       <c r="L92" s="69"/>
     </row>
-    <row r="93" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="244" t="s">
+    <row r="93" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="236" t="s">
         <v>350</v>
       </c>
-      <c r="B93" s="245"/>
+      <c r="B93" s="237"/>
       <c r="C93" s="137" t="s">
         <v>349</v>
       </c>
-      <c r="D93" s="215">
+      <c r="D93" s="208">
         <v>307200</v>
       </c>
       <c r="E93" s="68">
@@ -4551,15 +4553,15 @@
       <c r="J93" s="58"/>
       <c r="L93" s="69"/>
     </row>
-    <row r="94" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="244" t="s">
+    <row r="94" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="236" t="s">
         <v>331</v>
       </c>
-      <c r="B94" s="245"/>
+      <c r="B94" s="237"/>
       <c r="C94" s="137" t="s">
         <v>349</v>
       </c>
-      <c r="D94" s="215">
+      <c r="D94" s="208">
         <v>191400</v>
       </c>
       <c r="E94" s="68">
@@ -4573,15 +4575,15 @@
       <c r="J94" s="58"/>
       <c r="L94" s="69"/>
     </row>
-    <row r="95" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="247" t="s">
+    <row r="95" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="239" t="s">
         <v>330</v>
       </c>
-      <c r="B95" s="248"/>
+      <c r="B95" s="240"/>
       <c r="C95" s="137" t="s">
         <v>349</v>
       </c>
-      <c r="D95" s="215">
+      <c r="D95" s="208">
         <v>95700</v>
       </c>
       <c r="E95" s="68">
@@ -4596,13 +4598,13 @@
       <c r="L95" s="69"/>
       <c r="M95" s="43"/>
     </row>
-    <row r="96" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="33" t="s">
         <v>229</v>
       </c>
       <c r="B96" s="33"/>
       <c r="C96" s="33"/>
-      <c r="D96" s="224">
+      <c r="D96" s="216">
         <f t="shared" ref="D96:J96" si="16">SUM(D84:D95)</f>
         <v>2212000</v>
       </c>
@@ -4640,11 +4642,11 @@
       </c>
       <c r="N96" s="43"/>
     </row>
-    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
-      <c r="D97" s="220"/>
+      <c r="D97" s="212"/>
       <c r="E97" s="46"/>
       <c r="F97" s="46"/>
       <c r="G97" s="46"/>
@@ -4653,11 +4655,11 @@
       <c r="J97" s="6"/>
       <c r="L97" s="69"/>
     </row>
-    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
-      <c r="D98" s="220"/>
+      <c r="D98" s="212"/>
       <c r="E98" s="45"/>
       <c r="F98" s="45"/>
       <c r="G98" s="45"/>
@@ -4666,13 +4668,13 @@
       <c r="J98" s="6"/>
       <c r="L98" s="69"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="32" t="s">
         <v>6</v>
       </c>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
-      <c r="D99" s="220"/>
+      <c r="D99" s="212"/>
       <c r="E99" s="45"/>
       <c r="F99" s="45"/>
       <c r="G99" s="45"/>
@@ -4681,7 +4683,7 @@
       <c r="J99" s="6"/>
       <c r="L99" s="69"/>
     </row>
-    <row r="100" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
         <v>7</v>
       </c>
@@ -4689,7 +4691,7 @@
         <v>37</v>
       </c>
       <c r="C100" s="6"/>
-      <c r="D100" s="215">
+      <c r="D100" s="208">
         <v>753700</v>
       </c>
       <c r="E100" s="68">
@@ -4720,11 +4722,11 @@
         <v>310</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="32"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
-      <c r="D101" s="215"/>
+      <c r="D101" s="208"/>
       <c r="E101" s="68"/>
       <c r="F101" s="68"/>
       <c r="G101" s="68"/>
@@ -4734,11 +4736,11 @@
       <c r="L101" s="69"/>
       <c r="N101" s="44"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
-      <c r="D102" s="220"/>
+      <c r="D102" s="212"/>
       <c r="E102" s="47"/>
       <c r="F102" s="47"/>
       <c r="G102" s="47"/>
@@ -4748,13 +4750,13 @@
       <c r="L102" s="69"/>
       <c r="N102" s="43"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="33" t="s">
         <v>8</v>
       </c>
       <c r="B103" s="33"/>
       <c r="C103" s="33"/>
-      <c r="D103" s="224">
+      <c r="D103" s="216">
         <f>SUM(D100:D102)</f>
         <v>753700</v>
       </c>
@@ -4792,13 +4794,13 @@
       </c>
       <c r="N103" s="43"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
-      <c r="D104" s="215">
+      <c r="D104" s="208">
         <f>720+151.2+166246.56</f>
         <v>167117.76000000001</v>
       </c>
@@ -4828,7 +4830,7 @@
       </c>
       <c r="L104" s="69"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
         <v>29</v>
       </c>
@@ -4861,7 +4863,7 @@
       </c>
       <c r="L105" s="69"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" s="33" t="s">
         <v>230</v>
       </c>
@@ -4904,7 +4906,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="98"/>
       <c r="B107" s="98"/>
       <c r="C107" s="98"/>
@@ -4917,7 +4919,7 @@
       <c r="J107" s="98"/>
       <c r="L107" s="69"/>
     </row>
-    <row r="108" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="100" t="s">
         <v>317</v>
       </c>
@@ -4960,7 +4962,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="103"/>
       <c r="B109" s="104"/>
       <c r="C109" s="104"/>
@@ -4974,7 +4976,7 @@
       <c r="K109" s="43"/>
       <c r="L109" s="69"/>
     </row>
-    <row r="110" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
         <v>30</v>
       </c>
@@ -5021,7 +5023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D111" s="85"/>
       <c r="E111" s="43"/>
       <c r="F111" s="43"/>
@@ -5029,7 +5031,7 @@
       <c r="H111" s="43"/>
       <c r="I111" s="43"/>
     </row>
-    <row r="112" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="64" t="s">
         <v>39</v>
       </c>
@@ -5041,7 +5043,7 @@
       <c r="H112" s="43"/>
       <c r="I112" s="43"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>354</v>
       </c>
@@ -5057,7 +5059,7 @@
       <c r="H113" s="43"/>
       <c r="I113" s="43"/>
     </row>
-    <row r="114" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="1"/>
       <c r="C114" s="128"/>
       <c r="E114" s="43"/>
@@ -5066,7 +5068,7 @@
       <c r="H114" s="43"/>
       <c r="I114" s="43"/>
     </row>
-    <row r="115" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="65" t="s">
         <v>17</v>
       </c>
@@ -5081,27 +5083,27 @@
       <c r="H115" s="43"/>
       <c r="I115" s="43"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E116" s="43"/>
       <c r="F116" s="43"/>
       <c r="G116" s="43"/>
       <c r="H116" s="43"/>
       <c r="I116" s="43"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E117" s="60"/>
       <c r="F117" s="60"/>
       <c r="G117" s="60"/>
       <c r="H117" s="60"/>
       <c r="I117" s="60"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A118" s="238" t="s">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A118" s="230" t="s">
         <v>34</v>
       </c>
-      <c r="B118" s="239"/>
-      <c r="C118" s="239"/>
-      <c r="D118" s="239"/>
+      <c r="B118" s="231"/>
+      <c r="C118" s="231"/>
+      <c r="D118" s="231"/>
       <c r="E118" s="80" t="s">
         <v>11</v>
       </c>
@@ -5121,9 +5123,9 @@
         <v>174</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="240"/>
-      <c r="B119" s="241"/>
+    <row r="119" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="232"/>
+      <c r="B119" s="233"/>
       <c r="C119" s="82"/>
       <c r="D119" s="44"/>
       <c r="E119" s="68">
@@ -5136,9 +5138,9 @@
       <c r="I119" s="68"/>
       <c r="J119" s="58"/>
     </row>
-    <row r="120" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="240"/>
-      <c r="B120" s="241"/>
+    <row r="120" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="232"/>
+      <c r="B120" s="233"/>
       <c r="C120" s="82"/>
       <c r="D120" s="44"/>
       <c r="E120" s="68"/>
@@ -5148,12 +5150,12 @@
       <c r="I120" s="68"/>
       <c r="J120" s="58"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="235" t="s">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A121" s="227" t="s">
         <v>17</v>
       </c>
-      <c r="B121" s="236"/>
-      <c r="C121" s="237"/>
+      <c r="B121" s="228"/>
+      <c r="C121" s="229"/>
       <c r="D121" s="79">
         <f>SUM(D119:D120)</f>
         <v>0</v>
@@ -5179,14 +5181,14 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E123" s="43"/>
       <c r="F123" s="43"/>
       <c r="G123" s="43"/>
       <c r="H123" s="43"/>
       <c r="I123" s="43"/>
     </row>
-    <row r="124" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="38" t="s">
         <v>31</v>
       </c>
@@ -5195,7 +5197,7 @@
         <v>15667206.089999998</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="40" t="s">
         <v>33</v>
       </c>
@@ -5203,37 +5205,37 @@
         <f>D110-D108</f>
         <v>12343887.129999999</v>
       </c>
-      <c r="D125" s="243" t="s">
+      <c r="D125" s="235" t="s">
         <v>305</v>
       </c>
-      <c r="E125" s="243"/>
-      <c r="F125" s="243"/>
-      <c r="G125" s="243"/>
-      <c r="H125" s="243"/>
-      <c r="I125" s="243"/>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D126" s="243"/>
-      <c r="E126" s="243"/>
-      <c r="F126" s="243"/>
-      <c r="G126" s="243"/>
-      <c r="H126" s="243"/>
-      <c r="I126" s="243"/>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E125" s="235"/>
+      <c r="F125" s="235"/>
+      <c r="G125" s="235"/>
+      <c r="H125" s="235"/>
+      <c r="I125" s="235"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D126" s="235"/>
+      <c r="E126" s="235"/>
+      <c r="F126" s="235"/>
+      <c r="G126" s="235"/>
+      <c r="H126" s="235"/>
+      <c r="I126" s="235"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B127" s="17"/>
       <c r="C127" s="18"/>
-      <c r="D127" s="243"/>
-      <c r="E127" s="243"/>
-      <c r="F127" s="243"/>
-      <c r="G127" s="243"/>
-      <c r="H127" s="243"/>
-      <c r="I127" s="243"/>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D127" s="235"/>
+      <c r="E127" s="235"/>
+      <c r="F127" s="235"/>
+      <c r="G127" s="235"/>
+      <c r="H127" s="235"/>
+      <c r="I127" s="235"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128" s="19" t="s">
         <v>21</v>
       </c>
@@ -5241,14 +5243,14 @@
         <v>-1002261.6181467418</v>
       </c>
       <c r="C128" s="20"/>
-      <c r="D128" s="243"/>
-      <c r="E128" s="243"/>
-      <c r="F128" s="243"/>
-      <c r="G128" s="243"/>
-      <c r="H128" s="243"/>
-      <c r="I128" s="243"/>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D128" s="235"/>
+      <c r="E128" s="235"/>
+      <c r="F128" s="235"/>
+      <c r="G128" s="235"/>
+      <c r="H128" s="235"/>
+      <c r="I128" s="235"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="21" t="s">
         <v>22</v>
       </c>
@@ -5259,14 +5261,14 @@
       <c r="C129" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D129" s="243"/>
-      <c r="E129" s="243"/>
-      <c r="F129" s="243"/>
-      <c r="G129" s="243"/>
-      <c r="H129" s="243"/>
-      <c r="I129" s="243"/>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D129" s="235"/>
+      <c r="E129" s="235"/>
+      <c r="F129" s="235"/>
+      <c r="G129" s="235"/>
+      <c r="H129" s="235"/>
+      <c r="I129" s="235"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="21" t="s">
         <v>36</v>
       </c>
@@ -5275,15 +5277,15 @@
         <v>-12343887.129999999</v>
       </c>
       <c r="C130" s="18"/>
-      <c r="D130" s="243"/>
-      <c r="E130" s="243"/>
-      <c r="F130" s="243"/>
-      <c r="G130" s="243"/>
-      <c r="H130" s="243"/>
-      <c r="I130" s="243"/>
+      <c r="D130" s="235"/>
+      <c r="E130" s="235"/>
+      <c r="F130" s="235"/>
+      <c r="G130" s="235"/>
+      <c r="H130" s="235"/>
+      <c r="I130" s="235"/>
       <c r="K130" s="44"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="21" t="s">
         <v>35</v>
       </c>
@@ -5292,15 +5294,15 @@
         <v>0</v>
       </c>
       <c r="C131" s="18"/>
-      <c r="D131" s="243"/>
-      <c r="E131" s="243"/>
-      <c r="F131" s="243"/>
-      <c r="G131" s="243"/>
-      <c r="H131" s="243"/>
-      <c r="I131" s="243"/>
+      <c r="D131" s="235"/>
+      <c r="E131" s="235"/>
+      <c r="F131" s="235"/>
+      <c r="G131" s="235"/>
+      <c r="H131" s="235"/>
+      <c r="I131" s="235"/>
       <c r="K131" s="52"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="21" t="s">
         <v>294</v>
       </c>
@@ -5309,15 +5311,15 @@
         <v>143267</v>
       </c>
       <c r="C132" s="18"/>
-      <c r="D132" s="243"/>
-      <c r="E132" s="243"/>
-      <c r="F132" s="243"/>
-      <c r="G132" s="243"/>
-      <c r="H132" s="243"/>
-      <c r="I132" s="243"/>
+      <c r="D132" s="235"/>
+      <c r="E132" s="235"/>
+      <c r="F132" s="235"/>
+      <c r="G132" s="235"/>
+      <c r="H132" s="235"/>
+      <c r="I132" s="235"/>
       <c r="K132" s="52"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="21" t="s">
         <v>32</v>
       </c>
@@ -5326,45 +5328,45 @@
         <v>-120000</v>
       </c>
       <c r="C133" s="22"/>
-      <c r="D133" s="243"/>
-      <c r="E133" s="243"/>
-      <c r="F133" s="243"/>
-      <c r="G133" s="243"/>
-      <c r="H133" s="243"/>
-      <c r="I133" s="243"/>
-    </row>
-    <row r="134" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="232" t="s">
-        <v>365</v>
+      <c r="D133" s="235"/>
+      <c r="E133" s="235"/>
+      <c r="F133" s="235"/>
+      <c r="G133" s="235"/>
+      <c r="H133" s="235"/>
+      <c r="I133" s="235"/>
+    </row>
+    <row r="134" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="224" t="s">
+        <v>364</v>
       </c>
       <c r="B134" s="30">
         <v>426600</v>
       </c>
       <c r="C134" s="22"/>
-      <c r="D134" s="243"/>
-      <c r="E134" s="243"/>
-      <c r="F134" s="243"/>
-      <c r="G134" s="243"/>
-      <c r="H134" s="243"/>
-      <c r="I134" s="243"/>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D134" s="235"/>
+      <c r="E134" s="235"/>
+      <c r="F134" s="235"/>
+      <c r="G134" s="235"/>
+      <c r="H134" s="235"/>
+      <c r="I134" s="235"/>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="21" t="s">
         <v>292</v>
       </c>
-      <c r="B135" s="198">
+      <c r="B135" s="191">
         <f>-87300</f>
         <v>-87300</v>
       </c>
       <c r="C135" s="22"/>
-      <c r="D135" s="243"/>
-      <c r="E135" s="243"/>
-      <c r="F135" s="243"/>
-      <c r="G135" s="243"/>
-      <c r="H135" s="243"/>
-      <c r="I135" s="243"/>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D135" s="235"/>
+      <c r="E135" s="235"/>
+      <c r="F135" s="235"/>
+      <c r="G135" s="235"/>
+      <c r="H135" s="235"/>
+      <c r="I135" s="235"/>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="21" t="s">
         <v>39</v>
       </c>
@@ -5373,25 +5375,25 @@
         <v>-25000</v>
       </c>
       <c r="C136" s="22"/>
-      <c r="D136" s="243"/>
-      <c r="E136" s="243"/>
-      <c r="F136" s="243"/>
-      <c r="G136" s="243"/>
-      <c r="H136" s="243"/>
-      <c r="I136" s="243"/>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D136" s="235"/>
+      <c r="E136" s="235"/>
+      <c r="F136" s="235"/>
+      <c r="G136" s="235"/>
+      <c r="H136" s="235"/>
+      <c r="I136" s="235"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="21"/>
       <c r="B137" s="169"/>
       <c r="C137" s="22"/>
-      <c r="D137" s="243"/>
-      <c r="E137" s="243"/>
-      <c r="F137" s="243"/>
-      <c r="G137" s="243"/>
-      <c r="H137" s="243"/>
-      <c r="I137" s="243"/>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D137" s="235"/>
+      <c r="E137" s="235"/>
+      <c r="F137" s="235"/>
+      <c r="G137" s="235"/>
+      <c r="H137" s="235"/>
+      <c r="I137" s="235"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="19" t="s">
         <v>24</v>
       </c>
@@ -5400,37 +5402,37 @@
         <v>1767072.6013971008</v>
       </c>
       <c r="C138" s="70"/>
-      <c r="D138" s="243"/>
-      <c r="E138" s="243"/>
-      <c r="F138" s="243"/>
-      <c r="G138" s="243"/>
-      <c r="H138" s="243"/>
-      <c r="I138" s="243"/>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D138" s="235"/>
+      <c r="E138" s="235"/>
+      <c r="F138" s="235"/>
+      <c r="G138" s="235"/>
+      <c r="H138" s="235"/>
+      <c r="I138" s="235"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="22"/>
       <c r="C139" s="18"/>
-      <c r="D139" s="243"/>
-      <c r="E139" s="243"/>
-      <c r="F139" s="243"/>
-      <c r="G139" s="243"/>
-      <c r="H139" s="243"/>
-      <c r="I139" s="243"/>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D139" s="235"/>
+      <c r="E139" s="235"/>
+      <c r="F139" s="235"/>
+      <c r="G139" s="235"/>
+      <c r="H139" s="235"/>
+      <c r="I139" s="235"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="16" t="s">
         <v>293</v>
       </c>
       <c r="B140" s="8"/>
       <c r="C140" s="18"/>
-      <c r="D140" s="243"/>
-      <c r="E140" s="243"/>
-      <c r="F140" s="243"/>
-      <c r="G140" s="243"/>
-      <c r="H140" s="243"/>
-      <c r="I140" s="243"/>
-    </row>
-    <row r="141" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D140" s="235"/>
+      <c r="E140" s="235"/>
+      <c r="F140" s="235"/>
+      <c r="G140" s="235"/>
+      <c r="H140" s="235"/>
+      <c r="I140" s="235"/>
+    </row>
+    <row r="141" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="19" t="s">
         <v>362</v>
       </c>
@@ -5440,7 +5442,7 @@
       <c r="C141" s="18"/>
       <c r="D141" s="25"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="36" t="s">
         <v>17</v>
       </c>
@@ -5451,17 +5453,17 @@
       <c r="C142" s="18"/>
       <c r="D142" s="25"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="22"/>
       <c r="C143" s="18"/>
       <c r="D143" s="25"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="22"/>
       <c r="C144" s="18"/>
       <c r="D144" s="25"/>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C145" s="18"/>
       <c r="D145" s="43"/>
       <c r="E145" s="84"/>
@@ -5470,7 +5472,7 @@
       <c r="H145" s="84"/>
       <c r="I145" s="84"/>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146" s="16" t="s">
         <v>25</v>
       </c>
@@ -5486,7 +5488,7 @@
       <c r="I146" s="84"/>
       <c r="J146" s="84"/>
     </row>
-    <row r="147" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="19" t="s">
         <v>255</v>
       </c>
@@ -5501,7 +5503,7 @@
       <c r="H147" s="88"/>
       <c r="I147" s="88"/>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148" s="19" t="s">
         <v>360</v>
       </c>
@@ -5516,7 +5518,7 @@
       <c r="H148" s="43"/>
       <c r="I148" s="43"/>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A149" s="36" t="s">
         <v>17</v>
       </c>
@@ -5526,62 +5528,62 @@
       </c>
       <c r="C149" s="24"/>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C150" s="25"/>
       <c r="D150" s="84"/>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B151" s="22"/>
       <c r="C151" s="18"/>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="R153" s="9"/>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B156" s="234"/>
-      <c r="C156" s="234"/>
-      <c r="D156" s="234"/>
-      <c r="E156" s="234"/>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B156" s="226"/>
+      <c r="C156" s="226"/>
+      <c r="D156" s="226"/>
+      <c r="E156" s="226"/>
       <c r="F156" s="90"/>
       <c r="G156" s="90"/>
       <c r="H156" s="90"/>
       <c r="I156" s="90"/>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B157" s="234"/>
-      <c r="C157" s="234"/>
-      <c r="D157" s="234"/>
-      <c r="E157" s="234"/>
+    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B157" s="226"/>
+      <c r="C157" s="226"/>
+      <c r="D157" s="226"/>
+      <c r="E157" s="226"/>
       <c r="F157" s="90"/>
       <c r="G157" s="90"/>
       <c r="H157" s="90"/>
       <c r="I157" s="90"/>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B158" s="234"/>
-      <c r="C158" s="234"/>
-      <c r="D158" s="234"/>
-      <c r="E158" s="234"/>
+    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B158" s="226"/>
+      <c r="C158" s="226"/>
+      <c r="D158" s="226"/>
+      <c r="E158" s="226"/>
       <c r="F158" s="90"/>
       <c r="G158" s="90"/>
       <c r="H158" s="90"/>
       <c r="I158" s="90"/>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B159" s="234"/>
-      <c r="C159" s="234"/>
-      <c r="D159" s="234"/>
-      <c r="E159" s="234"/>
+    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B159" s="226"/>
+      <c r="C159" s="226"/>
+      <c r="D159" s="226"/>
+      <c r="E159" s="226"/>
       <c r="F159" s="90"/>
       <c r="G159" s="90"/>
       <c r="H159" s="90"/>
       <c r="I159" s="90"/>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B160" s="234"/>
-      <c r="C160" s="234"/>
-      <c r="D160" s="234"/>
-      <c r="E160" s="234"/>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B160" s="226"/>
+      <c r="C160" s="226"/>
+      <c r="D160" s="226"/>
+      <c r="E160" s="226"/>
       <c r="F160" s="90"/>
       <c r="G160" s="90"/>
       <c r="H160" s="90"/>
@@ -5615,36 +5617,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DI154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="5" width="25.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" customWidth="1"/>
-    <col min="13" max="13" width="15.42578125" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" customWidth="1"/>
+    <col min="13" max="13" width="15.44140625" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="284" t="s">
-        <v>364</v>
-      </c>
-      <c r="B1" s="285"/>
-      <c r="C1" s="285"/>
-      <c r="D1" s="285"/>
-      <c r="E1" s="285"/>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="272" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1" s="273"/>
+      <c r="C1" s="273"/>
+      <c r="D1" s="273"/>
+      <c r="E1" s="273"/>
       <c r="F1" s="158" t="s">
         <v>296</v>
       </c>
@@ -5652,23 +5654,23 @@
       <c r="H1" s="158"/>
       <c r="I1" s="158"/>
       <c r="J1" s="158"/>
-      <c r="K1" s="199" t="s">
+      <c r="K1" s="192" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="260">
+      <c r="L1" s="248">
         <f>RESUMEN!D110-RESUMEN!D108</f>
         <v>12343887.129999999</v>
       </c>
-      <c r="M1" s="261"/>
+      <c r="M1" s="249"/>
       <c r="N1" s="159"/>
       <c r="O1" s="59"/>
     </row>
-    <row r="2" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="286"/>
-      <c r="B2" s="287"/>
-      <c r="C2" s="287"/>
-      <c r="D2" s="287"/>
-      <c r="E2" s="287"/>
+    <row r="2" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="274"/>
+      <c r="B2" s="275"/>
+      <c r="C2" s="275"/>
+      <c r="D2" s="275"/>
+      <c r="E2" s="275"/>
       <c r="F2" s="7" t="s">
         <v>295</v>
       </c>
@@ -5676,22 +5678,22 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
-      <c r="K2" s="200" t="s">
+      <c r="K2" s="193" t="s">
         <v>42</v>
       </c>
-      <c r="L2" s="200"/>
-      <c r="M2" s="201">
+      <c r="L2" s="193"/>
+      <c r="M2" s="194">
         <v>15667206.09</v>
       </c>
       <c r="N2" s="160"/>
       <c r="O2" s="59"/>
     </row>
-    <row r="3" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="286"/>
-      <c r="B3" s="287"/>
-      <c r="C3" s="287"/>
-      <c r="D3" s="287"/>
-      <c r="E3" s="287"/>
+    <row r="3" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="274"/>
+      <c r="B3" s="275"/>
+      <c r="C3" s="275"/>
+      <c r="D3" s="275"/>
+      <c r="E3" s="275"/>
       <c r="F3" s="7" t="s">
         <v>297</v>
       </c>
@@ -5705,12 +5707,12 @@
       <c r="N3" s="163"/>
       <c r="O3" s="15"/>
     </row>
-    <row r="4" spans="1:18" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="288"/>
-      <c r="B4" s="289"/>
-      <c r="C4" s="289"/>
-      <c r="D4" s="289"/>
-      <c r="E4" s="289"/>
+    <row r="4" spans="1:18" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="276"/>
+      <c r="B4" s="277"/>
+      <c r="C4" s="277"/>
+      <c r="D4" s="277"/>
+      <c r="E4" s="277"/>
       <c r="F4" s="164"/>
       <c r="G4" s="164"/>
       <c r="H4" s="164"/>
@@ -5722,93 +5724,93 @@
       <c r="N4" s="167"/>
       <c r="O4" s="15"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="269" t="s">
+      <c r="C5" s="257" t="s">
         <v>314</v>
       </c>
-      <c r="D5" s="270"/>
-      <c r="E5" s="270"/>
-      <c r="F5" s="270"/>
-      <c r="G5" s="270"/>
-      <c r="H5" s="270"/>
-      <c r="I5" s="270"/>
-      <c r="J5" s="270"/>
-      <c r="K5" s="270"/>
-      <c r="L5" s="270"/>
-      <c r="M5" s="270"/>
-      <c r="N5" s="271"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="258"/>
+      <c r="K5" s="258"/>
+      <c r="L5" s="258"/>
+      <c r="M5" s="258"/>
+      <c r="N5" s="259"/>
       <c r="O5" s="15"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="272"/>
-      <c r="D6" s="273"/>
-      <c r="E6" s="273"/>
-      <c r="F6" s="273"/>
-      <c r="G6" s="273"/>
-      <c r="H6" s="273"/>
-      <c r="I6" s="273"/>
-      <c r="J6" s="273"/>
-      <c r="K6" s="273"/>
-      <c r="L6" s="273"/>
-      <c r="M6" s="273"/>
-      <c r="N6" s="274"/>
+      <c r="C6" s="260"/>
+      <c r="D6" s="261"/>
+      <c r="E6" s="261"/>
+      <c r="F6" s="261"/>
+      <c r="G6" s="261"/>
+      <c r="H6" s="261"/>
+      <c r="I6" s="261"/>
+      <c r="J6" s="261"/>
+      <c r="K6" s="261"/>
+      <c r="L6" s="261"/>
+      <c r="M6" s="261"/>
+      <c r="N6" s="262"/>
       <c r="O6" s="15"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="272"/>
-      <c r="D7" s="273"/>
-      <c r="E7" s="273"/>
-      <c r="F7" s="273"/>
-      <c r="G7" s="273"/>
-      <c r="H7" s="273"/>
-      <c r="I7" s="273"/>
-      <c r="J7" s="273"/>
-      <c r="K7" s="273"/>
-      <c r="L7" s="273"/>
-      <c r="M7" s="273"/>
-      <c r="N7" s="274"/>
+      <c r="C7" s="260"/>
+      <c r="D7" s="261"/>
+      <c r="E7" s="261"/>
+      <c r="F7" s="261"/>
+      <c r="G7" s="261"/>
+      <c r="H7" s="261"/>
+      <c r="I7" s="261"/>
+      <c r="J7" s="261"/>
+      <c r="K7" s="261"/>
+      <c r="L7" s="261"/>
+      <c r="M7" s="261"/>
+      <c r="N7" s="262"/>
       <c r="O7" s="15"/>
     </row>
-    <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="275"/>
-      <c r="D8" s="276"/>
-      <c r="E8" s="276"/>
-      <c r="F8" s="276"/>
-      <c r="G8" s="276"/>
-      <c r="H8" s="276"/>
-      <c r="I8" s="276"/>
-      <c r="J8" s="276"/>
-      <c r="K8" s="276"/>
-      <c r="L8" s="276"/>
-      <c r="M8" s="276"/>
-      <c r="N8" s="277"/>
+      <c r="C8" s="263"/>
+      <c r="D8" s="264"/>
+      <c r="E8" s="264"/>
+      <c r="F8" s="264"/>
+      <c r="G8" s="264"/>
+      <c r="H8" s="264"/>
+      <c r="I8" s="264"/>
+      <c r="J8" s="264"/>
+      <c r="K8" s="264"/>
+      <c r="L8" s="264"/>
+      <c r="M8" s="264"/>
+      <c r="N8" s="265"/>
       <c r="P8" s="84"/>
     </row>
-    <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="278" t="s">
+      <c r="C9" s="266" t="s">
         <v>312</v>
       </c>
-      <c r="D9" s="279"/>
-      <c r="E9" s="279"/>
-      <c r="F9" s="279"/>
-      <c r="G9" s="279"/>
-      <c r="H9" s="279"/>
-      <c r="I9" s="279"/>
-      <c r="J9" s="279"/>
-      <c r="K9" s="279"/>
-      <c r="L9" s="279"/>
-      <c r="M9" s="279"/>
-      <c r="N9" s="280"/>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
+      <c r="M9" s="267"/>
+      <c r="N9" s="268"/>
       <c r="P9" t="s">
         <v>250</v>
       </c>
@@ -5817,21 +5819,21 @@
         <v>141730.21116000001</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="281"/>
-      <c r="D10" s="282"/>
-      <c r="E10" s="282"/>
-      <c r="F10" s="282"/>
-      <c r="G10" s="282"/>
-      <c r="H10" s="282"/>
-      <c r="I10" s="282"/>
-      <c r="J10" s="282"/>
-      <c r="K10" s="282"/>
-      <c r="L10" s="282"/>
-      <c r="M10" s="282"/>
-      <c r="N10" s="283"/>
+      <c r="C10" s="269"/>
+      <c r="D10" s="270"/>
+      <c r="E10" s="270"/>
+      <c r="F10" s="270"/>
+      <c r="G10" s="270"/>
+      <c r="H10" s="270"/>
+      <c r="I10" s="270"/>
+      <c r="J10" s="270"/>
+      <c r="K10" s="270"/>
+      <c r="L10" s="270"/>
+      <c r="M10" s="270"/>
+      <c r="N10" s="271"/>
       <c r="P10" t="s">
         <v>251</v>
       </c>
@@ -5840,47 +5842,47 @@
         <v>167976.54656000002</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="251" t="s">
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="244" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="253" t="s">
+      <c r="B11" s="278" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="251" t="s">
+      <c r="C11" s="244" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="255" t="s">
+      <c r="D11" s="280" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="255" t="s">
+      <c r="E11" s="280" t="s">
         <v>269</v>
       </c>
-      <c r="F11" s="251" t="s">
+      <c r="F11" s="244" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="251" t="s">
+      <c r="G11" s="244" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="251" t="s">
+      <c r="H11" s="244" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="262" t="s">
+      <c r="I11" s="250" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="264" t="s">
+      <c r="J11" s="252" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="264" t="s">
+      <c r="K11" s="252" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="267" t="s">
+      <c r="L11" s="255" t="s">
         <v>40</v>
       </c>
-      <c r="M11" s="264" t="s">
+      <c r="M11" s="252" t="s">
         <v>280</v>
       </c>
-      <c r="N11" s="264" t="s">
+      <c r="N11" s="252" t="s">
         <v>279</v>
       </c>
       <c r="P11" t="s">
@@ -5891,21 +5893,21 @@
         <v>158790.32916999998</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="252"/>
-      <c r="B12" s="254"/>
-      <c r="C12" s="252"/>
-      <c r="D12" s="256"/>
-      <c r="E12" s="256"/>
-      <c r="F12" s="252"/>
-      <c r="G12" s="252"/>
-      <c r="H12" s="252"/>
-      <c r="I12" s="263"/>
-      <c r="J12" s="265"/>
-      <c r="K12" s="265"/>
-      <c r="L12" s="268"/>
-      <c r="M12" s="265"/>
-      <c r="N12" s="265"/>
+    <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="245"/>
+      <c r="B12" s="279"/>
+      <c r="C12" s="245"/>
+      <c r="D12" s="281"/>
+      <c r="E12" s="281"/>
+      <c r="F12" s="245"/>
+      <c r="G12" s="245"/>
+      <c r="H12" s="245"/>
+      <c r="I12" s="251"/>
+      <c r="J12" s="253"/>
+      <c r="K12" s="253"/>
+      <c r="L12" s="256"/>
+      <c r="M12" s="253"/>
+      <c r="N12" s="253"/>
       <c r="P12" t="s">
         <v>253</v>
       </c>
@@ -5914,19 +5916,19 @@
         <v>195535.19872999997</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="252"/>
-      <c r="B13" s="254"/>
-      <c r="C13" s="252"/>
-      <c r="D13" s="256"/>
-      <c r="E13" s="256"/>
-      <c r="F13" s="252"/>
-      <c r="G13" s="252"/>
-      <c r="H13" s="252"/>
-      <c r="I13" s="263"/>
-      <c r="J13" s="265"/>
-      <c r="K13" s="266"/>
-      <c r="L13" s="268"/>
+    <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="245"/>
+      <c r="B13" s="279"/>
+      <c r="C13" s="245"/>
+      <c r="D13" s="281"/>
+      <c r="E13" s="281"/>
+      <c r="F13" s="245"/>
+      <c r="G13" s="245"/>
+      <c r="H13" s="245"/>
+      <c r="I13" s="251"/>
+      <c r="J13" s="253"/>
+      <c r="K13" s="254"/>
+      <c r="L13" s="256"/>
       <c r="M13" s="132" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 16/02</v>
@@ -5943,7 +5945,7 @@
         <v>228343.11798000001</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>118</v>
       </c>
@@ -5963,7 +5965,7 @@
       <c r="G14" s="137">
         <v>274719.32308800006</v>
       </c>
-      <c r="H14" s="215"/>
+      <c r="H14" s="208"/>
       <c r="I14" s="144">
         <f>G14-H14</f>
         <v>274719.32308800006</v>
@@ -5986,10 +5988,10 @@
         <v>441436.50630288007</v>
       </c>
       <c r="O14" s="115"/>
-      <c r="Q14" s="257"/>
-      <c r="R14" s="257"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q14" s="243"/>
+      <c r="R14" s="243"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="35" t="s">
@@ -5998,14 +6000,14 @@
       <c r="D15" s="108" t="s">
         <v>359</v>
       </c>
-      <c r="E15" s="197"/>
+      <c r="E15" s="190"/>
       <c r="F15" s="143">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="G15" s="137">
         <v>183831.27180800005</v>
       </c>
-      <c r="H15" s="215">
+      <c r="H15" s="208">
         <v>61277</v>
       </c>
       <c r="I15" s="144">
@@ -6030,10 +6032,10 @@
         <v>307962.66747008008</v>
       </c>
       <c r="O15" s="115"/>
-      <c r="Q15" s="257"/>
-      <c r="R15" s="257"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q15" s="243"/>
+      <c r="R15" s="243"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>118</v>
       </c>
@@ -6050,10 +6052,10 @@
       <c r="F16" s="143">
         <v>1.21E-2</v>
       </c>
-      <c r="G16" s="215">
+      <c r="G16" s="208">
         <v>160512.294448</v>
       </c>
-      <c r="H16" s="215">
+      <c r="H16" s="208">
         <f t="shared" ref="H16:H21" si="3">G16</f>
         <v>160512.294448</v>
       </c>
@@ -6081,7 +6083,7 @@
       <c r="O16" s="115"/>
       <c r="R16" s="43"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>118</v>
       </c>
@@ -6099,7 +6101,7 @@
       <c r="G17" s="137">
         <v>551052.91796400002</v>
       </c>
-      <c r="H17" s="215"/>
+      <c r="H17" s="208"/>
       <c r="I17" s="144">
         <f t="shared" si="0"/>
         <v>551052.91796400002</v>
@@ -6124,7 +6126,7 @@
       <c r="O17" s="115"/>
       <c r="R17" s="43"/>
     </row>
-    <row r="18" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>118</v>
       </c>
@@ -6142,7 +6144,7 @@
       <c r="G18" s="151">
         <v>469159.55509584001</v>
       </c>
-      <c r="H18" s="216">
+      <c r="H18" s="209">
         <f>G18</f>
         <v>469159.55509584001</v>
       </c>
@@ -6156,7 +6158,7 @@
       <c r="K18" s="153">
         <v>228343.11798000001</v>
       </c>
-      <c r="L18" s="230">
+      <c r="L18" s="222">
         <v>0</v>
       </c>
       <c r="M18" s="154">
@@ -6170,12 +6172,12 @@
       <c r="O18" s="115"/>
       <c r="R18" s="43"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="57" t="s">
         <v>120</v>
       </c>
       <c r="B19" s="6"/>
-      <c r="C19" s="192" t="s">
+      <c r="C19" s="185" t="s">
         <v>44</v>
       </c>
       <c r="D19" s="135" t="s">
@@ -6185,33 +6187,33 @@
       <c r="F19" s="136">
         <v>1.8800000000000001E-2</v>
       </c>
-      <c r="G19" s="193">
+      <c r="G19" s="186">
         <v>261193.01</v>
       </c>
-      <c r="H19" s="217">
+      <c r="H19" s="210">
         <f>G19</f>
         <v>261193.01</v>
       </c>
-      <c r="I19" s="194">
+      <c r="I19" s="187">
         <f>G19-H19</f>
         <v>0</v>
       </c>
-      <c r="J19" s="195">
+      <c r="J19" s="188">
         <f t="shared" ref="J19:J50" si="4">M$8*F19</f>
         <v>0</v>
       </c>
-      <c r="K19" s="195">
+      <c r="K19" s="188">
         <f>M$2*F19</f>
         <v>294543.47449200001</v>
       </c>
-      <c r="L19" s="229">
-        <v>0</v>
-      </c>
-      <c r="M19" s="196">
+      <c r="L19" s="221">
+        <v>0</v>
+      </c>
+      <c r="M19" s="189">
         <f>ROUND((K19+J19+I19+L19),0) + O19</f>
         <v>294543.01</v>
       </c>
-      <c r="N19" s="196">
+      <c r="N19" s="189">
         <f>ROUND((M19*6% + M19 ),0) + O19</f>
         <v>312216.01</v>
       </c>
@@ -6223,7 +6225,7 @@
       </c>
       <c r="R19" s="43"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="57" t="s">
         <v>121</v>
       </c>
@@ -6241,7 +6243,7 @@
       <c r="G20" s="137">
         <v>131605.01999999999</v>
       </c>
-      <c r="H20" s="215">
+      <c r="H20" s="208">
         <f t="shared" ref="H20" si="5">G20</f>
         <v>131605.01999999999</v>
       </c>
@@ -6274,7 +6276,7 @@
       </c>
       <c r="R20" s="43"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="57" t="s">
         <v>120</v>
       </c>
@@ -6292,7 +6294,7 @@
       <c r="G21" s="137">
         <v>333806.03000000003</v>
       </c>
-      <c r="H21" s="215">
+      <c r="H21" s="208">
         <f t="shared" si="3"/>
         <v>333806.03000000003</v>
       </c>
@@ -6324,49 +6326,49 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="57" t="s">
         <v>122</v>
       </c>
       <c r="B22" s="6"/>
-      <c r="C22" s="205" t="s">
+      <c r="C22" s="198" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="206" t="s">
+      <c r="D22" s="199" t="s">
         <v>180</v>
       </c>
-      <c r="E22" s="207" t="s">
+      <c r="E22" s="200" t="s">
         <v>288</v>
       </c>
-      <c r="F22" s="208">
+      <c r="F22" s="201">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G22" s="209">
+      <c r="G22" s="202">
         <v>146444.04</v>
       </c>
-      <c r="H22" s="218">
+      <c r="H22" s="211">
         <v>147222</v>
       </c>
-      <c r="I22" s="210">
+      <c r="I22" s="203">
         <f t="shared" si="0"/>
         <v>-777.95999999999185</v>
       </c>
-      <c r="J22" s="211">
+      <c r="J22" s="204">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K22" s="211">
+      <c r="K22" s="204">
         <f t="shared" si="6"/>
         <v>147271.737246</v>
       </c>
-      <c r="L22" s="212">
-        <v>0</v>
-      </c>
-      <c r="M22" s="213">
+      <c r="L22" s="205">
+        <v>0</v>
+      </c>
+      <c r="M22" s="206">
         <f t="shared" si="8"/>
         <v>146494.04</v>
       </c>
-      <c r="N22" s="213">
+      <c r="N22" s="206">
         <f t="shared" si="7"/>
         <v>155284.04</v>
       </c>
@@ -6378,7 +6380,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="57" t="s">
         <v>122</v>
       </c>
@@ -6398,7 +6400,7 @@
       <c r="G23" s="137">
         <v>156305.04999999999</v>
       </c>
-      <c r="H23" s="215">
+      <c r="H23" s="208">
         <f>19700+136605.05</f>
         <v>156305.04999999999</v>
       </c>
@@ -6428,7 +6430,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="57" t="s">
         <v>122</v>
       </c>
@@ -6448,7 +6450,7 @@
       <c r="G24" s="137">
         <v>148838.06</v>
       </c>
-      <c r="H24" s="215">
+      <c r="H24" s="208">
         <f t="shared" ref="H24" si="10">G24</f>
         <v>148838.06</v>
       </c>
@@ -6480,7 +6482,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="57" t="s">
         <v>120</v>
       </c>
@@ -6500,7 +6502,7 @@
       <c r="G25" s="137">
         <v>300495.07</v>
       </c>
-      <c r="H25" s="215">
+      <c r="H25" s="208">
         <f>G25</f>
         <v>300495.07</v>
       </c>
@@ -6532,7 +6534,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="57" t="s">
         <v>121</v>
       </c>
@@ -6550,7 +6552,7 @@
       <c r="G26" s="137">
         <v>114371.08</v>
       </c>
-      <c r="H26" s="215">
+      <c r="H26" s="208">
         <f>G26</f>
         <v>114371.08</v>
       </c>
@@ -6582,51 +6584,51 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="108" t="s">
         <v>120</v>
       </c>
       <c r="B27" s="35"/>
-      <c r="C27" s="205" t="s">
+      <c r="C27" s="198" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="206" t="s">
+      <c r="D27" s="199" t="s">
         <v>182</v>
       </c>
-      <c r="E27" s="207" t="s">
+      <c r="E27" s="200" t="s">
         <v>361</v>
       </c>
-      <c r="F27" s="208">
+      <c r="F27" s="201">
         <v>1.78E-2</v>
       </c>
-      <c r="G27" s="209">
+      <c r="G27" s="202">
         <v>535348.09</v>
       </c>
-      <c r="H27" s="218">
+      <c r="H27" s="211">
         <f>278876+258100</f>
         <v>536976</v>
       </c>
-      <c r="I27" s="210">
+      <c r="I27" s="203">
         <f t="shared" si="0"/>
         <v>-1627.9100000000326</v>
       </c>
-      <c r="J27" s="211">
+      <c r="J27" s="204">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K27" s="211">
+      <c r="K27" s="204">
         <f t="shared" si="6"/>
         <v>278876.26840200002</v>
       </c>
-      <c r="L27" s="231">
+      <c r="L27" s="223">
         <f>13000*3</f>
         <v>39000</v>
       </c>
-      <c r="M27" s="213">
+      <c r="M27" s="206">
         <f t="shared" si="8"/>
         <v>316248.09000000003</v>
       </c>
-      <c r="N27" s="213">
+      <c r="N27" s="206">
         <f t="shared" si="7"/>
         <v>335223.09000000003</v>
       </c>
@@ -6635,7 +6637,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="108" t="s">
         <v>122</v>
       </c>
@@ -6653,7 +6655,7 @@
       <c r="G28" s="44">
         <v>133172.1</v>
       </c>
-      <c r="H28" s="215">
+      <c r="H28" s="208">
         <f t="shared" ref="H28:H29" si="11">G28</f>
         <v>133172.1</v>
       </c>
@@ -6685,7 +6687,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="108" t="s">
         <v>122</v>
       </c>
@@ -6703,7 +6705,7 @@
       <c r="G29" s="137">
         <v>136305.10999999999</v>
       </c>
-      <c r="H29" s="215">
+      <c r="H29" s="208">
         <f t="shared" si="11"/>
         <v>136305.10999999999</v>
       </c>
@@ -6735,7 +6737,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="108" t="s">
         <v>122</v>
       </c>
@@ -6753,7 +6755,7 @@
       <c r="G30" s="137">
         <v>666589.12</v>
       </c>
-      <c r="H30" s="215"/>
+      <c r="H30" s="208"/>
       <c r="I30" s="144">
         <f t="shared" si="0"/>
         <v>666589.12</v>
@@ -6782,7 +6784,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="108" t="s">
         <v>120</v>
       </c>
@@ -6800,7 +6802,7 @@
       <c r="G31" s="137">
         <v>276942.13</v>
       </c>
-      <c r="H31" s="215">
+      <c r="H31" s="208">
         <f>G31</f>
         <v>276942.13</v>
       </c>
@@ -6832,7 +6834,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="57" t="s">
         <v>121</v>
       </c>
@@ -6852,7 +6854,7 @@
       <c r="G32" s="137">
         <v>112804.14</v>
       </c>
-      <c r="H32" s="215">
+      <c r="H32" s="208">
         <f>G32</f>
         <v>112804.14</v>
       </c>
@@ -6884,7 +6886,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A33" s="57" t="s">
         <v>120</v>
       </c>
@@ -6902,7 +6904,7 @@
       <c r="G33" s="137">
         <v>271043.15000000002</v>
       </c>
-      <c r="H33" s="215">
+      <c r="H33" s="208">
         <f>G33</f>
         <v>271043.15000000002</v>
       </c>
@@ -6934,7 +6936,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A34" s="139" t="s">
         <v>122</v>
       </c>
@@ -6952,7 +6954,7 @@
       <c r="G34" s="137">
         <v>139543.16</v>
       </c>
-      <c r="H34" s="215">
+      <c r="H34" s="208">
         <f>G34</f>
         <v>139543.16</v>
       </c>
@@ -6987,7 +6989,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="35" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A35" s="57" t="s">
         <v>122</v>
       </c>
@@ -7007,7 +7009,7 @@
       <c r="G35" s="137">
         <v>136305.17000000001</v>
       </c>
-      <c r="H35" s="215">
+      <c r="H35" s="208">
         <f t="shared" ref="H35" si="12">G35</f>
         <v>136305.17000000001</v>
       </c>
@@ -7039,7 +7041,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="36" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A36" s="57" t="s">
         <v>122</v>
       </c>
@@ -7057,7 +7059,7 @@
       <c r="G36" s="137">
         <v>148838.18</v>
       </c>
-      <c r="H36" s="215"/>
+      <c r="H36" s="208"/>
       <c r="I36" s="156">
         <f t="shared" si="0"/>
         <v>148838.18</v>
@@ -7086,7 +7088,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A37" s="57" t="s">
         <v>120</v>
       </c>
@@ -7106,7 +7108,7 @@
       <c r="G37" s="137">
         <v>256942.19</v>
       </c>
-      <c r="H37" s="215">
+      <c r="H37" s="208">
         <f t="shared" ref="H37" si="13">G37</f>
         <v>256942.19</v>
       </c>
@@ -7139,7 +7141,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="38" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A38" s="57" t="s">
         <v>121</v>
       </c>
@@ -7157,7 +7159,7 @@
       <c r="G38" s="137">
         <v>112804.2</v>
       </c>
-      <c r="H38" s="215">
+      <c r="H38" s="208">
         <f>G38</f>
         <v>112804.2</v>
       </c>
@@ -7189,7 +7191,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="108" t="s">
         <v>120</v>
       </c>
@@ -7207,7 +7209,7 @@
       <c r="G39" s="137">
         <v>271043.21000000002</v>
       </c>
-      <c r="H39" s="215">
+      <c r="H39" s="208">
         <v>287306.21000000002</v>
       </c>
       <c r="I39" s="144">
@@ -7233,7 +7235,7 @@
         <f t="shared" si="7"/>
         <v>270067.21000000002</v>
       </c>
-      <c r="O39" s="180">
+      <c r="O39" s="173">
         <f t="shared" si="9"/>
         <v>0.21000000000000005</v>
       </c>
@@ -7336,7 +7338,7 @@
       <c r="DH39" s="73"/>
       <c r="DI39" s="73"/>
     </row>
-    <row r="40" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="108" t="s">
         <v>122</v>
       </c>
@@ -7354,7 +7356,7 @@
       <c r="G40" s="44">
         <v>220907.22</v>
       </c>
-      <c r="H40" s="215"/>
+      <c r="H40" s="208"/>
       <c r="I40" s="144">
         <f t="shared" si="0"/>
         <v>220907.22</v>
@@ -7376,7 +7378,7 @@
         <f t="shared" si="7"/>
         <v>390270.22</v>
       </c>
-      <c r="O40" s="180">
+      <c r="O40" s="173">
         <f t="shared" si="9"/>
         <v>0.22000000000000006</v>
       </c>
@@ -7481,7 +7483,7 @@
       <c r="DH40" s="73"/>
       <c r="DI40" s="73"/>
     </row>
-    <row r="41" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="108" t="s">
         <v>122</v>
       </c>
@@ -7499,7 +7501,7 @@
       <c r="G41" s="137">
         <v>136305.23000000001</v>
       </c>
-      <c r="H41" s="215">
+      <c r="H41" s="208">
         <f>G41</f>
         <v>136305.23000000001</v>
       </c>
@@ -7526,7 +7528,7 @@
         <f t="shared" si="7"/>
         <v>144484.23000000001</v>
       </c>
-      <c r="O41" s="180">
+      <c r="O41" s="173">
         <f t="shared" si="9"/>
         <v>0.23000000000000007</v>
       </c>
@@ -7631,7 +7633,7 @@
       <c r="DH41" s="73"/>
       <c r="DI41" s="73"/>
     </row>
-    <row r="42" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="108" t="s">
         <v>122</v>
       </c>
@@ -7649,7 +7651,7 @@
       <c r="G42" s="157">
         <v>148838.24</v>
       </c>
-      <c r="H42" s="215"/>
+      <c r="H42" s="208"/>
       <c r="I42" s="144">
         <f t="shared" si="0"/>
         <v>148838.24</v>
@@ -7673,7 +7675,7 @@
         <f t="shared" si="7"/>
         <v>315538.24</v>
       </c>
-      <c r="O42" s="180">
+      <c r="O42" s="173">
         <f t="shared" si="9"/>
         <v>0.24000000000000007</v>
       </c>
@@ -7776,7 +7778,7 @@
       <c r="DH42" s="73"/>
       <c r="DI42" s="73"/>
     </row>
-    <row r="43" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A43" s="57" t="s">
         <v>120</v>
       </c>
@@ -7794,7 +7796,7 @@
       <c r="G43" s="137">
         <v>256942.25</v>
       </c>
-      <c r="H43" s="215">
+      <c r="H43" s="208">
         <f t="shared" ref="H43" si="14">G43</f>
         <v>256942.25</v>
       </c>
@@ -7826,7 +7828,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A44" s="57" t="s">
         <v>121</v>
       </c>
@@ -7846,7 +7848,7 @@
       <c r="G44" s="137">
         <v>112804.26</v>
       </c>
-      <c r="H44" s="215">
+      <c r="H44" s="208">
         <f t="shared" ref="H44:H45" si="15">G44</f>
         <v>112804.26</v>
       </c>
@@ -7878,7 +7880,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A45" s="57" t="s">
         <v>120</v>
       </c>
@@ -7896,7 +7898,7 @@
       <c r="G45" s="137">
         <v>271043.27</v>
       </c>
-      <c r="H45" s="215">
+      <c r="H45" s="208">
         <f t="shared" si="15"/>
         <v>271043.27</v>
       </c>
@@ -7934,7 +7936,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="46" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A46" s="172" t="s">
         <v>122</v>
       </c>
@@ -7952,7 +7954,7 @@
       <c r="G46" s="137">
         <v>147272.28</v>
       </c>
-      <c r="H46" s="215">
+      <c r="H46" s="208">
         <f>G46</f>
         <v>147272.28</v>
       </c>
@@ -7984,7 +7986,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="47" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A47" s="57" t="s">
         <v>122</v>
       </c>
@@ -8004,7 +8006,7 @@
       <c r="G47" s="147">
         <v>136305.29</v>
       </c>
-      <c r="H47" s="215"/>
+      <c r="H47" s="208"/>
       <c r="I47" s="144">
         <f t="shared" si="0"/>
         <v>136305.29</v>
@@ -8033,7 +8035,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="48" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A48" s="57" t="s">
         <v>122</v>
       </c>
@@ -8051,7 +8053,7 @@
       <c r="G48" s="137">
         <v>148838.29999999999</v>
       </c>
-      <c r="H48" s="215">
+      <c r="H48" s="208">
         <f>G48</f>
         <v>148838.29999999999</v>
       </c>
@@ -8083,7 +8085,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="57" t="s">
         <v>120</v>
       </c>
@@ -8101,7 +8103,7 @@
       <c r="G49" s="137">
         <v>256942.31</v>
       </c>
-      <c r="H49" s="215">
+      <c r="H49" s="208">
         <f t="shared" ref="H49:H50" si="16">G49</f>
         <v>256942.31</v>
       </c>
@@ -8133,7 +8135,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="57" t="s">
         <v>121</v>
       </c>
@@ -8151,7 +8153,7 @@
       <c r="G50" s="137">
         <v>127620.32</v>
       </c>
-      <c r="H50" s="215">
+      <c r="H50" s="208">
         <f t="shared" si="16"/>
         <v>127620.32</v>
       </c>
@@ -8182,7 +8184,7 @@
       </c>
       <c r="P50" s="43"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="57" t="s">
         <v>120</v>
       </c>
@@ -8200,7 +8202,7 @@
       <c r="G51" s="137">
         <v>271043.33</v>
       </c>
-      <c r="H51" s="215">
+      <c r="H51" s="208">
         <f>G51</f>
         <v>271043.33</v>
       </c>
@@ -8233,7 +8235,7 @@
       </c>
       <c r="P51" s="43"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="57" t="s">
         <v>122</v>
       </c>
@@ -8251,7 +8253,7 @@
       <c r="G52" s="137">
         <v>147272.34</v>
       </c>
-      <c r="H52" s="215">
+      <c r="H52" s="208">
         <f>G52</f>
         <v>147272.34</v>
       </c>
@@ -8284,7 +8286,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="57" t="s">
         <v>122</v>
       </c>
@@ -8302,7 +8304,7 @@
       <c r="G53" s="137">
         <v>136305.35</v>
       </c>
-      <c r="H53" s="215">
+      <c r="H53" s="208">
         <f t="shared" ref="H53" si="19">G53</f>
         <v>136305.35</v>
       </c>
@@ -8334,7 +8336,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="57" t="s">
         <v>122</v>
       </c>
@@ -8352,7 +8354,7 @@
       <c r="G54" s="137">
         <v>122573.36</v>
       </c>
-      <c r="H54" s="215">
+      <c r="H54" s="208">
         <f>G54</f>
         <v>122573.36</v>
       </c>
@@ -8384,7 +8386,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="57" t="s">
         <v>120</v>
       </c>
@@ -8402,7 +8404,7 @@
       <c r="G55" s="137">
         <v>256942.37</v>
       </c>
-      <c r="H55" s="215">
+      <c r="H55" s="208">
         <f t="shared" ref="H55:H56" si="20">G55</f>
         <v>256942.37</v>
       </c>
@@ -8435,7 +8437,7 @@
       </c>
       <c r="Q55" s="59"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="57" t="s">
         <v>121</v>
       </c>
@@ -8455,7 +8457,7 @@
       <c r="G56" s="137">
         <v>112804.38</v>
       </c>
-      <c r="H56" s="215">
+      <c r="H56" s="208">
         <f t="shared" si="20"/>
         <v>112804.38</v>
       </c>
@@ -8487,47 +8489,47 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="57" t="s">
         <v>120</v>
       </c>
       <c r="B57" s="6"/>
-      <c r="C57" s="205" t="s">
+      <c r="C57" s="198" t="s">
         <v>82</v>
       </c>
-      <c r="D57" s="206" t="s">
+      <c r="D57" s="199" t="s">
         <v>197</v>
       </c>
-      <c r="E57" s="207"/>
-      <c r="F57" s="208">
+      <c r="E57" s="200"/>
+      <c r="F57" s="201">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="G57" s="209">
+      <c r="G57" s="202">
         <v>271043.39</v>
       </c>
-      <c r="H57" s="218">
+      <c r="H57" s="211">
         <v>271043</v>
       </c>
-      <c r="I57" s="210">
+      <c r="I57" s="203">
         <f t="shared" si="0"/>
         <v>0.39000000001396984</v>
       </c>
-      <c r="J57" s="211">
+      <c r="J57" s="204">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K57" s="211">
+      <c r="K57" s="204">
         <f t="shared" si="18"/>
         <v>271042.66535699996</v>
       </c>
-      <c r="L57" s="212">
-        <v>0</v>
-      </c>
-      <c r="M57" s="213">
+      <c r="L57" s="205">
+        <v>0</v>
+      </c>
+      <c r="M57" s="206">
         <f t="shared" si="8"/>
         <v>271043.39</v>
       </c>
-      <c r="N57" s="213">
+      <c r="N57" s="206">
         <f t="shared" si="7"/>
         <v>287306.39</v>
       </c>
@@ -8536,7 +8538,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="57" t="s">
         <v>122</v>
       </c>
@@ -8556,7 +8558,7 @@
       <c r="G58" s="137">
         <v>147272.4</v>
       </c>
-      <c r="H58" s="215">
+      <c r="H58" s="208">
         <f t="shared" ref="H58" si="21">G58</f>
         <v>147272.4</v>
       </c>
@@ -8572,7 +8574,7 @@
         <f t="shared" si="18"/>
         <v>147271.737246</v>
       </c>
-      <c r="L58" s="231">
+      <c r="L58" s="223">
         <f>13000*2</f>
         <v>26000</v>
       </c>
@@ -8589,48 +8591,48 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="108" t="s">
         <v>122</v>
       </c>
       <c r="B59" s="35"/>
-      <c r="C59" s="171" t="s">
+      <c r="C59" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D59" s="172" t="s">
-        <v>119</v>
-      </c>
-      <c r="E59" s="173"/>
-      <c r="F59" s="174">
+      <c r="D59" s="108" t="s">
+        <v>366</v>
+      </c>
+      <c r="E59" s="135"/>
+      <c r="F59" s="136">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G59" s="175">
+      <c r="G59" s="137">
         <v>136305.41</v>
       </c>
-      <c r="H59" s="219">
+      <c r="H59" s="208">
         <f>G59</f>
         <v>136305.41</v>
       </c>
-      <c r="I59" s="176">
+      <c r="I59" s="144">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J59" s="177">
+      <c r="J59" s="145">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K59" s="177">
+      <c r="K59" s="145">
         <f t="shared" si="18"/>
         <v>136304.69298299999</v>
       </c>
-      <c r="L59" s="178">
-        <v>0</v>
-      </c>
-      <c r="M59" s="179">
+      <c r="L59" s="168">
+        <v>0</v>
+      </c>
+      <c r="M59" s="147">
         <f t="shared" si="8"/>
         <v>136305.41</v>
       </c>
-      <c r="N59" s="179">
+      <c r="N59" s="147">
         <f t="shared" si="7"/>
         <v>144484.41</v>
       </c>
@@ -8642,7 +8644,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="108" t="s">
         <v>122</v>
       </c>
@@ -8660,7 +8662,7 @@
       <c r="G60" s="137">
         <v>148838.42000000001</v>
       </c>
-      <c r="H60" s="215">
+      <c r="H60" s="208">
         <f t="shared" ref="H60" si="22">G60</f>
         <v>148838.42000000001</v>
       </c>
@@ -8693,7 +8695,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="108" t="s">
         <v>120</v>
       </c>
@@ -8711,7 +8713,7 @@
       <c r="G61" s="137">
         <v>256942.43</v>
       </c>
-      <c r="H61" s="215">
+      <c r="H61" s="208">
         <f t="shared" ref="H61:H65" si="23">G61</f>
         <v>256942.43</v>
       </c>
@@ -8743,7 +8745,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="108" t="s">
         <v>121</v>
       </c>
@@ -8761,7 +8763,7 @@
       <c r="G62" s="137">
         <v>112804.44</v>
       </c>
-      <c r="H62" s="215">
+      <c r="H62" s="208">
         <f t="shared" si="23"/>
         <v>112804.44</v>
       </c>
@@ -8793,7 +8795,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="57" t="s">
         <v>120</v>
       </c>
@@ -8811,7 +8813,7 @@
       <c r="G63" s="137">
         <v>271043.45</v>
       </c>
-      <c r="H63" s="215">
+      <c r="H63" s="208">
         <f>G63</f>
         <v>271043.45</v>
       </c>
@@ -8843,7 +8845,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="57" t="s">
         <v>122</v>
       </c>
@@ -8863,7 +8865,7 @@
       <c r="G64" s="137">
         <v>283572.46000000002</v>
       </c>
-      <c r="H64" s="215">
+      <c r="H64" s="208">
         <v>147272.46</v>
       </c>
       <c r="I64" s="144">
@@ -8878,23 +8880,24 @@
         <f t="shared" si="18"/>
         <v>147271.737246</v>
       </c>
-      <c r="L64" s="231">
-        <v>13000</v>
+      <c r="L64" s="282">
+        <f>13000+K64*0.1</f>
+        <v>27727.173724600001</v>
       </c>
       <c r="M64" s="147">
         <f t="shared" si="8"/>
-        <v>296572.46000000002</v>
+        <v>311299.46000000002</v>
       </c>
       <c r="N64" s="147">
         <f t="shared" si="7"/>
-        <v>314367.46000000002</v>
-      </c>
-      <c r="O64" s="180">
+        <v>329977.46000000002</v>
+      </c>
+      <c r="O64" s="173">
         <f t="shared" si="9"/>
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" s="57" t="s">
         <v>122</v>
       </c>
@@ -8912,7 +8915,7 @@
       <c r="G65" s="137">
         <v>144484.47</v>
       </c>
-      <c r="H65" s="215">
+      <c r="H65" s="208">
         <f t="shared" si="23"/>
         <v>144484.47</v>
       </c>
@@ -8939,12 +8942,12 @@
         <f t="shared" si="7"/>
         <v>144484.47</v>
       </c>
-      <c r="O65" s="180">
+      <c r="O65" s="173">
         <f t="shared" si="9"/>
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="57" t="s">
         <v>122</v>
       </c>
@@ -8962,7 +8965,7 @@
       <c r="G66" s="137">
         <v>167838.48</v>
       </c>
-      <c r="H66" s="215">
+      <c r="H66" s="208">
         <v>148838.48000000001</v>
       </c>
       <c r="I66" s="144">
@@ -8988,13 +8991,13 @@
         <f t="shared" si="7"/>
         <v>177909.48</v>
       </c>
-      <c r="O66" s="180">
+      <c r="O66" s="173">
         <f t="shared" si="9"/>
         <v>0.48000000000000026</v>
       </c>
-      <c r="R66" s="190"/>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R66" s="183"/>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" s="57" t="s">
         <v>120</v>
       </c>
@@ -9012,7 +9015,7 @@
       <c r="G67" s="137">
         <v>268942.49</v>
       </c>
-      <c r="H67" s="215">
+      <c r="H67" s="208">
         <f t="shared" ref="H67" si="24">G67</f>
         <v>268942.49</v>
       </c>
@@ -9043,7 +9046,7 @@
       </c>
       <c r="R67" s="43"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" s="139" t="s">
         <v>121</v>
       </c>
@@ -9061,7 +9064,7 @@
       <c r="G68" s="137">
         <v>556636.5</v>
       </c>
-      <c r="H68" s="215"/>
+      <c r="H68" s="208"/>
       <c r="I68" s="144">
         <f t="shared" si="0"/>
         <v>556636.5</v>
@@ -9090,7 +9093,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" s="57" t="s">
         <v>120</v>
       </c>
@@ -9108,7 +9111,7 @@
       <c r="G69" s="137">
         <v>271043.51</v>
       </c>
-      <c r="H69" s="215">
+      <c r="H69" s="208">
         <f t="shared" ref="H69" si="25">G69</f>
         <v>271043.51</v>
       </c>
@@ -9140,7 +9143,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" s="57" t="s">
         <v>122</v>
       </c>
@@ -9158,7 +9161,7 @@
       <c r="G70" s="137">
         <v>419357.52</v>
       </c>
-      <c r="H70" s="215">
+      <c r="H70" s="208">
         <f>G70</f>
         <v>419357.52</v>
       </c>
@@ -9190,7 +9193,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71" s="57" t="s">
         <v>122</v>
       </c>
@@ -9208,7 +9211,7 @@
       <c r="G71" s="137">
         <v>136305.53</v>
       </c>
-      <c r="H71" s="215">
+      <c r="H71" s="208">
         <f t="shared" ref="H71:H73" si="26">G71</f>
         <v>136305.53</v>
       </c>
@@ -9243,7 +9246,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" s="57" t="s">
         <v>122</v>
       </c>
@@ -9261,7 +9264,7 @@
       <c r="G72" s="137">
         <v>148838.54</v>
       </c>
-      <c r="H72" s="215">
+      <c r="H72" s="208">
         <f t="shared" si="26"/>
         <v>148838.54</v>
       </c>
@@ -9293,7 +9296,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" s="57" t="s">
         <v>123</v>
       </c>
@@ -9311,7 +9314,7 @@
       <c r="G73" s="137">
         <v>388179.55</v>
       </c>
-      <c r="H73" s="215">
+      <c r="H73" s="208">
         <f t="shared" si="26"/>
         <v>388179.55</v>
       </c>
@@ -9342,7 +9345,7 @@
       </c>
       <c r="P73" s="73"/>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" s="57" t="s">
         <v>120</v>
       </c>
@@ -9360,7 +9363,7 @@
       <c r="G74" s="137">
         <v>271043.56</v>
       </c>
-      <c r="H74" s="215">
+      <c r="H74" s="208">
         <f>G74</f>
         <v>271043.56</v>
       </c>
@@ -9392,7 +9395,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" s="57" t="s">
         <v>122</v>
       </c>
@@ -9410,7 +9413,7 @@
       <c r="G75" s="137">
         <v>147272.57</v>
       </c>
-      <c r="H75" s="215">
+      <c r="H75" s="208">
         <f>G75</f>
         <v>147272.57</v>
       </c>
@@ -9442,7 +9445,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" s="57" t="s">
         <v>122</v>
       </c>
@@ -9462,7 +9465,7 @@
       <c r="G76" s="137">
         <v>136305.57999999999</v>
       </c>
-      <c r="H76" s="215"/>
+      <c r="H76" s="208"/>
       <c r="I76" s="144">
         <f t="shared" si="0"/>
         <v>136305.57999999999</v>
@@ -9491,7 +9494,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="57" t="s">
         <v>122</v>
       </c>
@@ -9509,7 +9512,7 @@
       <c r="G77" s="137">
         <v>149007.59</v>
       </c>
-      <c r="H77" s="215">
+      <c r="H77" s="208">
         <f>G77</f>
         <v>149007.59</v>
       </c>
@@ -9541,7 +9544,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" s="57" t="s">
         <v>123</v>
       </c>
@@ -9559,7 +9562,7 @@
       <c r="G78" s="137">
         <v>368179.6</v>
       </c>
-      <c r="H78" s="215">
+      <c r="H78" s="208">
         <f>G78</f>
         <v>368179.6</v>
       </c>
@@ -9591,7 +9594,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" s="57" t="s">
         <v>120</v>
       </c>
@@ -9609,7 +9612,7 @@
       <c r="G79" s="137">
         <v>271043.61</v>
       </c>
-      <c r="H79" s="215">
+      <c r="H79" s="208">
         <f t="shared" ref="H79" si="27">G79</f>
         <v>271043.61</v>
       </c>
@@ -9641,7 +9644,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" s="57" t="s">
         <v>122</v>
       </c>
@@ -9659,7 +9662,7 @@
       <c r="G80" s="137">
         <v>408372.62</v>
       </c>
-      <c r="H80" s="215"/>
+      <c r="H80" s="208"/>
       <c r="I80" s="144">
         <f t="shared" si="0"/>
         <v>408372.62</v>
@@ -9688,50 +9691,50 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="57" t="s">
         <v>122</v>
       </c>
       <c r="B81" s="6"/>
-      <c r="C81" s="205" t="s">
+      <c r="C81" s="198" t="s">
         <v>106</v>
       </c>
-      <c r="D81" s="206" t="s">
+      <c r="D81" s="199" t="s">
         <v>216</v>
       </c>
-      <c r="E81" s="207" t="s">
+      <c r="E81" s="200" t="s">
         <v>275</v>
       </c>
-      <c r="F81" s="208">
+      <c r="F81" s="201">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G81" s="209">
+      <c r="G81" s="202">
         <v>204457.63</v>
       </c>
-      <c r="H81" s="218">
+      <c r="H81" s="211">
         <f t="shared" ref="H81" si="28">G81</f>
         <v>204457.63</v>
       </c>
-      <c r="I81" s="210">
+      <c r="I81" s="203">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J81" s="211">
+      <c r="J81" s="204">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="K81" s="211">
+      <c r="K81" s="204">
         <f t="shared" si="18"/>
         <v>136304.69298299999</v>
       </c>
-      <c r="L81" s="212">
+      <c r="L81" s="205">
         <v>20000</v>
       </c>
-      <c r="M81" s="213">
+      <c r="M81" s="206">
         <f t="shared" si="8"/>
         <v>156305.63</v>
       </c>
-      <c r="N81" s="213">
+      <c r="N81" s="206">
         <f t="shared" si="7"/>
         <v>165684.63</v>
       </c>
@@ -9740,7 +9743,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="57" t="s">
         <v>122</v>
       </c>
@@ -9758,7 +9761,7 @@
       <c r="G82" s="137">
         <v>148838.64000000001</v>
       </c>
-      <c r="H82" s="215">
+      <c r="H82" s="208">
         <f>G82</f>
         <v>148838.64000000001</v>
       </c>
@@ -9793,7 +9796,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="57" t="s">
         <v>123</v>
       </c>
@@ -9811,7 +9814,7 @@
       <c r="G83" s="137">
         <v>368179.65</v>
       </c>
-      <c r="H83" s="215">
+      <c r="H83" s="208">
         <f t="shared" ref="H83:H96" si="29">G83</f>
         <v>368179.65</v>
       </c>
@@ -9843,7 +9846,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="57" t="s">
         <v>120</v>
       </c>
@@ -9861,7 +9864,7 @@
       <c r="G84" s="137">
         <v>311043.65999999997</v>
       </c>
-      <c r="H84" s="215">
+      <c r="H84" s="208">
         <f t="shared" si="29"/>
         <v>311043.65999999997</v>
       </c>
@@ -9891,7 +9894,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="57" t="s">
         <v>122</v>
       </c>
@@ -9909,7 +9912,7 @@
       <c r="G85" s="137">
         <v>147272.67000000001</v>
       </c>
-      <c r="H85" s="215">
+      <c r="H85" s="208">
         <f t="shared" si="29"/>
         <v>147272.67000000001</v>
       </c>
@@ -9939,7 +9942,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="57" t="s">
         <v>122</v>
       </c>
@@ -9957,7 +9960,7 @@
       <c r="G86" s="137">
         <v>136305.68</v>
       </c>
-      <c r="H86" s="215">
+      <c r="H86" s="208">
         <f>G86</f>
         <v>136305.68</v>
       </c>
@@ -9989,7 +9992,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="108" t="s">
         <v>122</v>
       </c>
@@ -10007,7 +10010,7 @@
       <c r="G87" s="137">
         <v>148838.69</v>
       </c>
-      <c r="H87" s="215">
+      <c r="H87" s="208">
         <f>G87</f>
         <v>148838.69</v>
       </c>
@@ -10039,7 +10042,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="108"/>
       <c r="B88" s="35"/>
       <c r="C88" s="35" t="s">
@@ -10055,7 +10058,7 @@
       <c r="G88" s="137">
         <v>36035.699999999997</v>
       </c>
-      <c r="H88" s="215">
+      <c r="H88" s="208">
         <f>G88</f>
         <v>36035.699999999997</v>
       </c>
@@ -10087,7 +10090,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="108"/>
       <c r="B89" s="35"/>
       <c r="C89" s="35" t="s">
@@ -10103,7 +10106,7 @@
       <c r="G89" s="137">
         <v>36035.71</v>
       </c>
-      <c r="H89" s="215">
+      <c r="H89" s="208">
         <f t="shared" si="29"/>
         <v>36035.71</v>
       </c>
@@ -10135,7 +10138,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="108"/>
       <c r="B90" s="35"/>
       <c r="C90" s="35" t="s">
@@ -10151,7 +10154,7 @@
       <c r="G90" s="137">
         <v>38198.720000000001</v>
       </c>
-      <c r="H90" s="215">
+      <c r="H90" s="208">
         <f t="shared" si="29"/>
         <v>38198.720000000001</v>
       </c>
@@ -10183,7 +10186,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="108"/>
       <c r="B91" s="35"/>
       <c r="C91" s="35" t="s">
@@ -10199,7 +10202,7 @@
       <c r="G91" s="137">
         <v>36035.730000000003</v>
       </c>
-      <c r="H91" s="215">
+      <c r="H91" s="208">
         <f t="shared" si="29"/>
         <v>36035.730000000003</v>
       </c>
@@ -10231,46 +10234,46 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="108"/>
       <c r="B92" s="35"/>
-      <c r="C92" s="183" t="s">
+      <c r="C92" s="176" t="s">
         <v>128</v>
       </c>
-      <c r="D92" s="184" t="s">
+      <c r="D92" s="177" t="s">
         <v>199</v>
       </c>
-      <c r="E92" s="184"/>
-      <c r="F92" s="185">
+      <c r="E92" s="177"/>
+      <c r="F92" s="178">
         <v>2.3E-3</v>
       </c>
       <c r="G92" s="44">
         <v>36035.74</v>
       </c>
-      <c r="H92" s="215">
+      <c r="H92" s="208">
         <f t="shared" si="29"/>
         <v>36035.74</v>
       </c>
-      <c r="I92" s="186">
+      <c r="I92" s="179">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J92" s="187">
+      <c r="J92" s="180">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K92" s="187">
+      <c r="K92" s="180">
         <f t="shared" si="31"/>
         <v>36034.574006999996</v>
       </c>
-      <c r="L92" s="188">
-        <v>0</v>
-      </c>
-      <c r="M92" s="189">
+      <c r="L92" s="181">
+        <v>0</v>
+      </c>
+      <c r="M92" s="182">
         <f t="shared" si="32"/>
         <v>36035.74</v>
       </c>
-      <c r="N92" s="189">
+      <c r="N92" s="182">
         <f t="shared" si="33"/>
         <v>38198.74</v>
       </c>
@@ -10282,7 +10285,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="108"/>
       <c r="B93" s="35"/>
       <c r="C93" s="35" t="s">
@@ -10298,7 +10301,7 @@
       <c r="G93" s="44">
         <v>36035.75</v>
       </c>
-      <c r="H93" s="215">
+      <c r="H93" s="208">
         <v>38198.75</v>
       </c>
       <c r="I93" s="144">
@@ -10329,7 +10332,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" s="108"/>
       <c r="B94" s="35"/>
       <c r="C94" s="35" t="s">
@@ -10345,7 +10348,7 @@
       <c r="G94" s="137">
         <v>36035.760000000002</v>
       </c>
-      <c r="H94" s="215">
+      <c r="H94" s="208">
         <f t="shared" si="29"/>
         <v>36035.760000000002</v>
       </c>
@@ -10377,7 +10380,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="108"/>
       <c r="B95" s="35"/>
       <c r="C95" s="35" t="s">
@@ -10393,7 +10396,7 @@
       <c r="G95" s="137">
         <v>36035.769999999997</v>
       </c>
-      <c r="H95" s="215">
+      <c r="H95" s="208">
         <f t="shared" si="29"/>
         <v>36035.769999999997</v>
       </c>
@@ -10425,7 +10428,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" s="108"/>
       <c r="B96" s="35"/>
       <c r="C96" s="35" t="s">
@@ -10441,7 +10444,7 @@
       <c r="G96" s="137">
         <v>36035.78</v>
       </c>
-      <c r="H96" s="215">
+      <c r="H96" s="208">
         <f t="shared" si="29"/>
         <v>36035.78</v>
       </c>
@@ -10473,7 +10476,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="108"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35" t="s">
@@ -10489,7 +10492,7 @@
       <c r="G97" s="137">
         <v>177818.79</v>
       </c>
-      <c r="H97" s="215"/>
+      <c r="H97" s="208"/>
       <c r="I97" s="144">
         <f t="shared" si="0"/>
         <v>177818.79</v>
@@ -10518,7 +10521,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="108"/>
       <c r="B98" s="35"/>
       <c r="C98" s="35" t="s">
@@ -10534,7 +10537,7 @@
       <c r="G98" s="137">
         <v>36035.800000000003</v>
       </c>
-      <c r="H98" s="215">
+      <c r="H98" s="208">
         <f>G98</f>
         <v>36035.800000000003</v>
       </c>
@@ -10566,7 +10569,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="108"/>
       <c r="B99" s="35"/>
       <c r="C99" s="35" t="s">
@@ -10582,7 +10585,7 @@
       <c r="G99" s="134">
         <v>36035.81</v>
       </c>
-      <c r="H99" s="215"/>
+      <c r="H99" s="208"/>
       <c r="I99" s="56">
         <f t="shared" si="0"/>
         <v>36035.81</v>
@@ -10611,7 +10614,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="108"/>
       <c r="B100" s="35"/>
       <c r="C100" s="35" t="s">
@@ -10627,7 +10630,7 @@
       <c r="G100" s="134">
         <v>36035.82</v>
       </c>
-      <c r="H100" s="215">
+      <c r="H100" s="208">
         <f t="shared" ref="H100:H104" si="35">G100</f>
         <v>36035.82</v>
       </c>
@@ -10659,7 +10662,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="108"/>
       <c r="B101" s="35"/>
       <c r="C101" s="35" t="s">
@@ -10675,7 +10678,7 @@
       <c r="G101" s="137">
         <v>36035.83</v>
       </c>
-      <c r="H101" s="215">
+      <c r="H101" s="208">
         <f t="shared" si="35"/>
         <v>36035.83</v>
       </c>
@@ -10707,7 +10710,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="108"/>
       <c r="B102" s="35"/>
       <c r="C102" s="35" t="s">
@@ -10723,7 +10726,7 @@
       <c r="G102" s="137">
         <v>36035.839999999997</v>
       </c>
-      <c r="H102" s="215">
+      <c r="H102" s="208">
         <f t="shared" si="35"/>
         <v>36035.839999999997</v>
       </c>
@@ -10755,7 +10758,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="108"/>
       <c r="B103" s="35"/>
       <c r="C103" s="35" t="s">
@@ -10771,7 +10774,7 @@
       <c r="G103" s="137">
         <v>36035.85</v>
       </c>
-      <c r="H103" s="215">
+      <c r="H103" s="208">
         <f t="shared" si="35"/>
         <v>36035.85</v>
       </c>
@@ -10803,7 +10806,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="108"/>
       <c r="B104" s="35"/>
       <c r="C104" s="35" t="s">
@@ -10819,7 +10822,7 @@
       <c r="G104" s="134">
         <v>36035.86</v>
       </c>
-      <c r="H104" s="215">
+      <c r="H104" s="208">
         <f t="shared" si="35"/>
         <v>36035.86</v>
       </c>
@@ -10851,7 +10854,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="108"/>
       <c r="B105" s="35"/>
       <c r="C105" s="35" t="s">
@@ -10867,7 +10870,7 @@
       <c r="G105" s="134">
         <v>36035.870000000003</v>
       </c>
-      <c r="H105" s="220">
+      <c r="H105" s="212">
         <f t="shared" ref="H105:H110" si="36">G105</f>
         <v>36035.870000000003</v>
       </c>
@@ -10899,7 +10902,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="108"/>
       <c r="B106" s="35"/>
       <c r="C106" s="35" t="s">
@@ -10915,7 +10918,7 @@
       <c r="G106" s="134">
         <v>36076.879999999997</v>
       </c>
-      <c r="H106" s="220">
+      <c r="H106" s="212">
         <f>G106</f>
         <v>36076.879999999997</v>
       </c>
@@ -10947,7 +10950,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="108"/>
       <c r="B107" s="35"/>
       <c r="C107" s="35" t="s">
@@ -10963,7 +10966,7 @@
       <c r="G107" s="134">
         <v>40635.89</v>
       </c>
-      <c r="H107" s="220">
+      <c r="H107" s="212">
         <v>36035.89</v>
       </c>
       <c r="I107" s="56">
@@ -10994,7 +10997,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="108"/>
       <c r="B108" s="35"/>
       <c r="C108" s="35" t="s">
@@ -11010,7 +11013,7 @@
       <c r="G108" s="134">
         <v>36035.9</v>
       </c>
-      <c r="H108" s="215">
+      <c r="H108" s="208">
         <f t="shared" ref="H108" si="37">G108</f>
         <v>36035.9</v>
       </c>
@@ -11042,7 +11045,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="108"/>
       <c r="B109" s="35"/>
       <c r="C109" s="35" t="s">
@@ -11058,7 +11061,7 @@
       <c r="G109" s="134">
         <v>38198.910000000003</v>
       </c>
-      <c r="H109" s="215">
+      <c r="H109" s="208">
         <f t="shared" si="36"/>
         <v>38198.910000000003</v>
       </c>
@@ -11090,7 +11093,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="108"/>
       <c r="B110" s="35"/>
       <c r="C110" s="35" t="s">
@@ -11106,7 +11109,7 @@
       <c r="G110" s="137">
         <v>36035.919999999998</v>
       </c>
-      <c r="H110" s="215">
+      <c r="H110" s="208">
         <f t="shared" si="36"/>
         <v>36035.919999999998</v>
       </c>
@@ -11138,7 +11141,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="108"/>
       <c r="B111" s="35"/>
       <c r="C111" s="35" t="s">
@@ -11154,7 +11157,7 @@
       <c r="G111" s="137">
         <v>36035.93</v>
       </c>
-      <c r="H111" s="215">
+      <c r="H111" s="208">
         <f>G111</f>
         <v>36035.93</v>
       </c>
@@ -11186,7 +11189,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="108"/>
       <c r="B112" s="35"/>
       <c r="C112" s="35" t="s">
@@ -11202,7 +11205,7 @@
       <c r="G112" s="137">
         <v>69386.94</v>
       </c>
-      <c r="H112" s="215">
+      <c r="H112" s="208">
         <f>G112</f>
         <v>69386.94</v>
       </c>
@@ -11234,7 +11237,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="108"/>
       <c r="B113" s="35"/>
       <c r="C113" s="35" t="s">
@@ -11250,7 +11253,7 @@
       <c r="G113" s="137">
         <v>36035.949999999997</v>
       </c>
-      <c r="H113" s="215">
+      <c r="H113" s="208">
         <f t="shared" ref="H113" si="38">G113</f>
         <v>36035.949999999997</v>
       </c>
@@ -11282,7 +11285,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="108"/>
       <c r="B114" s="35"/>
       <c r="C114" s="35" t="s">
@@ -11298,7 +11301,7 @@
       <c r="G114" s="137">
         <v>36035.96</v>
       </c>
-      <c r="H114" s="215">
+      <c r="H114" s="208">
         <f>G114</f>
         <v>36035.96</v>
       </c>
@@ -11330,7 +11333,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="108"/>
       <c r="B115" s="35"/>
       <c r="C115" s="35" t="s">
@@ -11346,7 +11349,7 @@
       <c r="G115" s="137">
         <v>36035.97</v>
       </c>
-      <c r="H115" s="215">
+      <c r="H115" s="208">
         <f t="shared" ref="H115" si="39">G115</f>
         <v>36035.97</v>
       </c>
@@ -11378,7 +11381,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="108"/>
       <c r="B116" s="35"/>
       <c r="C116" s="35" t="s">
@@ -11396,7 +11399,7 @@
       <c r="G116" s="137">
         <v>38198.980000000003</v>
       </c>
-      <c r="H116" s="215">
+      <c r="H116" s="208">
         <f>G116</f>
         <v>38198.980000000003</v>
       </c>
@@ -11428,7 +11431,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" s="108"/>
       <c r="B117" s="35"/>
       <c r="C117" s="35" t="s">
@@ -11444,7 +11447,7 @@
       <c r="G117" s="137">
         <v>69189.990000000005</v>
       </c>
-      <c r="H117" s="215"/>
+      <c r="H117" s="208"/>
       <c r="I117" s="144">
         <f t="shared" si="0"/>
         <v>69189.990000000005</v>
@@ -11473,7 +11476,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="108"/>
       <c r="B118" s="35"/>
       <c r="C118" s="35" t="s">
@@ -11489,7 +11492,7 @@
       <c r="G118" s="137">
         <v>36036</v>
       </c>
-      <c r="H118" s="215">
+      <c r="H118" s="208">
         <f t="shared" ref="H118:H120" si="42">G118</f>
         <v>36036</v>
       </c>
@@ -11524,7 +11527,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="127"/>
       <c r="B119" s="35"/>
       <c r="C119" s="35" t="s">
@@ -11540,7 +11543,7 @@
       <c r="G119" s="137">
         <v>36036.01</v>
       </c>
-      <c r="H119" s="215">
+      <c r="H119" s="208">
         <f t="shared" si="42"/>
         <v>36036.01</v>
       </c>
@@ -11572,7 +11575,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="127"/>
       <c r="B120" s="35"/>
       <c r="C120" s="35" t="s">
@@ -11588,7 +11591,7 @@
       <c r="G120" s="137">
         <v>36036.019999999997</v>
       </c>
-      <c r="H120" s="215">
+      <c r="H120" s="208">
         <f t="shared" si="42"/>
         <v>36036.019999999997</v>
       </c>
@@ -11620,7 +11623,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" s="127"/>
       <c r="B121" s="35"/>
       <c r="C121" s="35" t="s">
@@ -11636,7 +11639,7 @@
       <c r="G121" s="137">
         <v>28236.03</v>
       </c>
-      <c r="H121" s="215">
+      <c r="H121" s="208">
         <f>G121</f>
         <v>28236.03</v>
       </c>
@@ -11668,7 +11671,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" s="127"/>
       <c r="B122" s="35"/>
       <c r="C122" s="35" t="s">
@@ -11684,7 +11687,7 @@
       <c r="G122" s="137">
         <v>36036.04</v>
       </c>
-      <c r="H122" s="215">
+      <c r="H122" s="208">
         <f>G122</f>
         <v>36036.04</v>
       </c>
@@ -11716,7 +11719,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" s="127"/>
       <c r="B123" s="35"/>
       <c r="C123" s="35" t="s">
@@ -11732,7 +11735,7 @@
       <c r="G123" s="137">
         <v>36036.050000000003</v>
       </c>
-      <c r="H123" s="215">
+      <c r="H123" s="208">
         <f>G123</f>
         <v>36036.050000000003</v>
       </c>
@@ -11764,7 +11767,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" s="127"/>
       <c r="B124" s="35"/>
       <c r="C124" s="35" t="s">
@@ -11780,7 +11783,7 @@
       <c r="G124" s="137">
         <v>15336.06</v>
       </c>
-      <c r="H124" s="215">
+      <c r="H124" s="208">
         <f>G124</f>
         <v>15336.06</v>
       </c>
@@ -11815,8 +11818,8 @@
         <v>322</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A125" s="182"/>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A125" s="175"/>
       <c r="B125" s="170"/>
       <c r="C125" s="35" t="s">
         <v>161</v>
@@ -11833,7 +11836,7 @@
       <c r="G125" s="137">
         <v>59040.07</v>
       </c>
-      <c r="H125" s="215">
+      <c r="H125" s="208">
         <v>36035</v>
       </c>
       <c r="I125" s="144">
@@ -11864,8 +11867,8 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A126" s="182"/>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A126" s="175"/>
       <c r="B126" s="170"/>
       <c r="C126" s="35" t="s">
         <v>162</v>
@@ -11880,7 +11883,7 @@
       <c r="G126" s="137">
         <v>36036.080000000002</v>
       </c>
-      <c r="H126" s="215">
+      <c r="H126" s="208">
         <f t="shared" ref="H126:H127" si="43">G126</f>
         <v>36036.080000000002</v>
       </c>
@@ -11912,7 +11915,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127" s="127"/>
       <c r="B127" s="35"/>
       <c r="C127" s="35" t="s">
@@ -11928,7 +11931,7 @@
       <c r="G127" s="137">
         <v>36036.089999999997</v>
       </c>
-      <c r="H127" s="215">
+      <c r="H127" s="208">
         <f t="shared" si="43"/>
         <v>36036.089999999997</v>
       </c>
@@ -11960,7 +11963,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128" s="127"/>
       <c r="B128" s="35"/>
       <c r="C128" s="35" t="s">
@@ -11976,7 +11979,7 @@
       <c r="G128" s="134">
         <v>36036.1</v>
       </c>
-      <c r="H128" s="215">
+      <c r="H128" s="208">
         <f>G128</f>
         <v>36036.1</v>
       </c>
@@ -12008,7 +12011,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A129" s="127"/>
       <c r="B129" s="35"/>
       <c r="C129" s="35" t="s">
@@ -12024,7 +12027,7 @@
       <c r="G129" s="134">
         <v>36036.11</v>
       </c>
-      <c r="H129" s="215">
+      <c r="H129" s="208">
         <f>G129</f>
         <v>36036.11</v>
       </c>
@@ -12056,7 +12059,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" s="127" t="s">
         <v>26</v>
       </c>
@@ -12074,7 +12077,7 @@
       <c r="G130" s="134">
         <v>36036.120000000003</v>
       </c>
-      <c r="H130" s="215">
+      <c r="H130" s="208">
         <f>G130</f>
         <v>36036.120000000003</v>
       </c>
@@ -12106,7 +12109,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" s="127" t="s">
         <v>26</v>
       </c>
@@ -12124,7 +12127,7 @@
       <c r="G131" s="134">
         <v>36036.129999999997</v>
       </c>
-      <c r="H131" s="220">
+      <c r="H131" s="212">
         <f>36036.13+6006.02</f>
         <v>42042.149999999994</v>
       </c>
@@ -12156,7 +12159,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" s="53" t="s">
         <v>26</v>
       </c>
@@ -12174,7 +12177,7 @@
       <c r="M132" s="5"/>
       <c r="N132" s="8"/>
     </row>
-    <row r="133" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="27"/>
       <c r="B133" s="27"/>
       <c r="C133" s="27"/>
@@ -12201,55 +12204,55 @@
         <f>SUM(K14:K132)</f>
         <v>15462877.067300022</v>
       </c>
-      <c r="L133" s="181">
+      <c r="L133" s="174">
         <f>SUM(L14:L132)</f>
-        <v>223000</v>
+        <v>237727.1737246</v>
       </c>
       <c r="M133" s="29">
         <f>SUM(M14:M132)</f>
-        <v>19496193.326460004</v>
+        <v>19510920.326460004</v>
       </c>
       <c r="N133" s="28">
         <f>SUM(N14:N132)</f>
-        <v>20666030.441447597</v>
+        <v>20681640.441447597</v>
       </c>
       <c r="P133" s="59"/>
     </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="K134" s="61">
         <f>K133-L1</f>
         <v>3118989.9373000227</v>
       </c>
     </row>
-    <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="259"/>
-      <c r="D135" s="259"/>
-      <c r="E135" s="259"/>
-      <c r="F135" s="259"/>
-      <c r="G135" s="259"/>
-      <c r="H135" s="259"/>
-      <c r="I135" s="259"/>
-      <c r="J135" s="259"/>
-      <c r="K135" s="259"/>
-      <c r="L135" s="259"/>
-      <c r="M135" s="259"/>
-      <c r="N135" s="259"/>
-    </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="259"/>
-      <c r="D136" s="259"/>
-      <c r="E136" s="259"/>
-      <c r="F136" s="259"/>
-      <c r="G136" s="259"/>
-      <c r="H136" s="259"/>
-      <c r="I136" s="259"/>
-      <c r="J136" s="259"/>
-      <c r="K136" s="259"/>
-      <c r="L136" s="259"/>
-      <c r="M136" s="259"/>
-      <c r="N136" s="259"/>
-    </row>
-    <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C135" s="247"/>
+      <c r="D135" s="247"/>
+      <c r="E135" s="247"/>
+      <c r="F135" s="247"/>
+      <c r="G135" s="247"/>
+      <c r="H135" s="247"/>
+      <c r="I135" s="247"/>
+      <c r="J135" s="247"/>
+      <c r="K135" s="247"/>
+      <c r="L135" s="247"/>
+      <c r="M135" s="247"/>
+      <c r="N135" s="247"/>
+    </row>
+    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C136" s="247"/>
+      <c r="D136" s="247"/>
+      <c r="E136" s="247"/>
+      <c r="F136" s="247"/>
+      <c r="G136" s="247"/>
+      <c r="H136" s="247"/>
+      <c r="I136" s="247"/>
+      <c r="J136" s="247"/>
+      <c r="K136" s="247"/>
+      <c r="L136" s="247"/>
+      <c r="M136" s="247"/>
+      <c r="N136" s="247"/>
+    </row>
+    <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="77"/>
       <c r="D137" s="77"/>
       <c r="E137" s="77"/>
@@ -12263,121 +12266,121 @@
       <c r="M137" s="77"/>
       <c r="N137" s="77"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C138" s="243" t="s">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C138" s="235" t="s">
         <v>260</v>
       </c>
-      <c r="D138" s="243"/>
-      <c r="E138" s="243"/>
-      <c r="F138" s="243"/>
-      <c r="G138" s="243"/>
-      <c r="H138" s="243"/>
-      <c r="I138" s="243"/>
-      <c r="J138" s="243"/>
-      <c r="K138" s="243"/>
-      <c r="L138" s="243"/>
-      <c r="M138" s="243"/>
-      <c r="N138" s="243"/>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C139" s="243"/>
-      <c r="D139" s="243"/>
-      <c r="E139" s="243"/>
-      <c r="F139" s="243"/>
-      <c r="G139" s="243"/>
-      <c r="H139" s="243"/>
-      <c r="I139" s="243"/>
-      <c r="J139" s="243"/>
-      <c r="K139" s="243"/>
-      <c r="L139" s="243"/>
-      <c r="M139" s="243"/>
-      <c r="N139" s="243"/>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C140" s="243"/>
-      <c r="D140" s="243"/>
-      <c r="E140" s="243"/>
-      <c r="F140" s="243"/>
-      <c r="G140" s="243"/>
-      <c r="H140" s="243"/>
-      <c r="I140" s="243"/>
-      <c r="J140" s="243"/>
-      <c r="K140" s="243"/>
-      <c r="L140" s="243"/>
-      <c r="M140" s="243"/>
-      <c r="N140" s="243"/>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C141" s="243"/>
-      <c r="D141" s="243"/>
-      <c r="E141" s="243"/>
-      <c r="F141" s="243"/>
-      <c r="G141" s="243"/>
-      <c r="H141" s="243"/>
-      <c r="I141" s="243"/>
-      <c r="J141" s="243"/>
-      <c r="K141" s="243"/>
-      <c r="L141" s="243"/>
-      <c r="M141" s="243"/>
-      <c r="N141" s="243"/>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C142" s="243"/>
-      <c r="D142" s="243"/>
-      <c r="E142" s="243"/>
-      <c r="F142" s="243"/>
-      <c r="G142" s="243"/>
-      <c r="H142" s="243"/>
-      <c r="I142" s="243"/>
-      <c r="J142" s="243"/>
-      <c r="K142" s="243"/>
-      <c r="L142" s="243"/>
-      <c r="M142" s="243"/>
-      <c r="N142" s="243"/>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C143" s="243"/>
-      <c r="D143" s="243"/>
-      <c r="E143" s="243"/>
-      <c r="F143" s="243"/>
-      <c r="G143" s="243"/>
-      <c r="H143" s="243"/>
-      <c r="I143" s="243"/>
-      <c r="J143" s="243"/>
-      <c r="K143" s="243"/>
-      <c r="L143" s="243"/>
-      <c r="M143" s="243"/>
-      <c r="N143" s="243"/>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C144" s="243"/>
-      <c r="D144" s="243"/>
-      <c r="E144" s="243"/>
-      <c r="F144" s="243"/>
-      <c r="G144" s="243"/>
-      <c r="H144" s="243"/>
-      <c r="I144" s="243"/>
-      <c r="J144" s="243"/>
-      <c r="K144" s="243"/>
-      <c r="L144" s="243"/>
-      <c r="M144" s="243"/>
-      <c r="N144" s="243"/>
-    </row>
-    <row r="145" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C145" s="243"/>
-      <c r="D145" s="243"/>
-      <c r="E145" s="243"/>
-      <c r="F145" s="243"/>
-      <c r="G145" s="243"/>
-      <c r="H145" s="243"/>
-      <c r="I145" s="243"/>
-      <c r="J145" s="243"/>
-      <c r="K145" s="243"/>
-      <c r="L145" s="243"/>
-      <c r="M145" s="243"/>
-      <c r="N145" s="243"/>
-    </row>
-    <row r="146" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D138" s="235"/>
+      <c r="E138" s="235"/>
+      <c r="F138" s="235"/>
+      <c r="G138" s="235"/>
+      <c r="H138" s="235"/>
+      <c r="I138" s="235"/>
+      <c r="J138" s="235"/>
+      <c r="K138" s="235"/>
+      <c r="L138" s="235"/>
+      <c r="M138" s="235"/>
+      <c r="N138" s="235"/>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C139" s="235"/>
+      <c r="D139" s="235"/>
+      <c r="E139" s="235"/>
+      <c r="F139" s="235"/>
+      <c r="G139" s="235"/>
+      <c r="H139" s="235"/>
+      <c r="I139" s="235"/>
+      <c r="J139" s="235"/>
+      <c r="K139" s="235"/>
+      <c r="L139" s="235"/>
+      <c r="M139" s="235"/>
+      <c r="N139" s="235"/>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C140" s="235"/>
+      <c r="D140" s="235"/>
+      <c r="E140" s="235"/>
+      <c r="F140" s="235"/>
+      <c r="G140" s="235"/>
+      <c r="H140" s="235"/>
+      <c r="I140" s="235"/>
+      <c r="J140" s="235"/>
+      <c r="K140" s="235"/>
+      <c r="L140" s="235"/>
+      <c r="M140" s="235"/>
+      <c r="N140" s="235"/>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C141" s="235"/>
+      <c r="D141" s="235"/>
+      <c r="E141" s="235"/>
+      <c r="F141" s="235"/>
+      <c r="G141" s="235"/>
+      <c r="H141" s="235"/>
+      <c r="I141" s="235"/>
+      <c r="J141" s="235"/>
+      <c r="K141" s="235"/>
+      <c r="L141" s="235"/>
+      <c r="M141" s="235"/>
+      <c r="N141" s="235"/>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C142" s="235"/>
+      <c r="D142" s="235"/>
+      <c r="E142" s="235"/>
+      <c r="F142" s="235"/>
+      <c r="G142" s="235"/>
+      <c r="H142" s="235"/>
+      <c r="I142" s="235"/>
+      <c r="J142" s="235"/>
+      <c r="K142" s="235"/>
+      <c r="L142" s="235"/>
+      <c r="M142" s="235"/>
+      <c r="N142" s="235"/>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C143" s="235"/>
+      <c r="D143" s="235"/>
+      <c r="E143" s="235"/>
+      <c r="F143" s="235"/>
+      <c r="G143" s="235"/>
+      <c r="H143" s="235"/>
+      <c r="I143" s="235"/>
+      <c r="J143" s="235"/>
+      <c r="K143" s="235"/>
+      <c r="L143" s="235"/>
+      <c r="M143" s="235"/>
+      <c r="N143" s="235"/>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C144" s="235"/>
+      <c r="D144" s="235"/>
+      <c r="E144" s="235"/>
+      <c r="F144" s="235"/>
+      <c r="G144" s="235"/>
+      <c r="H144" s="235"/>
+      <c r="I144" s="235"/>
+      <c r="J144" s="235"/>
+      <c r="K144" s="235"/>
+      <c r="L144" s="235"/>
+      <c r="M144" s="235"/>
+      <c r="N144" s="235"/>
+    </row>
+    <row r="145" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C145" s="235"/>
+      <c r="D145" s="235"/>
+      <c r="E145" s="235"/>
+      <c r="F145" s="235"/>
+      <c r="G145" s="235"/>
+      <c r="H145" s="235"/>
+      <c r="I145" s="235"/>
+      <c r="J145" s="235"/>
+      <c r="K145" s="235"/>
+      <c r="L145" s="235"/>
+      <c r="M145" s="235"/>
+      <c r="N145" s="235"/>
+    </row>
+    <row r="146" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C146" s="77"/>
       <c r="D146" s="77"/>
       <c r="E146" s="77"/>
@@ -12391,7 +12394,7 @@
       <c r="M146" s="77"/>
       <c r="N146" s="77"/>
     </row>
-    <row r="147" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C147" s="77"/>
       <c r="D147" s="77"/>
       <c r="E147" s="77"/>
@@ -12405,112 +12408,118 @@
       <c r="M147" s="77"/>
       <c r="N147" s="77"/>
     </row>
-    <row r="148" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C148" s="258" t="s">
+    <row r="148" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C148" s="246" t="s">
         <v>259</v>
       </c>
-      <c r="D148" s="258"/>
-      <c r="E148" s="258"/>
-      <c r="F148" s="258"/>
-      <c r="G148" s="258"/>
-      <c r="H148" s="258"/>
-      <c r="I148" s="258"/>
-      <c r="J148" s="258"/>
-      <c r="K148" s="258"/>
-      <c r="L148" s="258"/>
-      <c r="M148" s="258"/>
-      <c r="N148" s="258"/>
-    </row>
-    <row r="149" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C149" s="258"/>
-      <c r="D149" s="258"/>
-      <c r="E149" s="258"/>
-      <c r="F149" s="258"/>
-      <c r="G149" s="258"/>
-      <c r="H149" s="258"/>
-      <c r="I149" s="258"/>
-      <c r="J149" s="258"/>
-      <c r="K149" s="258"/>
-      <c r="L149" s="258"/>
-      <c r="M149" s="258"/>
-      <c r="N149" s="258"/>
-    </row>
-    <row r="150" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C150" s="258"/>
-      <c r="D150" s="258"/>
-      <c r="E150" s="258"/>
-      <c r="F150" s="258"/>
-      <c r="G150" s="258"/>
-      <c r="H150" s="258"/>
-      <c r="I150" s="258"/>
-      <c r="J150" s="258"/>
-      <c r="K150" s="258"/>
-      <c r="L150" s="258"/>
-      <c r="M150" s="258"/>
-      <c r="N150" s="258"/>
+      <c r="D148" s="246"/>
+      <c r="E148" s="246"/>
+      <c r="F148" s="246"/>
+      <c r="G148" s="246"/>
+      <c r="H148" s="246"/>
+      <c r="I148" s="246"/>
+      <c r="J148" s="246"/>
+      <c r="K148" s="246"/>
+      <c r="L148" s="246"/>
+      <c r="M148" s="246"/>
+      <c r="N148" s="246"/>
+    </row>
+    <row r="149" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C149" s="246"/>
+      <c r="D149" s="246"/>
+      <c r="E149" s="246"/>
+      <c r="F149" s="246"/>
+      <c r="G149" s="246"/>
+      <c r="H149" s="246"/>
+      <c r="I149" s="246"/>
+      <c r="J149" s="246"/>
+      <c r="K149" s="246"/>
+      <c r="L149" s="246"/>
+      <c r="M149" s="246"/>
+      <c r="N149" s="246"/>
+    </row>
+    <row r="150" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C150" s="246"/>
+      <c r="D150" s="246"/>
+      <c r="E150" s="246"/>
+      <c r="F150" s="246"/>
+      <c r="G150" s="246"/>
+      <c r="H150" s="246"/>
+      <c r="I150" s="246"/>
+      <c r="J150" s="246"/>
+      <c r="K150" s="246"/>
+      <c r="L150" s="246"/>
+      <c r="M150" s="246"/>
+      <c r="N150" s="246"/>
       <c r="P150" s="84">
         <f>L1-K133</f>
         <v>-3118989.9373000227</v>
       </c>
     </row>
-    <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="258"/>
-      <c r="D151" s="258"/>
-      <c r="E151" s="258"/>
-      <c r="F151" s="258"/>
-      <c r="G151" s="258"/>
-      <c r="H151" s="258"/>
-      <c r="I151" s="258"/>
-      <c r="J151" s="258"/>
-      <c r="K151" s="258"/>
-      <c r="L151" s="258"/>
-      <c r="M151" s="258"/>
-      <c r="N151" s="258"/>
-    </row>
-    <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="258"/>
-      <c r="D152" s="258"/>
-      <c r="E152" s="258"/>
-      <c r="F152" s="258"/>
-      <c r="G152" s="258"/>
-      <c r="H152" s="258"/>
-      <c r="I152" s="258"/>
-      <c r="J152" s="258"/>
-      <c r="K152" s="258"/>
-      <c r="L152" s="258"/>
-      <c r="M152" s="258"/>
-      <c r="N152" s="258"/>
-    </row>
-    <row r="153" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="258"/>
-      <c r="D153" s="258"/>
-      <c r="E153" s="258"/>
-      <c r="F153" s="258"/>
-      <c r="G153" s="258"/>
-      <c r="H153" s="258"/>
-      <c r="I153" s="258"/>
-      <c r="J153" s="258"/>
-      <c r="K153" s="258"/>
-      <c r="L153" s="258"/>
-      <c r="M153" s="258"/>
-      <c r="N153" s="258"/>
-    </row>
-    <row r="154" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="258"/>
-      <c r="D154" s="258"/>
-      <c r="E154" s="258"/>
-      <c r="F154" s="258"/>
-      <c r="G154" s="258"/>
-      <c r="H154" s="258"/>
-      <c r="I154" s="258"/>
-      <c r="J154" s="258"/>
-      <c r="K154" s="258"/>
-      <c r="L154" s="258"/>
-      <c r="M154" s="258"/>
-      <c r="N154" s="258"/>
+    <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C151" s="246"/>
+      <c r="D151" s="246"/>
+      <c r="E151" s="246"/>
+      <c r="F151" s="246"/>
+      <c r="G151" s="246"/>
+      <c r="H151" s="246"/>
+      <c r="I151" s="246"/>
+      <c r="J151" s="246"/>
+      <c r="K151" s="246"/>
+      <c r="L151" s="246"/>
+      <c r="M151" s="246"/>
+      <c r="N151" s="246"/>
+    </row>
+    <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C152" s="246"/>
+      <c r="D152" s="246"/>
+      <c r="E152" s="246"/>
+      <c r="F152" s="246"/>
+      <c r="G152" s="246"/>
+      <c r="H152" s="246"/>
+      <c r="I152" s="246"/>
+      <c r="J152" s="246"/>
+      <c r="K152" s="246"/>
+      <c r="L152" s="246"/>
+      <c r="M152" s="246"/>
+      <c r="N152" s="246"/>
+    </row>
+    <row r="153" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C153" s="246"/>
+      <c r="D153" s="246"/>
+      <c r="E153" s="246"/>
+      <c r="F153" s="246"/>
+      <c r="G153" s="246"/>
+      <c r="H153" s="246"/>
+      <c r="I153" s="246"/>
+      <c r="J153" s="246"/>
+      <c r="K153" s="246"/>
+      <c r="L153" s="246"/>
+      <c r="M153" s="246"/>
+      <c r="N153" s="246"/>
+    </row>
+    <row r="154" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C154" s="246"/>
+      <c r="D154" s="246"/>
+      <c r="E154" s="246"/>
+      <c r="F154" s="246"/>
+      <c r="G154" s="246"/>
+      <c r="H154" s="246"/>
+      <c r="I154" s="246"/>
+      <c r="J154" s="246"/>
+      <c r="K154" s="246"/>
+      <c r="L154" s="246"/>
+      <c r="M154" s="246"/>
+      <c r="N154" s="246"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
     <mergeCell ref="Q14:R15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:N154"/>
@@ -12527,12 +12536,6 @@
     <mergeCell ref="C5:N8"/>
     <mergeCell ref="C9:N10"/>
     <mergeCell ref="A1:E4"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12543,9 +12546,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
   <dimension ref="A13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026/EL MIRADOR/ENERO/Enero - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/ENERO/Enero - EL MIRADOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF72D4D-D25C-427A-AEDC-1E1368733602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A50910-F34C-4BDD-96CC-127017CADA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/2026/EL MIRADOR/ENERO/Enero - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/ENERO/Enero - EL MIRADOR.xlsx
@@ -5,19 +5,21 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\EL MIRADOR\ENERO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A50910-F34C-4BDD-96CC-127017CADA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9559E049-2CBF-4EF7-ACB1-525558FA34DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
     <sheet name="PRORRATEO" sheetId="2" r:id="rId2"/>
-    <sheet name="ANOTACIONES" sheetId="3" r:id="rId3"/>
+    <sheet name="ARBA" sheetId="4" r:id="rId3"/>
+    <sheet name="ANOTACIONES" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">ARBA!$A$1:$K$82</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$155</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$150</definedName>
   </definedNames>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="400">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1136,6 +1138,105 @@
   </si>
   <si>
     <t>Lorenzo, Sergio</t>
+  </si>
+  <si>
+    <t>IMPORTANTE: RESPETAR CENTAVOS AL ABONAR.</t>
+  </si>
+  <si>
+    <t>DPTOS</t>
+  </si>
+  <si>
+    <t>COCH</t>
+  </si>
+  <si>
+    <t>29-30</t>
+  </si>
+  <si>
+    <t>34-39</t>
+  </si>
+  <si>
+    <t>37-38</t>
+  </si>
+  <si>
+    <t>1-11</t>
+  </si>
+  <si>
+    <t>13-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LOC 2 </t>
+  </si>
+  <si>
+    <t>Frigidi Guillermo Ariel</t>
+  </si>
+  <si>
+    <t>Schiaffino, Edgardo Ángel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orsi, José Luis - Fernández, Cristián Gabriel </t>
+  </si>
+  <si>
+    <t>Ferraro, Jose -  ------ALEJANDRO</t>
+  </si>
+  <si>
+    <t>Ayala, Roberto Adrian/BALDUZZI</t>
+  </si>
+  <si>
+    <t>Ayala, Roberto Adrian /CALZETTA</t>
+  </si>
+  <si>
+    <t>Calzetta, Gabriel Andrés Felipe</t>
+  </si>
+  <si>
+    <t>Ayala, Roberto Adrian/SKARLATIUK</t>
+  </si>
+  <si>
+    <t>Ayala, Roberto Adrian/CALZETTA/ BASAEZ ROGELIO</t>
+  </si>
+  <si>
+    <t>GRIZEK RUBEN EDUARDO (ex Orellano)</t>
+  </si>
+  <si>
+    <t>ANCHIPI GASTON (Cedido x Hecimovic)Hecimovic, Mariano Hernán (Cedido x Lopez Malara, Ramiro Alejandro)</t>
+  </si>
+  <si>
+    <t>ALEXIA JOANA MAZZIA</t>
+  </si>
+  <si>
+    <t>Acosta, Daniela Pilar</t>
+  </si>
+  <si>
+    <t>Nuñez Leyes Javier Damian</t>
+  </si>
+  <si>
+    <t>Di Sabato Guillermo Damian</t>
+  </si>
+  <si>
+    <t>Guillermo Antonio PUISYS (EX Fernández, Marcela Fabiana)</t>
+  </si>
+  <si>
+    <t>Hecimovic, Mariano Hernán</t>
+  </si>
+  <si>
+    <t>Silvestre Villarruel Eduardo (EX De Mieri, Fernando Emanuel</t>
+  </si>
+  <si>
+    <t>Yudchak, Carlos Alberto</t>
+  </si>
+  <si>
+    <t>Gazzaneo Francisco</t>
+  </si>
+  <si>
+    <t>ARBA REVALUO</t>
+  </si>
+  <si>
+    <t>POSESION</t>
+  </si>
+  <si>
+    <t>A PAGAR PROPIETARIO</t>
+  </si>
+  <si>
+    <t>A PAGAR CONSTRUCTORA</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1253,7 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.000_-;\-&quot;$&quot;\ * #,##0.000_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1320,6 +1421,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="16">
     <fill>
@@ -1413,7 +1532,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1757,14 +1876,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="283">
+  <cellXfs count="314">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2036,6 +2169,51 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="11" fillId="15" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2207,13 +2385,44 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="15" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="9" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="23" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="12" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Moneda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="4" xr:uid="{F448D45D-4768-48C8-A208-BDCED71CF03D}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2574,24 +2783,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R160"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.44140625" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.6640625" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" customWidth="1"/>
-    <col min="11" max="11" width="15.88671875" customWidth="1"/>
-    <col min="12" max="12" width="16.109375" customWidth="1"/>
+    <col min="6" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.33203125" customWidth="1"/>
+    <col min="17" max="17" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="112"/>
       <c r="B1" s="121"/>
       <c r="C1" s="129" t="s">
@@ -2605,7 +2814,7 @@
       <c r="I1" s="110"/>
       <c r="J1" s="111"/>
     </row>
-    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="113"/>
       <c r="B2" s="122"/>
       <c r="C2" s="122" t="s">
@@ -2619,7 +2828,7 @@
       <c r="I2" s="123"/>
       <c r="J2" s="109"/>
     </row>
-    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="113"/>
       <c r="B3" s="122"/>
       <c r="C3" s="122" t="s">
@@ -2635,7 +2844,7 @@
       <c r="I3" s="123"/>
       <c r="J3" s="109"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="113"/>
       <c r="B4" s="122"/>
       <c r="C4" s="122" t="s">
@@ -2649,7 +2858,7 @@
       <c r="I4" s="123"/>
       <c r="J4" s="109"/>
     </row>
-    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="117"/>
       <c r="B5" s="122"/>
       <c r="C5" s="122" t="s">
@@ -2665,7 +2874,7 @@
       <c r="I5" s="122"/>
       <c r="J5" s="118"/>
     </row>
-    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="117"/>
       <c r="B6" s="122"/>
       <c r="C6" s="122" t="s">
@@ -2679,7 +2888,7 @@
       <c r="I6" s="122"/>
       <c r="J6" s="118"/>
     </row>
-    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="119"/>
       <c r="B7" s="120"/>
       <c r="C7" s="120"/>
@@ -2691,118 +2900,118 @@
       <c r="I7" s="120"/>
       <c r="J7" s="124"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="225" t="s">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="244" t="s">
         <v>260</v>
       </c>
-      <c r="B14" s="225"/>
-      <c r="C14" s="225"/>
-      <c r="D14" s="225"/>
-      <c r="E14" s="225"/>
-      <c r="F14" s="225"/>
-      <c r="G14" s="225"/>
-      <c r="H14" s="225"/>
-      <c r="I14" s="225"/>
-      <c r="J14" s="225"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="225"/>
-      <c r="B15" s="225"/>
-      <c r="C15" s="225"/>
-      <c r="D15" s="225"/>
-      <c r="E15" s="225"/>
-      <c r="F15" s="225"/>
-      <c r="G15" s="225"/>
-      <c r="H15" s="225"/>
-      <c r="I15" s="225"/>
-      <c r="J15" s="225"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="225"/>
-      <c r="B16" s="225"/>
-      <c r="C16" s="225"/>
-      <c r="D16" s="225"/>
-      <c r="E16" s="225"/>
-      <c r="F16" s="225"/>
-      <c r="G16" s="225"/>
-      <c r="H16" s="225"/>
-      <c r="I16" s="225"/>
-      <c r="J16" s="225"/>
-    </row>
-    <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="225"/>
-      <c r="B17" s="225"/>
-      <c r="C17" s="225"/>
-      <c r="D17" s="225"/>
-      <c r="E17" s="225"/>
-      <c r="F17" s="225"/>
-      <c r="G17" s="225"/>
-      <c r="H17" s="225"/>
-      <c r="I17" s="225"/>
-      <c r="J17" s="225"/>
-    </row>
-    <row r="18" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="225"/>
-      <c r="B18" s="225"/>
-      <c r="C18" s="225"/>
-      <c r="D18" s="225"/>
-      <c r="E18" s="225"/>
-      <c r="F18" s="225"/>
-      <c r="G18" s="225"/>
-      <c r="H18" s="225"/>
-      <c r="I18" s="225"/>
-      <c r="J18" s="225"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B14" s="244"/>
+      <c r="C14" s="244"/>
+      <c r="D14" s="244"/>
+      <c r="E14" s="244"/>
+      <c r="F14" s="244"/>
+      <c r="G14" s="244"/>
+      <c r="H14" s="244"/>
+      <c r="I14" s="244"/>
+      <c r="J14" s="244"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="244"/>
+      <c r="B15" s="244"/>
+      <c r="C15" s="244"/>
+      <c r="D15" s="244"/>
+      <c r="E15" s="244"/>
+      <c r="F15" s="244"/>
+      <c r="G15" s="244"/>
+      <c r="H15" s="244"/>
+      <c r="I15" s="244"/>
+      <c r="J15" s="244"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="244"/>
+      <c r="B16" s="244"/>
+      <c r="C16" s="244"/>
+      <c r="D16" s="244"/>
+      <c r="E16" s="244"/>
+      <c r="F16" s="244"/>
+      <c r="G16" s="244"/>
+      <c r="H16" s="244"/>
+      <c r="I16" s="244"/>
+      <c r="J16" s="244"/>
+    </row>
+    <row r="17" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="244"/>
+      <c r="B17" s="244"/>
+      <c r="C17" s="244"/>
+      <c r="D17" s="244"/>
+      <c r="E17" s="244"/>
+      <c r="F17" s="244"/>
+      <c r="G17" s="244"/>
+      <c r="H17" s="244"/>
+      <c r="I17" s="244"/>
+      <c r="J17" s="244"/>
+    </row>
+    <row r="18" spans="1:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="244"/>
+      <c r="B18" s="244"/>
+      <c r="C18" s="244"/>
+      <c r="D18" s="244"/>
+      <c r="E18" s="244"/>
+      <c r="F18" s="244"/>
+      <c r="G18" s="244"/>
+      <c r="H18" s="244"/>
+      <c r="I18" s="244"/>
+      <c r="J18" s="244"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="H19" s="94"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="234" t="s">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="253" t="s">
         <v>324</v>
       </c>
-      <c r="B20" s="234"/>
-      <c r="C20" s="234"/>
-      <c r="D20" s="234"/>
-      <c r="E20" s="234"/>
-      <c r="F20" s="234"/>
-      <c r="G20" s="234"/>
-      <c r="H20" s="234"/>
-      <c r="I20" s="234"/>
-      <c r="J20" s="234"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="234"/>
-      <c r="B21" s="234"/>
-      <c r="C21" s="234"/>
-      <c r="D21" s="234"/>
-      <c r="E21" s="234"/>
-      <c r="F21" s="234"/>
-      <c r="G21" s="234"/>
-      <c r="H21" s="234"/>
-      <c r="I21" s="234"/>
-      <c r="J21" s="234"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="234"/>
-      <c r="B22" s="234"/>
-      <c r="C22" s="234"/>
-      <c r="D22" s="234"/>
-      <c r="E22" s="234"/>
-      <c r="F22" s="234"/>
-      <c r="G22" s="234"/>
-      <c r="H22" s="234"/>
-      <c r="I22" s="234"/>
-      <c r="J22" s="234"/>
-    </row>
-    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="253"/>
+      <c r="C20" s="253"/>
+      <c r="D20" s="253"/>
+      <c r="E20" s="253"/>
+      <c r="F20" s="253"/>
+      <c r="G20" s="253"/>
+      <c r="H20" s="253"/>
+      <c r="I20" s="253"/>
+      <c r="J20" s="253"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="253"/>
+      <c r="B21" s="253"/>
+      <c r="C21" s="253"/>
+      <c r="D21" s="253"/>
+      <c r="E21" s="253"/>
+      <c r="F21" s="253"/>
+      <c r="G21" s="253"/>
+      <c r="H21" s="253"/>
+      <c r="I21" s="253"/>
+      <c r="J21" s="253"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="253"/>
+      <c r="B22" s="253"/>
+      <c r="C22" s="253"/>
+      <c r="D22" s="253"/>
+      <c r="E22" s="253"/>
+      <c r="F22" s="253"/>
+      <c r="G22" s="253"/>
+      <c r="H22" s="253"/>
+      <c r="I22" s="253"/>
+      <c r="J22" s="253"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H23" s="94"/>
     </row>
-    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>19</v>
       </c>
@@ -2828,7 +3037,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="50" t="s">
         <v>235</v>
       </c>
@@ -2842,7 +3051,7 @@
       <c r="I25" s="95"/>
       <c r="J25" s="95"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>43</v>
       </c>
@@ -2858,7 +3067,7 @@
       <c r="I26" s="58"/>
       <c r="J26" s="58"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>238</v>
       </c>
@@ -2874,7 +3083,7 @@
       <c r="I27" s="58"/>
       <c r="J27" s="58"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>236</v>
       </c>
@@ -2891,7 +3100,7 @@
       <c r="I28" s="58"/>
       <c r="J28" s="58"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>237</v>
       </c>
@@ -2907,7 +3116,7 @@
       <c r="I29" s="58"/>
       <c r="J29" s="58"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>298</v>
       </c>
@@ -2923,7 +3132,7 @@
       <c r="I30" s="58"/>
       <c r="J30" s="58"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>239</v>
       </c>
@@ -2939,7 +3148,7 @@
       <c r="I31" s="58"/>
       <c r="J31" s="58"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>338</v>
       </c>
@@ -2955,7 +3164,7 @@
       <c r="I32" s="58"/>
       <c r="J32" s="58"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="93" t="s">
         <v>168</v>
       </c>
@@ -2972,7 +3181,7 @@
       <c r="I33" s="92"/>
       <c r="J33" s="92"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="50" t="s">
         <v>234</v>
       </c>
@@ -2986,7 +3195,7 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>43</v>
       </c>
@@ -3002,7 +3211,7 @@
       <c r="I35" s="58"/>
       <c r="J35" s="58"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>238</v>
       </c>
@@ -3019,7 +3228,7 @@
       <c r="I36" s="58"/>
       <c r="J36" s="58"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>236</v>
       </c>
@@ -3036,7 +3245,7 @@
       <c r="I37" s="58"/>
       <c r="J37" s="58"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>237</v>
       </c>
@@ -3053,7 +3262,7 @@
       <c r="I38" s="58"/>
       <c r="J38" s="58"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>298</v>
       </c>
@@ -3070,7 +3279,7 @@
       <c r="I39" s="58"/>
       <c r="J39" s="58"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>239</v>
       </c>
@@ -3086,7 +3295,7 @@
       <c r="I40" s="58"/>
       <c r="J40" s="58"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>339</v>
       </c>
@@ -3102,7 +3311,7 @@
       <c r="I41" s="58"/>
       <c r="J41" s="58"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="93" t="s">
         <v>168</v>
       </c>
@@ -3119,7 +3328,7 @@
       <c r="I42" s="92"/>
       <c r="J42" s="92"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="33" t="s">
         <v>1</v>
       </c>
@@ -3162,7 +3371,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="32" t="s">
         <v>340</v>
       </c>
@@ -3179,7 +3388,7 @@
       <c r="J44" s="58"/>
       <c r="L44" s="69"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="32"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -3192,7 +3401,7 @@
       <c r="J45" s="6"/>
       <c r="L45" s="69"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="33" t="s">
         <v>38</v>
       </c>
@@ -3235,7 +3444,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="32" t="s">
         <v>249</v>
       </c>
@@ -3253,7 +3462,7 @@
       <c r="J47" s="58"/>
       <c r="L47" s="69"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>341</v>
       </c>
@@ -3275,7 +3484,7 @@
       <c r="J48" s="58"/>
       <c r="L48" s="69"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>341</v>
       </c>
@@ -3297,7 +3506,7 @@
       <c r="J49" s="58"/>
       <c r="L49" s="69"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>341</v>
       </c>
@@ -3319,7 +3528,7 @@
       <c r="J50" s="58"/>
       <c r="L50" s="69"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>341</v>
       </c>
@@ -3341,7 +3550,7 @@
       <c r="J51" s="58"/>
       <c r="L51" s="69"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>341</v>
       </c>
@@ -3363,7 +3572,7 @@
       <c r="J52" s="58"/>
       <c r="L52" s="69"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -3376,7 +3585,7 @@
       <c r="J53" s="58"/>
       <c r="L53" s="69"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="33" t="s">
         <v>17</v>
       </c>
@@ -3404,7 +3613,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="32" t="s">
         <v>244</v>
       </c>
@@ -3419,7 +3628,7 @@
       <c r="J55" s="49"/>
       <c r="L55" s="69"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="35" t="s">
         <v>247</v>
       </c>
@@ -3434,7 +3643,7 @@
       <c r="J56" s="49"/>
       <c r="L56" s="69"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="35" t="s">
         <v>248</v>
       </c>
@@ -3455,7 +3664,7 @@
       <c r="J57" s="49"/>
       <c r="L57" s="69"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="35" t="s">
         <v>248</v>
       </c>
@@ -3476,7 +3685,7 @@
       <c r="J58" s="49"/>
       <c r="L58" s="69"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="33" t="s">
         <v>246</v>
       </c>
@@ -3519,7 +3728,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="32" t="s">
         <v>2</v>
       </c>
@@ -3534,7 +3743,7 @@
       <c r="J60" s="6"/>
       <c r="L60" s="69"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>240</v>
       </c>
@@ -3553,7 +3762,7 @@
       <c r="J61" s="6"/>
       <c r="L61" s="69"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>282</v>
       </c>
@@ -3572,7 +3781,7 @@
       <c r="J62" s="6"/>
       <c r="L62" s="69"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
         <v>282</v>
       </c>
@@ -3593,7 +3802,7 @@
       <c r="J63" s="6"/>
       <c r="L63" s="69"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="33" t="s">
         <v>245</v>
       </c>
@@ -3636,7 +3845,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="32" t="s">
         <v>227</v>
       </c>
@@ -3651,7 +3860,7 @@
       <c r="J65" s="36"/>
       <c r="L65" s="69"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>231</v>
       </c>
@@ -3692,11 +3901,11 @@
       </c>
       <c r="L66" s="69"/>
     </row>
-    <row r="67" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="236" t="s">
+    <row r="67" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="255" t="s">
         <v>232</v>
       </c>
-      <c r="B67" s="237"/>
+      <c r="B67" s="256"/>
       <c r="C67" s="35" t="s">
         <v>315</v>
       </c>
@@ -3735,11 +3944,11 @@
         <v>363</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="236" t="s">
+    <row r="68" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="255" t="s">
         <v>233</v>
       </c>
-      <c r="B68" s="237"/>
+      <c r="B68" s="256"/>
       <c r="C68" s="35" t="s">
         <v>315</v>
       </c>
@@ -3776,7 +3985,7 @@
       </c>
       <c r="L68" s="69"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="33" t="s">
         <v>3</v>
       </c>
@@ -3819,7 +4028,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="32" t="s">
         <v>4</v>
       </c>
@@ -3834,7 +4043,7 @@
       <c r="J70" s="6"/>
       <c r="L70" s="69"/>
     </row>
-    <row r="71" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="71" t="s">
         <v>241</v>
       </c>
@@ -3880,7 +4089,7 @@
       <c r="M71" s="84"/>
       <c r="N71" s="84"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
         <v>242</v>
       </c>
@@ -3926,7 +4135,7 @@
       <c r="M72" s="84"/>
       <c r="N72" s="84"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
         <v>243</v>
       </c>
@@ -3963,7 +4172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
         <v>327</v>
       </c>
@@ -3994,11 +4203,11 @@
       <c r="M74" s="84"/>
       <c r="N74" s="84"/>
     </row>
-    <row r="75" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="232" t="s">
+    <row r="75" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="251" t="s">
         <v>328</v>
       </c>
-      <c r="B75" s="238"/>
+      <c r="B75" s="257"/>
       <c r="C75" s="35" t="s">
         <v>332</v>
       </c>
@@ -4031,11 +4240,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="232" t="s">
+    <row r="76" spans="1:14" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="251" t="s">
         <v>356</v>
       </c>
-      <c r="B76" s="238"/>
+      <c r="B76" s="257"/>
       <c r="C76" s="184" t="s">
         <v>357</v>
       </c>
@@ -4059,7 +4268,7 @@
       <c r="M76" s="84"/>
       <c r="N76" s="84"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="35" t="s">
         <v>277</v>
       </c>
@@ -4111,7 +4320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="35" t="s">
         <v>278</v>
       </c>
@@ -4163,7 +4372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="142" t="s">
         <v>276</v>
       </c>
@@ -4215,7 +4424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="33" t="s">
         <v>5</v>
       </c>
@@ -4262,7 +4471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -4275,7 +4484,7 @@
       <c r="J81" s="6"/>
       <c r="L81" s="69"/>
     </row>
-    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -4288,7 +4497,7 @@
       <c r="J82" s="6"/>
       <c r="L82" s="69"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="32" t="s">
         <v>228</v>
       </c>
@@ -4303,7 +4512,7 @@
       <c r="J83" s="6"/>
       <c r="L83" s="69"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
         <v>329</v>
       </c>
@@ -4340,7 +4549,7 @@
       </c>
       <c r="L84" s="69"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
         <v>333</v>
       </c>
@@ -4362,7 +4571,7 @@
       <c r="J85" s="58"/>
       <c r="L85" s="69"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
         <v>345</v>
       </c>
@@ -4399,7 +4608,7 @@
       </c>
       <c r="L86" s="69"/>
     </row>
-    <row r="87" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="71" t="s">
         <v>334</v>
       </c>
@@ -4421,11 +4630,11 @@
       <c r="J87" s="58"/>
       <c r="L87" s="69"/>
     </row>
-    <row r="88" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="241" t="s">
+    <row r="88" spans="1:14" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="260" t="s">
         <v>347</v>
       </c>
-      <c r="B88" s="242"/>
+      <c r="B88" s="261"/>
       <c r="C88" s="35" t="s">
         <v>332</v>
       </c>
@@ -4443,7 +4652,7 @@
       <c r="J88" s="58"/>
       <c r="L88" s="69"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
         <v>348</v>
       </c>
@@ -4465,7 +4674,7 @@
       <c r="J89" s="58"/>
       <c r="L89" s="69"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
         <v>336</v>
       </c>
@@ -4487,7 +4696,7 @@
       <c r="J90" s="58"/>
       <c r="L90" s="69"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="45" t="s">
         <v>351</v>
       </c>
@@ -4509,7 +4718,7 @@
       <c r="J91" s="58"/>
       <c r="L91" s="69"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="45" t="s">
         <v>351</v>
       </c>
@@ -4531,11 +4740,11 @@
       <c r="J92" s="58"/>
       <c r="L92" s="69"/>
     </row>
-    <row r="93" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="236" t="s">
+    <row r="93" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="255" t="s">
         <v>350</v>
       </c>
-      <c r="B93" s="237"/>
+      <c r="B93" s="256"/>
       <c r="C93" s="137" t="s">
         <v>349</v>
       </c>
@@ -4553,11 +4762,11 @@
       <c r="J93" s="58"/>
       <c r="L93" s="69"/>
     </row>
-    <row r="94" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="236" t="s">
+    <row r="94" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="255" t="s">
         <v>331</v>
       </c>
-      <c r="B94" s="237"/>
+      <c r="B94" s="256"/>
       <c r="C94" s="137" t="s">
         <v>349</v>
       </c>
@@ -4575,11 +4784,11 @@
       <c r="J94" s="58"/>
       <c r="L94" s="69"/>
     </row>
-    <row r="95" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="239" t="s">
+    <row r="95" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="258" t="s">
         <v>330</v>
       </c>
-      <c r="B95" s="240"/>
+      <c r="B95" s="259"/>
       <c r="C95" s="137" t="s">
         <v>349</v>
       </c>
@@ -4598,7 +4807,7 @@
       <c r="L95" s="69"/>
       <c r="M95" s="43"/>
     </row>
-    <row r="96" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="33" t="s">
         <v>229</v>
       </c>
@@ -4642,7 +4851,7 @@
       </c>
       <c r="N96" s="43"/>
     </row>
-    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -4655,7 +4864,7 @@
       <c r="J97" s="6"/>
       <c r="L97" s="69"/>
     </row>
-    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -4668,7 +4877,7 @@
       <c r="J98" s="6"/>
       <c r="L98" s="69"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="32" t="s">
         <v>6</v>
       </c>
@@ -4683,7 +4892,7 @@
       <c r="J99" s="6"/>
       <c r="L99" s="69"/>
     </row>
-    <row r="100" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
         <v>7</v>
       </c>
@@ -4722,7 +4931,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="32"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -4736,7 +4945,7 @@
       <c r="L101" s="69"/>
       <c r="N101" s="44"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -4750,7 +4959,7 @@
       <c r="L102" s="69"/>
       <c r="N102" s="43"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="33" t="s">
         <v>8</v>
       </c>
@@ -4794,7 +5003,7 @@
       </c>
       <c r="N103" s="43"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
         <v>28</v>
       </c>
@@ -4830,7 +5039,7 @@
       </c>
       <c r="L104" s="69"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
         <v>29</v>
       </c>
@@ -4863,7 +5072,7 @@
       </c>
       <c r="L105" s="69"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" s="33" t="s">
         <v>230</v>
       </c>
@@ -4906,7 +5115,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="98"/>
       <c r="B107" s="98"/>
       <c r="C107" s="98"/>
@@ -4919,7 +5128,7 @@
       <c r="J107" s="98"/>
       <c r="L107" s="69"/>
     </row>
-    <row r="108" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="100" t="s">
         <v>317</v>
       </c>
@@ -4962,7 +5171,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="103"/>
       <c r="B109" s="104"/>
       <c r="C109" s="104"/>
@@ -4976,7 +5185,7 @@
       <c r="K109" s="43"/>
       <c r="L109" s="69"/>
     </row>
-    <row r="110" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>30</v>
       </c>
@@ -5023,7 +5232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D111" s="85"/>
       <c r="E111" s="43"/>
       <c r="F111" s="43"/>
@@ -5031,7 +5240,7 @@
       <c r="H111" s="43"/>
       <c r="I111" s="43"/>
     </row>
-    <row r="112" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="64" t="s">
         <v>39</v>
       </c>
@@ -5043,7 +5252,7 @@
       <c r="H112" s="43"/>
       <c r="I112" s="43"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>354</v>
       </c>
@@ -5059,7 +5268,7 @@
       <c r="H113" s="43"/>
       <c r="I113" s="43"/>
     </row>
-    <row r="114" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="C114" s="128"/>
       <c r="E114" s="43"/>
@@ -5068,7 +5277,7 @@
       <c r="H114" s="43"/>
       <c r="I114" s="43"/>
     </row>
-    <row r="115" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="65" t="s">
         <v>17</v>
       </c>
@@ -5083,27 +5292,27 @@
       <c r="H115" s="43"/>
       <c r="I115" s="43"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E116" s="43"/>
       <c r="F116" s="43"/>
       <c r="G116" s="43"/>
       <c r="H116" s="43"/>
       <c r="I116" s="43"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="E117" s="60"/>
       <c r="F117" s="60"/>
       <c r="G117" s="60"/>
       <c r="H117" s="60"/>
       <c r="I117" s="60"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A118" s="230" t="s">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" s="249" t="s">
         <v>34</v>
       </c>
-      <c r="B118" s="231"/>
-      <c r="C118" s="231"/>
-      <c r="D118" s="231"/>
+      <c r="B118" s="250"/>
+      <c r="C118" s="250"/>
+      <c r="D118" s="250"/>
       <c r="E118" s="80" t="s">
         <v>11</v>
       </c>
@@ -5123,9 +5332,9 @@
         <v>174</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="232"/>
-      <c r="B119" s="233"/>
+    <row r="119" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="251"/>
+      <c r="B119" s="252"/>
       <c r="C119" s="82"/>
       <c r="D119" s="44"/>
       <c r="E119" s="68">
@@ -5138,9 +5347,9 @@
       <c r="I119" s="68"/>
       <c r="J119" s="58"/>
     </row>
-    <row r="120" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="232"/>
-      <c r="B120" s="233"/>
+    <row r="120" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="251"/>
+      <c r="B120" s="252"/>
       <c r="C120" s="82"/>
       <c r="D120" s="44"/>
       <c r="E120" s="68"/>
@@ -5150,12 +5359,12 @@
       <c r="I120" s="68"/>
       <c r="J120" s="58"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121" s="227" t="s">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="246" t="s">
         <v>17</v>
       </c>
-      <c r="B121" s="228"/>
-      <c r="C121" s="229"/>
+      <c r="B121" s="247"/>
+      <c r="C121" s="248"/>
       <c r="D121" s="79">
         <f>SUM(D119:D120)</f>
         <v>0</v>
@@ -5181,14 +5390,14 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E123" s="43"/>
       <c r="F123" s="43"/>
       <c r="G123" s="43"/>
       <c r="H123" s="43"/>
       <c r="I123" s="43"/>
     </row>
-    <row r="124" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="38" t="s">
         <v>31</v>
       </c>
@@ -5197,7 +5406,7 @@
         <v>15667206.089999998</v>
       </c>
     </row>
-    <row r="125" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="40" t="s">
         <v>33</v>
       </c>
@@ -5205,37 +5414,37 @@
         <f>D110-D108</f>
         <v>12343887.129999999</v>
       </c>
-      <c r="D125" s="235" t="s">
+      <c r="D125" s="254" t="s">
         <v>305</v>
       </c>
-      <c r="E125" s="235"/>
-      <c r="F125" s="235"/>
-      <c r="G125" s="235"/>
-      <c r="H125" s="235"/>
-      <c r="I125" s="235"/>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D126" s="235"/>
-      <c r="E126" s="235"/>
-      <c r="F126" s="235"/>
-      <c r="G126" s="235"/>
-      <c r="H126" s="235"/>
-      <c r="I126" s="235"/>
-    </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="E125" s="254"/>
+      <c r="F125" s="254"/>
+      <c r="G125" s="254"/>
+      <c r="H125" s="254"/>
+      <c r="I125" s="254"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D126" s="254"/>
+      <c r="E126" s="254"/>
+      <c r="F126" s="254"/>
+      <c r="G126" s="254"/>
+      <c r="H126" s="254"/>
+      <c r="I126" s="254"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A127" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B127" s="17"/>
       <c r="C127" s="18"/>
-      <c r="D127" s="235"/>
-      <c r="E127" s="235"/>
-      <c r="F127" s="235"/>
-      <c r="G127" s="235"/>
-      <c r="H127" s="235"/>
-      <c r="I127" s="235"/>
-    </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D127" s="254"/>
+      <c r="E127" s="254"/>
+      <c r="F127" s="254"/>
+      <c r="G127" s="254"/>
+      <c r="H127" s="254"/>
+      <c r="I127" s="254"/>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A128" s="19" t="s">
         <v>21</v>
       </c>
@@ -5243,14 +5452,14 @@
         <v>-1002261.6181467418</v>
       </c>
       <c r="C128" s="20"/>
-      <c r="D128" s="235"/>
-      <c r="E128" s="235"/>
-      <c r="F128" s="235"/>
-      <c r="G128" s="235"/>
-      <c r="H128" s="235"/>
-      <c r="I128" s="235"/>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D128" s="254"/>
+      <c r="E128" s="254"/>
+      <c r="F128" s="254"/>
+      <c r="G128" s="254"/>
+      <c r="H128" s="254"/>
+      <c r="I128" s="254"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="21" t="s">
         <v>22</v>
       </c>
@@ -5261,14 +5470,14 @@
       <c r="C129" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D129" s="235"/>
-      <c r="E129" s="235"/>
-      <c r="F129" s="235"/>
-      <c r="G129" s="235"/>
-      <c r="H129" s="235"/>
-      <c r="I129" s="235"/>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D129" s="254"/>
+      <c r="E129" s="254"/>
+      <c r="F129" s="254"/>
+      <c r="G129" s="254"/>
+      <c r="H129" s="254"/>
+      <c r="I129" s="254"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="21" t="s">
         <v>36</v>
       </c>
@@ -5277,15 +5486,15 @@
         <v>-12343887.129999999</v>
       </c>
       <c r="C130" s="18"/>
-      <c r="D130" s="235"/>
-      <c r="E130" s="235"/>
-      <c r="F130" s="235"/>
-      <c r="G130" s="235"/>
-      <c r="H130" s="235"/>
-      <c r="I130" s="235"/>
+      <c r="D130" s="254"/>
+      <c r="E130" s="254"/>
+      <c r="F130" s="254"/>
+      <c r="G130" s="254"/>
+      <c r="H130" s="254"/>
+      <c r="I130" s="254"/>
       <c r="K130" s="44"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="21" t="s">
         <v>35</v>
       </c>
@@ -5294,15 +5503,15 @@
         <v>0</v>
       </c>
       <c r="C131" s="18"/>
-      <c r="D131" s="235"/>
-      <c r="E131" s="235"/>
-      <c r="F131" s="235"/>
-      <c r="G131" s="235"/>
-      <c r="H131" s="235"/>
-      <c r="I131" s="235"/>
+      <c r="D131" s="254"/>
+      <c r="E131" s="254"/>
+      <c r="F131" s="254"/>
+      <c r="G131" s="254"/>
+      <c r="H131" s="254"/>
+      <c r="I131" s="254"/>
       <c r="K131" s="52"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="21" t="s">
         <v>294</v>
       </c>
@@ -5311,15 +5520,15 @@
         <v>143267</v>
       </c>
       <c r="C132" s="18"/>
-      <c r="D132" s="235"/>
-      <c r="E132" s="235"/>
-      <c r="F132" s="235"/>
-      <c r="G132" s="235"/>
-      <c r="H132" s="235"/>
-      <c r="I132" s="235"/>
+      <c r="D132" s="254"/>
+      <c r="E132" s="254"/>
+      <c r="F132" s="254"/>
+      <c r="G132" s="254"/>
+      <c r="H132" s="254"/>
+      <c r="I132" s="254"/>
       <c r="K132" s="52"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="21" t="s">
         <v>32</v>
       </c>
@@ -5328,14 +5537,14 @@
         <v>-120000</v>
       </c>
       <c r="C133" s="22"/>
-      <c r="D133" s="235"/>
-      <c r="E133" s="235"/>
-      <c r="F133" s="235"/>
-      <c r="G133" s="235"/>
-      <c r="H133" s="235"/>
-      <c r="I133" s="235"/>
-    </row>
-    <row r="134" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D133" s="254"/>
+      <c r="E133" s="254"/>
+      <c r="F133" s="254"/>
+      <c r="G133" s="254"/>
+      <c r="H133" s="254"/>
+      <c r="I133" s="254"/>
+    </row>
+    <row r="134" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="224" t="s">
         <v>364</v>
       </c>
@@ -5343,14 +5552,14 @@
         <v>426600</v>
       </c>
       <c r="C134" s="22"/>
-      <c r="D134" s="235"/>
-      <c r="E134" s="235"/>
-      <c r="F134" s="235"/>
-      <c r="G134" s="235"/>
-      <c r="H134" s="235"/>
-      <c r="I134" s="235"/>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D134" s="254"/>
+      <c r="E134" s="254"/>
+      <c r="F134" s="254"/>
+      <c r="G134" s="254"/>
+      <c r="H134" s="254"/>
+      <c r="I134" s="254"/>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="21" t="s">
         <v>292</v>
       </c>
@@ -5359,14 +5568,14 @@
         <v>-87300</v>
       </c>
       <c r="C135" s="22"/>
-      <c r="D135" s="235"/>
-      <c r="E135" s="235"/>
-      <c r="F135" s="235"/>
-      <c r="G135" s="235"/>
-      <c r="H135" s="235"/>
-      <c r="I135" s="235"/>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D135" s="254"/>
+      <c r="E135" s="254"/>
+      <c r="F135" s="254"/>
+      <c r="G135" s="254"/>
+      <c r="H135" s="254"/>
+      <c r="I135" s="254"/>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="21" t="s">
         <v>39</v>
       </c>
@@ -5375,25 +5584,25 @@
         <v>-25000</v>
       </c>
       <c r="C136" s="22"/>
-      <c r="D136" s="235"/>
-      <c r="E136" s="235"/>
-      <c r="F136" s="235"/>
-      <c r="G136" s="235"/>
-      <c r="H136" s="235"/>
-      <c r="I136" s="235"/>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D136" s="254"/>
+      <c r="E136" s="254"/>
+      <c r="F136" s="254"/>
+      <c r="G136" s="254"/>
+      <c r="H136" s="254"/>
+      <c r="I136" s="254"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="21"/>
       <c r="B137" s="169"/>
       <c r="C137" s="22"/>
-      <c r="D137" s="235"/>
-      <c r="E137" s="235"/>
-      <c r="F137" s="235"/>
-      <c r="G137" s="235"/>
-      <c r="H137" s="235"/>
-      <c r="I137" s="235"/>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D137" s="254"/>
+      <c r="E137" s="254"/>
+      <c r="F137" s="254"/>
+      <c r="G137" s="254"/>
+      <c r="H137" s="254"/>
+      <c r="I137" s="254"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="19" t="s">
         <v>24</v>
       </c>
@@ -5402,37 +5611,37 @@
         <v>1767072.6013971008</v>
       </c>
       <c r="C138" s="70"/>
-      <c r="D138" s="235"/>
-      <c r="E138" s="235"/>
-      <c r="F138" s="235"/>
-      <c r="G138" s="235"/>
-      <c r="H138" s="235"/>
-      <c r="I138" s="235"/>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D138" s="254"/>
+      <c r="E138" s="254"/>
+      <c r="F138" s="254"/>
+      <c r="G138" s="254"/>
+      <c r="H138" s="254"/>
+      <c r="I138" s="254"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="22"/>
       <c r="C139" s="18"/>
-      <c r="D139" s="235"/>
-      <c r="E139" s="235"/>
-      <c r="F139" s="235"/>
-      <c r="G139" s="235"/>
-      <c r="H139" s="235"/>
-      <c r="I139" s="235"/>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D139" s="254"/>
+      <c r="E139" s="254"/>
+      <c r="F139" s="254"/>
+      <c r="G139" s="254"/>
+      <c r="H139" s="254"/>
+      <c r="I139" s="254"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="16" t="s">
         <v>293</v>
       </c>
       <c r="B140" s="8"/>
       <c r="C140" s="18"/>
-      <c r="D140" s="235"/>
-      <c r="E140" s="235"/>
-      <c r="F140" s="235"/>
-      <c r="G140" s="235"/>
-      <c r="H140" s="235"/>
-      <c r="I140" s="235"/>
-    </row>
-    <row r="141" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D140" s="254"/>
+      <c r="E140" s="254"/>
+      <c r="F140" s="254"/>
+      <c r="G140" s="254"/>
+      <c r="H140" s="254"/>
+      <c r="I140" s="254"/>
+    </row>
+    <row r="141" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="19" t="s">
         <v>362</v>
       </c>
@@ -5442,7 +5651,7 @@
       <c r="C141" s="18"/>
       <c r="D141" s="25"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="36" t="s">
         <v>17</v>
       </c>
@@ -5453,17 +5662,17 @@
       <c r="C142" s="18"/>
       <c r="D142" s="25"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="22"/>
       <c r="C143" s="18"/>
       <c r="D143" s="25"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="22"/>
       <c r="C144" s="18"/>
       <c r="D144" s="25"/>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C145" s="18"/>
       <c r="D145" s="43"/>
       <c r="E145" s="84"/>
@@ -5472,7 +5681,7 @@
       <c r="H145" s="84"/>
       <c r="I145" s="84"/>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" s="16" t="s">
         <v>25</v>
       </c>
@@ -5488,7 +5697,7 @@
       <c r="I146" s="84"/>
       <c r="J146" s="84"/>
     </row>
-    <row r="147" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="19" t="s">
         <v>255</v>
       </c>
@@ -5503,7 +5712,7 @@
       <c r="H147" s="88"/>
       <c r="I147" s="88"/>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" s="19" t="s">
         <v>360</v>
       </c>
@@ -5518,7 +5727,7 @@
       <c r="H148" s="43"/>
       <c r="I148" s="43"/>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" s="36" t="s">
         <v>17</v>
       </c>
@@ -5528,62 +5737,62 @@
       </c>
       <c r="C149" s="24"/>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C150" s="25"/>
       <c r="D150" s="84"/>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B151" s="22"/>
       <c r="C151" s="18"/>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="R153" s="9"/>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B156" s="226"/>
-      <c r="C156" s="226"/>
-      <c r="D156" s="226"/>
-      <c r="E156" s="226"/>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B156" s="245"/>
+      <c r="C156" s="245"/>
+      <c r="D156" s="245"/>
+      <c r="E156" s="245"/>
       <c r="F156" s="90"/>
       <c r="G156" s="90"/>
       <c r="H156" s="90"/>
       <c r="I156" s="90"/>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B157" s="226"/>
-      <c r="C157" s="226"/>
-      <c r="D157" s="226"/>
-      <c r="E157" s="226"/>
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B157" s="245"/>
+      <c r="C157" s="245"/>
+      <c r="D157" s="245"/>
+      <c r="E157" s="245"/>
       <c r="F157" s="90"/>
       <c r="G157" s="90"/>
       <c r="H157" s="90"/>
       <c r="I157" s="90"/>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B158" s="226"/>
-      <c r="C158" s="226"/>
-      <c r="D158" s="226"/>
-      <c r="E158" s="226"/>
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B158" s="245"/>
+      <c r="C158" s="245"/>
+      <c r="D158" s="245"/>
+      <c r="E158" s="245"/>
       <c r="F158" s="90"/>
       <c r="G158" s="90"/>
       <c r="H158" s="90"/>
       <c r="I158" s="90"/>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B159" s="226"/>
-      <c r="C159" s="226"/>
-      <c r="D159" s="226"/>
-      <c r="E159" s="226"/>
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B159" s="245"/>
+      <c r="C159" s="245"/>
+      <c r="D159" s="245"/>
+      <c r="E159" s="245"/>
       <c r="F159" s="90"/>
       <c r="G159" s="90"/>
       <c r="H159" s="90"/>
       <c r="I159" s="90"/>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="B160" s="226"/>
-      <c r="C160" s="226"/>
-      <c r="D160" s="226"/>
-      <c r="E160" s="226"/>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B160" s="245"/>
+      <c r="C160" s="245"/>
+      <c r="D160" s="245"/>
+      <c r="E160" s="245"/>
       <c r="F160" s="90"/>
       <c r="G160" s="90"/>
       <c r="H160" s="90"/>
@@ -5617,36 +5826,36 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DI154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" customWidth="1"/>
-    <col min="4" max="4" width="42.6640625" customWidth="1"/>
-    <col min="5" max="5" width="25.5546875" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" customWidth="1"/>
+    <col min="4" max="4" width="42.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.88671875" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" customWidth="1"/>
-    <col min="13" max="13" width="15.44140625" customWidth="1"/>
-    <col min="14" max="14" width="13.6640625" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="15.42578125" customWidth="1"/>
+    <col min="14" max="14" width="13.7109375" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="272" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="291" t="s">
         <v>365</v>
       </c>
-      <c r="B1" s="273"/>
-      <c r="C1" s="273"/>
-      <c r="D1" s="273"/>
-      <c r="E1" s="273"/>
+      <c r="B1" s="292"/>
+      <c r="C1" s="292"/>
+      <c r="D1" s="292"/>
+      <c r="E1" s="292"/>
       <c r="F1" s="158" t="s">
         <v>296</v>
       </c>
@@ -5657,20 +5866,20 @@
       <c r="K1" s="192" t="s">
         <v>41</v>
       </c>
-      <c r="L1" s="248">
+      <c r="L1" s="267">
         <f>RESUMEN!D110-RESUMEN!D108</f>
         <v>12343887.129999999</v>
       </c>
-      <c r="M1" s="249"/>
+      <c r="M1" s="268"/>
       <c r="N1" s="159"/>
       <c r="O1" s="59"/>
     </row>
-    <row r="2" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="274"/>
-      <c r="B2" s="275"/>
-      <c r="C2" s="275"/>
-      <c r="D2" s="275"/>
-      <c r="E2" s="275"/>
+    <row r="2" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="293"/>
+      <c r="B2" s="294"/>
+      <c r="C2" s="294"/>
+      <c r="D2" s="294"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="7" t="s">
         <v>295</v>
       </c>
@@ -5688,12 +5897,12 @@
       <c r="N2" s="160"/>
       <c r="O2" s="59"/>
     </row>
-    <row r="3" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="274"/>
-      <c r="B3" s="275"/>
-      <c r="C3" s="275"/>
-      <c r="D3" s="275"/>
-      <c r="E3" s="275"/>
+    <row r="3" spans="1:18" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="293"/>
+      <c r="B3" s="294"/>
+      <c r="C3" s="294"/>
+      <c r="D3" s="294"/>
+      <c r="E3" s="294"/>
       <c r="F3" s="7" t="s">
         <v>297</v>
       </c>
@@ -5707,12 +5916,12 @@
       <c r="N3" s="163"/>
       <c r="O3" s="15"/>
     </row>
-    <row r="4" spans="1:18" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="276"/>
-      <c r="B4" s="277"/>
-      <c r="C4" s="277"/>
-      <c r="D4" s="277"/>
-      <c r="E4" s="277"/>
+    <row r="4" spans="1:18" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="295"/>
+      <c r="B4" s="296"/>
+      <c r="C4" s="296"/>
+      <c r="D4" s="296"/>
+      <c r="E4" s="296"/>
       <c r="F4" s="164"/>
       <c r="G4" s="164"/>
       <c r="H4" s="164"/>
@@ -5724,93 +5933,93 @@
       <c r="N4" s="167"/>
       <c r="O4" s="15"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="257" t="s">
+      <c r="C5" s="276" t="s">
         <v>314</v>
       </c>
-      <c r="D5" s="258"/>
-      <c r="E5" s="258"/>
-      <c r="F5" s="258"/>
-      <c r="G5" s="258"/>
-      <c r="H5" s="258"/>
-      <c r="I5" s="258"/>
-      <c r="J5" s="258"/>
-      <c r="K5" s="258"/>
-      <c r="L5" s="258"/>
-      <c r="M5" s="258"/>
-      <c r="N5" s="259"/>
+      <c r="D5" s="277"/>
+      <c r="E5" s="277"/>
+      <c r="F5" s="277"/>
+      <c r="G5" s="277"/>
+      <c r="H5" s="277"/>
+      <c r="I5" s="277"/>
+      <c r="J5" s="277"/>
+      <c r="K5" s="277"/>
+      <c r="L5" s="277"/>
+      <c r="M5" s="277"/>
+      <c r="N5" s="278"/>
       <c r="O5" s="15"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="260"/>
-      <c r="D6" s="261"/>
-      <c r="E6" s="261"/>
-      <c r="F6" s="261"/>
-      <c r="G6" s="261"/>
-      <c r="H6" s="261"/>
-      <c r="I6" s="261"/>
-      <c r="J6" s="261"/>
-      <c r="K6" s="261"/>
-      <c r="L6" s="261"/>
-      <c r="M6" s="261"/>
-      <c r="N6" s="262"/>
+      <c r="C6" s="279"/>
+      <c r="D6" s="280"/>
+      <c r="E6" s="280"/>
+      <c r="F6" s="280"/>
+      <c r="G6" s="280"/>
+      <c r="H6" s="280"/>
+      <c r="I6" s="280"/>
+      <c r="J6" s="280"/>
+      <c r="K6" s="280"/>
+      <c r="L6" s="280"/>
+      <c r="M6" s="280"/>
+      <c r="N6" s="281"/>
       <c r="O6" s="15"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="260"/>
-      <c r="D7" s="261"/>
-      <c r="E7" s="261"/>
-      <c r="F7" s="261"/>
-      <c r="G7" s="261"/>
-      <c r="H7" s="261"/>
-      <c r="I7" s="261"/>
-      <c r="J7" s="261"/>
-      <c r="K7" s="261"/>
-      <c r="L7" s="261"/>
-      <c r="M7" s="261"/>
-      <c r="N7" s="262"/>
+      <c r="C7" s="279"/>
+      <c r="D7" s="280"/>
+      <c r="E7" s="280"/>
+      <c r="F7" s="280"/>
+      <c r="G7" s="280"/>
+      <c r="H7" s="280"/>
+      <c r="I7" s="280"/>
+      <c r="J7" s="280"/>
+      <c r="K7" s="280"/>
+      <c r="L7" s="280"/>
+      <c r="M7" s="280"/>
+      <c r="N7" s="281"/>
       <c r="O7" s="15"/>
     </row>
-    <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="263"/>
-      <c r="D8" s="264"/>
-      <c r="E8" s="264"/>
-      <c r="F8" s="264"/>
-      <c r="G8" s="264"/>
-      <c r="H8" s="264"/>
-      <c r="I8" s="264"/>
-      <c r="J8" s="264"/>
-      <c r="K8" s="264"/>
-      <c r="L8" s="264"/>
-      <c r="M8" s="264"/>
-      <c r="N8" s="265"/>
+      <c r="C8" s="282"/>
+      <c r="D8" s="283"/>
+      <c r="E8" s="283"/>
+      <c r="F8" s="283"/>
+      <c r="G8" s="283"/>
+      <c r="H8" s="283"/>
+      <c r="I8" s="283"/>
+      <c r="J8" s="283"/>
+      <c r="K8" s="283"/>
+      <c r="L8" s="283"/>
+      <c r="M8" s="283"/>
+      <c r="N8" s="284"/>
       <c r="P8" s="84"/>
     </row>
-    <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="266" t="s">
+      <c r="C9" s="285" t="s">
         <v>312</v>
       </c>
-      <c r="D9" s="267"/>
-      <c r="E9" s="267"/>
-      <c r="F9" s="267"/>
-      <c r="G9" s="267"/>
-      <c r="H9" s="267"/>
-      <c r="I9" s="267"/>
-      <c r="J9" s="267"/>
-      <c r="K9" s="267"/>
-      <c r="L9" s="267"/>
-      <c r="M9" s="267"/>
-      <c r="N9" s="268"/>
+      <c r="D9" s="286"/>
+      <c r="E9" s="286"/>
+      <c r="F9" s="286"/>
+      <c r="G9" s="286"/>
+      <c r="H9" s="286"/>
+      <c r="I9" s="286"/>
+      <c r="J9" s="286"/>
+      <c r="K9" s="286"/>
+      <c r="L9" s="286"/>
+      <c r="M9" s="286"/>
+      <c r="N9" s="287"/>
       <c r="P9" t="s">
         <v>250</v>
       </c>
@@ -5819,21 +6028,21 @@
         <v>141730.21116000001</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="269"/>
-      <c r="D10" s="270"/>
-      <c r="E10" s="270"/>
-      <c r="F10" s="270"/>
-      <c r="G10" s="270"/>
-      <c r="H10" s="270"/>
-      <c r="I10" s="270"/>
-      <c r="J10" s="270"/>
-      <c r="K10" s="270"/>
-      <c r="L10" s="270"/>
-      <c r="M10" s="270"/>
-      <c r="N10" s="271"/>
+      <c r="C10" s="288"/>
+      <c r="D10" s="289"/>
+      <c r="E10" s="289"/>
+      <c r="F10" s="289"/>
+      <c r="G10" s="289"/>
+      <c r="H10" s="289"/>
+      <c r="I10" s="289"/>
+      <c r="J10" s="289"/>
+      <c r="K10" s="289"/>
+      <c r="L10" s="289"/>
+      <c r="M10" s="289"/>
+      <c r="N10" s="290"/>
       <c r="P10" t="s">
         <v>251</v>
       </c>
@@ -5842,47 +6051,47 @@
         <v>167976.54656000002</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="244" t="s">
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="263" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="278" t="s">
+      <c r="B11" s="297" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="244" t="s">
+      <c r="C11" s="263" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="280" t="s">
+      <c r="D11" s="299" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="280" t="s">
+      <c r="E11" s="299" t="s">
         <v>269</v>
       </c>
-      <c r="F11" s="244" t="s">
+      <c r="F11" s="263" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="244" t="s">
+      <c r="G11" s="263" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="244" t="s">
+      <c r="H11" s="263" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="250" t="s">
+      <c r="I11" s="269" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="252" t="s">
+      <c r="J11" s="271" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="252" t="s">
+      <c r="K11" s="271" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="255" t="s">
+      <c r="L11" s="274" t="s">
         <v>40</v>
       </c>
-      <c r="M11" s="252" t="s">
+      <c r="M11" s="271" t="s">
         <v>280</v>
       </c>
-      <c r="N11" s="252" t="s">
+      <c r="N11" s="271" t="s">
         <v>279</v>
       </c>
       <c r="P11" t="s">
@@ -5893,21 +6102,21 @@
         <v>158790.32916999998</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="245"/>
-      <c r="B12" s="279"/>
-      <c r="C12" s="245"/>
-      <c r="D12" s="281"/>
-      <c r="E12" s="281"/>
-      <c r="F12" s="245"/>
-      <c r="G12" s="245"/>
-      <c r="H12" s="245"/>
-      <c r="I12" s="251"/>
-      <c r="J12" s="253"/>
-      <c r="K12" s="253"/>
-      <c r="L12" s="256"/>
-      <c r="M12" s="253"/>
-      <c r="N12" s="253"/>
+    <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="264"/>
+      <c r="B12" s="298"/>
+      <c r="C12" s="264"/>
+      <c r="D12" s="300"/>
+      <c r="E12" s="300"/>
+      <c r="F12" s="264"/>
+      <c r="G12" s="264"/>
+      <c r="H12" s="264"/>
+      <c r="I12" s="270"/>
+      <c r="J12" s="272"/>
+      <c r="K12" s="272"/>
+      <c r="L12" s="275"/>
+      <c r="M12" s="272"/>
+      <c r="N12" s="272"/>
       <c r="P12" t="s">
         <v>253</v>
       </c>
@@ -5916,19 +6125,19 @@
         <v>195535.19872999997</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="245"/>
-      <c r="B13" s="279"/>
-      <c r="C13" s="245"/>
-      <c r="D13" s="281"/>
-      <c r="E13" s="281"/>
-      <c r="F13" s="245"/>
-      <c r="G13" s="245"/>
-      <c r="H13" s="245"/>
-      <c r="I13" s="251"/>
-      <c r="J13" s="253"/>
-      <c r="K13" s="254"/>
-      <c r="L13" s="256"/>
+    <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="264"/>
+      <c r="B13" s="298"/>
+      <c r="C13" s="264"/>
+      <c r="D13" s="300"/>
+      <c r="E13" s="300"/>
+      <c r="F13" s="264"/>
+      <c r="G13" s="264"/>
+      <c r="H13" s="264"/>
+      <c r="I13" s="270"/>
+      <c r="J13" s="272"/>
+      <c r="K13" s="273"/>
+      <c r="L13" s="275"/>
       <c r="M13" s="132" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 16/02</v>
@@ -5945,7 +6154,7 @@
         <v>228343.11798000001</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>118</v>
       </c>
@@ -5988,10 +6197,10 @@
         <v>441436.50630288007</v>
       </c>
       <c r="O14" s="115"/>
-      <c r="Q14" s="243"/>
-      <c r="R14" s="243"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q14" s="262"/>
+      <c r="R14" s="262"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="35" t="s">
@@ -6032,10 +6241,10 @@
         <v>307962.66747008008</v>
       </c>
       <c r="O15" s="115"/>
-      <c r="Q15" s="243"/>
-      <c r="R15" s="243"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q15" s="262"/>
+      <c r="R15" s="262"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>118</v>
       </c>
@@ -6083,7 +6292,7 @@
       <c r="O16" s="115"/>
       <c r="R16" s="43"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>118</v>
       </c>
@@ -6126,7 +6335,7 @@
       <c r="O17" s="115"/>
       <c r="R17" s="43"/>
     </row>
-    <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>118</v>
       </c>
@@ -6172,7 +6381,7 @@
       <c r="O18" s="115"/>
       <c r="R18" s="43"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="57" t="s">
         <v>120</v>
       </c>
@@ -6225,7 +6434,7 @@
       </c>
       <c r="R19" s="43"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="57" t="s">
         <v>121</v>
       </c>
@@ -6276,7 +6485,7 @@
       </c>
       <c r="R20" s="43"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="57" t="s">
         <v>120</v>
       </c>
@@ -6326,7 +6535,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="57" t="s">
         <v>122</v>
       </c>
@@ -6380,7 +6589,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="57" t="s">
         <v>122</v>
       </c>
@@ -6430,7 +6639,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="57" t="s">
         <v>122</v>
       </c>
@@ -6482,7 +6691,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="57" t="s">
         <v>120</v>
       </c>
@@ -6534,7 +6743,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="57" t="s">
         <v>121</v>
       </c>
@@ -6584,7 +6793,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="108" t="s">
         <v>120</v>
       </c>
@@ -6637,7 +6846,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="108" t="s">
         <v>122</v>
       </c>
@@ -6687,7 +6896,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="108" t="s">
         <v>122</v>
       </c>
@@ -6737,7 +6946,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="108" t="s">
         <v>122</v>
       </c>
@@ -6784,7 +6993,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="108" t="s">
         <v>120</v>
       </c>
@@ -6834,7 +7043,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="57" t="s">
         <v>121</v>
       </c>
@@ -6886,7 +7095,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A33" s="57" t="s">
         <v>120</v>
       </c>
@@ -6936,7 +7145,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A34" s="139" t="s">
         <v>122</v>
       </c>
@@ -6989,7 +7198,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="35" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A35" s="57" t="s">
         <v>122</v>
       </c>
@@ -7041,7 +7250,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="36" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A36" s="57" t="s">
         <v>122</v>
       </c>
@@ -7088,7 +7297,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A37" s="57" t="s">
         <v>120</v>
       </c>
@@ -7141,7 +7350,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="38" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A38" s="57" t="s">
         <v>121</v>
       </c>
@@ -7191,7 +7400,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="108" t="s">
         <v>120</v>
       </c>
@@ -7338,7 +7547,7 @@
       <c r="DH39" s="73"/>
       <c r="DI39" s="73"/>
     </row>
-    <row r="40" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="108" t="s">
         <v>122</v>
       </c>
@@ -7483,7 +7692,7 @@
       <c r="DH40" s="73"/>
       <c r="DI40" s="73"/>
     </row>
-    <row r="41" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="108" t="s">
         <v>122</v>
       </c>
@@ -7633,7 +7842,7 @@
       <c r="DH41" s="73"/>
       <c r="DI41" s="73"/>
     </row>
-    <row r="42" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:113" s="140" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="108" t="s">
         <v>122</v>
       </c>
@@ -7778,7 +7987,7 @@
       <c r="DH42" s="73"/>
       <c r="DI42" s="73"/>
     </row>
-    <row r="43" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A43" s="57" t="s">
         <v>120</v>
       </c>
@@ -7828,7 +8037,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A44" s="57" t="s">
         <v>121</v>
       </c>
@@ -7880,7 +8089,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A45" s="57" t="s">
         <v>120</v>
       </c>
@@ -7936,7 +8145,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="46" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A46" s="172" t="s">
         <v>122</v>
       </c>
@@ -7986,7 +8195,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="47" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A47" s="57" t="s">
         <v>122</v>
       </c>
@@ -8035,7 +8244,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="48" spans="1:113" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A48" s="57" t="s">
         <v>122</v>
       </c>
@@ -8085,7 +8294,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="57" t="s">
         <v>120</v>
       </c>
@@ -8135,7 +8344,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="57" t="s">
         <v>121</v>
       </c>
@@ -8184,7 +8393,7 @@
       </c>
       <c r="P50" s="43"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="57" t="s">
         <v>120</v>
       </c>
@@ -8235,7 +8444,7 @@
       </c>
       <c r="P51" s="43"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="57" t="s">
         <v>122</v>
       </c>
@@ -8286,7 +8495,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="57" t="s">
         <v>122</v>
       </c>
@@ -8336,7 +8545,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="57" t="s">
         <v>122</v>
       </c>
@@ -8386,7 +8595,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="57" t="s">
         <v>120</v>
       </c>
@@ -8437,7 +8646,7 @@
       </c>
       <c r="Q55" s="59"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="57" t="s">
         <v>121</v>
       </c>
@@ -8489,7 +8698,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="57" t="s">
         <v>120</v>
       </c>
@@ -8538,7 +8747,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="57" t="s">
         <v>122</v>
       </c>
@@ -8591,7 +8800,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="108" t="s">
         <v>122</v>
       </c>
@@ -8644,7 +8853,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="108" t="s">
         <v>122</v>
       </c>
@@ -8695,7 +8904,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="108" t="s">
         <v>120</v>
       </c>
@@ -8745,7 +8954,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="108" t="s">
         <v>121</v>
       </c>
@@ -8795,7 +9004,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="57" t="s">
         <v>120</v>
       </c>
@@ -8845,7 +9054,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="57" t="s">
         <v>122</v>
       </c>
@@ -8880,7 +9089,7 @@
         <f t="shared" si="18"/>
         <v>147271.737246</v>
       </c>
-      <c r="L64" s="282">
+      <c r="L64" s="225">
         <f>13000+K64*0.1</f>
         <v>27727.173724600001</v>
       </c>
@@ -8897,7 +9106,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="57" t="s">
         <v>122</v>
       </c>
@@ -8947,7 +9156,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="57" t="s">
         <v>122</v>
       </c>
@@ -8997,7 +9206,7 @@
       </c>
       <c r="R66" s="183"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="57" t="s">
         <v>120</v>
       </c>
@@ -9046,7 +9255,7 @@
       </c>
       <c r="R67" s="43"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="139" t="s">
         <v>121</v>
       </c>
@@ -9093,7 +9302,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="57" t="s">
         <v>120</v>
       </c>
@@ -9143,7 +9352,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="57" t="s">
         <v>122</v>
       </c>
@@ -9193,7 +9402,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="57" t="s">
         <v>122</v>
       </c>
@@ -9246,7 +9455,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="57" t="s">
         <v>122</v>
       </c>
@@ -9296,7 +9505,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="57" t="s">
         <v>123</v>
       </c>
@@ -9345,7 +9554,7 @@
       </c>
       <c r="P73" s="73"/>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="57" t="s">
         <v>120</v>
       </c>
@@ -9395,7 +9604,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="57" t="s">
         <v>122</v>
       </c>
@@ -9445,7 +9654,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="57" t="s">
         <v>122</v>
       </c>
@@ -9494,7 +9703,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="57" t="s">
         <v>122</v>
       </c>
@@ -9544,7 +9753,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="57" t="s">
         <v>123</v>
       </c>
@@ -9594,7 +9803,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="57" t="s">
         <v>120</v>
       </c>
@@ -9644,7 +9853,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="57" t="s">
         <v>122</v>
       </c>
@@ -9691,7 +9900,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="57" t="s">
         <v>122</v>
       </c>
@@ -9743,7 +9952,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="57" t="s">
         <v>122</v>
       </c>
@@ -9796,7 +10005,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="57" t="s">
         <v>123</v>
       </c>
@@ -9846,7 +10055,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="57" t="s">
         <v>120</v>
       </c>
@@ -9894,7 +10103,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="57" t="s">
         <v>122</v>
       </c>
@@ -9942,7 +10151,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="57" t="s">
         <v>122</v>
       </c>
@@ -9992,7 +10201,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="108" t="s">
         <v>122</v>
       </c>
@@ -10042,7 +10251,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="108"/>
       <c r="B88" s="35"/>
       <c r="C88" s="35" t="s">
@@ -10090,7 +10299,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="108"/>
       <c r="B89" s="35"/>
       <c r="C89" s="35" t="s">
@@ -10138,7 +10347,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="108"/>
       <c r="B90" s="35"/>
       <c r="C90" s="35" t="s">
@@ -10186,7 +10395,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="108"/>
       <c r="B91" s="35"/>
       <c r="C91" s="35" t="s">
@@ -10234,7 +10443,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="108"/>
       <c r="B92" s="35"/>
       <c r="C92" s="176" t="s">
@@ -10285,7 +10494,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="108"/>
       <c r="B93" s="35"/>
       <c r="C93" s="35" t="s">
@@ -10332,7 +10541,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="108"/>
       <c r="B94" s="35"/>
       <c r="C94" s="35" t="s">
@@ -10380,7 +10589,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="108"/>
       <c r="B95" s="35"/>
       <c r="C95" s="35" t="s">
@@ -10428,7 +10637,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="108"/>
       <c r="B96" s="35"/>
       <c r="C96" s="35" t="s">
@@ -10476,7 +10685,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="108"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35" t="s">
@@ -10521,7 +10730,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="108"/>
       <c r="B98" s="35"/>
       <c r="C98" s="35" t="s">
@@ -10569,7 +10778,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="108"/>
       <c r="B99" s="35"/>
       <c r="C99" s="35" t="s">
@@ -10614,7 +10823,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="108"/>
       <c r="B100" s="35"/>
       <c r="C100" s="35" t="s">
@@ -10662,7 +10871,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="108"/>
       <c r="B101" s="35"/>
       <c r="C101" s="35" t="s">
@@ -10710,7 +10919,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="108"/>
       <c r="B102" s="35"/>
       <c r="C102" s="35" t="s">
@@ -10758,7 +10967,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="108"/>
       <c r="B103" s="35"/>
       <c r="C103" s="35" t="s">
@@ -10806,7 +11015,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="108"/>
       <c r="B104" s="35"/>
       <c r="C104" s="35" t="s">
@@ -10854,7 +11063,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="108"/>
       <c r="B105" s="35"/>
       <c r="C105" s="35" t="s">
@@ -10902,7 +11111,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="108"/>
       <c r="B106" s="35"/>
       <c r="C106" s="35" t="s">
@@ -10950,7 +11159,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="108"/>
       <c r="B107" s="35"/>
       <c r="C107" s="35" t="s">
@@ -10997,7 +11206,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="108"/>
       <c r="B108" s="35"/>
       <c r="C108" s="35" t="s">
@@ -11045,7 +11254,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="108"/>
       <c r="B109" s="35"/>
       <c r="C109" s="35" t="s">
@@ -11093,7 +11302,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="108"/>
       <c r="B110" s="35"/>
       <c r="C110" s="35" t="s">
@@ -11141,7 +11350,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="108"/>
       <c r="B111" s="35"/>
       <c r="C111" s="35" t="s">
@@ -11189,7 +11398,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="108"/>
       <c r="B112" s="35"/>
       <c r="C112" s="35" t="s">
@@ -11237,7 +11446,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="108"/>
       <c r="B113" s="35"/>
       <c r="C113" s="35" t="s">
@@ -11285,7 +11494,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="108"/>
       <c r="B114" s="35"/>
       <c r="C114" s="35" t="s">
@@ -11333,7 +11542,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="108"/>
       <c r="B115" s="35"/>
       <c r="C115" s="35" t="s">
@@ -11381,7 +11590,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="108"/>
       <c r="B116" s="35"/>
       <c r="C116" s="35" t="s">
@@ -11431,7 +11640,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="108"/>
       <c r="B117" s="35"/>
       <c r="C117" s="35" t="s">
@@ -11476,7 +11685,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="108"/>
       <c r="B118" s="35"/>
       <c r="C118" s="35" t="s">
@@ -11527,7 +11736,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" s="127"/>
       <c r="B119" s="35"/>
       <c r="C119" s="35" t="s">
@@ -11575,7 +11784,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="127"/>
       <c r="B120" s="35"/>
       <c r="C120" s="35" t="s">
@@ -11623,7 +11832,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="127"/>
       <c r="B121" s="35"/>
       <c r="C121" s="35" t="s">
@@ -11671,7 +11880,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" s="127"/>
       <c r="B122" s="35"/>
       <c r="C122" s="35" t="s">
@@ -11719,7 +11928,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" s="127"/>
       <c r="B123" s="35"/>
       <c r="C123" s="35" t="s">
@@ -11767,7 +11976,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="127"/>
       <c r="B124" s="35"/>
       <c r="C124" s="35" t="s">
@@ -11818,7 +12027,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" s="175"/>
       <c r="B125" s="170"/>
       <c r="C125" s="35" t="s">
@@ -11867,7 +12076,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="175"/>
       <c r="B126" s="170"/>
       <c r="C126" s="35" t="s">
@@ -11915,7 +12124,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="127"/>
       <c r="B127" s="35"/>
       <c r="C127" s="35" t="s">
@@ -11963,7 +12172,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="127"/>
       <c r="B128" s="35"/>
       <c r="C128" s="35" t="s">
@@ -12011,7 +12220,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="127"/>
       <c r="B129" s="35"/>
       <c r="C129" s="35" t="s">
@@ -12059,7 +12268,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="127" t="s">
         <v>26</v>
       </c>
@@ -12109,7 +12318,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="127" t="s">
         <v>26</v>
       </c>
@@ -12159,7 +12368,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="53" t="s">
         <v>26</v>
       </c>
@@ -12177,7 +12386,7 @@
       <c r="M132" s="5"/>
       <c r="N132" s="8"/>
     </row>
-    <row r="133" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="27"/>
       <c r="B133" s="27"/>
       <c r="C133" s="27"/>
@@ -12218,41 +12427,41 @@
       </c>
       <c r="P133" s="59"/>
     </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K134" s="61">
         <f>K133-L1</f>
         <v>3118989.9373000227</v>
       </c>
     </row>
-    <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C135" s="247"/>
-      <c r="D135" s="247"/>
-      <c r="E135" s="247"/>
-      <c r="F135" s="247"/>
-      <c r="G135" s="247"/>
-      <c r="H135" s="247"/>
-      <c r="I135" s="247"/>
-      <c r="J135" s="247"/>
-      <c r="K135" s="247"/>
-      <c r="L135" s="247"/>
-      <c r="M135" s="247"/>
-      <c r="N135" s="247"/>
-    </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C136" s="247"/>
-      <c r="D136" s="247"/>
-      <c r="E136" s="247"/>
-      <c r="F136" s="247"/>
-      <c r="G136" s="247"/>
-      <c r="H136" s="247"/>
-      <c r="I136" s="247"/>
-      <c r="J136" s="247"/>
-      <c r="K136" s="247"/>
-      <c r="L136" s="247"/>
-      <c r="M136" s="247"/>
-      <c r="N136" s="247"/>
-    </row>
-    <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C135" s="266"/>
+      <c r="D135" s="266"/>
+      <c r="E135" s="266"/>
+      <c r="F135" s="266"/>
+      <c r="G135" s="266"/>
+      <c r="H135" s="266"/>
+      <c r="I135" s="266"/>
+      <c r="J135" s="266"/>
+      <c r="K135" s="266"/>
+      <c r="L135" s="266"/>
+      <c r="M135" s="266"/>
+      <c r="N135" s="266"/>
+    </row>
+    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C136" s="266"/>
+      <c r="D136" s="266"/>
+      <c r="E136" s="266"/>
+      <c r="F136" s="266"/>
+      <c r="G136" s="266"/>
+      <c r="H136" s="266"/>
+      <c r="I136" s="266"/>
+      <c r="J136" s="266"/>
+      <c r="K136" s="266"/>
+      <c r="L136" s="266"/>
+      <c r="M136" s="266"/>
+      <c r="N136" s="266"/>
+    </row>
+    <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="77"/>
       <c r="D137" s="77"/>
       <c r="E137" s="77"/>
@@ -12266,121 +12475,121 @@
       <c r="M137" s="77"/>
       <c r="N137" s="77"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C138" s="235" t="s">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C138" s="254" t="s">
         <v>260</v>
       </c>
-      <c r="D138" s="235"/>
-      <c r="E138" s="235"/>
-      <c r="F138" s="235"/>
-      <c r="G138" s="235"/>
-      <c r="H138" s="235"/>
-      <c r="I138" s="235"/>
-      <c r="J138" s="235"/>
-      <c r="K138" s="235"/>
-      <c r="L138" s="235"/>
-      <c r="M138" s="235"/>
-      <c r="N138" s="235"/>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C139" s="235"/>
-      <c r="D139" s="235"/>
-      <c r="E139" s="235"/>
-      <c r="F139" s="235"/>
-      <c r="G139" s="235"/>
-      <c r="H139" s="235"/>
-      <c r="I139" s="235"/>
-      <c r="J139" s="235"/>
-      <c r="K139" s="235"/>
-      <c r="L139" s="235"/>
-      <c r="M139" s="235"/>
-      <c r="N139" s="235"/>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C140" s="235"/>
-      <c r="D140" s="235"/>
-      <c r="E140" s="235"/>
-      <c r="F140" s="235"/>
-      <c r="G140" s="235"/>
-      <c r="H140" s="235"/>
-      <c r="I140" s="235"/>
-      <c r="J140" s="235"/>
-      <c r="K140" s="235"/>
-      <c r="L140" s="235"/>
-      <c r="M140" s="235"/>
-      <c r="N140" s="235"/>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C141" s="235"/>
-      <c r="D141" s="235"/>
-      <c r="E141" s="235"/>
-      <c r="F141" s="235"/>
-      <c r="G141" s="235"/>
-      <c r="H141" s="235"/>
-      <c r="I141" s="235"/>
-      <c r="J141" s="235"/>
-      <c r="K141" s="235"/>
-      <c r="L141" s="235"/>
-      <c r="M141" s="235"/>
-      <c r="N141" s="235"/>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C142" s="235"/>
-      <c r="D142" s="235"/>
-      <c r="E142" s="235"/>
-      <c r="F142" s="235"/>
-      <c r="G142" s="235"/>
-      <c r="H142" s="235"/>
-      <c r="I142" s="235"/>
-      <c r="J142" s="235"/>
-      <c r="K142" s="235"/>
-      <c r="L142" s="235"/>
-      <c r="M142" s="235"/>
-      <c r="N142" s="235"/>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C143" s="235"/>
-      <c r="D143" s="235"/>
-      <c r="E143" s="235"/>
-      <c r="F143" s="235"/>
-      <c r="G143" s="235"/>
-      <c r="H143" s="235"/>
-      <c r="I143" s="235"/>
-      <c r="J143" s="235"/>
-      <c r="K143" s="235"/>
-      <c r="L143" s="235"/>
-      <c r="M143" s="235"/>
-      <c r="N143" s="235"/>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C144" s="235"/>
-      <c r="D144" s="235"/>
-      <c r="E144" s="235"/>
-      <c r="F144" s="235"/>
-      <c r="G144" s="235"/>
-      <c r="H144" s="235"/>
-      <c r="I144" s="235"/>
-      <c r="J144" s="235"/>
-      <c r="K144" s="235"/>
-      <c r="L144" s="235"/>
-      <c r="M144" s="235"/>
-      <c r="N144" s="235"/>
-    </row>
-    <row r="145" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C145" s="235"/>
-      <c r="D145" s="235"/>
-      <c r="E145" s="235"/>
-      <c r="F145" s="235"/>
-      <c r="G145" s="235"/>
-      <c r="H145" s="235"/>
-      <c r="I145" s="235"/>
-      <c r="J145" s="235"/>
-      <c r="K145" s="235"/>
-      <c r="L145" s="235"/>
-      <c r="M145" s="235"/>
-      <c r="N145" s="235"/>
-    </row>
-    <row r="146" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D138" s="254"/>
+      <c r="E138" s="254"/>
+      <c r="F138" s="254"/>
+      <c r="G138" s="254"/>
+      <c r="H138" s="254"/>
+      <c r="I138" s="254"/>
+      <c r="J138" s="254"/>
+      <c r="K138" s="254"/>
+      <c r="L138" s="254"/>
+      <c r="M138" s="254"/>
+      <c r="N138" s="254"/>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C139" s="254"/>
+      <c r="D139" s="254"/>
+      <c r="E139" s="254"/>
+      <c r="F139" s="254"/>
+      <c r="G139" s="254"/>
+      <c r="H139" s="254"/>
+      <c r="I139" s="254"/>
+      <c r="J139" s="254"/>
+      <c r="K139" s="254"/>
+      <c r="L139" s="254"/>
+      <c r="M139" s="254"/>
+      <c r="N139" s="254"/>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C140" s="254"/>
+      <c r="D140" s="254"/>
+      <c r="E140" s="254"/>
+      <c r="F140" s="254"/>
+      <c r="G140" s="254"/>
+      <c r="H140" s="254"/>
+      <c r="I140" s="254"/>
+      <c r="J140" s="254"/>
+      <c r="K140" s="254"/>
+      <c r="L140" s="254"/>
+      <c r="M140" s="254"/>
+      <c r="N140" s="254"/>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C141" s="254"/>
+      <c r="D141" s="254"/>
+      <c r="E141" s="254"/>
+      <c r="F141" s="254"/>
+      <c r="G141" s="254"/>
+      <c r="H141" s="254"/>
+      <c r="I141" s="254"/>
+      <c r="J141" s="254"/>
+      <c r="K141" s="254"/>
+      <c r="L141" s="254"/>
+      <c r="M141" s="254"/>
+      <c r="N141" s="254"/>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C142" s="254"/>
+      <c r="D142" s="254"/>
+      <c r="E142" s="254"/>
+      <c r="F142" s="254"/>
+      <c r="G142" s="254"/>
+      <c r="H142" s="254"/>
+      <c r="I142" s="254"/>
+      <c r="J142" s="254"/>
+      <c r="K142" s="254"/>
+      <c r="L142" s="254"/>
+      <c r="M142" s="254"/>
+      <c r="N142" s="254"/>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C143" s="254"/>
+      <c r="D143" s="254"/>
+      <c r="E143" s="254"/>
+      <c r="F143" s="254"/>
+      <c r="G143" s="254"/>
+      <c r="H143" s="254"/>
+      <c r="I143" s="254"/>
+      <c r="J143" s="254"/>
+      <c r="K143" s="254"/>
+      <c r="L143" s="254"/>
+      <c r="M143" s="254"/>
+      <c r="N143" s="254"/>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C144" s="254"/>
+      <c r="D144" s="254"/>
+      <c r="E144" s="254"/>
+      <c r="F144" s="254"/>
+      <c r="G144" s="254"/>
+      <c r="H144" s="254"/>
+      <c r="I144" s="254"/>
+      <c r="J144" s="254"/>
+      <c r="K144" s="254"/>
+      <c r="L144" s="254"/>
+      <c r="M144" s="254"/>
+      <c r="N144" s="254"/>
+    </row>
+    <row r="145" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C145" s="254"/>
+      <c r="D145" s="254"/>
+      <c r="E145" s="254"/>
+      <c r="F145" s="254"/>
+      <c r="G145" s="254"/>
+      <c r="H145" s="254"/>
+      <c r="I145" s="254"/>
+      <c r="J145" s="254"/>
+      <c r="K145" s="254"/>
+      <c r="L145" s="254"/>
+      <c r="M145" s="254"/>
+      <c r="N145" s="254"/>
+    </row>
+    <row r="146" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="77"/>
       <c r="D146" s="77"/>
       <c r="E146" s="77"/>
@@ -12394,7 +12603,7 @@
       <c r="M146" s="77"/>
       <c r="N146" s="77"/>
     </row>
-    <row r="147" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C147" s="77"/>
       <c r="D147" s="77"/>
       <c r="E147" s="77"/>
@@ -12408,109 +12617,109 @@
       <c r="M147" s="77"/>
       <c r="N147" s="77"/>
     </row>
-    <row r="148" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C148" s="246" t="s">
+    <row r="148" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C148" s="265" t="s">
         <v>259</v>
       </c>
-      <c r="D148" s="246"/>
-      <c r="E148" s="246"/>
-      <c r="F148" s="246"/>
-      <c r="G148" s="246"/>
-      <c r="H148" s="246"/>
-      <c r="I148" s="246"/>
-      <c r="J148" s="246"/>
-      <c r="K148" s="246"/>
-      <c r="L148" s="246"/>
-      <c r="M148" s="246"/>
-      <c r="N148" s="246"/>
-    </row>
-    <row r="149" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C149" s="246"/>
-      <c r="D149" s="246"/>
-      <c r="E149" s="246"/>
-      <c r="F149" s="246"/>
-      <c r="G149" s="246"/>
-      <c r="H149" s="246"/>
-      <c r="I149" s="246"/>
-      <c r="J149" s="246"/>
-      <c r="K149" s="246"/>
-      <c r="L149" s="246"/>
-      <c r="M149" s="246"/>
-      <c r="N149" s="246"/>
-    </row>
-    <row r="150" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C150" s="246"/>
-      <c r="D150" s="246"/>
-      <c r="E150" s="246"/>
-      <c r="F150" s="246"/>
-      <c r="G150" s="246"/>
-      <c r="H150" s="246"/>
-      <c r="I150" s="246"/>
-      <c r="J150" s="246"/>
-      <c r="K150" s="246"/>
-      <c r="L150" s="246"/>
-      <c r="M150" s="246"/>
-      <c r="N150" s="246"/>
+      <c r="D148" s="265"/>
+      <c r="E148" s="265"/>
+      <c r="F148" s="265"/>
+      <c r="G148" s="265"/>
+      <c r="H148" s="265"/>
+      <c r="I148" s="265"/>
+      <c r="J148" s="265"/>
+      <c r="K148" s="265"/>
+      <c r="L148" s="265"/>
+      <c r="M148" s="265"/>
+      <c r="N148" s="265"/>
+    </row>
+    <row r="149" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C149" s="265"/>
+      <c r="D149" s="265"/>
+      <c r="E149" s="265"/>
+      <c r="F149" s="265"/>
+      <c r="G149" s="265"/>
+      <c r="H149" s="265"/>
+      <c r="I149" s="265"/>
+      <c r="J149" s="265"/>
+      <c r="K149" s="265"/>
+      <c r="L149" s="265"/>
+      <c r="M149" s="265"/>
+      <c r="N149" s="265"/>
+    </row>
+    <row r="150" spans="3:16" x14ac:dyDescent="0.25">
+      <c r="C150" s="265"/>
+      <c r="D150" s="265"/>
+      <c r="E150" s="265"/>
+      <c r="F150" s="265"/>
+      <c r="G150" s="265"/>
+      <c r="H150" s="265"/>
+      <c r="I150" s="265"/>
+      <c r="J150" s="265"/>
+      <c r="K150" s="265"/>
+      <c r="L150" s="265"/>
+      <c r="M150" s="265"/>
+      <c r="N150" s="265"/>
       <c r="P150" s="84">
         <f>L1-K133</f>
         <v>-3118989.9373000227</v>
       </c>
     </row>
-    <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C151" s="246"/>
-      <c r="D151" s="246"/>
-      <c r="E151" s="246"/>
-      <c r="F151" s="246"/>
-      <c r="G151" s="246"/>
-      <c r="H151" s="246"/>
-      <c r="I151" s="246"/>
-      <c r="J151" s="246"/>
-      <c r="K151" s="246"/>
-      <c r="L151" s="246"/>
-      <c r="M151" s="246"/>
-      <c r="N151" s="246"/>
-    </row>
-    <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C152" s="246"/>
-      <c r="D152" s="246"/>
-      <c r="E152" s="246"/>
-      <c r="F152" s="246"/>
-      <c r="G152" s="246"/>
-      <c r="H152" s="246"/>
-      <c r="I152" s="246"/>
-      <c r="J152" s="246"/>
-      <c r="K152" s="246"/>
-      <c r="L152" s="246"/>
-      <c r="M152" s="246"/>
-      <c r="N152" s="246"/>
-    </row>
-    <row r="153" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="246"/>
-      <c r="D153" s="246"/>
-      <c r="E153" s="246"/>
-      <c r="F153" s="246"/>
-      <c r="G153" s="246"/>
-      <c r="H153" s="246"/>
-      <c r="I153" s="246"/>
-      <c r="J153" s="246"/>
-      <c r="K153" s="246"/>
-      <c r="L153" s="246"/>
-      <c r="M153" s="246"/>
-      <c r="N153" s="246"/>
-    </row>
-    <row r="154" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="246"/>
-      <c r="D154" s="246"/>
-      <c r="E154" s="246"/>
-      <c r="F154" s="246"/>
-      <c r="G154" s="246"/>
-      <c r="H154" s="246"/>
-      <c r="I154" s="246"/>
-      <c r="J154" s="246"/>
-      <c r="K154" s="246"/>
-      <c r="L154" s="246"/>
-      <c r="M154" s="246"/>
-      <c r="N154" s="246"/>
+    <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C151" s="265"/>
+      <c r="D151" s="265"/>
+      <c r="E151" s="265"/>
+      <c r="F151" s="265"/>
+      <c r="G151" s="265"/>
+      <c r="H151" s="265"/>
+      <c r="I151" s="265"/>
+      <c r="J151" s="265"/>
+      <c r="K151" s="265"/>
+      <c r="L151" s="265"/>
+      <c r="M151" s="265"/>
+      <c r="N151" s="265"/>
+    </row>
+    <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C152" s="265"/>
+      <c r="D152" s="265"/>
+      <c r="E152" s="265"/>
+      <c r="F152" s="265"/>
+      <c r="G152" s="265"/>
+      <c r="H152" s="265"/>
+      <c r="I152" s="265"/>
+      <c r="J152" s="265"/>
+      <c r="K152" s="265"/>
+      <c r="L152" s="265"/>
+      <c r="M152" s="265"/>
+      <c r="N152" s="265"/>
+    </row>
+    <row r="153" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C153" s="265"/>
+      <c r="D153" s="265"/>
+      <c r="E153" s="265"/>
+      <c r="F153" s="265"/>
+      <c r="G153" s="265"/>
+      <c r="H153" s="265"/>
+      <c r="I153" s="265"/>
+      <c r="J153" s="265"/>
+      <c r="K153" s="265"/>
+      <c r="L153" s="265"/>
+      <c r="M153" s="265"/>
+      <c r="N153" s="265"/>
+    </row>
+    <row r="154" spans="3:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C154" s="265"/>
+      <c r="D154" s="265"/>
+      <c r="E154" s="265"/>
+      <c r="F154" s="265"/>
+      <c r="G154" s="265"/>
+      <c r="H154" s="265"/>
+      <c r="I154" s="265"/>
+      <c r="J154" s="265"/>
+      <c r="K154" s="265"/>
+      <c r="L154" s="265"/>
+      <c r="M154" s="265"/>
+      <c r="N154" s="265"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -12544,11 +12753,3651 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7AB47CA-548A-40FB-AC1D-01E96423736C}">
+  <dimension ref="A1:DF81"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
+    <col min="11" max="11" width="19.5703125" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="303" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1" s="303"/>
+      <c r="C1" s="303"/>
+      <c r="D1" s="303"/>
+      <c r="E1" s="303"/>
+      <c r="F1" s="303"/>
+      <c r="G1" s="303"/>
+      <c r="H1" s="303"/>
+      <c r="I1" s="303"/>
+      <c r="J1" s="303"/>
+      <c r="K1" s="304"/>
+      <c r="N1" s="43"/>
+    </row>
+    <row r="2" spans="1:15" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="305"/>
+      <c r="B2" s="305"/>
+      <c r="C2" s="305"/>
+      <c r="D2" s="305"/>
+      <c r="E2" s="305"/>
+      <c r="F2" s="305"/>
+      <c r="G2" s="305"/>
+      <c r="H2" s="305"/>
+      <c r="I2" s="305"/>
+      <c r="J2" s="305"/>
+      <c r="K2" s="306"/>
+      <c r="N2" s="43"/>
+    </row>
+    <row r="3" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="263" t="s">
+        <v>368</v>
+      </c>
+      <c r="B3" s="263" t="s">
+        <v>369</v>
+      </c>
+      <c r="C3" s="263" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="263" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="271" t="s">
+        <v>396</v>
+      </c>
+      <c r="F3" s="271" t="s">
+        <v>397</v>
+      </c>
+      <c r="G3" s="271" t="s">
+        <v>280</v>
+      </c>
+      <c r="H3" s="311" t="s">
+        <v>398</v>
+      </c>
+      <c r="I3" s="226"/>
+      <c r="J3" s="271" t="s">
+        <v>399</v>
+      </c>
+      <c r="K3" s="271" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" s="43"/>
+    </row>
+    <row r="4" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="264"/>
+      <c r="B4" s="264"/>
+      <c r="C4" s="264"/>
+      <c r="D4" s="264"/>
+      <c r="E4" s="272"/>
+      <c r="F4" s="272"/>
+      <c r="G4" s="272"/>
+      <c r="H4" s="312"/>
+      <c r="I4" s="131"/>
+      <c r="J4" s="272"/>
+      <c r="K4" s="272"/>
+      <c r="N4" s="43"/>
+    </row>
+    <row r="5" spans="1:15" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="301"/>
+      <c r="B5" s="301"/>
+      <c r="C5" s="301"/>
+      <c r="D5" s="301"/>
+      <c r="E5" s="302"/>
+      <c r="F5" s="302"/>
+      <c r="G5" s="302"/>
+      <c r="H5" s="313"/>
+      <c r="I5" s="227"/>
+      <c r="J5" s="302"/>
+      <c r="K5" s="302"/>
+      <c r="N5" s="43"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="228" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="229"/>
+      <c r="C6" s="230" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="136">
+        <v>1.0800000000000001E-2</v>
+      </c>
+      <c r="E6" s="188">
+        <v>282914.37972000003</v>
+      </c>
+      <c r="F6" s="240">
+        <v>45856</v>
+      </c>
+      <c r="G6" s="243">
+        <v>-197064.48265741928</v>
+      </c>
+      <c r="H6" s="309">
+        <f>ROUND((-G6),0)+L6</f>
+        <v>197064.7</v>
+      </c>
+      <c r="I6" s="243">
+        <v>-85849.897062580741</v>
+      </c>
+      <c r="J6" s="243">
+        <f>-I6</f>
+        <v>85849.897062580741</v>
+      </c>
+      <c r="K6" s="307">
+        <f>ROUND((H6+J6),0) + L6</f>
+        <v>282915.7</v>
+      </c>
+      <c r="L6" s="115">
+        <v>0.7</v>
+      </c>
+      <c r="N6" s="262"/>
+      <c r="O6" s="262"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="228" t="s">
+        <v>375</v>
+      </c>
+      <c r="B7" s="229"/>
+      <c r="C7" s="35" t="s">
+        <v>376</v>
+      </c>
+      <c r="D7" s="143">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="E7" s="145">
+        <v>335305.93151999998</v>
+      </c>
+      <c r="F7" s="240">
+        <v>46001</v>
+      </c>
+      <c r="G7" s="146">
+        <v>-34751.379392876712</v>
+      </c>
+      <c r="H7" s="309">
+        <f t="shared" ref="H7:H70" si="0">ROUND((-G7),0)+L7</f>
+        <v>34751.71</v>
+      </c>
+      <c r="I7" s="146">
+        <v>-300554.55212712329</v>
+      </c>
+      <c r="J7" s="243">
+        <f t="shared" ref="J7:J10" si="1">-I7</f>
+        <v>300554.55212712329</v>
+      </c>
+      <c r="K7" s="307">
+        <f t="shared" ref="K7:K10" si="2">ROUND((H7+J7),0) + L7</f>
+        <v>335306.71000000002</v>
+      </c>
+      <c r="L7" s="115">
+        <f>L6+0.01</f>
+        <v>0.71</v>
+      </c>
+      <c r="N7" s="262"/>
+      <c r="O7" s="262"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="228" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="229"/>
+      <c r="C8" s="231" t="s">
+        <v>377</v>
+      </c>
+      <c r="D8" s="143">
+        <v>1.21E-2</v>
+      </c>
+      <c r="E8" s="145">
+        <v>316968.88838999998</v>
+      </c>
+      <c r="F8" s="240">
+        <v>45856</v>
+      </c>
+      <c r="G8" s="146">
+        <v>-220785.20742173825</v>
+      </c>
+      <c r="H8" s="309">
+        <f t="shared" si="0"/>
+        <v>220785.72</v>
+      </c>
+      <c r="I8" s="146">
+        <v>-96183.680968261731</v>
+      </c>
+      <c r="J8" s="243">
+        <f t="shared" si="1"/>
+        <v>96183.680968261731</v>
+      </c>
+      <c r="K8" s="307">
+        <f t="shared" si="2"/>
+        <v>316969.71999999997</v>
+      </c>
+      <c r="L8" s="115">
+        <f t="shared" ref="L8:L10" si="3">L7+0.01</f>
+        <v>0.72</v>
+      </c>
+      <c r="O8" s="43"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="228" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="229"/>
+      <c r="C9" s="230" t="s">
+        <v>176</v>
+      </c>
+      <c r="D9" s="143">
+        <v>1.49E-2</v>
+      </c>
+      <c r="E9" s="145">
+        <v>390317.06091</v>
+      </c>
+      <c r="F9" s="240">
+        <v>45856</v>
+      </c>
+      <c r="G9" s="146">
+        <v>-271875.99922180991</v>
+      </c>
+      <c r="H9" s="309">
+        <f t="shared" si="0"/>
+        <v>271876.73</v>
+      </c>
+      <c r="I9" s="146">
+        <v>-118441.06168819009</v>
+      </c>
+      <c r="J9" s="243">
+        <f t="shared" si="1"/>
+        <v>118441.06168819009</v>
+      </c>
+      <c r="K9" s="307">
+        <f t="shared" si="2"/>
+        <v>390318.73</v>
+      </c>
+      <c r="L9" s="115">
+        <f t="shared" si="3"/>
+        <v>0.73</v>
+      </c>
+      <c r="O9" s="43"/>
+    </row>
+    <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="232" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="233"/>
+      <c r="C10" s="234" t="s">
+        <v>378</v>
+      </c>
+      <c r="D10" s="150">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="E10" s="153">
+        <v>458426.07825000002</v>
+      </c>
+      <c r="F10" s="241">
+        <v>45856</v>
+      </c>
+      <c r="G10" s="154">
+        <v>-319317.44875044789</v>
+      </c>
+      <c r="H10" s="310">
+        <f t="shared" si="0"/>
+        <v>319317.74</v>
+      </c>
+      <c r="I10" s="154">
+        <v>-139108.62949955213</v>
+      </c>
+      <c r="J10" s="154">
+        <f t="shared" si="1"/>
+        <v>139108.62949955213</v>
+      </c>
+      <c r="K10" s="308">
+        <f t="shared" si="2"/>
+        <v>458426.74</v>
+      </c>
+      <c r="L10" s="115">
+        <f t="shared" si="3"/>
+        <v>0.74</v>
+      </c>
+      <c r="O10" s="43"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="235" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="236">
+        <v>25</v>
+      </c>
+      <c r="C11" s="135" t="s">
+        <v>177</v>
+      </c>
+      <c r="D11" s="136">
+        <v>2.12E-2</v>
+      </c>
+      <c r="E11" s="188">
+        <v>555350.44907999993</v>
+      </c>
+      <c r="F11" s="242">
+        <v>45777</v>
+      </c>
+      <c r="G11" s="189">
+        <v>-519626.96981144731</v>
+      </c>
+      <c r="H11" s="309">
+        <f t="shared" si="0"/>
+        <v>519627.01</v>
+      </c>
+      <c r="I11" s="189">
+        <v>-35723.479268552619</v>
+      </c>
+      <c r="J11" s="189">
+        <f>-I11</f>
+        <v>35723.479268552619</v>
+      </c>
+      <c r="K11" s="307">
+        <f>ROUND((H11+J11),0) + L11</f>
+        <v>555350.01</v>
+      </c>
+      <c r="L11" s="133">
+        <v>0.01</v>
+      </c>
+      <c r="O11" s="43"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="228" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="229"/>
+      <c r="C12" s="108" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" s="136">
+        <v>8.3999999999999995E-3</v>
+      </c>
+      <c r="E12" s="145">
+        <v>220044.51755999998</v>
+      </c>
+      <c r="F12" s="240">
+        <v>45775</v>
+      </c>
+      <c r="G12" s="147">
+        <v>-206492.25424856588</v>
+      </c>
+      <c r="H12" s="309">
+        <f t="shared" si="0"/>
+        <v>206492.02</v>
+      </c>
+      <c r="I12" s="147">
+        <v>-13552.263311434101</v>
+      </c>
+      <c r="J12" s="189">
+        <f t="shared" ref="J12:J75" si="4">-I12</f>
+        <v>13552.263311434101</v>
+      </c>
+      <c r="K12" s="307">
+        <f t="shared" ref="K12:K75" si="5">ROUND((H12+J12),0) + L12</f>
+        <v>220044.02</v>
+      </c>
+      <c r="L12" s="133">
+        <f>L11+0.01</f>
+        <v>0.02</v>
+      </c>
+      <c r="O12" s="43"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="228" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="229">
+        <v>22</v>
+      </c>
+      <c r="C13" s="108" t="s">
+        <v>179</v>
+      </c>
+      <c r="D13" s="136">
+        <v>2.2499999999999999E-2</v>
+      </c>
+      <c r="E13" s="145">
+        <v>589404.95774999994</v>
+      </c>
+      <c r="F13" s="240">
+        <v>45770</v>
+      </c>
+      <c r="G13" s="147">
+        <v>-557137.66415134736</v>
+      </c>
+      <c r="H13" s="309">
+        <f t="shared" si="0"/>
+        <v>557138.03</v>
+      </c>
+      <c r="I13" s="147">
+        <v>-32267.293598652584</v>
+      </c>
+      <c r="J13" s="189">
+        <f t="shared" si="4"/>
+        <v>32267.293598652584</v>
+      </c>
+      <c r="K13" s="307">
+        <f t="shared" si="5"/>
+        <v>589405.03</v>
+      </c>
+      <c r="L13" s="133">
+        <f t="shared" ref="L13:L76" si="6">L12+0.01</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="228" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="229" t="s">
+        <v>370</v>
+      </c>
+      <c r="C14" s="108" t="s">
+        <v>180</v>
+      </c>
+      <c r="D14" s="136">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E14" s="145">
+        <v>366740.86259999999</v>
+      </c>
+      <c r="F14" s="240">
+        <v>45805</v>
+      </c>
+      <c r="G14" s="147">
+        <v>-327282.74303127197</v>
+      </c>
+      <c r="H14" s="309">
+        <f t="shared" si="0"/>
+        <v>327283.03999999998</v>
+      </c>
+      <c r="I14" s="147">
+        <v>-39458.119568728027</v>
+      </c>
+      <c r="J14" s="189">
+        <f t="shared" si="4"/>
+        <v>39458.119568728027</v>
+      </c>
+      <c r="K14" s="307">
+        <f t="shared" si="5"/>
+        <v>366741.04</v>
+      </c>
+      <c r="L14" s="133">
+        <f t="shared" si="6"/>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="228" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="229"/>
+      <c r="C15" s="108" t="s">
+        <v>181</v>
+      </c>
+      <c r="D15" s="136">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="E15" s="145">
+        <v>227903.25032999998</v>
+      </c>
+      <c r="F15" s="240">
+        <v>45800</v>
+      </c>
+      <c r="G15" s="147">
+        <v>-206069.04832824506</v>
+      </c>
+      <c r="H15" s="309">
+        <f t="shared" si="0"/>
+        <v>206069.05</v>
+      </c>
+      <c r="I15" s="147">
+        <v>-21834.202001754922</v>
+      </c>
+      <c r="J15" s="189">
+        <f t="shared" si="4"/>
+        <v>21834.202001754922</v>
+      </c>
+      <c r="K15" s="307">
+        <f t="shared" si="5"/>
+        <v>227903.05</v>
+      </c>
+      <c r="L15" s="133">
+        <f t="shared" si="6"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="228" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="229" t="s">
+        <v>371</v>
+      </c>
+      <c r="C16" s="108" t="s">
+        <v>182</v>
+      </c>
+      <c r="D16" s="136">
+        <v>1.41E-2</v>
+      </c>
+      <c r="E16" s="145">
+        <v>369360.44018999999</v>
+      </c>
+      <c r="F16" s="240">
+        <v>45805</v>
+      </c>
+      <c r="G16" s="147">
+        <v>-329620.47691006673</v>
+      </c>
+      <c r="H16" s="309">
+        <f t="shared" si="0"/>
+        <v>329620.06</v>
+      </c>
+      <c r="I16" s="147">
+        <v>-39739.963279933261</v>
+      </c>
+      <c r="J16" s="189">
+        <f t="shared" si="4"/>
+        <v>39739.963279933261</v>
+      </c>
+      <c r="K16" s="307">
+        <f t="shared" si="5"/>
+        <v>369360.06</v>
+      </c>
+      <c r="L16" s="133">
+        <f t="shared" si="6"/>
+        <v>6.0000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A17" s="228" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="229" t="s">
+        <v>372</v>
+      </c>
+      <c r="C17" s="108" t="s">
+        <v>379</v>
+      </c>
+      <c r="D17" s="136">
+        <v>2.1100000000000001E-2</v>
+      </c>
+      <c r="E17" s="145">
+        <v>552730.87148999993</v>
+      </c>
+      <c r="F17" s="240">
+        <v>45805</v>
+      </c>
+      <c r="G17" s="147">
+        <v>-493261.84842570277</v>
+      </c>
+      <c r="H17" s="309">
+        <f t="shared" si="0"/>
+        <v>493262.07</v>
+      </c>
+      <c r="I17" s="147">
+        <v>-59469.023064297158</v>
+      </c>
+      <c r="J17" s="189">
+        <f t="shared" si="4"/>
+        <v>59469.023064297158</v>
+      </c>
+      <c r="K17" s="307">
+        <f t="shared" si="5"/>
+        <v>552731.06999999995</v>
+      </c>
+      <c r="L17" s="133">
+        <f t="shared" si="6"/>
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A18" s="228" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="229"/>
+      <c r="C18" s="108" t="s">
+        <v>380</v>
+      </c>
+      <c r="D18" s="136">
+        <v>7.4000000000000003E-3</v>
+      </c>
+      <c r="E18" s="145">
+        <v>193848.74166</v>
+      </c>
+      <c r="F18" s="240">
+        <v>45839</v>
+      </c>
+      <c r="G18" s="147">
+        <v>-147681.21170563609</v>
+      </c>
+      <c r="H18" s="309">
+        <f t="shared" si="0"/>
+        <v>147681.07999999999</v>
+      </c>
+      <c r="I18" s="147">
+        <v>-46167.529954363912</v>
+      </c>
+      <c r="J18" s="189">
+        <f t="shared" si="4"/>
+        <v>46167.529954363912</v>
+      </c>
+      <c r="K18" s="307">
+        <f t="shared" si="5"/>
+        <v>193849.08</v>
+      </c>
+      <c r="L18" s="133">
+        <f t="shared" si="6"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="19" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A19" s="228" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="229"/>
+      <c r="C19" s="108" t="s">
+        <v>182</v>
+      </c>
+      <c r="D19" s="136">
+        <v>1.7899999999999999E-2</v>
+      </c>
+      <c r="E19" s="145">
+        <v>468904.38860999997</v>
+      </c>
+      <c r="F19" s="240">
+        <v>45805</v>
+      </c>
+      <c r="G19" s="147">
+        <v>-418454.36430426914</v>
+      </c>
+      <c r="H19" s="309">
+        <f t="shared" si="0"/>
+        <v>418454.09</v>
+      </c>
+      <c r="I19" s="147">
+        <v>-50450.024305730825</v>
+      </c>
+      <c r="J19" s="189">
+        <f t="shared" si="4"/>
+        <v>50450.024305730825</v>
+      </c>
+      <c r="K19" s="307">
+        <f t="shared" si="5"/>
+        <v>468904.09</v>
+      </c>
+      <c r="L19" s="133">
+        <f t="shared" si="6"/>
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="20" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A20" s="228" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="229"/>
+      <c r="C20" s="108" t="s">
+        <v>183</v>
+      </c>
+      <c r="D20" s="136">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="E20" s="145">
+        <v>246240.29345999999</v>
+      </c>
+      <c r="F20" s="240">
+        <v>45839</v>
+      </c>
+      <c r="G20" s="147">
+        <v>-187595.05270715937</v>
+      </c>
+      <c r="H20" s="309">
+        <f t="shared" si="0"/>
+        <v>187595.1</v>
+      </c>
+      <c r="I20" s="147">
+        <v>-58645.240752840618</v>
+      </c>
+      <c r="J20" s="189">
+        <f t="shared" si="4"/>
+        <v>58645.240752840618</v>
+      </c>
+      <c r="K20" s="307">
+        <f t="shared" si="5"/>
+        <v>246240.1</v>
+      </c>
+      <c r="L20" s="133">
+        <f t="shared" si="6"/>
+        <v>9.9999999999999992E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A21" s="228" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="229"/>
+      <c r="C21" s="108" t="s">
+        <v>381</v>
+      </c>
+      <c r="D21" s="136">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="E21" s="145">
+        <v>227903.25032999998</v>
+      </c>
+      <c r="F21" s="240">
+        <v>45839</v>
+      </c>
+      <c r="G21" s="147">
+        <v>-173625.20835662619</v>
+      </c>
+      <c r="H21" s="309">
+        <f t="shared" si="0"/>
+        <v>173625.11</v>
+      </c>
+      <c r="I21" s="147">
+        <v>-54278.041973373794</v>
+      </c>
+      <c r="J21" s="189">
+        <f t="shared" si="4"/>
+        <v>54278.041973373794</v>
+      </c>
+      <c r="K21" s="307">
+        <f t="shared" si="5"/>
+        <v>227903.11</v>
+      </c>
+      <c r="L21" s="133">
+        <f t="shared" si="6"/>
+        <v>0.10999999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A22" s="228" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="229"/>
+      <c r="C22" s="108" t="s">
+        <v>183</v>
+      </c>
+      <c r="D22" s="136">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="E22" s="145">
+        <v>248859.87104999999</v>
+      </c>
+      <c r="F22" s="240">
+        <v>45839</v>
+      </c>
+      <c r="G22" s="147">
+        <v>-189590.74475723552</v>
+      </c>
+      <c r="H22" s="309">
+        <f t="shared" si="0"/>
+        <v>189591.12</v>
+      </c>
+      <c r="I22" s="147">
+        <v>-59269.126292764471</v>
+      </c>
+      <c r="J22" s="189">
+        <f t="shared" si="4"/>
+        <v>59269.126292764471</v>
+      </c>
+      <c r="K22" s="307">
+        <f t="shared" si="5"/>
+        <v>248860.12</v>
+      </c>
+      <c r="L22" s="133">
+        <f t="shared" si="6"/>
+        <v>0.11999999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A23" s="228" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="229"/>
+      <c r="C23" s="108" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" s="136">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="E23" s="145">
+        <v>429610.72476000001</v>
+      </c>
+      <c r="F23" s="240">
+        <v>45775</v>
+      </c>
+      <c r="G23" s="147">
+        <v>-403151.54400910489</v>
+      </c>
+      <c r="H23" s="309">
+        <f t="shared" si="0"/>
+        <v>403152.13</v>
+      </c>
+      <c r="I23" s="147">
+        <v>-26459.180750895117</v>
+      </c>
+      <c r="J23" s="189">
+        <f t="shared" si="4"/>
+        <v>26459.180750895117</v>
+      </c>
+      <c r="K23" s="307">
+        <f t="shared" si="5"/>
+        <v>429611.13</v>
+      </c>
+      <c r="L23" s="133">
+        <f t="shared" si="6"/>
+        <v>0.12999999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A24" s="228" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="229"/>
+      <c r="C24" s="108" t="s">
+        <v>382</v>
+      </c>
+      <c r="D24" s="136">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="E24" s="145">
+        <v>191229.16407</v>
+      </c>
+      <c r="F24" s="240">
+        <v>45800</v>
+      </c>
+      <c r="G24" s="147">
+        <v>-172908.51181565388</v>
+      </c>
+      <c r="H24" s="309">
+        <f t="shared" si="0"/>
+        <v>172909.14</v>
+      </c>
+      <c r="I24" s="147">
+        <v>-18320.652254346118</v>
+      </c>
+      <c r="J24" s="189">
+        <f t="shared" si="4"/>
+        <v>18320.652254346118</v>
+      </c>
+      <c r="K24" s="307">
+        <f t="shared" si="5"/>
+        <v>191230.14</v>
+      </c>
+      <c r="L24" s="133">
+        <f t="shared" si="6"/>
+        <v>0.13999999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A25" s="228" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="237" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" s="108" t="s">
+        <v>185</v>
+      </c>
+      <c r="D25" s="136">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="E25" s="145">
+        <v>576307.06979999994</v>
+      </c>
+      <c r="F25" s="240">
+        <v>45775</v>
+      </c>
+      <c r="G25" s="147">
+        <v>-540813.04684148217</v>
+      </c>
+      <c r="H25" s="309">
+        <f t="shared" si="0"/>
+        <v>540813.15</v>
+      </c>
+      <c r="I25" s="147">
+        <v>-35494.022958517773</v>
+      </c>
+      <c r="J25" s="189">
+        <f t="shared" si="4"/>
+        <v>35494.022958517773</v>
+      </c>
+      <c r="K25" s="307">
+        <f t="shared" si="5"/>
+        <v>576307.15</v>
+      </c>
+      <c r="L25" s="133">
+        <f t="shared" si="6"/>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A26" s="228" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="229"/>
+      <c r="C26" s="108" t="s">
+        <v>183</v>
+      </c>
+      <c r="D26" s="136">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="E26" s="145">
+        <v>246240.29345999999</v>
+      </c>
+      <c r="F26" s="240">
+        <v>45839</v>
+      </c>
+      <c r="G26" s="147">
+        <v>-187595.05270715937</v>
+      </c>
+      <c r="H26" s="309">
+        <f t="shared" si="0"/>
+        <v>187595.16</v>
+      </c>
+      <c r="I26" s="147">
+        <v>-58645.240752840618</v>
+      </c>
+      <c r="J26" s="189">
+        <f t="shared" si="4"/>
+        <v>58645.240752840618</v>
+      </c>
+      <c r="K26" s="307">
+        <f t="shared" si="5"/>
+        <v>246240.16</v>
+      </c>
+      <c r="L26" s="133">
+        <f t="shared" si="6"/>
+        <v>0.16</v>
+      </c>
+      <c r="M26" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="27" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A27" s="228" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="229"/>
+      <c r="C27" s="108" t="s">
+        <v>383</v>
+      </c>
+      <c r="D27" s="136">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="E27" s="145">
+        <v>227903.25032999998</v>
+      </c>
+      <c r="F27" s="240">
+        <v>45839</v>
+      </c>
+      <c r="G27" s="147">
+        <v>-173625.20835662619</v>
+      </c>
+      <c r="H27" s="309">
+        <f t="shared" si="0"/>
+        <v>173625.17</v>
+      </c>
+      <c r="I27" s="147">
+        <v>-54278.041973373794</v>
+      </c>
+      <c r="J27" s="189">
+        <f t="shared" si="4"/>
+        <v>54278.041973373794</v>
+      </c>
+      <c r="K27" s="307">
+        <f t="shared" si="5"/>
+        <v>227903.17</v>
+      </c>
+      <c r="L27" s="133">
+        <f t="shared" si="6"/>
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A28" s="228" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="229"/>
+      <c r="C28" s="108" t="s">
+        <v>183</v>
+      </c>
+      <c r="D28" s="136">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="E28" s="145">
+        <v>248859.87104999999</v>
+      </c>
+      <c r="F28" s="240">
+        <v>45839</v>
+      </c>
+      <c r="G28" s="147">
+        <v>-189590.74475723552</v>
+      </c>
+      <c r="H28" s="309">
+        <f t="shared" si="0"/>
+        <v>189591.18</v>
+      </c>
+      <c r="I28" s="147">
+        <v>-59269.126292764471</v>
+      </c>
+      <c r="J28" s="189">
+        <f t="shared" si="4"/>
+        <v>59269.126292764471</v>
+      </c>
+      <c r="K28" s="307">
+        <f t="shared" si="5"/>
+        <v>248860.18</v>
+      </c>
+      <c r="L28" s="133">
+        <f t="shared" si="6"/>
+        <v>0.18000000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A29" s="228" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="229"/>
+      <c r="C29" s="108" t="s">
+        <v>186</v>
+      </c>
+      <c r="D29" s="136">
+        <v>1.6400000000000001E-2</v>
+      </c>
+      <c r="E29" s="145">
+        <v>429610.72476000001</v>
+      </c>
+      <c r="F29" s="240">
+        <v>45800</v>
+      </c>
+      <c r="G29" s="147">
+        <v>-388451.99914749648</v>
+      </c>
+      <c r="H29" s="309">
+        <f t="shared" si="0"/>
+        <v>388452.19</v>
+      </c>
+      <c r="I29" s="147">
+        <v>-41158.725612503535</v>
+      </c>
+      <c r="J29" s="189">
+        <f t="shared" si="4"/>
+        <v>41158.725612503535</v>
+      </c>
+      <c r="K29" s="307">
+        <f t="shared" si="5"/>
+        <v>429611.19</v>
+      </c>
+      <c r="L29" s="133">
+        <f t="shared" si="6"/>
+        <v>0.19000000000000003</v>
+      </c>
+      <c r="M29" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="30" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A30" s="228" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" s="229">
+        <v>16</v>
+      </c>
+      <c r="C30" s="108" t="s">
+        <v>222</v>
+      </c>
+      <c r="D30" s="136">
+        <v>9.6000000000000009E-3</v>
+      </c>
+      <c r="E30" s="145">
+        <v>251479.44864000002</v>
+      </c>
+      <c r="F30" s="240">
+        <v>45805</v>
+      </c>
+      <c r="G30" s="147">
+        <v>-224422.45236430079</v>
+      </c>
+      <c r="H30" s="309">
+        <f t="shared" si="0"/>
+        <v>224422.2</v>
+      </c>
+      <c r="I30" s="147">
+        <v>-27056.996275699232</v>
+      </c>
+      <c r="J30" s="189">
+        <f t="shared" si="4"/>
+        <v>27056.996275699232</v>
+      </c>
+      <c r="K30" s="307">
+        <f t="shared" si="5"/>
+        <v>251479.2</v>
+      </c>
+      <c r="L30" s="133">
+        <f t="shared" si="6"/>
+        <v>0.20000000000000004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:110" s="140" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="228" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="229">
+        <v>6</v>
+      </c>
+      <c r="C31" s="108" t="s">
+        <v>187</v>
+      </c>
+      <c r="D31" s="136">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="E31" s="145">
+        <v>516056.78522999992</v>
+      </c>
+      <c r="F31" s="240">
+        <v>45805</v>
+      </c>
+      <c r="G31" s="147">
+        <v>-460533.57412257558</v>
+      </c>
+      <c r="H31" s="309">
+        <f t="shared" si="0"/>
+        <v>460534.21</v>
+      </c>
+      <c r="I31" s="147">
+        <v>-55523.211107424344</v>
+      </c>
+      <c r="J31" s="189">
+        <f t="shared" si="4"/>
+        <v>55523.211107424344</v>
+      </c>
+      <c r="K31" s="307">
+        <f t="shared" si="5"/>
+        <v>516057.21</v>
+      </c>
+      <c r="L31" s="173">
+        <f t="shared" si="6"/>
+        <v>0.21000000000000005</v>
+      </c>
+      <c r="M31" s="73"/>
+      <c r="N31" s="73"/>
+      <c r="O31" s="73"/>
+      <c r="P31" s="73"/>
+      <c r="Q31" s="73"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="73"/>
+      <c r="T31" s="73"/>
+      <c r="U31" s="73"/>
+      <c r="V31" s="73"/>
+      <c r="W31" s="73"/>
+      <c r="X31" s="73"/>
+      <c r="Y31" s="73"/>
+      <c r="Z31" s="73"/>
+      <c r="AA31" s="73"/>
+      <c r="AB31" s="73"/>
+      <c r="AC31" s="73"/>
+      <c r="AD31" s="73"/>
+      <c r="AE31" s="73"/>
+      <c r="AF31" s="73"/>
+      <c r="AG31" s="73"/>
+      <c r="AH31" s="73"/>
+      <c r="AI31" s="73"/>
+      <c r="AJ31" s="73"/>
+      <c r="AK31" s="73"/>
+      <c r="AL31" s="73"/>
+      <c r="AM31" s="73"/>
+      <c r="AN31" s="73"/>
+      <c r="AO31" s="73"/>
+      <c r="AP31" s="73"/>
+      <c r="AQ31" s="73"/>
+      <c r="AR31" s="73"/>
+      <c r="AS31" s="73"/>
+      <c r="AT31" s="73"/>
+      <c r="AU31" s="73"/>
+      <c r="AV31" s="73"/>
+      <c r="AW31" s="73"/>
+      <c r="AX31" s="73"/>
+      <c r="AY31" s="73"/>
+      <c r="AZ31" s="73"/>
+      <c r="BA31" s="73"/>
+      <c r="BB31" s="73"/>
+      <c r="BC31" s="73"/>
+      <c r="BD31" s="73"/>
+      <c r="BE31" s="73"/>
+      <c r="BF31" s="73"/>
+      <c r="BG31" s="73"/>
+      <c r="BH31" s="73"/>
+      <c r="BI31" s="73"/>
+      <c r="BJ31" s="73"/>
+      <c r="BK31" s="73"/>
+      <c r="BL31" s="73"/>
+      <c r="BM31" s="73"/>
+      <c r="BN31" s="73"/>
+      <c r="BO31" s="73"/>
+      <c r="BP31" s="73"/>
+      <c r="BQ31" s="73"/>
+      <c r="BR31" s="73"/>
+      <c r="BS31" s="73"/>
+      <c r="BT31" s="73"/>
+      <c r="BU31" s="73"/>
+      <c r="BV31" s="73"/>
+      <c r="BW31" s="73"/>
+      <c r="BX31" s="73"/>
+      <c r="BY31" s="73"/>
+      <c r="BZ31" s="73"/>
+      <c r="CA31" s="73"/>
+      <c r="CB31" s="73"/>
+      <c r="CC31" s="73"/>
+      <c r="CD31" s="73"/>
+      <c r="CE31" s="73"/>
+      <c r="CF31" s="73"/>
+      <c r="CG31" s="73"/>
+      <c r="CH31" s="73"/>
+      <c r="CI31" s="73"/>
+      <c r="CJ31" s="73"/>
+      <c r="CK31" s="73"/>
+      <c r="CL31" s="73"/>
+      <c r="CM31" s="73"/>
+      <c r="CN31" s="73"/>
+      <c r="CO31" s="73"/>
+      <c r="CP31" s="73"/>
+      <c r="CQ31" s="73"/>
+      <c r="CR31" s="73"/>
+      <c r="CS31" s="73"/>
+      <c r="CT31" s="73"/>
+      <c r="CU31" s="73"/>
+      <c r="CV31" s="73"/>
+      <c r="CW31" s="73"/>
+      <c r="CX31" s="73"/>
+      <c r="CY31" s="73"/>
+      <c r="CZ31" s="73"/>
+      <c r="DA31" s="73"/>
+      <c r="DB31" s="73"/>
+      <c r="DC31" s="73"/>
+      <c r="DD31" s="73"/>
+      <c r="DE31" s="73"/>
+      <c r="DF31" s="73"/>
+    </row>
+    <row r="32" spans="1:110" s="140" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="228" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="229"/>
+      <c r="C32" s="108" t="s">
+        <v>183</v>
+      </c>
+      <c r="D32" s="136">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="E32" s="145">
+        <v>246240.29345999999</v>
+      </c>
+      <c r="F32" s="240">
+        <v>45839</v>
+      </c>
+      <c r="G32" s="147">
+        <v>-187595.05270715937</v>
+      </c>
+      <c r="H32" s="309">
+        <f t="shared" si="0"/>
+        <v>187595.22</v>
+      </c>
+      <c r="I32" s="147">
+        <v>-58645.240752840618</v>
+      </c>
+      <c r="J32" s="189">
+        <f t="shared" si="4"/>
+        <v>58645.240752840618</v>
+      </c>
+      <c r="K32" s="307">
+        <f t="shared" si="5"/>
+        <v>246240.22</v>
+      </c>
+      <c r="L32" s="173">
+        <f t="shared" si="6"/>
+        <v>0.22000000000000006</v>
+      </c>
+      <c r="M32" s="73" t="s">
+        <v>319</v>
+      </c>
+      <c r="N32" s="73"/>
+      <c r="O32" s="73"/>
+      <c r="P32" s="73"/>
+      <c r="Q32" s="73"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="73"/>
+      <c r="T32" s="73"/>
+      <c r="U32" s="73"/>
+      <c r="V32" s="73"/>
+      <c r="W32" s="73"/>
+      <c r="X32" s="73"/>
+      <c r="Y32" s="73"/>
+      <c r="Z32" s="73"/>
+      <c r="AA32" s="73"/>
+      <c r="AB32" s="73"/>
+      <c r="AC32" s="73"/>
+      <c r="AD32" s="73"/>
+      <c r="AE32" s="73"/>
+      <c r="AF32" s="73"/>
+      <c r="AG32" s="73"/>
+      <c r="AH32" s="73"/>
+      <c r="AI32" s="73"/>
+      <c r="AJ32" s="73"/>
+      <c r="AK32" s="73"/>
+      <c r="AL32" s="73"/>
+      <c r="AM32" s="73"/>
+      <c r="AN32" s="73"/>
+      <c r="AO32" s="73"/>
+      <c r="AP32" s="73"/>
+      <c r="AQ32" s="73"/>
+      <c r="AR32" s="73"/>
+      <c r="AS32" s="73"/>
+      <c r="AT32" s="73"/>
+      <c r="AU32" s="73"/>
+      <c r="AV32" s="73"/>
+      <c r="AW32" s="73"/>
+      <c r="AX32" s="73"/>
+      <c r="AY32" s="73"/>
+      <c r="AZ32" s="73"/>
+      <c r="BA32" s="73"/>
+      <c r="BB32" s="73"/>
+      <c r="BC32" s="73"/>
+      <c r="BD32" s="73"/>
+      <c r="BE32" s="73"/>
+      <c r="BF32" s="73"/>
+      <c r="BG32" s="73"/>
+      <c r="BH32" s="73"/>
+      <c r="BI32" s="73"/>
+      <c r="BJ32" s="73"/>
+      <c r="BK32" s="73"/>
+      <c r="BL32" s="73"/>
+      <c r="BM32" s="73"/>
+      <c r="BN32" s="73"/>
+      <c r="BO32" s="73"/>
+      <c r="BP32" s="73"/>
+      <c r="BQ32" s="73"/>
+      <c r="BR32" s="73"/>
+      <c r="BS32" s="73"/>
+      <c r="BT32" s="73"/>
+      <c r="BU32" s="73"/>
+      <c r="BV32" s="73"/>
+      <c r="BW32" s="73"/>
+      <c r="BX32" s="73"/>
+      <c r="BY32" s="73"/>
+      <c r="BZ32" s="73"/>
+      <c r="CA32" s="73"/>
+      <c r="CB32" s="73"/>
+      <c r="CC32" s="73"/>
+      <c r="CD32" s="73"/>
+      <c r="CE32" s="73"/>
+      <c r="CF32" s="73"/>
+      <c r="CG32" s="73"/>
+      <c r="CH32" s="73"/>
+      <c r="CI32" s="73"/>
+      <c r="CJ32" s="73"/>
+      <c r="CK32" s="73"/>
+      <c r="CL32" s="73"/>
+      <c r="CM32" s="73"/>
+      <c r="CN32" s="73"/>
+      <c r="CO32" s="73"/>
+      <c r="CP32" s="73"/>
+      <c r="CQ32" s="73"/>
+      <c r="CR32" s="73"/>
+      <c r="CS32" s="73"/>
+      <c r="CT32" s="73"/>
+      <c r="CU32" s="73"/>
+      <c r="CV32" s="73"/>
+      <c r="CW32" s="73"/>
+      <c r="CX32" s="73"/>
+      <c r="CY32" s="73"/>
+      <c r="CZ32" s="73"/>
+      <c r="DA32" s="73"/>
+      <c r="DB32" s="73"/>
+      <c r="DC32" s="73"/>
+      <c r="DD32" s="73"/>
+      <c r="DE32" s="73"/>
+      <c r="DF32" s="73"/>
+    </row>
+    <row r="33" spans="1:110" s="140" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="228" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="229">
+        <v>31</v>
+      </c>
+      <c r="C33" s="108" t="s">
+        <v>384</v>
+      </c>
+      <c r="D33" s="136">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="E33" s="145">
+        <v>288153.53489999997</v>
+      </c>
+      <c r="F33" s="240">
+        <v>45839</v>
+      </c>
+      <c r="G33" s="147">
+        <v>-219526.12550837794</v>
+      </c>
+      <c r="H33" s="309">
+        <f t="shared" si="0"/>
+        <v>219526.23</v>
+      </c>
+      <c r="I33" s="147">
+        <v>-68627.40939162203</v>
+      </c>
+      <c r="J33" s="189">
+        <f t="shared" si="4"/>
+        <v>68627.40939162203</v>
+      </c>
+      <c r="K33" s="307">
+        <f t="shared" si="5"/>
+        <v>288154.23</v>
+      </c>
+      <c r="L33" s="173">
+        <f t="shared" si="6"/>
+        <v>0.23000000000000007</v>
+      </c>
+      <c r="M33" s="73" t="s">
+        <v>300</v>
+      </c>
+      <c r="N33" s="73"/>
+      <c r="O33" s="73"/>
+      <c r="P33" s="73"/>
+      <c r="Q33" s="73"/>
+      <c r="R33" s="73"/>
+      <c r="S33" s="73"/>
+      <c r="T33" s="73"/>
+      <c r="U33" s="73"/>
+      <c r="V33" s="73"/>
+      <c r="W33" s="73"/>
+      <c r="X33" s="73"/>
+      <c r="Y33" s="73"/>
+      <c r="Z33" s="73"/>
+      <c r="AA33" s="73"/>
+      <c r="AB33" s="73"/>
+      <c r="AC33" s="73"/>
+      <c r="AD33" s="73"/>
+      <c r="AE33" s="73"/>
+      <c r="AF33" s="73"/>
+      <c r="AG33" s="73"/>
+      <c r="AH33" s="73"/>
+      <c r="AI33" s="73"/>
+      <c r="AJ33" s="73"/>
+      <c r="AK33" s="73"/>
+      <c r="AL33" s="73"/>
+      <c r="AM33" s="73"/>
+      <c r="AN33" s="73"/>
+      <c r="AO33" s="73"/>
+      <c r="AP33" s="73"/>
+      <c r="AQ33" s="73"/>
+      <c r="AR33" s="73"/>
+      <c r="AS33" s="73"/>
+      <c r="AT33" s="73"/>
+      <c r="AU33" s="73"/>
+      <c r="AV33" s="73"/>
+      <c r="AW33" s="73"/>
+      <c r="AX33" s="73"/>
+      <c r="AY33" s="73"/>
+      <c r="AZ33" s="73"/>
+      <c r="BA33" s="73"/>
+      <c r="BB33" s="73"/>
+      <c r="BC33" s="73"/>
+      <c r="BD33" s="73"/>
+      <c r="BE33" s="73"/>
+      <c r="BF33" s="73"/>
+      <c r="BG33" s="73"/>
+      <c r="BH33" s="73"/>
+      <c r="BI33" s="73"/>
+      <c r="BJ33" s="73"/>
+      <c r="BK33" s="73"/>
+      <c r="BL33" s="73"/>
+      <c r="BM33" s="73"/>
+      <c r="BN33" s="73"/>
+      <c r="BO33" s="73"/>
+      <c r="BP33" s="73"/>
+      <c r="BQ33" s="73"/>
+      <c r="BR33" s="73"/>
+      <c r="BS33" s="73"/>
+      <c r="BT33" s="73"/>
+      <c r="BU33" s="73"/>
+      <c r="BV33" s="73"/>
+      <c r="BW33" s="73"/>
+      <c r="BX33" s="73"/>
+      <c r="BY33" s="73"/>
+      <c r="BZ33" s="73"/>
+      <c r="CA33" s="73"/>
+      <c r="CB33" s="73"/>
+      <c r="CC33" s="73"/>
+      <c r="CD33" s="73"/>
+      <c r="CE33" s="73"/>
+      <c r="CF33" s="73"/>
+      <c r="CG33" s="73"/>
+      <c r="CH33" s="73"/>
+      <c r="CI33" s="73"/>
+      <c r="CJ33" s="73"/>
+      <c r="CK33" s="73"/>
+      <c r="CL33" s="73"/>
+      <c r="CM33" s="73"/>
+      <c r="CN33" s="73"/>
+      <c r="CO33" s="73"/>
+      <c r="CP33" s="73"/>
+      <c r="CQ33" s="73"/>
+      <c r="CR33" s="73"/>
+      <c r="CS33" s="73"/>
+      <c r="CT33" s="73"/>
+      <c r="CU33" s="73"/>
+      <c r="CV33" s="73"/>
+      <c r="CW33" s="73"/>
+      <c r="CX33" s="73"/>
+      <c r="CY33" s="73"/>
+      <c r="CZ33" s="73"/>
+      <c r="DA33" s="73"/>
+      <c r="DB33" s="73"/>
+      <c r="DC33" s="73"/>
+      <c r="DD33" s="73"/>
+      <c r="DE33" s="73"/>
+      <c r="DF33" s="73"/>
+    </row>
+    <row r="34" spans="1:110" s="140" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="228" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="229"/>
+      <c r="C34" s="108" t="s">
+        <v>183</v>
+      </c>
+      <c r="D34" s="136">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="E34" s="145">
+        <v>248859.87104999999</v>
+      </c>
+      <c r="F34" s="240">
+        <v>45839</v>
+      </c>
+      <c r="G34" s="147">
+        <v>-189590.74475723552</v>
+      </c>
+      <c r="H34" s="309">
+        <f t="shared" si="0"/>
+        <v>189591.24</v>
+      </c>
+      <c r="I34" s="147">
+        <v>-59269.126292764471</v>
+      </c>
+      <c r="J34" s="189">
+        <f t="shared" si="4"/>
+        <v>59269.126292764471</v>
+      </c>
+      <c r="K34" s="307">
+        <f t="shared" si="5"/>
+        <v>248860.24</v>
+      </c>
+      <c r="L34" s="173">
+        <f t="shared" si="6"/>
+        <v>0.24000000000000007</v>
+      </c>
+      <c r="M34" s="73"/>
+      <c r="N34" s="73"/>
+      <c r="O34" s="73"/>
+      <c r="P34" s="73"/>
+      <c r="Q34" s="73"/>
+      <c r="R34" s="73"/>
+      <c r="S34" s="73"/>
+      <c r="T34" s="73"/>
+      <c r="U34" s="73"/>
+      <c r="V34" s="73"/>
+      <c r="W34" s="73"/>
+      <c r="X34" s="73"/>
+      <c r="Y34" s="73"/>
+      <c r="Z34" s="73"/>
+      <c r="AA34" s="73"/>
+      <c r="AB34" s="73"/>
+      <c r="AC34" s="73"/>
+      <c r="AD34" s="73"/>
+      <c r="AE34" s="73"/>
+      <c r="AF34" s="73"/>
+      <c r="AG34" s="73"/>
+      <c r="AH34" s="73"/>
+      <c r="AI34" s="73"/>
+      <c r="AJ34" s="73"/>
+      <c r="AK34" s="73"/>
+      <c r="AL34" s="73"/>
+      <c r="AM34" s="73"/>
+      <c r="AN34" s="73"/>
+      <c r="AO34" s="73"/>
+      <c r="AP34" s="73"/>
+      <c r="AQ34" s="73"/>
+      <c r="AR34" s="73"/>
+      <c r="AS34" s="73"/>
+      <c r="AT34" s="73"/>
+      <c r="AU34" s="73"/>
+      <c r="AV34" s="73"/>
+      <c r="AW34" s="73"/>
+      <c r="AX34" s="73"/>
+      <c r="AY34" s="73"/>
+      <c r="AZ34" s="73"/>
+      <c r="BA34" s="73"/>
+      <c r="BB34" s="73"/>
+      <c r="BC34" s="73"/>
+      <c r="BD34" s="73"/>
+      <c r="BE34" s="73"/>
+      <c r="BF34" s="73"/>
+      <c r="BG34" s="73"/>
+      <c r="BH34" s="73"/>
+      <c r="BI34" s="73"/>
+      <c r="BJ34" s="73"/>
+      <c r="BK34" s="73"/>
+      <c r="BL34" s="73"/>
+      <c r="BM34" s="73"/>
+      <c r="BN34" s="73"/>
+      <c r="BO34" s="73"/>
+      <c r="BP34" s="73"/>
+      <c r="BQ34" s="73"/>
+      <c r="BR34" s="73"/>
+      <c r="BS34" s="73"/>
+      <c r="BT34" s="73"/>
+      <c r="BU34" s="73"/>
+      <c r="BV34" s="73"/>
+      <c r="BW34" s="73"/>
+      <c r="BX34" s="73"/>
+      <c r="BY34" s="73"/>
+      <c r="BZ34" s="73"/>
+      <c r="CA34" s="73"/>
+      <c r="CB34" s="73"/>
+      <c r="CC34" s="73"/>
+      <c r="CD34" s="73"/>
+      <c r="CE34" s="73"/>
+      <c r="CF34" s="73"/>
+      <c r="CG34" s="73"/>
+      <c r="CH34" s="73"/>
+      <c r="CI34" s="73"/>
+      <c r="CJ34" s="73"/>
+      <c r="CK34" s="73"/>
+      <c r="CL34" s="73"/>
+      <c r="CM34" s="73"/>
+      <c r="CN34" s="73"/>
+      <c r="CO34" s="73"/>
+      <c r="CP34" s="73"/>
+      <c r="CQ34" s="73"/>
+      <c r="CR34" s="73"/>
+      <c r="CS34" s="73"/>
+      <c r="CT34" s="73"/>
+      <c r="CU34" s="73"/>
+      <c r="CV34" s="73"/>
+      <c r="CW34" s="73"/>
+      <c r="CX34" s="73"/>
+      <c r="CY34" s="73"/>
+      <c r="CZ34" s="73"/>
+      <c r="DA34" s="73"/>
+      <c r="DB34" s="73"/>
+      <c r="DC34" s="73"/>
+      <c r="DD34" s="73"/>
+      <c r="DE34" s="73"/>
+      <c r="DF34" s="73"/>
+    </row>
+    <row r="35" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A35" s="228" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="229">
+        <v>28</v>
+      </c>
+      <c r="C35" s="108" t="s">
+        <v>188</v>
+      </c>
+      <c r="D35" s="136">
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="E35" s="145">
+        <v>489861.00933000003</v>
+      </c>
+      <c r="F35" s="240">
+        <v>45786</v>
+      </c>
+      <c r="G35" s="147">
+        <v>-452316.22060054552</v>
+      </c>
+      <c r="H35" s="309">
+        <f t="shared" si="0"/>
+        <v>452316.25</v>
+      </c>
+      <c r="I35" s="147">
+        <v>-37544.788729454507</v>
+      </c>
+      <c r="J35" s="189">
+        <f t="shared" si="4"/>
+        <v>37544.788729454507</v>
+      </c>
+      <c r="K35" s="307">
+        <f t="shared" si="5"/>
+        <v>489861.25</v>
+      </c>
+      <c r="L35" s="133">
+        <f t="shared" si="6"/>
+        <v>0.25000000000000006</v>
+      </c>
+    </row>
+    <row r="36" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A36" s="228" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="229"/>
+      <c r="C36" s="108" t="s">
+        <v>385</v>
+      </c>
+      <c r="D36" s="136">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="E36" s="145">
+        <v>191229.16407</v>
+      </c>
+      <c r="F36" s="240">
+        <v>45789</v>
+      </c>
+      <c r="G36" s="147">
+        <v>-175787.47145562258</v>
+      </c>
+      <c r="H36" s="309">
+        <f t="shared" si="0"/>
+        <v>175787.26</v>
+      </c>
+      <c r="I36" s="147">
+        <v>-15441.692614377418</v>
+      </c>
+      <c r="J36" s="189">
+        <f t="shared" si="4"/>
+        <v>15441.692614377418</v>
+      </c>
+      <c r="K36" s="307">
+        <f t="shared" si="5"/>
+        <v>191229.26</v>
+      </c>
+      <c r="L36" s="133">
+        <f t="shared" si="6"/>
+        <v>0.26000000000000006</v>
+      </c>
+    </row>
+    <row r="37" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A37" s="228" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" s="229">
+        <v>33</v>
+      </c>
+      <c r="C37" s="108" t="s">
+        <v>190</v>
+      </c>
+      <c r="D37" s="136">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="E37" s="145">
+        <v>516056.78522999992</v>
+      </c>
+      <c r="F37" s="240">
+        <v>45793</v>
+      </c>
+      <c r="G37" s="147">
+        <v>-471560.18735745805</v>
+      </c>
+      <c r="H37" s="309">
+        <f t="shared" si="0"/>
+        <v>471560.27</v>
+      </c>
+      <c r="I37" s="147">
+        <v>-44496.597872541868</v>
+      </c>
+      <c r="J37" s="189">
+        <f t="shared" si="4"/>
+        <v>44496.597872541868</v>
+      </c>
+      <c r="K37" s="307">
+        <f t="shared" si="5"/>
+        <v>516057.27</v>
+      </c>
+      <c r="L37" s="133">
+        <f t="shared" si="6"/>
+        <v>0.27000000000000007</v>
+      </c>
+      <c r="M37" t="s">
+        <v>266</v>
+      </c>
+      <c r="N37" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="38" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A38" s="228" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="229">
+        <v>44</v>
+      </c>
+      <c r="C38" s="108" t="s">
+        <v>386</v>
+      </c>
+      <c r="D38" s="136">
+        <v>1.17E-2</v>
+      </c>
+      <c r="E38" s="145">
+        <v>306490.57802999998</v>
+      </c>
+      <c r="F38" s="240">
+        <v>45800</v>
+      </c>
+      <c r="G38" s="147">
+        <v>-277127.3408552261</v>
+      </c>
+      <c r="H38" s="309">
+        <f t="shared" si="0"/>
+        <v>277127.28000000003</v>
+      </c>
+      <c r="I38" s="147">
+        <v>-29363.23717477388</v>
+      </c>
+      <c r="J38" s="189">
+        <f t="shared" si="4"/>
+        <v>29363.23717477388</v>
+      </c>
+      <c r="K38" s="307">
+        <f t="shared" si="5"/>
+        <v>306491.28000000003</v>
+      </c>
+      <c r="L38" s="133">
+        <f t="shared" si="6"/>
+        <v>0.28000000000000008</v>
+      </c>
+    </row>
+    <row r="39" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A39" s="228" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" s="229"/>
+      <c r="C39" s="108" t="s">
+        <v>181</v>
+      </c>
+      <c r="D39" s="136">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="E39" s="145">
+        <v>227903.25032999998</v>
+      </c>
+      <c r="F39" s="240">
+        <v>45800</v>
+      </c>
+      <c r="G39" s="147">
+        <v>-206069.04832824506</v>
+      </c>
+      <c r="H39" s="309">
+        <f t="shared" si="0"/>
+        <v>206069.29</v>
+      </c>
+      <c r="I39" s="147">
+        <v>-21834.202001754922</v>
+      </c>
+      <c r="J39" s="189">
+        <f t="shared" si="4"/>
+        <v>21834.202001754922</v>
+      </c>
+      <c r="K39" s="307">
+        <f t="shared" si="5"/>
+        <v>227903.29</v>
+      </c>
+      <c r="L39" s="133">
+        <f t="shared" si="6"/>
+        <v>0.29000000000000009</v>
+      </c>
+    </row>
+    <row r="40" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A40" s="228" t="s">
+        <v>73</v>
+      </c>
+      <c r="B40" s="229"/>
+      <c r="C40" s="108" t="s">
+        <v>387</v>
+      </c>
+      <c r="D40" s="136">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="E40" s="145">
+        <v>248859.87104999999</v>
+      </c>
+      <c r="F40" s="240">
+        <v>45800</v>
+      </c>
+      <c r="G40" s="147">
+        <v>-225017.92633544002</v>
+      </c>
+      <c r="H40" s="309">
+        <f t="shared" si="0"/>
+        <v>225018.3</v>
+      </c>
+      <c r="I40" s="147">
+        <v>-23841.94471455997</v>
+      </c>
+      <c r="J40" s="189">
+        <f t="shared" si="4"/>
+        <v>23841.94471455997</v>
+      </c>
+      <c r="K40" s="307">
+        <f t="shared" si="5"/>
+        <v>248860.3</v>
+      </c>
+      <c r="L40" s="133">
+        <f t="shared" si="6"/>
+        <v>0.3000000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A41" s="228" t="s">
+        <v>74</v>
+      </c>
+      <c r="B41" s="229">
+        <v>7</v>
+      </c>
+      <c r="C41" s="108" t="s">
+        <v>192</v>
+      </c>
+      <c r="D41" s="136">
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="E41" s="145">
+        <v>489861.00933000003</v>
+      </c>
+      <c r="F41" s="240">
+        <v>45806</v>
+      </c>
+      <c r="G41" s="147">
+        <v>-435275.0052766751</v>
+      </c>
+      <c r="H41" s="309">
+        <f t="shared" si="0"/>
+        <v>435275.31</v>
+      </c>
+      <c r="I41" s="147">
+        <v>-54586.004053324927</v>
+      </c>
+      <c r="J41" s="189">
+        <f t="shared" si="4"/>
+        <v>54586.004053324927</v>
+      </c>
+      <c r="K41" s="307">
+        <f t="shared" si="5"/>
+        <v>489861.31</v>
+      </c>
+      <c r="L41" s="133">
+        <f t="shared" si="6"/>
+        <v>0.31000000000000011</v>
+      </c>
+    </row>
+    <row r="42" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A42" s="228" t="s">
+        <v>75</v>
+      </c>
+      <c r="B42" s="229">
+        <v>3</v>
+      </c>
+      <c r="C42" s="108" t="s">
+        <v>193</v>
+      </c>
+      <c r="D42" s="136">
+        <v>9.6000000000000009E-3</v>
+      </c>
+      <c r="E42" s="145">
+        <v>251479.44864000002</v>
+      </c>
+      <c r="F42" s="240">
+        <v>45775</v>
+      </c>
+      <c r="G42" s="147">
+        <v>-235991.14771264675</v>
+      </c>
+      <c r="H42" s="309">
+        <f t="shared" si="0"/>
+        <v>235991.32</v>
+      </c>
+      <c r="I42" s="147">
+        <v>-15488.300927353266</v>
+      </c>
+      <c r="J42" s="189">
+        <f t="shared" si="4"/>
+        <v>15488.300927353266</v>
+      </c>
+      <c r="K42" s="307">
+        <f t="shared" si="5"/>
+        <v>251480.32000000001</v>
+      </c>
+      <c r="L42" s="133">
+        <f t="shared" si="6"/>
+        <v>0.32000000000000012</v>
+      </c>
+      <c r="M42" s="43"/>
+    </row>
+    <row r="43" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A43" s="228" t="s">
+        <v>76</v>
+      </c>
+      <c r="B43" s="229">
+        <v>24</v>
+      </c>
+      <c r="C43" s="108" t="s">
+        <v>194</v>
+      </c>
+      <c r="D43" s="136">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="E43" s="145">
+        <v>516056.78522999992</v>
+      </c>
+      <c r="F43" s="240">
+        <v>45793</v>
+      </c>
+      <c r="G43" s="147">
+        <v>-471560.18735745805</v>
+      </c>
+      <c r="H43" s="309">
+        <f t="shared" si="0"/>
+        <v>471560.33</v>
+      </c>
+      <c r="I43" s="147">
+        <v>-44496.597872541868</v>
+      </c>
+      <c r="J43" s="189">
+        <f t="shared" si="4"/>
+        <v>44496.597872541868</v>
+      </c>
+      <c r="K43" s="307">
+        <f t="shared" si="5"/>
+        <v>516057.33</v>
+      </c>
+      <c r="L43" s="133">
+        <f t="shared" si="6"/>
+        <v>0.33000000000000013</v>
+      </c>
+      <c r="M43" s="43"/>
+    </row>
+    <row r="44" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A44" s="228" t="s">
+        <v>77</v>
+      </c>
+      <c r="B44" s="229"/>
+      <c r="C44" s="108" t="s">
+        <v>388</v>
+      </c>
+      <c r="D44" s="136">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="E44" s="145">
+        <v>246240.29345999999</v>
+      </c>
+      <c r="F44" s="240">
+        <v>45786</v>
+      </c>
+      <c r="G44" s="147">
+        <v>-227367.51195963251</v>
+      </c>
+      <c r="H44" s="309">
+        <f t="shared" si="0"/>
+        <v>227368.34</v>
+      </c>
+      <c r="I44" s="147">
+        <v>-18872.781500367477</v>
+      </c>
+      <c r="J44" s="189">
+        <f t="shared" si="4"/>
+        <v>18872.781500367477</v>
+      </c>
+      <c r="K44" s="307">
+        <f t="shared" si="5"/>
+        <v>246241.34</v>
+      </c>
+      <c r="L44" s="133">
+        <f t="shared" si="6"/>
+        <v>0.34000000000000014</v>
+      </c>
+      <c r="M44" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="45" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A45" s="228" t="s">
+        <v>78</v>
+      </c>
+      <c r="B45" s="229"/>
+      <c r="C45" s="108" t="s">
+        <v>389</v>
+      </c>
+      <c r="D45" s="136">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="E45" s="145">
+        <v>227903.25032999998</v>
+      </c>
+      <c r="F45" s="240">
+        <v>45807</v>
+      </c>
+      <c r="G45" s="147">
+        <v>-201632.39809641102</v>
+      </c>
+      <c r="H45" s="309">
+        <f t="shared" si="0"/>
+        <v>201632.35</v>
+      </c>
+      <c r="I45" s="147">
+        <v>-26270.852233588957</v>
+      </c>
+      <c r="J45" s="189">
+        <f t="shared" si="4"/>
+        <v>26270.852233588957</v>
+      </c>
+      <c r="K45" s="307">
+        <f t="shared" si="5"/>
+        <v>227903.35</v>
+      </c>
+      <c r="L45" s="133">
+        <f t="shared" si="6"/>
+        <v>0.35000000000000014</v>
+      </c>
+    </row>
+    <row r="46" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A46" s="228" t="s">
+        <v>79</v>
+      </c>
+      <c r="B46" s="229"/>
+      <c r="C46" s="108" t="s">
+        <v>195</v>
+      </c>
+      <c r="D46" s="136">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="E46" s="145">
+        <v>248859.87104999999</v>
+      </c>
+      <c r="F46" s="240">
+        <v>45786</v>
+      </c>
+      <c r="G46" s="147">
+        <v>-229786.31527835201</v>
+      </c>
+      <c r="H46" s="309">
+        <f t="shared" si="0"/>
+        <v>229786.36</v>
+      </c>
+      <c r="I46" s="147">
+        <v>-19073.555771647982</v>
+      </c>
+      <c r="J46" s="189">
+        <f t="shared" si="4"/>
+        <v>19073.555771647982</v>
+      </c>
+      <c r="K46" s="307">
+        <f t="shared" si="5"/>
+        <v>248860.36</v>
+      </c>
+      <c r="L46" s="133">
+        <f t="shared" si="6"/>
+        <v>0.36000000000000015</v>
+      </c>
+    </row>
+    <row r="47" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A47" s="228" t="s">
+        <v>80</v>
+      </c>
+      <c r="B47" s="229">
+        <v>8</v>
+      </c>
+      <c r="C47" s="108" t="s">
+        <v>192</v>
+      </c>
+      <c r="D47" s="136">
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="E47" s="145">
+        <v>489861.00933000003</v>
+      </c>
+      <c r="F47" s="240">
+        <v>45793</v>
+      </c>
+      <c r="G47" s="147">
+        <v>-447623.12200936372</v>
+      </c>
+      <c r="H47" s="309">
+        <f t="shared" si="0"/>
+        <v>447623.37</v>
+      </c>
+      <c r="I47" s="147">
+        <v>-42237.887320636306</v>
+      </c>
+      <c r="J47" s="189">
+        <f t="shared" si="4"/>
+        <v>42237.887320636306</v>
+      </c>
+      <c r="K47" s="307">
+        <f t="shared" si="5"/>
+        <v>489861.37</v>
+      </c>
+      <c r="L47" s="133">
+        <f t="shared" si="6"/>
+        <v>0.37000000000000016</v>
+      </c>
+      <c r="N47" s="59"/>
+    </row>
+    <row r="48" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A48" s="228" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48" s="229"/>
+      <c r="C48" s="108" t="s">
+        <v>196</v>
+      </c>
+      <c r="D48" s="136">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="E48" s="145">
+        <v>191229.16407</v>
+      </c>
+      <c r="F48" s="240">
+        <v>45805</v>
+      </c>
+      <c r="G48" s="147">
+        <v>-170654.57315202037</v>
+      </c>
+      <c r="H48" s="309">
+        <f t="shared" si="0"/>
+        <v>170655.38</v>
+      </c>
+      <c r="I48" s="147">
+        <v>-20574.590917979629</v>
+      </c>
+      <c r="J48" s="189">
+        <f t="shared" si="4"/>
+        <v>20574.590917979629</v>
+      </c>
+      <c r="K48" s="307">
+        <f t="shared" si="5"/>
+        <v>191230.38</v>
+      </c>
+      <c r="L48" s="133">
+        <f t="shared" si="6"/>
+        <v>0.38000000000000017</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A49" s="228" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" s="229">
+        <v>14</v>
+      </c>
+      <c r="C49" s="108" t="s">
+        <v>197</v>
+      </c>
+      <c r="D49" s="136">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="E49" s="145">
+        <v>516056.78522999992</v>
+      </c>
+      <c r="F49" s="240">
+        <v>45805</v>
+      </c>
+      <c r="G49" s="147">
+        <v>-460533.57412257558</v>
+      </c>
+      <c r="H49" s="309">
+        <f t="shared" si="0"/>
+        <v>460534.39</v>
+      </c>
+      <c r="I49" s="147">
+        <v>-55523.211107424344</v>
+      </c>
+      <c r="J49" s="189">
+        <f t="shared" si="4"/>
+        <v>55523.211107424344</v>
+      </c>
+      <c r="K49" s="307">
+        <f t="shared" si="5"/>
+        <v>516058.39</v>
+      </c>
+      <c r="L49" s="133">
+        <f t="shared" si="6"/>
+        <v>0.39000000000000018</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" s="228" t="s">
+        <v>83</v>
+      </c>
+      <c r="B50" s="229"/>
+      <c r="C50" s="108" t="s">
+        <v>198</v>
+      </c>
+      <c r="D50" s="136">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="E50" s="145">
+        <v>246240.29345999999</v>
+      </c>
+      <c r="F50" s="240">
+        <v>45793</v>
+      </c>
+      <c r="G50" s="147">
+        <v>-225008.41427208658</v>
+      </c>
+      <c r="H50" s="309">
+        <f t="shared" si="0"/>
+        <v>225008.4</v>
+      </c>
+      <c r="I50" s="147">
+        <v>-21231.879187913408</v>
+      </c>
+      <c r="J50" s="189">
+        <f t="shared" si="4"/>
+        <v>21231.879187913408</v>
+      </c>
+      <c r="K50" s="307">
+        <f t="shared" si="5"/>
+        <v>246240.4</v>
+      </c>
+      <c r="L50" s="133">
+        <f t="shared" si="6"/>
+        <v>0.40000000000000019</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" s="228" t="s">
+        <v>84</v>
+      </c>
+      <c r="B51" s="229"/>
+      <c r="C51" s="108" t="s">
+        <v>390</v>
+      </c>
+      <c r="D51" s="136">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="E51" s="145">
+        <v>227903.25032999998</v>
+      </c>
+      <c r="F51" s="240">
+        <v>45800</v>
+      </c>
+      <c r="G51" s="147">
+        <v>-206069.04832824506</v>
+      </c>
+      <c r="H51" s="309">
+        <f t="shared" si="0"/>
+        <v>206069.41</v>
+      </c>
+      <c r="I51" s="147">
+        <v>-21834.202001754922</v>
+      </c>
+      <c r="J51" s="189">
+        <f t="shared" si="4"/>
+        <v>21834.202001754922</v>
+      </c>
+      <c r="K51" s="307">
+        <f t="shared" si="5"/>
+        <v>227904.41</v>
+      </c>
+      <c r="L51" s="133">
+        <f t="shared" si="6"/>
+        <v>0.4100000000000002</v>
+      </c>
+      <c r="N51" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="228" t="s">
+        <v>85</v>
+      </c>
+      <c r="B52" s="238">
+        <v>5</v>
+      </c>
+      <c r="C52" s="108" t="s">
+        <v>199</v>
+      </c>
+      <c r="D52" s="136">
+        <v>1.18E-2</v>
+      </c>
+      <c r="E52" s="145">
+        <v>309110.15561999998</v>
+      </c>
+      <c r="F52" s="240">
+        <v>45793</v>
+      </c>
+      <c r="G52" s="147">
+        <v>-282457.37110751297</v>
+      </c>
+      <c r="H52" s="309">
+        <f t="shared" si="0"/>
+        <v>282457.42</v>
+      </c>
+      <c r="I52" s="147">
+        <v>-26652.784512487007</v>
+      </c>
+      <c r="J52" s="189">
+        <f t="shared" si="4"/>
+        <v>26652.784512487007</v>
+      </c>
+      <c r="K52" s="307">
+        <f t="shared" si="5"/>
+        <v>309110.42</v>
+      </c>
+      <c r="L52" s="133">
+        <f t="shared" si="6"/>
+        <v>0.42000000000000021</v>
+      </c>
+      <c r="M52" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A53" s="228" t="s">
+        <v>86</v>
+      </c>
+      <c r="B53" s="229">
+        <v>26</v>
+      </c>
+      <c r="C53" s="108" t="s">
+        <v>200</v>
+      </c>
+      <c r="D53" s="136">
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="E53" s="145">
+        <v>489861.00933000003</v>
+      </c>
+      <c r="F53" s="240">
+        <v>45793</v>
+      </c>
+      <c r="G53" s="147">
+        <v>-447623.12200936372</v>
+      </c>
+      <c r="H53" s="309">
+        <f t="shared" si="0"/>
+        <v>447623.43</v>
+      </c>
+      <c r="I53" s="147">
+        <v>-42237.887320636306</v>
+      </c>
+      <c r="J53" s="189">
+        <f t="shared" si="4"/>
+        <v>42237.887320636306</v>
+      </c>
+      <c r="K53" s="307">
+        <f t="shared" si="5"/>
+        <v>489861.43</v>
+      </c>
+      <c r="L53" s="133">
+        <f t="shared" si="6"/>
+        <v>0.43000000000000022</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A54" s="228" t="s">
+        <v>87</v>
+      </c>
+      <c r="B54" s="229"/>
+      <c r="C54" s="108" t="s">
+        <v>200</v>
+      </c>
+      <c r="D54" s="136">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="E54" s="145">
+        <v>191229.16407</v>
+      </c>
+      <c r="F54" s="240">
+        <v>45793</v>
+      </c>
+      <c r="G54" s="147">
+        <v>-174740.57704108849</v>
+      </c>
+      <c r="H54" s="309">
+        <f t="shared" si="0"/>
+        <v>174741.44</v>
+      </c>
+      <c r="I54" s="147">
+        <v>-16488.587028911512</v>
+      </c>
+      <c r="J54" s="189">
+        <f t="shared" si="4"/>
+        <v>16488.587028911512</v>
+      </c>
+      <c r="K54" s="307">
+        <f t="shared" si="5"/>
+        <v>191230.44</v>
+      </c>
+      <c r="L54" s="133">
+        <f t="shared" si="6"/>
+        <v>0.44000000000000022</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A55" s="228" t="s">
+        <v>88</v>
+      </c>
+      <c r="B55" s="229">
+        <v>43</v>
+      </c>
+      <c r="C55" s="108" t="s">
+        <v>201</v>
+      </c>
+      <c r="D55" s="136">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="E55" s="145">
+        <v>516056.78522999992</v>
+      </c>
+      <c r="F55" s="240">
+        <v>45770</v>
+      </c>
+      <c r="G55" s="147">
+        <v>-487804.97705695755</v>
+      </c>
+      <c r="H55" s="309">
+        <f t="shared" si="0"/>
+        <v>487805.45</v>
+      </c>
+      <c r="I55" s="147">
+        <v>-28251.808173042373</v>
+      </c>
+      <c r="J55" s="189">
+        <f t="shared" si="4"/>
+        <v>28251.808173042373</v>
+      </c>
+      <c r="K55" s="307">
+        <f t="shared" si="5"/>
+        <v>516057.45</v>
+      </c>
+      <c r="L55" s="133">
+        <f t="shared" si="6"/>
+        <v>0.45000000000000023</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" s="228" t="s">
+        <v>89</v>
+      </c>
+      <c r="B56" s="229">
+        <v>10</v>
+      </c>
+      <c r="C56" s="108" t="s">
+        <v>202</v>
+      </c>
+      <c r="D56" s="136">
+        <v>1.17E-2</v>
+      </c>
+      <c r="E56" s="145">
+        <v>306490.57802999998</v>
+      </c>
+      <c r="F56" s="240">
+        <v>45793</v>
+      </c>
+      <c r="G56" s="147">
+        <v>-280063.66457270354</v>
+      </c>
+      <c r="H56" s="309">
+        <f t="shared" si="0"/>
+        <v>280064.46000000002</v>
+      </c>
+      <c r="I56" s="147">
+        <v>-26426.913457296439</v>
+      </c>
+      <c r="J56" s="189">
+        <f t="shared" si="4"/>
+        <v>26426.913457296439</v>
+      </c>
+      <c r="K56" s="307">
+        <f t="shared" si="5"/>
+        <v>306491.46000000002</v>
+      </c>
+      <c r="L56" s="173">
+        <f t="shared" si="6"/>
+        <v>0.46000000000000024</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" s="228" t="s">
+        <v>90</v>
+      </c>
+      <c r="B57" s="238">
+        <v>12</v>
+      </c>
+      <c r="C57" s="108" t="s">
+        <v>181</v>
+      </c>
+      <c r="D57" s="136">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="E57" s="145">
+        <v>288153.53489999997</v>
+      </c>
+      <c r="F57" s="240">
+        <v>45800</v>
+      </c>
+      <c r="G57" s="147">
+        <v>-260547.07259893051</v>
+      </c>
+      <c r="H57" s="309">
+        <f t="shared" si="0"/>
+        <v>260547.47</v>
+      </c>
+      <c r="I57" s="147">
+        <v>-27606.462301069463</v>
+      </c>
+      <c r="J57" s="189">
+        <f t="shared" si="4"/>
+        <v>27606.462301069463</v>
+      </c>
+      <c r="K57" s="307">
+        <f t="shared" si="5"/>
+        <v>288154.46999999997</v>
+      </c>
+      <c r="L57" s="173">
+        <f t="shared" si="6"/>
+        <v>0.47000000000000025</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" s="228" t="s">
+        <v>91</v>
+      </c>
+      <c r="B58" s="229">
+        <v>20</v>
+      </c>
+      <c r="C58" s="108" t="s">
+        <v>203</v>
+      </c>
+      <c r="D58" s="136">
+        <v>1.18E-2</v>
+      </c>
+      <c r="E58" s="145">
+        <v>309110.15561999998</v>
+      </c>
+      <c r="F58" s="240">
+        <v>45805</v>
+      </c>
+      <c r="G58" s="147">
+        <v>-275852.5976977864</v>
+      </c>
+      <c r="H58" s="309">
+        <f t="shared" si="0"/>
+        <v>275853.48</v>
+      </c>
+      <c r="I58" s="147">
+        <v>-33257.557922213571</v>
+      </c>
+      <c r="J58" s="189">
+        <f t="shared" si="4"/>
+        <v>33257.557922213571</v>
+      </c>
+      <c r="K58" s="307">
+        <f t="shared" si="5"/>
+        <v>309111.48</v>
+      </c>
+      <c r="L58" s="173">
+        <f t="shared" si="6"/>
+        <v>0.48000000000000026</v>
+      </c>
+      <c r="O58" s="183"/>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" s="228" t="s">
+        <v>92</v>
+      </c>
+      <c r="B59" s="229">
+        <v>4</v>
+      </c>
+      <c r="C59" s="108" t="s">
+        <v>391</v>
+      </c>
+      <c r="D59" s="136">
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="E59" s="145">
+        <v>489861.00933000003</v>
+      </c>
+      <c r="F59" s="240">
+        <v>45793</v>
+      </c>
+      <c r="G59" s="147">
+        <v>-447623.12200936372</v>
+      </c>
+      <c r="H59" s="309">
+        <f t="shared" si="0"/>
+        <v>447623.49</v>
+      </c>
+      <c r="I59" s="147">
+        <v>-42237.887320636306</v>
+      </c>
+      <c r="J59" s="189">
+        <f t="shared" si="4"/>
+        <v>42237.887320636306</v>
+      </c>
+      <c r="K59" s="307">
+        <f t="shared" si="5"/>
+        <v>489861.49</v>
+      </c>
+      <c r="L59" s="133">
+        <f t="shared" si="6"/>
+        <v>0.49000000000000027</v>
+      </c>
+      <c r="O59" s="43"/>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" s="228" t="s">
+        <v>93</v>
+      </c>
+      <c r="B60" s="229"/>
+      <c r="C60" s="108" t="s">
+        <v>205</v>
+      </c>
+      <c r="D60" s="136">
+        <v>7.3000000000000001E-3</v>
+      </c>
+      <c r="E60" s="145">
+        <v>191229.16407</v>
+      </c>
+      <c r="F60" s="240">
+        <v>45793</v>
+      </c>
+      <c r="G60" s="147">
+        <v>-174740.57704108849</v>
+      </c>
+      <c r="H60" s="309">
+        <f t="shared" si="0"/>
+        <v>174741.5</v>
+      </c>
+      <c r="I60" s="147">
+        <v>-16488.587028911512</v>
+      </c>
+      <c r="J60" s="189">
+        <f t="shared" si="4"/>
+        <v>16488.587028911512</v>
+      </c>
+      <c r="K60" s="307">
+        <f t="shared" si="5"/>
+        <v>191230.5</v>
+      </c>
+      <c r="L60" s="133">
+        <f t="shared" si="6"/>
+        <v>0.50000000000000022</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" s="228" t="s">
+        <v>94</v>
+      </c>
+      <c r="B61" s="229">
+        <v>17</v>
+      </c>
+      <c r="C61" s="108" t="s">
+        <v>206</v>
+      </c>
+      <c r="D61" s="136">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="E61" s="145">
+        <v>516056.78522999992</v>
+      </c>
+      <c r="F61" s="240">
+        <v>45796</v>
+      </c>
+      <c r="G61" s="147">
+        <v>-469441.3017444798</v>
+      </c>
+      <c r="H61" s="309">
+        <f t="shared" si="0"/>
+        <v>469441.51</v>
+      </c>
+      <c r="I61" s="147">
+        <v>-46615.483485520119</v>
+      </c>
+      <c r="J61" s="189">
+        <f t="shared" si="4"/>
+        <v>46615.483485520119</v>
+      </c>
+      <c r="K61" s="307">
+        <f t="shared" si="5"/>
+        <v>516057.51</v>
+      </c>
+      <c r="L61" s="133">
+        <f t="shared" si="6"/>
+        <v>0.51000000000000023</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" s="228" t="s">
+        <v>95</v>
+      </c>
+      <c r="B62" s="229"/>
+      <c r="C62" s="108" t="s">
+        <v>207</v>
+      </c>
+      <c r="D62" s="136">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="E62" s="145">
+        <v>246240.29345999999</v>
+      </c>
+      <c r="F62" s="240">
+        <v>45863</v>
+      </c>
+      <c r="G62" s="147">
+        <v>-164899.57136629923</v>
+      </c>
+      <c r="H62" s="309">
+        <f t="shared" si="0"/>
+        <v>164900.51999999999</v>
+      </c>
+      <c r="I62" s="147">
+        <v>-81340.722093700751</v>
+      </c>
+      <c r="J62" s="189">
+        <f t="shared" si="4"/>
+        <v>81340.722093700751</v>
+      </c>
+      <c r="K62" s="307">
+        <f t="shared" si="5"/>
+        <v>246241.52</v>
+      </c>
+      <c r="L62" s="133">
+        <f t="shared" si="6"/>
+        <v>0.52000000000000024</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" s="228" t="s">
+        <v>96</v>
+      </c>
+      <c r="B63" s="229"/>
+      <c r="C63" s="108" t="s">
+        <v>392</v>
+      </c>
+      <c r="D63" s="136">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="E63" s="145">
+        <v>227903.25032999998</v>
+      </c>
+      <c r="F63" s="240">
+        <v>45800</v>
+      </c>
+      <c r="G63" s="147">
+        <v>-206069.04832824506</v>
+      </c>
+      <c r="H63" s="309">
+        <f t="shared" si="0"/>
+        <v>206069.53</v>
+      </c>
+      <c r="I63" s="147">
+        <v>-21834.202001754922</v>
+      </c>
+      <c r="J63" s="189">
+        <f t="shared" si="4"/>
+        <v>21834.202001754922</v>
+      </c>
+      <c r="K63" s="307">
+        <f t="shared" si="5"/>
+        <v>227904.53</v>
+      </c>
+      <c r="L63" s="133">
+        <f t="shared" si="6"/>
+        <v>0.53000000000000025</v>
+      </c>
+      <c r="N63" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" s="228" t="s">
+        <v>97</v>
+      </c>
+      <c r="B64" s="229">
+        <v>23</v>
+      </c>
+      <c r="C64" s="108" t="s">
+        <v>208</v>
+      </c>
+      <c r="D64" s="136">
+        <v>1.18E-2</v>
+      </c>
+      <c r="E64" s="145">
+        <v>309110.15561999998</v>
+      </c>
+      <c r="F64" s="240">
+        <v>45786</v>
+      </c>
+      <c r="G64" s="147">
+        <v>-285418.79160890041</v>
+      </c>
+      <c r="H64" s="309">
+        <f t="shared" si="0"/>
+        <v>285419.53999999998</v>
+      </c>
+      <c r="I64" s="147">
+        <v>-23691.364011099562</v>
+      </c>
+      <c r="J64" s="189">
+        <f t="shared" si="4"/>
+        <v>23691.364011099562</v>
+      </c>
+      <c r="K64" s="307">
+        <f t="shared" si="5"/>
+        <v>309111.53999999998</v>
+      </c>
+      <c r="L64" s="133">
+        <f t="shared" si="6"/>
+        <v>0.54000000000000026</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" s="228" t="s">
+        <v>98</v>
+      </c>
+      <c r="B65" s="239">
+        <v>21</v>
+      </c>
+      <c r="C65" s="108" t="s">
+        <v>209</v>
+      </c>
+      <c r="D65" s="136">
+        <v>2.58E-2</v>
+      </c>
+      <c r="E65" s="145">
+        <v>675851.01821999997</v>
+      </c>
+      <c r="F65" s="240">
+        <v>45775</v>
+      </c>
+      <c r="G65" s="147">
+        <v>-634226.20947773824</v>
+      </c>
+      <c r="H65" s="309">
+        <f t="shared" si="0"/>
+        <v>634226.55000000005</v>
+      </c>
+      <c r="I65" s="147">
+        <v>-41624.808742261725</v>
+      </c>
+      <c r="J65" s="189">
+        <f t="shared" si="4"/>
+        <v>41624.808742261725</v>
+      </c>
+      <c r="K65" s="307">
+        <f t="shared" si="5"/>
+        <v>675851.55</v>
+      </c>
+      <c r="L65" s="133">
+        <f t="shared" si="6"/>
+        <v>0.55000000000000027</v>
+      </c>
+      <c r="M65" s="73"/>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" s="228" t="s">
+        <v>99</v>
+      </c>
+      <c r="B66" s="229">
+        <v>41</v>
+      </c>
+      <c r="C66" s="108" t="s">
+        <v>393</v>
+      </c>
+      <c r="D66" s="136">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="E66" s="145">
+        <v>516056.78522999992</v>
+      </c>
+      <c r="F66" s="240">
+        <v>45790</v>
+      </c>
+      <c r="G66" s="147">
+        <v>-473679.07297043619</v>
+      </c>
+      <c r="H66" s="309">
+        <f t="shared" si="0"/>
+        <v>473679.56</v>
+      </c>
+      <c r="I66" s="147">
+        <v>-42377.712259563734</v>
+      </c>
+      <c r="J66" s="189">
+        <f t="shared" si="4"/>
+        <v>42377.712259563734</v>
+      </c>
+      <c r="K66" s="307">
+        <f t="shared" si="5"/>
+        <v>516057.56</v>
+      </c>
+      <c r="L66" s="133">
+        <f t="shared" si="6"/>
+        <v>0.56000000000000028</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" s="228" t="s">
+        <v>100</v>
+      </c>
+      <c r="B67" s="229">
+        <v>2</v>
+      </c>
+      <c r="C67" s="108" t="s">
+        <v>394</v>
+      </c>
+      <c r="D67" s="136">
+        <v>1.17E-2</v>
+      </c>
+      <c r="E67" s="145">
+        <v>306490.57802999998</v>
+      </c>
+      <c r="F67" s="240"/>
+      <c r="G67" s="147">
+        <v>0</v>
+      </c>
+      <c r="H67" s="309"/>
+      <c r="I67" s="147">
+        <v>-306490.57802999998</v>
+      </c>
+      <c r="J67" s="189">
+        <f t="shared" si="4"/>
+        <v>306490.57802999998</v>
+      </c>
+      <c r="K67" s="307">
+        <f t="shared" si="5"/>
+        <v>306491.57</v>
+      </c>
+      <c r="L67" s="133">
+        <f t="shared" si="6"/>
+        <v>0.57000000000000028</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" s="228" t="s">
+        <v>101</v>
+      </c>
+      <c r="B68" s="229"/>
+      <c r="C68" s="108" t="s">
+        <v>211</v>
+      </c>
+      <c r="D68" s="136">
+        <v>8.6999999999999994E-3</v>
+      </c>
+      <c r="E68" s="145">
+        <v>227903.25032999998</v>
+      </c>
+      <c r="F68" s="240">
+        <v>45775</v>
+      </c>
+      <c r="G68" s="147">
+        <v>-213866.97761458607</v>
+      </c>
+      <c r="H68" s="309">
+        <f t="shared" si="0"/>
+        <v>213867.58</v>
+      </c>
+      <c r="I68" s="147">
+        <v>-14036.272715413914</v>
+      </c>
+      <c r="J68" s="189">
+        <f t="shared" si="4"/>
+        <v>14036.272715413914</v>
+      </c>
+      <c r="K68" s="307">
+        <f t="shared" si="5"/>
+        <v>227904.58</v>
+      </c>
+      <c r="L68" s="133">
+        <f t="shared" si="6"/>
+        <v>0.58000000000000029</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" s="228" t="s">
+        <v>102</v>
+      </c>
+      <c r="B69" s="229">
+        <v>19</v>
+      </c>
+      <c r="C69" s="108" t="s">
+        <v>212</v>
+      </c>
+      <c r="D69" s="136">
+        <v>1.18E-2</v>
+      </c>
+      <c r="E69" s="145">
+        <v>309110.15561999998</v>
+      </c>
+      <c r="F69" s="240">
+        <v>45821</v>
+      </c>
+      <c r="G69" s="147">
+        <v>-256859.2161501162</v>
+      </c>
+      <c r="H69" s="309">
+        <f t="shared" si="0"/>
+        <v>256859.59</v>
+      </c>
+      <c r="I69" s="147">
+        <v>-52250.939469883771</v>
+      </c>
+      <c r="J69" s="189">
+        <f t="shared" si="4"/>
+        <v>52250.939469883771</v>
+      </c>
+      <c r="K69" s="307">
+        <f t="shared" si="5"/>
+        <v>309111.59000000003</v>
+      </c>
+      <c r="L69" s="133">
+        <f t="shared" si="6"/>
+        <v>0.5900000000000003</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" s="228" t="s">
+        <v>103</v>
+      </c>
+      <c r="B70" s="229">
+        <v>36</v>
+      </c>
+      <c r="C70" s="108" t="s">
+        <v>213</v>
+      </c>
+      <c r="D70" s="136">
+        <v>2.58E-2</v>
+      </c>
+      <c r="E70" s="145">
+        <v>675851.01821999997</v>
+      </c>
+      <c r="F70" s="240">
+        <v>45891</v>
+      </c>
+      <c r="G70" s="147">
+        <v>-382821.80090465758</v>
+      </c>
+      <c r="H70" s="309">
+        <f t="shared" si="0"/>
+        <v>382822.6</v>
+      </c>
+      <c r="I70" s="147">
+        <v>-293029.21731534239</v>
+      </c>
+      <c r="J70" s="189">
+        <f t="shared" si="4"/>
+        <v>293029.21731534239</v>
+      </c>
+      <c r="K70" s="307">
+        <f t="shared" si="5"/>
+        <v>675852.6</v>
+      </c>
+      <c r="L70" s="133">
+        <f t="shared" si="6"/>
+        <v>0.60000000000000031</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" s="228" t="s">
+        <v>104</v>
+      </c>
+      <c r="B71" s="229">
+        <v>15</v>
+      </c>
+      <c r="C71" s="108" t="s">
+        <v>214</v>
+      </c>
+      <c r="D71" s="136">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="E71" s="145">
+        <v>516056.78522999992</v>
+      </c>
+      <c r="F71" s="240">
+        <v>45800</v>
+      </c>
+      <c r="G71" s="147">
+        <v>-466616.12092717562</v>
+      </c>
+      <c r="H71" s="309">
+        <f t="shared" ref="H71:H79" si="7">ROUND((-G71),0)+L71</f>
+        <v>466616.61</v>
+      </c>
+      <c r="I71" s="147">
+        <v>-49440.664302824298</v>
+      </c>
+      <c r="J71" s="189">
+        <f t="shared" si="4"/>
+        <v>49440.664302824298</v>
+      </c>
+      <c r="K71" s="307">
+        <f t="shared" si="5"/>
+        <v>516057.61</v>
+      </c>
+      <c r="L71" s="133">
+        <f t="shared" si="6"/>
+        <v>0.61000000000000032</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" s="228" t="s">
+        <v>105</v>
+      </c>
+      <c r="B72" s="229"/>
+      <c r="C72" s="108" t="s">
+        <v>215</v>
+      </c>
+      <c r="D72" s="136">
+        <v>9.4000000000000004E-3</v>
+      </c>
+      <c r="E72" s="145">
+        <v>246240.29345999999</v>
+      </c>
+      <c r="F72" s="240">
+        <v>45784</v>
+      </c>
+      <c r="G72" s="147">
+        <v>-228041.53987035993</v>
+      </c>
+      <c r="H72" s="309">
+        <f t="shared" si="7"/>
+        <v>228042.62</v>
+      </c>
+      <c r="I72" s="147">
+        <v>-18198.753589640051</v>
+      </c>
+      <c r="J72" s="189">
+        <f t="shared" si="4"/>
+        <v>18198.753589640051</v>
+      </c>
+      <c r="K72" s="307">
+        <f t="shared" si="5"/>
+        <v>246241.62</v>
+      </c>
+      <c r="L72" s="133">
+        <f t="shared" si="6"/>
+        <v>0.62000000000000033</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" s="228" t="s">
+        <v>106</v>
+      </c>
+      <c r="B73" s="229">
+        <v>40</v>
+      </c>
+      <c r="C73" s="108" t="s">
+        <v>216</v>
+      </c>
+      <c r="D73" s="136">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="E73" s="145">
+        <v>288153.53489999997</v>
+      </c>
+      <c r="F73" s="240">
+        <v>45784</v>
+      </c>
+      <c r="G73" s="147">
+        <v>-266857.12112488924</v>
+      </c>
+      <c r="H73" s="309">
+        <f t="shared" si="7"/>
+        <v>266857.63</v>
+      </c>
+      <c r="I73" s="147">
+        <v>-21296.413775110734</v>
+      </c>
+      <c r="J73" s="189">
+        <f t="shared" si="4"/>
+        <v>21296.413775110734</v>
+      </c>
+      <c r="K73" s="307">
+        <f t="shared" si="5"/>
+        <v>288154.63</v>
+      </c>
+      <c r="L73" s="133">
+        <f t="shared" si="6"/>
+        <v>0.63000000000000034</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" s="228" t="s">
+        <v>107</v>
+      </c>
+      <c r="B74" s="229"/>
+      <c r="C74" s="108" t="s">
+        <v>217</v>
+      </c>
+      <c r="D74" s="136">
+        <v>9.4999999999999998E-3</v>
+      </c>
+      <c r="E74" s="145">
+        <v>248859.87104999999</v>
+      </c>
+      <c r="F74" s="240">
+        <v>45786</v>
+      </c>
+      <c r="G74" s="147">
+        <v>-229786.31527835201</v>
+      </c>
+      <c r="H74" s="309">
+        <f t="shared" si="7"/>
+        <v>229786.64</v>
+      </c>
+      <c r="I74" s="147">
+        <v>-19073.555771647982</v>
+      </c>
+      <c r="J74" s="189">
+        <f t="shared" si="4"/>
+        <v>19073.555771647982</v>
+      </c>
+      <c r="K74" s="307">
+        <f t="shared" si="5"/>
+        <v>248860.64</v>
+      </c>
+      <c r="L74" s="133">
+        <f t="shared" si="6"/>
+        <v>0.64000000000000035</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" s="228" t="s">
+        <v>108</v>
+      </c>
+      <c r="B75" s="229">
+        <v>9</v>
+      </c>
+      <c r="C75" s="108" t="s">
+        <v>395</v>
+      </c>
+      <c r="D75" s="136">
+        <v>2.58E-2</v>
+      </c>
+      <c r="E75" s="145">
+        <v>675851.01821999997</v>
+      </c>
+      <c r="F75" s="240">
+        <v>45835</v>
+      </c>
+      <c r="G75" s="147">
+        <v>-525270.52442663931</v>
+      </c>
+      <c r="H75" s="309">
+        <f t="shared" si="7"/>
+        <v>525271.65</v>
+      </c>
+      <c r="I75" s="147">
+        <v>-150580.49379336066</v>
+      </c>
+      <c r="J75" s="189">
+        <f t="shared" si="4"/>
+        <v>150580.49379336066</v>
+      </c>
+      <c r="K75" s="307">
+        <f t="shared" si="5"/>
+        <v>675852.65</v>
+      </c>
+      <c r="L75" s="133">
+        <f t="shared" si="6"/>
+        <v>0.65000000000000036</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" s="228" t="s">
+        <v>109</v>
+      </c>
+      <c r="B76" s="229">
+        <v>35</v>
+      </c>
+      <c r="C76" s="108" t="s">
+        <v>218</v>
+      </c>
+      <c r="D76" s="136">
+        <v>1.9699999999999999E-2</v>
+      </c>
+      <c r="E76" s="145">
+        <v>516056.78522999992</v>
+      </c>
+      <c r="F76" s="240">
+        <v>45784</v>
+      </c>
+      <c r="G76" s="147">
+        <v>-477916.84419639257</v>
+      </c>
+      <c r="H76" s="309">
+        <f t="shared" si="7"/>
+        <v>477917.66</v>
+      </c>
+      <c r="I76" s="147">
+        <v>-38139.941033607349</v>
+      </c>
+      <c r="J76" s="189">
+        <f t="shared" ref="J76:J79" si="8">-I76</f>
+        <v>38139.941033607349</v>
+      </c>
+      <c r="K76" s="307">
+        <f t="shared" ref="K76:K79" si="9">ROUND((H76+J76),0) + L76</f>
+        <v>516058.66</v>
+      </c>
+      <c r="L76" s="133">
+        <f t="shared" si="6"/>
+        <v>0.66000000000000036</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" s="228" t="s">
+        <v>110</v>
+      </c>
+      <c r="B77" s="229" t="s">
+        <v>374</v>
+      </c>
+      <c r="C77" s="108" t="s">
+        <v>219</v>
+      </c>
+      <c r="D77" s="136">
+        <v>1.4E-2</v>
+      </c>
+      <c r="E77" s="145">
+        <v>366740.86259999999</v>
+      </c>
+      <c r="F77" s="240">
+        <v>45786</v>
+      </c>
+      <c r="G77" s="147">
+        <v>-338632.46462072933</v>
+      </c>
+      <c r="H77" s="309">
+        <f t="shared" si="7"/>
+        <v>338632.67</v>
+      </c>
+      <c r="I77" s="147">
+        <v>-28108.397979270667</v>
+      </c>
+      <c r="J77" s="189">
+        <f t="shared" si="8"/>
+        <v>28108.397979270667</v>
+      </c>
+      <c r="K77" s="307">
+        <f t="shared" si="9"/>
+        <v>366741.67</v>
+      </c>
+      <c r="L77" s="133">
+        <f t="shared" ref="L77:L79" si="10">L76+0.01</f>
+        <v>0.67000000000000037</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" s="228" t="s">
+        <v>111</v>
+      </c>
+      <c r="B78" s="228">
+        <v>42</v>
+      </c>
+      <c r="C78" s="108" t="s">
+        <v>220</v>
+      </c>
+      <c r="D78" s="136">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="E78" s="145">
+        <v>288153.53489999997</v>
+      </c>
+      <c r="F78" s="240">
+        <v>45777</v>
+      </c>
+      <c r="G78" s="147">
+        <v>-269617.76735499618</v>
+      </c>
+      <c r="H78" s="309">
+        <f t="shared" si="7"/>
+        <v>269618.68</v>
+      </c>
+      <c r="I78" s="147">
+        <v>-18535.767545003793</v>
+      </c>
+      <c r="J78" s="189">
+        <f t="shared" si="8"/>
+        <v>18535.767545003793</v>
+      </c>
+      <c r="K78" s="307">
+        <f t="shared" si="9"/>
+        <v>288154.68</v>
+      </c>
+      <c r="L78" s="133">
+        <f t="shared" si="10"/>
+        <v>0.68000000000000038</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" s="228" t="s">
+        <v>112</v>
+      </c>
+      <c r="B79" s="229">
+        <v>27</v>
+      </c>
+      <c r="C79" s="108" t="s">
+        <v>221</v>
+      </c>
+      <c r="D79" s="136">
+        <v>1.18E-2</v>
+      </c>
+      <c r="E79" s="145">
+        <v>309110.15561999998</v>
+      </c>
+      <c r="F79" s="240">
+        <v>45800</v>
+      </c>
+      <c r="G79" s="147">
+        <v>-279495.95060612552</v>
+      </c>
+      <c r="H79" s="309">
+        <f t="shared" si="7"/>
+        <v>279496.69</v>
+      </c>
+      <c r="I79" s="147">
+        <v>-29614.205013874453</v>
+      </c>
+      <c r="J79" s="189">
+        <f t="shared" si="8"/>
+        <v>29614.205013874453</v>
+      </c>
+      <c r="K79" s="307">
+        <f t="shared" si="9"/>
+        <v>309111.69</v>
+      </c>
+      <c r="L79" s="133">
+        <f t="shared" si="10"/>
+        <v>0.69000000000000039</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" s="35"/>
+      <c r="B80" s="35"/>
+      <c r="C80" s="108"/>
+      <c r="D80" s="35"/>
+      <c r="E80" s="145"/>
+      <c r="F80" s="76"/>
+      <c r="G80" s="146"/>
+      <c r="H80" s="146"/>
+      <c r="I80" s="146"/>
+      <c r="J80" s="146"/>
+      <c r="K80" s="147"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" s="27"/>
+      <c r="B81" s="27"/>
+      <c r="C81" s="27"/>
+      <c r="D81" s="116">
+        <f>SUM(D6:D80)</f>
+        <v>0.99790000000000079</v>
+      </c>
+      <c r="E81" s="28">
+        <f>SUM(E6:E80)</f>
+        <v>26140764.770610008</v>
+      </c>
+      <c r="F81" s="174">
+        <f>SUM(F6:F80)</f>
+        <v>3344000</v>
+      </c>
+      <c r="G81" s="29">
+        <f>SUM(G6:G80)</f>
+        <v>-22258385.373480178</v>
+      </c>
+      <c r="H81" s="29"/>
+      <c r="I81" s="29"/>
+      <c r="J81" s="29"/>
+      <c r="K81" s="28">
+        <f>SUM(K6:K80)</f>
+        <v>26140811.75</v>
+      </c>
+      <c r="M81" s="59"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="A1:K2"/>
+    <mergeCell ref="N6:O7"/>
+  </mergeCells>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="3" scale="110" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
   <dimension ref="A13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="13" ht="15.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
